--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU326"/>
+  <dimension ref="A1:AU328"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G17">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G54">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G82">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G95">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G99">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G123">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G133">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G144">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G167">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G178">
@@ -29439,12 +29439,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G179">
@@ -29590,7 +29590,7 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2026-08-29 12:45:00</t>
+          <t>2026-08-29 12:30:00</t>
         </is>
       </c>
     </row>
@@ -29602,12 +29602,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G180">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>2026-08-29 13:00:00</t>
+          <t>2026-08-29 12:30:00</t>
         </is>
       </c>
     </row>
@@ -29765,12 +29765,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G181">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2026-08-29 13:00:00</t>
+          <t>2026-08-29 12:45:00</t>
         </is>
       </c>
     </row>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G184">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G185">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,22 +30748,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G187">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,22 +31074,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,22 +31237,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G191">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G195">
@@ -32210,12 +32210,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G196">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>2026-08-29 13:05:00</t>
+          <t>2026-08-29 13:00:00</t>
         </is>
       </c>
     </row>
@@ -32373,12 +32373,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G197">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>2026-08-29 13:15:00</t>
+          <t>2026-08-29 13:00:00</t>
         </is>
       </c>
     </row>
@@ -32536,27 +32536,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G198">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>2026-08-29 13:30:00</t>
+          <t>2026-08-29 13:00:00</t>
         </is>
       </c>
     </row>
@@ -32699,12 +32699,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G199">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>2026-08-29 13:30:00</t>
+          <t>2026-08-29 13:05:00</t>
         </is>
       </c>
     </row>
@@ -32862,12 +32862,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G200">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-08-29 13:30:00</t>
+          <t>2026-08-29 13:15:00</t>
         </is>
       </c>
     </row>
@@ -33030,22 +33030,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,7 +33845,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G207">
@@ -34166,12 +34166,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G208">
@@ -34317,7 +34317,7 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>2026-08-29 13:45:00</t>
+          <t>2026-08-29 13:30:00</t>
         </is>
       </c>
     </row>
@@ -34329,12 +34329,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G209">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>2026-08-29 14:00:00</t>
+          <t>2026-08-29 13:30:00</t>
         </is>
       </c>
     </row>
@@ -34492,12 +34492,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G210">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>2026-08-29 14:00:00</t>
+          <t>2026-08-29 13:30:00</t>
         </is>
       </c>
     </row>
@@ -34655,12 +34655,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G211">
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>2026-08-29 14:00:00</t>
+          <t>2026-08-29 13:45:00</t>
         </is>
       </c>
     </row>
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G213">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G214">
@@ -35187,7 +35187,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N214">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,22 +35638,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G225">
@@ -37100,12 +37100,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G226">
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>2026-08-29 14:15:00</t>
+          <t>2026-08-29 14:00:00</t>
         </is>
       </c>
     </row>
@@ -37263,12 +37263,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G227">
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>2026-08-29 14:15:00</t>
+          <t>2026-08-29 14:00:00</t>
         </is>
       </c>
     </row>
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G228">
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-08-29 14:30:00</t>
+          <t>2026-08-29 14:15:00</t>
         </is>
       </c>
     </row>
@@ -37589,12 +37589,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G229">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-08-29 14:30:00</t>
+          <t>2026-08-29 14:15:00</t>
         </is>
       </c>
     </row>
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G230">
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G231">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-08-29 15:00:00</t>
+          <t>2026-08-29 14:30:00</t>
         </is>
       </c>
     </row>
@@ -38078,12 +38078,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G232">
@@ -38229,7 +38229,7 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>2026-08-29 15:00:00</t>
+          <t>2026-08-29 14:30:00</t>
         </is>
       </c>
     </row>
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,22 +38409,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G235">
@@ -38735,22 +38735,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G236">
@@ -38898,22 +38898,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G237">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G238">
@@ -39224,22 +39224,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G239">
@@ -39382,12 +39382,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G240">
@@ -39533,7 +39533,7 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>2026-08-29 15:15:00</t>
+          <t>2026-08-29 15:00:00</t>
         </is>
       </c>
     </row>
@@ -39545,12 +39545,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G241">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>2026-08-29 15:15:00</t>
+          <t>2026-08-29 15:00:00</t>
         </is>
       </c>
     </row>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G242">
@@ -39871,12 +39871,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G243">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>2026-08-29 15:30:00</t>
+          <t>2026-08-29 15:15:00</t>
         </is>
       </c>
     </row>
@@ -40034,12 +40034,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G244">
@@ -40185,7 +40185,7 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>2026-08-29 15:30:00</t>
+          <t>2026-08-29 15:15:00</t>
         </is>
       </c>
     </row>
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,22 +40365,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,22 +40691,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G248">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G249">
@@ -41012,12 +41012,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G250">
@@ -41163,7 +41163,7 @@
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>2026-08-29 15:45:00</t>
+          <t>2026-08-29 15:30:00</t>
         </is>
       </c>
     </row>
@@ -41175,12 +41175,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G251">
@@ -41326,7 +41326,7 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>2026-08-29 15:45:00</t>
+          <t>2026-08-29 15:30:00</t>
         </is>
       </c>
     </row>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G252">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G253">
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G256">
@@ -42153,12 +42153,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G257">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00:00</t>
+          <t>2026-08-29 15:45:00</t>
         </is>
       </c>
     </row>
@@ -42316,12 +42316,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G258">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00:00</t>
+          <t>2026-08-29 15:45:00</t>
         </is>
       </c>
     </row>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,22 +42647,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,7 +42810,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G261">
@@ -42973,22 +42973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G262">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,22 +43299,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,22 +43462,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G265">
@@ -43625,22 +43625,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G266">
@@ -43788,22 +43788,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G267">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G268">
@@ -44114,7 +44114,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G269">
@@ -44277,7 +44277,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G270">
@@ -44435,12 +44435,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G271">
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-08-29 16:30:00</t>
+          <t>2026-08-29 16:00:00</t>
         </is>
       </c>
     </row>
@@ -44598,12 +44598,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G272">
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-08-29 16:30:00</t>
+          <t>2026-08-29 16:00:00</t>
         </is>
       </c>
     </row>
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G273">
@@ -44924,27 +44924,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G274">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-08-29 17:00:00</t>
+          <t>2026-08-29 16:30:00</t>
         </is>
       </c>
     </row>
@@ -45087,27 +45087,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G275">
@@ -45238,7 +45238,7 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>2026-08-29 17:00:00</t>
+          <t>2026-08-29 16:30:00</t>
         </is>
       </c>
     </row>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G276">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G278">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G279">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G280">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G281">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G283">
@@ -46559,22 +46559,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G284">
@@ -46717,12 +46717,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-08-29 17:30:00</t>
+          <t>2026-08-29 17:00:00</t>
         </is>
       </c>
     </row>
@@ -46880,27 +46880,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G286">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-08-29 18:00:00</t>
+          <t>2026-08-29 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47043,12 +47043,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G287">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-08-29 18:00:00</t>
+          <t>2026-08-29 17:30:00</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G288">
@@ -47369,12 +47369,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G289">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-08-29 18:30:00</t>
+          <t>2026-08-29 18:00:00</t>
         </is>
       </c>
     </row>
@@ -47532,12 +47532,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-08-29 18:30:00</t>
+          <t>2026-08-29 18:00:00</t>
         </is>
       </c>
     </row>
@@ -47700,7 +47700,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G291">
@@ -47863,7 +47863,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G292">
@@ -48021,12 +48021,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G293">
@@ -48172,7 +48172,7 @@
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30:00</t>
+          <t>2026-08-29 18:30:00</t>
         </is>
       </c>
     </row>
@@ -48184,12 +48184,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G294">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-08-29 20:00:00</t>
+          <t>2026-08-29 18:30:00</t>
         </is>
       </c>
     </row>
@@ -48347,12 +48347,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G295">
@@ -48498,7 +48498,7 @@
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>2026-08-29 20:00:00</t>
+          <t>2026-08-29 19:30:00</t>
         </is>
       </c>
     </row>
@@ -48515,7 +48515,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G297">
@@ -48841,7 +48841,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G298">
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G299">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-08-29 20:30:00</t>
+          <t>2026-08-29 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49162,12 +49162,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G300">
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-08-29 20:30:00</t>
+          <t>2026-08-29 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G301">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G302">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G303">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G304">
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G305">
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-08-29 21:00:00</t>
+          <t>2026-08-29 20:30:00</t>
         </is>
       </c>
     </row>
@@ -50140,12 +50140,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G306">
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-08-29 21:00:00</t>
+          <t>2026-08-29 20:30:00</t>
         </is>
       </c>
     </row>
@@ -50308,7 +50308,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G307">
@@ -50471,7 +50471,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G308">
@@ -50634,22 +50634,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G309">
@@ -50797,22 +50797,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G310">
@@ -50960,22 +50960,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G311">
@@ -51118,27 +51118,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G312">
@@ -51269,7 +51269,7 @@
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>2026-08-29 21:20:00</t>
+          <t>2026-08-29 21:00:00</t>
         </is>
       </c>
     </row>
@@ -51281,12 +51281,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G313">
@@ -51432,7 +51432,7 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30:00</t>
+          <t>2026-08-29 21:00:00</t>
         </is>
       </c>
     </row>
@@ -51444,12 +51444,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G314">
@@ -51595,7 +51595,7 @@
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30:00</t>
+          <t>2026-08-29 21:20:00</t>
         </is>
       </c>
     </row>
@@ -51612,7 +51612,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G315">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G316">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G317">
@@ -52096,12 +52096,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G318">
@@ -52247,7 +52247,7 @@
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>2026-08-29 21:45:00</t>
+          <t>2026-08-29 21:30:00</t>
         </is>
       </c>
     </row>
@@ -52259,12 +52259,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G319">
@@ -52410,7 +52410,7 @@
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>2026-08-29 22:00:00</t>
+          <t>2026-08-29 21:30:00</t>
         </is>
       </c>
     </row>
@@ -52422,12 +52422,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G320">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30:00</t>
+          <t>2026-08-29 21:45:00</t>
         </is>
       </c>
     </row>
@@ -52585,12 +52585,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G321">
@@ -52736,7 +52736,7 @@
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30:00</t>
+          <t>2026-08-29 22:00:00</t>
         </is>
       </c>
     </row>
@@ -52748,7 +52748,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G322">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00:00</t>
+          <t>2026-08-29 22:30:00</t>
         </is>
       </c>
     </row>
@@ -52911,12 +52911,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G323">
@@ -53062,7 +53062,7 @@
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>2026-08-29 23:30:00</t>
+          <t>2026-08-29 22:30:00</t>
         </is>
       </c>
     </row>
@@ -53074,7 +53074,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G324">
@@ -53225,7 +53225,7 @@
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>2026-08-29 23:30:00</t>
+          <t>2026-08-29 23:00:00</t>
         </is>
       </c>
     </row>
@@ -53242,7 +53242,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G325">
@@ -53405,151 +53405,477 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="G326">
+        <v>0</v>
+      </c>
+      <c r="H326">
+        <v>0</v>
+      </c>
+      <c r="I326">
+        <v>0</v>
+      </c>
+      <c r="J326">
+        <v>0</v>
+      </c>
+      <c r="K326">
+        <v>0</v>
+      </c>
+      <c r="L326">
+        <v>0</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N326">
+        <v>0</v>
+      </c>
+      <c r="O326">
+        <v>0</v>
+      </c>
+      <c r="P326">
+        <v>0</v>
+      </c>
+      <c r="Q326">
+        <v>0</v>
+      </c>
+      <c r="R326">
+        <v>0</v>
+      </c>
+      <c r="S326">
+        <v>0</v>
+      </c>
+      <c r="T326">
+        <v>0</v>
+      </c>
+      <c r="U326">
+        <v>0</v>
+      </c>
+      <c r="V326">
+        <v>0</v>
+      </c>
+      <c r="W326">
+        <v>0</v>
+      </c>
+      <c r="X326">
+        <v>0</v>
+      </c>
+      <c r="Y326">
+        <v>0</v>
+      </c>
+      <c r="Z326">
+        <v>0</v>
+      </c>
+      <c r="AA326">
+        <v>0</v>
+      </c>
+      <c r="AB326">
+        <v>0</v>
+      </c>
+      <c r="AC326">
+        <v>0</v>
+      </c>
+      <c r="AD326">
+        <v>0</v>
+      </c>
+      <c r="AE326">
+        <v>0</v>
+      </c>
+      <c r="AF326">
+        <v>0</v>
+      </c>
+      <c r="AG326">
+        <v>0</v>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ326">
+        <v>0</v>
+      </c>
+      <c r="AK326">
+        <v>0</v>
+      </c>
+      <c r="AL326">
+        <v>0</v>
+      </c>
+      <c r="AM326">
+        <v>-1</v>
+      </c>
+      <c r="AN326">
+        <v>-1</v>
+      </c>
+      <c r="AO326">
+        <v>-1</v>
+      </c>
+      <c r="AP326">
+        <v>-1</v>
+      </c>
+      <c r="AQ326">
+        <v>0</v>
+      </c>
+      <c r="AR326">
+        <v>0</v>
+      </c>
+      <c r="AS326">
+        <v>0</v>
+      </c>
+      <c r="AT326">
+        <v>0</v>
+      </c>
+      <c r="AU326" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
+      <c r="D327" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr">
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="G327">
+        <v>0</v>
+      </c>
+      <c r="H327">
+        <v>0</v>
+      </c>
+      <c r="I327">
+        <v>0</v>
+      </c>
+      <c r="J327">
+        <v>0</v>
+      </c>
+      <c r="K327">
+        <v>0</v>
+      </c>
+      <c r="L327">
+        <v>0</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N327">
+        <v>0</v>
+      </c>
+      <c r="O327">
+        <v>0</v>
+      </c>
+      <c r="P327">
+        <v>0</v>
+      </c>
+      <c r="Q327">
+        <v>0</v>
+      </c>
+      <c r="R327">
+        <v>0</v>
+      </c>
+      <c r="S327">
+        <v>0</v>
+      </c>
+      <c r="T327">
+        <v>0</v>
+      </c>
+      <c r="U327">
+        <v>0</v>
+      </c>
+      <c r="V327">
+        <v>0</v>
+      </c>
+      <c r="W327">
+        <v>0</v>
+      </c>
+      <c r="X327">
+        <v>0</v>
+      </c>
+      <c r="Y327">
+        <v>0</v>
+      </c>
+      <c r="Z327">
+        <v>0</v>
+      </c>
+      <c r="AA327">
+        <v>0</v>
+      </c>
+      <c r="AB327">
+        <v>0</v>
+      </c>
+      <c r="AC327">
+        <v>0</v>
+      </c>
+      <c r="AD327">
+        <v>0</v>
+      </c>
+      <c r="AE327">
+        <v>0</v>
+      </c>
+      <c r="AF327">
+        <v>0</v>
+      </c>
+      <c r="AG327">
+        <v>0</v>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ327">
+        <v>0</v>
+      </c>
+      <c r="AK327">
+        <v>0</v>
+      </c>
+      <c r="AL327">
+        <v>0</v>
+      </c>
+      <c r="AM327">
+        <v>-1</v>
+      </c>
+      <c r="AN327">
+        <v>-1</v>
+      </c>
+      <c r="AO327">
+        <v>-1</v>
+      </c>
+      <c r="AP327">
+        <v>-1</v>
+      </c>
+      <c r="AQ327">
+        <v>0</v>
+      </c>
+      <c r="AR327">
+        <v>0</v>
+      </c>
+      <c r="AS327">
+        <v>0</v>
+      </c>
+      <c r="AT327">
+        <v>0</v>
+      </c>
+      <c r="AU327" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
+      <c r="F328" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="G326">
-        <v>0</v>
-      </c>
-      <c r="H326">
-        <v>0</v>
-      </c>
-      <c r="I326">
-        <v>0</v>
-      </c>
-      <c r="J326">
-        <v>0</v>
-      </c>
-      <c r="K326">
-        <v>0</v>
-      </c>
-      <c r="L326">
-        <v>0</v>
-      </c>
-      <c r="M326" t="inlineStr">
+      <c r="G328">
+        <v>0</v>
+      </c>
+      <c r="H328">
+        <v>0</v>
+      </c>
+      <c r="I328">
+        <v>0</v>
+      </c>
+      <c r="J328">
+        <v>0</v>
+      </c>
+      <c r="K328">
+        <v>0</v>
+      </c>
+      <c r="L328">
+        <v>0</v>
+      </c>
+      <c r="M328" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N326">
-        <v>0</v>
-      </c>
-      <c r="O326">
-        <v>0</v>
-      </c>
-      <c r="P326">
-        <v>0</v>
-      </c>
-      <c r="Q326">
-        <v>0</v>
-      </c>
-      <c r="R326">
-        <v>0</v>
-      </c>
-      <c r="S326">
-        <v>0</v>
-      </c>
-      <c r="T326">
-        <v>0</v>
-      </c>
-      <c r="U326">
-        <v>0</v>
-      </c>
-      <c r="V326">
-        <v>0</v>
-      </c>
-      <c r="W326">
-        <v>0</v>
-      </c>
-      <c r="X326">
-        <v>0</v>
-      </c>
-      <c r="Y326">
-        <v>0</v>
-      </c>
-      <c r="Z326">
-        <v>0</v>
-      </c>
-      <c r="AA326">
-        <v>0</v>
-      </c>
-      <c r="AB326">
-        <v>0</v>
-      </c>
-      <c r="AC326">
-        <v>0</v>
-      </c>
-      <c r="AD326">
-        <v>0</v>
-      </c>
-      <c r="AE326">
-        <v>0</v>
-      </c>
-      <c r="AF326">
-        <v>0</v>
-      </c>
-      <c r="AG326">
-        <v>0</v>
-      </c>
-      <c r="AH326" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI326" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ326">
-        <v>0</v>
-      </c>
-      <c r="AK326">
-        <v>0</v>
-      </c>
-      <c r="AL326">
-        <v>0</v>
-      </c>
-      <c r="AM326">
-        <v>-1</v>
-      </c>
-      <c r="AN326">
-        <v>-1</v>
-      </c>
-      <c r="AO326">
-        <v>-1</v>
-      </c>
-      <c r="AP326">
-        <v>-1</v>
-      </c>
-      <c r="AQ326">
-        <v>0</v>
-      </c>
-      <c r="AR326">
-        <v>0</v>
-      </c>
-      <c r="AS326">
-        <v>0</v>
-      </c>
-      <c r="AT326">
-        <v>0</v>
-      </c>
-      <c r="AU326" t="inlineStr">
+      <c r="N328">
+        <v>0</v>
+      </c>
+      <c r="O328">
+        <v>0</v>
+      </c>
+      <c r="P328">
+        <v>0</v>
+      </c>
+      <c r="Q328">
+        <v>0</v>
+      </c>
+      <c r="R328">
+        <v>0</v>
+      </c>
+      <c r="S328">
+        <v>0</v>
+      </c>
+      <c r="T328">
+        <v>0</v>
+      </c>
+      <c r="U328">
+        <v>0</v>
+      </c>
+      <c r="V328">
+        <v>0</v>
+      </c>
+      <c r="W328">
+        <v>0</v>
+      </c>
+      <c r="X328">
+        <v>0</v>
+      </c>
+      <c r="Y328">
+        <v>0</v>
+      </c>
+      <c r="Z328">
+        <v>0</v>
+      </c>
+      <c r="AA328">
+        <v>0</v>
+      </c>
+      <c r="AB328">
+        <v>0</v>
+      </c>
+      <c r="AC328">
+        <v>0</v>
+      </c>
+      <c r="AD328">
+        <v>0</v>
+      </c>
+      <c r="AE328">
+        <v>0</v>
+      </c>
+      <c r="AF328">
+        <v>0</v>
+      </c>
+      <c r="AG328">
+        <v>0</v>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI328" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ328">
+        <v>0</v>
+      </c>
+      <c r="AK328">
+        <v>0</v>
+      </c>
+      <c r="AL328">
+        <v>0</v>
+      </c>
+      <c r="AM328">
+        <v>-1</v>
+      </c>
+      <c r="AN328">
+        <v>-1</v>
+      </c>
+      <c r="AO328">
+        <v>-1</v>
+      </c>
+      <c r="AP328">
+        <v>-1</v>
+      </c>
+      <c r="AQ328">
+        <v>0</v>
+      </c>
+      <c r="AR328">
+        <v>0</v>
+      </c>
+      <c r="AS328">
+        <v>0</v>
+      </c>
+      <c r="AT328">
+        <v>0</v>
+      </c>
+      <c r="AU328" t="inlineStr">
         <is>
           <t>2026-08-29 23:30:00</t>
         </is>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G24">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G82">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G89">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G99">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G123">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G133">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G144">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G257">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G258">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G283">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G284">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G301">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G302">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G303">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G305">

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G2">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G3">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G17">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G81">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G99">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G133">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G140">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G174">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G195">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G283">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G284">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G285">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G298">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G299">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G305">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G308">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G309">

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G77">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G94">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G143">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G183">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G257">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G258">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G263">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G264">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G265">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G316">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G319">

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G15">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G17">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G96">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G183">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G229">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G230">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G234">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G235">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G252">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G253">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G263">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G264">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G281">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G282">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G293">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G295">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G297">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G298">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G299">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G319">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G320">

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G83">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G177">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G227">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G228">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G229">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G230">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G330">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G331">

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU340"/>
+  <dimension ref="A1:AU341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G35">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G43">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G54">
@@ -27814,22 +27814,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G170">
@@ -28135,27 +28135,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G171">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-08-29 12:15:00</t>
+          <t>2026-08-29 12:00:00</t>
         </is>
       </c>
     </row>
@@ -28298,12 +28298,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G172">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>2026-08-29 12:30:00</t>
+          <t>2026-08-29 12:15:00</t>
         </is>
       </c>
     </row>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G173">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,22 +28792,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,22 +28955,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O178">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P178">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q178">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R178">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S178">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T178">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U178">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V178">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W178">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X178">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y178">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z178">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA178">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AB178">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC178">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD178">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE178">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF178">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG178">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK178">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G183">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G184">
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G185">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-08-29 12:45:00</t>
+          <t>2026-08-29 12:30:00</t>
         </is>
       </c>
     </row>
@@ -30580,12 +30580,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G186">
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2026-08-29 13:00:00</t>
+          <t>2026-08-29 12:45:00</t>
         </is>
       </c>
     </row>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,22 +31726,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,22 +32052,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G197">
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G199">
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G202">
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G203">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-08-29 13:05:00</t>
+          <t>2026-08-29 13:00:00</t>
         </is>
       </c>
     </row>
@@ -33514,12 +33514,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G204">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>2026-08-29 13:15:00</t>
+          <t>2026-08-29 13:05:00</t>
         </is>
       </c>
     </row>
@@ -33677,27 +33677,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G205">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>2026-08-29 13:30:00</t>
+          <t>2026-08-29 13:15:00</t>
         </is>
       </c>
     </row>
@@ -33845,22 +33845,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G212">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G213">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G215">
@@ -35470,12 +35470,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G216">
@@ -35621,7 +35621,7 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>2026-08-29 13:45:00</t>
+          <t>2026-08-29 13:30:00</t>
         </is>
       </c>
     </row>
@@ -35633,12 +35633,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G217">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>2026-08-29 14:00:00</t>
+          <t>2026-08-29 13:45:00</t>
         </is>
       </c>
     </row>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G219">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,22 +36616,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,22 +36779,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G225">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G227">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G229">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G232">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G248">
@@ -40849,12 +40849,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G249">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>2026-08-29 15:15:00</t>
+          <t>2026-08-29 15:00:00</t>
         </is>
       </c>
     </row>
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G251">
@@ -41338,12 +41338,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G252">
@@ -41489,7 +41489,7 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>2026-08-29 15:30:00</t>
+          <t>2026-08-29 15:15:00</t>
         </is>
       </c>
     </row>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G253">
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,22 +41832,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,22 +41995,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O256">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P256">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q256">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R256">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S256">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T256">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U256">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V256">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W256">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X256">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y256">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z256">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA256">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB256">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC256">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD256">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE256">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF256">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG256">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK256">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="G257">
@@ -42200,64 +42200,64 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S257">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T257">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U257">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V257">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W257">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X257">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y257">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z257">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC257">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD257">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE257">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF257">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG257">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK257">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G258">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O260">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P260">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42805,12 +42805,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-08-29 15:45:00</t>
+          <t>2026-08-29 15:30:00</t>
         </is>
       </c>
     </row>
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G262">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G263">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G265">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G266">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G267">
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-08-29 16:00:00</t>
+          <t>2026-08-29 15:45:00</t>
         </is>
       </c>
     </row>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G269">
@@ -44440,22 +44440,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,22 +44603,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G272">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G273">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G275">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G276">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G277">
@@ -45581,22 +45581,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G278">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,22 +45907,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G280">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G281">
@@ -46396,7 +46396,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G283">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G284">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G285">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G286">
@@ -47043,12 +47043,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G287">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-08-29 16:30:00</t>
+          <t>2026-08-29 16:00:00</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G288">
@@ -47374,7 +47374,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G289">
@@ -47532,27 +47532,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-08-29 17:00:00</t>
+          <t>2026-08-29 16:30:00</t>
         </is>
       </c>
     </row>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G293">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G295">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G297">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G298">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G299">
@@ -49167,22 +49167,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G300">
@@ -49325,27 +49325,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G301">
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-08-29 17:30:00</t>
+          <t>2026-08-29 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49488,12 +49488,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G302">
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-08-29 18:00:00</t>
+          <t>2026-08-29 17:30:00</t>
         </is>
       </c>
     </row>
@@ -49656,7 +49656,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G303">
@@ -49819,7 +49819,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G304">
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G305">
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-08-29 18:30:00</t>
+          <t>2026-08-29 18:00:00</t>
         </is>
       </c>
     </row>
@@ -50145,7 +50145,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G306">
@@ -50308,7 +50308,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G307">
@@ -50471,7 +50471,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G308">
@@ -50629,12 +50629,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G309">
@@ -50780,7 +50780,7 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>2026-08-29 19:30:00</t>
+          <t>2026-08-29 18:30:00</t>
         </is>
       </c>
     </row>
@@ -50792,12 +50792,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G310">
@@ -50943,7 +50943,7 @@
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>2026-08-29 20:00:00</t>
+          <t>2026-08-29 19:30:00</t>
         </is>
       </c>
     </row>
@@ -50960,7 +50960,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G311">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G312">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G313">
@@ -51449,7 +51449,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G314">
@@ -51607,12 +51607,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G315">
@@ -51758,7 +51758,7 @@
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>2026-08-29 20:30:00</t>
+          <t>2026-08-29 20:00:00</t>
         </is>
       </c>
     </row>
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G316">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G319">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G320">
@@ -52585,12 +52585,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G321">
@@ -52736,7 +52736,7 @@
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>2026-08-29 21:00:00</t>
+          <t>2026-08-29 20:30:00</t>
         </is>
       </c>
     </row>
@@ -52753,7 +52753,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G322">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G323">
@@ -53079,7 +53079,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G324">
@@ -53242,7 +53242,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G325">
@@ -53400,12 +53400,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G326">
@@ -53551,7 +53551,7 @@
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>2026-08-29 21:20:00</t>
+          <t>2026-08-29 21:00:00</t>
         </is>
       </c>
     </row>
@@ -53563,12 +53563,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G327">
@@ -53714,7 +53714,7 @@
       </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>2026-08-29 21:30:00</t>
+          <t>2026-08-29 21:20:00</t>
         </is>
       </c>
     </row>
@@ -53731,7 +53731,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G328">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G330">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G331">
@@ -54378,12 +54378,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G332">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>2026-08-29 21:45:00</t>
+          <t>2026-08-29 21:30:00</t>
         </is>
       </c>
     </row>
@@ -54541,12 +54541,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G333">
@@ -54692,7 +54692,7 @@
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>2026-08-29 22:00:00</t>
+          <t>2026-08-29 21:45:00</t>
         </is>
       </c>
     </row>
@@ -54704,7 +54704,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G334">
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-08-29 22:30:00</t>
+          <t>2026-08-29 22:00:00</t>
         </is>
       </c>
     </row>
@@ -54872,7 +54872,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G335">
@@ -55030,12 +55030,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G336">
@@ -55181,7 +55181,7 @@
       </c>
       <c r="AU336" t="inlineStr">
         <is>
-          <t>2026-08-29 23:00:00</t>
+          <t>2026-08-29 22:30:00</t>
         </is>
       </c>
     </row>
@@ -55193,7 +55193,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G337">
@@ -55344,7 +55344,7 @@
       </c>
       <c r="AU337" t="inlineStr">
         <is>
-          <t>2026-08-29 23:30:00</t>
+          <t>2026-08-29 23:00:00</t>
         </is>
       </c>
     </row>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G338">
@@ -55524,7 +55524,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G339">
@@ -55697,141 +55697,304 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="G340">
+        <v>0</v>
+      </c>
+      <c r="H340">
+        <v>0</v>
+      </c>
+      <c r="I340">
+        <v>0</v>
+      </c>
+      <c r="J340">
+        <v>0</v>
+      </c>
+      <c r="K340">
+        <v>0</v>
+      </c>
+      <c r="L340">
+        <v>0</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N340">
+        <v>0</v>
+      </c>
+      <c r="O340">
+        <v>0</v>
+      </c>
+      <c r="P340">
+        <v>0</v>
+      </c>
+      <c r="Q340">
+        <v>0</v>
+      </c>
+      <c r="R340">
+        <v>0</v>
+      </c>
+      <c r="S340">
+        <v>0</v>
+      </c>
+      <c r="T340">
+        <v>0</v>
+      </c>
+      <c r="U340">
+        <v>0</v>
+      </c>
+      <c r="V340">
+        <v>0</v>
+      </c>
+      <c r="W340">
+        <v>0</v>
+      </c>
+      <c r="X340">
+        <v>0</v>
+      </c>
+      <c r="Y340">
+        <v>0</v>
+      </c>
+      <c r="Z340">
+        <v>0</v>
+      </c>
+      <c r="AA340">
+        <v>0</v>
+      </c>
+      <c r="AB340">
+        <v>0</v>
+      </c>
+      <c r="AC340">
+        <v>0</v>
+      </c>
+      <c r="AD340">
+        <v>0</v>
+      </c>
+      <c r="AE340">
+        <v>0</v>
+      </c>
+      <c r="AF340">
+        <v>0</v>
+      </c>
+      <c r="AG340">
+        <v>0</v>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI340" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ340">
+        <v>0</v>
+      </c>
+      <c r="AK340">
+        <v>0</v>
+      </c>
+      <c r="AL340">
+        <v>0</v>
+      </c>
+      <c r="AM340">
+        <v>-1</v>
+      </c>
+      <c r="AN340">
+        <v>-1</v>
+      </c>
+      <c r="AO340">
+        <v>-1</v>
+      </c>
+      <c r="AP340">
+        <v>-1</v>
+      </c>
+      <c r="AQ340">
+        <v>0</v>
+      </c>
+      <c r="AR340">
+        <v>0</v>
+      </c>
+      <c r="AS340">
+        <v>0</v>
+      </c>
+      <c r="AT340">
+        <v>0</v>
+      </c>
+      <c r="AU340" t="inlineStr">
+        <is>
+          <t>2026-08-29 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr">
+      <c r="F341" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="G340">
-        <v>0</v>
-      </c>
-      <c r="H340">
-        <v>0</v>
-      </c>
-      <c r="I340">
-        <v>0</v>
-      </c>
-      <c r="J340">
-        <v>0</v>
-      </c>
-      <c r="K340">
-        <v>0</v>
-      </c>
-      <c r="L340">
-        <v>0</v>
-      </c>
-      <c r="M340" t="inlineStr">
+      <c r="G341">
+        <v>0</v>
+      </c>
+      <c r="H341">
+        <v>0</v>
+      </c>
+      <c r="I341">
+        <v>0</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <v>0</v>
+      </c>
+      <c r="L341">
+        <v>0</v>
+      </c>
+      <c r="M341" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N340">
-        <v>0</v>
-      </c>
-      <c r="O340">
-        <v>0</v>
-      </c>
-      <c r="P340">
-        <v>0</v>
-      </c>
-      <c r="Q340">
-        <v>0</v>
-      </c>
-      <c r="R340">
-        <v>0</v>
-      </c>
-      <c r="S340">
-        <v>0</v>
-      </c>
-      <c r="T340">
-        <v>0</v>
-      </c>
-      <c r="U340">
-        <v>0</v>
-      </c>
-      <c r="V340">
-        <v>0</v>
-      </c>
-      <c r="W340">
-        <v>0</v>
-      </c>
-      <c r="X340">
-        <v>0</v>
-      </c>
-      <c r="Y340">
-        <v>0</v>
-      </c>
-      <c r="Z340">
-        <v>0</v>
-      </c>
-      <c r="AA340">
-        <v>0</v>
-      </c>
-      <c r="AB340">
-        <v>0</v>
-      </c>
-      <c r="AC340">
-        <v>0</v>
-      </c>
-      <c r="AD340">
-        <v>0</v>
-      </c>
-      <c r="AE340">
-        <v>0</v>
-      </c>
-      <c r="AF340">
-        <v>0</v>
-      </c>
-      <c r="AG340">
-        <v>0</v>
-      </c>
-      <c r="AH340" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI340" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ340">
-        <v>0</v>
-      </c>
-      <c r="AK340">
-        <v>0</v>
-      </c>
-      <c r="AL340">
-        <v>0</v>
-      </c>
-      <c r="AM340">
-        <v>-1</v>
-      </c>
-      <c r="AN340">
-        <v>-1</v>
-      </c>
-      <c r="AO340">
-        <v>-1</v>
-      </c>
-      <c r="AP340">
-        <v>-1</v>
-      </c>
-      <c r="AQ340">
-        <v>0</v>
-      </c>
-      <c r="AR340">
-        <v>0</v>
-      </c>
-      <c r="AS340">
-        <v>0</v>
-      </c>
-      <c r="AT340">
-        <v>0</v>
-      </c>
-      <c r="AU340" t="inlineStr">
+      <c r="N341">
+        <v>0</v>
+      </c>
+      <c r="O341">
+        <v>0</v>
+      </c>
+      <c r="P341">
+        <v>0</v>
+      </c>
+      <c r="Q341">
+        <v>0</v>
+      </c>
+      <c r="R341">
+        <v>0</v>
+      </c>
+      <c r="S341">
+        <v>0</v>
+      </c>
+      <c r="T341">
+        <v>0</v>
+      </c>
+      <c r="U341">
+        <v>0</v>
+      </c>
+      <c r="V341">
+        <v>0</v>
+      </c>
+      <c r="W341">
+        <v>0</v>
+      </c>
+      <c r="X341">
+        <v>0</v>
+      </c>
+      <c r="Y341">
+        <v>0</v>
+      </c>
+      <c r="Z341">
+        <v>0</v>
+      </c>
+      <c r="AA341">
+        <v>0</v>
+      </c>
+      <c r="AB341">
+        <v>0</v>
+      </c>
+      <c r="AC341">
+        <v>0</v>
+      </c>
+      <c r="AD341">
+        <v>0</v>
+      </c>
+      <c r="AE341">
+        <v>0</v>
+      </c>
+      <c r="AF341">
+        <v>0</v>
+      </c>
+      <c r="AG341">
+        <v>0</v>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ341">
+        <v>0</v>
+      </c>
+      <c r="AK341">
+        <v>0</v>
+      </c>
+      <c r="AL341">
+        <v>0</v>
+      </c>
+      <c r="AM341">
+        <v>-1</v>
+      </c>
+      <c r="AN341">
+        <v>-1</v>
+      </c>
+      <c r="AO341">
+        <v>-1</v>
+      </c>
+      <c r="AP341">
+        <v>-1</v>
+      </c>
+      <c r="AQ341">
+        <v>0</v>
+      </c>
+      <c r="AR341">
+        <v>0</v>
+      </c>
+      <c r="AS341">
+        <v>0</v>
+      </c>
+      <c r="AT341">
+        <v>0</v>
+      </c>
+      <c r="AU341" t="inlineStr">
         <is>
           <t>2026-08-29 23:30:00</t>
         </is>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -17270,55 +17270,55 @@
         <v>0</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G114">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G135">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G161">
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q203">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R203">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S203">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T203">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U203">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V203">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W203">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y203">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z203">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA203">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB203">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC203">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD203">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG203">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK203">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G226">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G227">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G253">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G254">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G269">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G270">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G271">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G282">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G283">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G340">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G341">

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.94</v>
+        <v>2.45</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q19">
-        <v>5.25</v>
+        <v>2.95</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S19">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V19">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z19">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA19">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>4.03</v>
+        <v>3.7</v>
       </c>
       <c r="AD19">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,43 +3569,43 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="Q20">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="R20">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T20">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="U20">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z20">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA20">
         <v>2.1</v>
@@ -3614,19 +3614,19 @@
         <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG20">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AK20">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="O21">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="P21">
+        <v>3.68</v>
+      </c>
+      <c r="Q21">
+        <v>2.38</v>
+      </c>
+      <c r="R21">
+        <v>2.15</v>
+      </c>
+      <c r="S21">
+        <v>1.38</v>
+      </c>
+      <c r="T21">
+        <v>2.81</v>
+      </c>
+      <c r="U21">
         <v>2.77</v>
       </c>
-      <c r="Q21">
-        <v>3.04</v>
-      </c>
-      <c r="R21">
-        <v>2.1</v>
-      </c>
-      <c r="S21">
-        <v>1.41</v>
-      </c>
-      <c r="T21">
-        <v>2.53</v>
-      </c>
-      <c r="U21">
-        <v>3.09</v>
-      </c>
       <c r="V21">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z21">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AA21">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB21">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC21">
-        <v>3.6</v>
+        <v>3.29</v>
       </c>
       <c r="AD21">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE21">
         <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG21">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.82</v>
+        <v>2.33</v>
       </c>
       <c r="O22">
-        <v>3.41</v>
+        <v>3.08</v>
       </c>
       <c r="P22">
-        <v>3.68</v>
+        <v>2.78</v>
       </c>
       <c r="Q22">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="S22">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="T22">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="U22">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="V22">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
+        <v>1.1</v>
+      </c>
+      <c r="Y22">
+        <v>1.5</v>
+      </c>
+      <c r="Z22">
+        <v>2.55</v>
+      </c>
+      <c r="AA22">
+        <v>2.5</v>
+      </c>
+      <c r="AB22">
+        <v>1.5</v>
+      </c>
+      <c r="AC22">
+        <v>4.75</v>
+      </c>
+      <c r="AD22">
+        <v>1.18</v>
+      </c>
+      <c r="AE22">
         <v>1.01</v>
       </c>
-      <c r="Y22">
-        <v>1.29</v>
-      </c>
-      <c r="Z22">
-        <v>3.24</v>
-      </c>
-      <c r="AA22">
-        <v>1.94</v>
-      </c>
-      <c r="AB22">
-        <v>1.89</v>
-      </c>
-      <c r="AC22">
-        <v>3.29</v>
-      </c>
-      <c r="AD22">
-        <v>1.28</v>
-      </c>
-      <c r="AE22">
-        <v>1.07</v>
-      </c>
       <c r="AF22">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="AG22">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK22">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="O23">
-        <v>3.08</v>
+        <v>4.15</v>
       </c>
       <c r="P23">
-        <v>2.78</v>
+        <v>5.05</v>
       </c>
       <c r="Q23">
-        <v>3.2</v>
+        <v>2.07</v>
       </c>
       <c r="R23">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="U23">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="W23">
+        <v>1.09</v>
+      </c>
+      <c r="X23">
         <v>1.01</v>
       </c>
-      <c r="X23">
-        <v>1.1</v>
-      </c>
       <c r="Y23">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA23">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB23">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC23">
-        <v>4.75</v>
+        <v>2.38</v>
       </c>
       <c r="AD23">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AE23">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>1.67</v>
+        <v>2.11</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.55</v>
+        <v>3.94</v>
       </c>
       <c r="O24">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>5.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q24">
-        <v>2.07</v>
+        <v>5.25</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="T24">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="V24">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="Z24">
-        <v>4.75</v>
+        <v>2.85</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB24">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="AC24">
-        <v>2.38</v>
+        <v>4.03</v>
       </c>
       <c r="AD24">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG24">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.1</v>
+        <v>1.94</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
+        <v>3.35</v>
+      </c>
+      <c r="Q31">
+        <v>2.62</v>
+      </c>
+      <c r="R31">
         <v>2.06</v>
       </c>
-      <c r="Q31">
-        <v>3.9</v>
-      </c>
-      <c r="R31">
-        <v>2.07</v>
-      </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U31">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="V31">
         <v>1.36</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
         <v>1.29</v>
       </c>
       <c r="Z31">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AA31">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AB31">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC31">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="AD31">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE31">
         <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG31">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,16 +5525,16 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.94</v>
+        <v>2.68</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="Q32">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="R32">
         <v>2.06</v>
@@ -5543,46 +5543,46 @@
         <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U32">
-        <v>3.01</v>
+        <v>2.82</v>
       </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1.06</v>
       </c>
       <c r="Y32">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="AA32">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB32">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC32">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AD32">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AK32">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="O33">
         <v>3.1</v>
       </c>
       <c r="P33">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q33">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R33">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
         <v>2.78</v>
       </c>
       <c r="U33">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
         <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z33">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="AA33">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AB33">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC33">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD33">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
         <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O55">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>3.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="R55">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S55">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="T55">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U55">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="V55">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z55">
-        <v>4.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA55">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB55">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC55">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="AD55">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE55">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF55">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG55">
         <v>2.25</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AK55">
-        <v>1.97</v>
+        <v>1.35</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,61 +9437,61 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P56">
+        <v>3.55</v>
+      </c>
+      <c r="Q56">
         <v>2.25</v>
       </c>
-      <c r="Q56">
-        <v>3.35</v>
-      </c>
       <c r="R56">
+        <v>2.4</v>
+      </c>
+      <c r="S56">
+        <v>1.27</v>
+      </c>
+      <c r="T56">
+        <v>3.4</v>
+      </c>
+      <c r="U56">
         <v>2.18</v>
       </c>
-      <c r="S56">
-        <v>1.34</v>
-      </c>
-      <c r="T56">
-        <v>2.91</v>
-      </c>
-      <c r="U56">
-        <v>2.41</v>
-      </c>
       <c r="V56">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W56">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
-        <v>3.82</v>
+        <v>4.9</v>
       </c>
       <c r="AA56">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB56">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC56">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AD56">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE56">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF56">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG56">
         <v>2.25</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AK56">
-        <v>1.35</v>
+        <v>1.97</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,25 +10415,25 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="O62">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P62">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="Q62">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="R62">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="S62">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="U62">
         <v>2.1</v>
@@ -10442,37 +10442,37 @@
         <v>1.67</v>
       </c>
       <c r="W62">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z62">
-        <v>5.55</v>
+        <v>5.3</v>
       </c>
       <c r="AA62">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB62">
         <v>2.59</v>
       </c>
       <c r="AC62">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AD62">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE62">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF62">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG62">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK62">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.31</v>
+        <v>2.05</v>
       </c>
       <c r="O63">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>7</v>
+        <v>2.88</v>
       </c>
       <c r="Q63">
-        <v>1.67</v>
+        <v>2.56</v>
       </c>
       <c r="R63">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T63">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="U63">
         <v>2.1</v>
       </c>
       <c r="V63">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W63">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z63">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA63">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB63">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AC63">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AD63">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE63">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF63">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AG63">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>2.94</v>
+        <v>1.6</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P64">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="Q64">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="R64">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S64">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V64">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W64">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z64">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="AA64">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB64">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AC64">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AD64">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AE64">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF64">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG64">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Q65">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="R65">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="S65">
         <v>1.22</v>
@@ -10928,40 +10928,40 @@
         <v>2.2</v>
       </c>
       <c r="V65">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W65">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
         <v>1.11</v>
       </c>
       <c r="Z65">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AA65">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AB65">
+        <v>2.4</v>
+      </c>
+      <c r="AC65">
         <v>2.35</v>
       </c>
-      <c r="AC65">
-        <v>2.27</v>
-      </c>
       <c r="AD65">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE65">
         <v>1.19</v>
       </c>
       <c r="AF65">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AG65">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="P66">
-        <v>2.35</v>
+        <v>5.25</v>
       </c>
       <c r="Q66">
-        <v>3.12</v>
+        <v>1.85</v>
       </c>
       <c r="R66">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="S66">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T66">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="U66">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V66">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="W66">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z66">
-        <v>4.9</v>
+        <v>5.55</v>
       </c>
       <c r="AA66">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AB66">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="AC66">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AD66">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AE66">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AF66">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AG66">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK66">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O76">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P76">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q76">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R76">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S76">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T76">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U76">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V76">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W76">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y76">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z76">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA76">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC76">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AD76">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG76">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK76">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q77">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R77">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S77">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T77">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U77">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V77">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W77">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y77">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z77">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA77">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC77">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD77">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK77">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S82">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T82">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U82">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V82">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W82">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y82">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z82">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AA82">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC82">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG82">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AK82">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="O83">
         <v>3</v>
       </c>
       <c r="P83">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="Q83">
-        <v>3.67</v>
+        <v>2.98</v>
       </c>
       <c r="R83">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="S83">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T83">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U83">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="V83">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W83">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z83">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="AA83">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AB83">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC83">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="AD83">
         <v>1.19</v>
       </c>
       <c r="AE83">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF83">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG83">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AK83">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
+        <v>5.4</v>
+      </c>
+      <c r="O100">
+        <v>4.64</v>
+      </c>
+      <c r="P100">
+        <v>1.54</v>
+      </c>
+      <c r="Q100">
+        <v>4</v>
+      </c>
+      <c r="R100">
+        <v>2.82</v>
+      </c>
+      <c r="S100">
+        <v>1.22</v>
+      </c>
+      <c r="T100">
+        <v>4.05</v>
+      </c>
+      <c r="U100">
+        <v>2.19</v>
+      </c>
+      <c r="V100">
         <v>1.7</v>
       </c>
-      <c r="O100">
-        <v>3.9</v>
-      </c>
-      <c r="P100">
-        <v>4.5</v>
-      </c>
-      <c r="Q100">
-        <v>2.24</v>
-      </c>
-      <c r="R100">
-        <v>2.2</v>
-      </c>
-      <c r="S100">
-        <v>1.3</v>
-      </c>
-      <c r="T100">
-        <v>3.36</v>
-      </c>
-      <c r="U100">
-        <v>2.45</v>
-      </c>
-      <c r="V100">
-        <v>1.54</v>
-      </c>
       <c r="W100">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z100">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AA100">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="AB100">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="AC100">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="AD100">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AE100">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AF100">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG100">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.19</v>
+        <v>2.53</v>
       </c>
       <c r="AK100">
-        <v>2.21</v>
+        <v>1.15</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="O101">
-        <v>4.64</v>
+        <v>3.9</v>
       </c>
       <c r="P101">
+        <v>4.5</v>
+      </c>
+      <c r="Q101">
+        <v>2.24</v>
+      </c>
+      <c r="R101">
+        <v>2.2</v>
+      </c>
+      <c r="S101">
+        <v>1.3</v>
+      </c>
+      <c r="T101">
+        <v>3.36</v>
+      </c>
+      <c r="U101">
+        <v>2.45</v>
+      </c>
+      <c r="V101">
         <v>1.54</v>
       </c>
-      <c r="Q101">
-        <v>4</v>
-      </c>
-      <c r="R101">
-        <v>2.82</v>
-      </c>
-      <c r="S101">
-        <v>1.22</v>
-      </c>
-      <c r="T101">
-        <v>4.05</v>
-      </c>
-      <c r="U101">
-        <v>2.19</v>
-      </c>
-      <c r="V101">
-        <v>1.7</v>
-      </c>
       <c r="W101">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
+        <v>1.18</v>
+      </c>
+      <c r="Z101">
+        <v>4.2</v>
+      </c>
+      <c r="AA101">
+        <v>1.69</v>
+      </c>
+      <c r="AB101">
+        <v>2.24</v>
+      </c>
+      <c r="AC101">
+        <v>2.63</v>
+      </c>
+      <c r="AD101">
+        <v>1.43</v>
+      </c>
+      <c r="AE101">
         <v>1.13</v>
       </c>
-      <c r="Z101">
-        <v>5.6</v>
-      </c>
-      <c r="AA101">
-        <v>1.43</v>
-      </c>
-      <c r="AB101">
-        <v>2.7</v>
-      </c>
-      <c r="AC101">
-        <v>2.27</v>
-      </c>
-      <c r="AD101">
-        <v>1.74</v>
-      </c>
-      <c r="AE101">
-        <v>1.25</v>
-      </c>
       <c r="AF101">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>2.53</v>
+        <v>1.19</v>
       </c>
       <c r="AK101">
-        <v>1.15</v>
+        <v>2.21</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,28 +19869,28 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="O120">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P120">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q120">
-        <v>2.9</v>
+        <v>2.41</v>
       </c>
       <c r="R120">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S120">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T120">
         <v>2.62</v>
       </c>
       <c r="U120">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="V120">
         <v>1.37</v>
@@ -19905,28 +19905,28 @@
         <v>1.3</v>
       </c>
       <c r="Z120">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="AA120">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB120">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC120">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="AD120">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE120">
         <v>1.06</v>
       </c>
       <c r="AF120">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG120">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK120">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="O121">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P121">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q121">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R121">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="S121">
+        <v>1.36</v>
+      </c>
+      <c r="T121">
+        <v>3.05</v>
+      </c>
+      <c r="U121">
+        <v>2.69</v>
+      </c>
+      <c r="V121">
         <v>1.4</v>
       </c>
-      <c r="T121">
-        <v>2.62</v>
-      </c>
-      <c r="U121">
-        <v>2.93</v>
-      </c>
-      <c r="V121">
-        <v>1.37</v>
-      </c>
       <c r="W121">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X121">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z121">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA121">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB121">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC121">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="AD121">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE121">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF121">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AG121">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O123">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P123">
         <v>2.7</v>
       </c>
       <c r="Q123">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R123">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S123">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T123">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="U123">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="V123">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W123">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X123">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y123">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z123">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="AA123">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB123">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC123">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AD123">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE123">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF123">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG123">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK123">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,65 +20521,65 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="O124">
+        <v>3.2</v>
+      </c>
+      <c r="P124">
+        <v>2.9</v>
+      </c>
+      <c r="Q124">
+        <v>2.9</v>
+      </c>
+      <c r="R124">
+        <v>2.1</v>
+      </c>
+      <c r="S124">
+        <v>1.41</v>
+      </c>
+      <c r="T124">
+        <v>2.62</v>
+      </c>
+      <c r="U124">
+        <v>2.81</v>
+      </c>
+      <c r="V124">
+        <v>1.37</v>
+      </c>
+      <c r="W124">
+        <v>1.05</v>
+      </c>
+      <c r="X124">
+        <v>1.02</v>
+      </c>
+      <c r="Y124">
+        <v>1.3</v>
+      </c>
+      <c r="Z124">
+        <v>3.36</v>
+      </c>
+      <c r="AA124">
+        <v>1.97</v>
+      </c>
+      <c r="AB124">
+        <v>1.79</v>
+      </c>
+      <c r="AC124">
         <v>3.45</v>
       </c>
-      <c r="P124">
-        <v>3.5</v>
-      </c>
-      <c r="Q124">
-        <v>2.4</v>
-      </c>
-      <c r="R124">
-        <v>2.08</v>
-      </c>
-      <c r="S124">
-        <v>1.36</v>
-      </c>
-      <c r="T124">
-        <v>3.05</v>
-      </c>
-      <c r="U124">
-        <v>2.69</v>
-      </c>
-      <c r="V124">
-        <v>1.4</v>
-      </c>
-      <c r="W124">
-        <v>1.04</v>
-      </c>
-      <c r="X124">
-        <v>1.03</v>
-      </c>
-      <c r="Y124">
-        <v>1.25</v>
-      </c>
-      <c r="Z124">
-        <v>3.42</v>
-      </c>
-      <c r="AA124">
+      <c r="AD124">
+        <v>1.26</v>
+      </c>
+      <c r="AE124">
+        <v>1.06</v>
+      </c>
+      <c r="AF124">
+        <v>1.75</v>
+      </c>
+      <c r="AG124">
         <v>1.95</v>
       </c>
-      <c r="AB124">
-        <v>1.85</v>
-      </c>
-      <c r="AC124">
-        <v>3.25</v>
-      </c>
-      <c r="AD124">
-        <v>1.33</v>
-      </c>
-      <c r="AE124">
-        <v>1.07</v>
-      </c>
-      <c r="AF124">
-        <v>1.72</v>
-      </c>
-      <c r="AG124">
-        <v>2</v>
-      </c>
       <c r="AH124" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK124">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,80 +20684,80 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O125">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P125">
         <v>2.7</v>
       </c>
       <c r="Q125">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R125">
+        <v>1.99</v>
+      </c>
+      <c r="S125">
+        <v>1.41</v>
+      </c>
+      <c r="T125">
+        <v>2.66</v>
+      </c>
+      <c r="U125">
+        <v>2.97</v>
+      </c>
+      <c r="V125">
+        <v>1.37</v>
+      </c>
+      <c r="W125">
+        <v>1.03</v>
+      </c>
+      <c r="X125">
+        <v>1.06</v>
+      </c>
+      <c r="Y125">
+        <v>1.33</v>
+      </c>
+      <c r="Z125">
+        <v>3.36</v>
+      </c>
+      <c r="AA125">
         <v>2</v>
       </c>
-      <c r="S125">
-        <v>1.42</v>
-      </c>
-      <c r="T125">
-        <v>2.73</v>
-      </c>
-      <c r="U125">
-        <v>3.17</v>
-      </c>
-      <c r="V125">
-        <v>1.33</v>
-      </c>
-      <c r="W125">
-        <v>1.05</v>
-      </c>
-      <c r="X125">
-        <v>1.07</v>
-      </c>
-      <c r="Y125">
+      <c r="AB125">
+        <v>1.8</v>
+      </c>
+      <c r="AC125">
+        <v>3.34</v>
+      </c>
+      <c r="AD125">
+        <v>1.24</v>
+      </c>
+      <c r="AE125">
+        <v>1.04</v>
+      </c>
+      <c r="AF125">
+        <v>1.73</v>
+      </c>
+      <c r="AG125">
+        <v>1.95</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
         <v>1.32</v>
       </c>
-      <c r="Z125">
-        <v>2.88</v>
-      </c>
-      <c r="AA125">
-        <v>2.1</v>
-      </c>
-      <c r="AB125">
-        <v>1.66</v>
-      </c>
-      <c r="AC125">
-        <v>3.75</v>
-      </c>
-      <c r="AD125">
-        <v>1.21</v>
-      </c>
-      <c r="AE125">
-        <v>1.08</v>
-      </c>
-      <c r="AF125">
-        <v>1.82</v>
-      </c>
-      <c r="AG125">
-        <v>1.88</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.4</v>
-      </c>
       <c r="AK125">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="O134">
+        <v>3.25</v>
+      </c>
+      <c r="P134">
+        <v>3.02</v>
+      </c>
+      <c r="Q134">
+        <v>2.53</v>
+      </c>
+      <c r="R134">
+        <v>2.06</v>
+      </c>
+      <c r="S134">
+        <v>1.42</v>
+      </c>
+      <c r="T134">
+        <v>2.83</v>
+      </c>
+      <c r="U134">
+        <v>2.94</v>
+      </c>
+      <c r="V134">
+        <v>1.35</v>
+      </c>
+      <c r="W134">
+        <v>1.04</v>
+      </c>
+      <c r="X134">
+        <v>1.06</v>
+      </c>
+      <c r="Y134">
+        <v>1.34</v>
+      </c>
+      <c r="Z134">
         <v>3.22</v>
       </c>
-      <c r="P134">
-        <v>2.87</v>
-      </c>
-      <c r="Q134">
-        <v>3.1</v>
-      </c>
-      <c r="R134">
-        <v>2.1</v>
-      </c>
-      <c r="S134">
-        <v>1.36</v>
-      </c>
-      <c r="T134">
-        <v>2.88</v>
-      </c>
-      <c r="U134">
-        <v>2.95</v>
-      </c>
-      <c r="V134">
-        <v>1.4</v>
-      </c>
-      <c r="W134">
-        <v>1.08</v>
-      </c>
-      <c r="X134">
-        <v>1.05</v>
-      </c>
-      <c r="Y134">
-        <v>1.28</v>
-      </c>
-      <c r="Z134">
+      <c r="AA134">
+        <v>1.99</v>
+      </c>
+      <c r="AB134">
+        <v>1.7</v>
+      </c>
+      <c r="AC134">
         <v>3.35</v>
-      </c>
-      <c r="AA134">
-        <v>1.91</v>
-      </c>
-      <c r="AB134">
-        <v>1.9</v>
-      </c>
-      <c r="AC134">
-        <v>3.54</v>
       </c>
       <c r="AD134">
         <v>1.26</v>
       </c>
       <c r="AE134">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF134">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG134">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK134">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="O135">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P135">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="Q135">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="R135">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S135">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T135">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="U135">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="V135">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W135">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z135">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="AA135">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AB135">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC135">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="AD135">
         <v>1.26</v>
       </c>
       <c r="AE135">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF135">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG135">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK135">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="O138">
-        <v>3.75</v>
+        <v>6.45</v>
       </c>
       <c r="P138">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="Q138">
-        <v>2.27</v>
+        <v>1.45</v>
       </c>
       <c r="R138">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="S138">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="T138">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="U138">
-        <v>2.71</v>
+        <v>1.91</v>
       </c>
       <c r="V138">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="W138">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X138">
+        <v>1.01</v>
+      </c>
+      <c r="Y138">
         <v>1.05</v>
       </c>
-      <c r="Y138">
-        <v>1.26</v>
-      </c>
       <c r="Z138">
-        <v>3.54</v>
+        <v>6.7</v>
       </c>
       <c r="AA138">
-        <v>1.86</v>
+        <v>1.31</v>
       </c>
       <c r="AB138">
-        <v>1.97</v>
+        <v>3.12</v>
       </c>
       <c r="AC138">
-        <v>2.85</v>
+        <v>1.93</v>
       </c>
       <c r="AD138">
-        <v>1.33</v>
+        <v>1.89</v>
       </c>
       <c r="AE138">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AF138">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG138">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK138">
-        <v>2.04</v>
+        <v>3.91</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="O139">
-        <v>6.45</v>
+        <v>3.75</v>
       </c>
       <c r="P139">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="Q139">
-        <v>1.45</v>
+        <v>2.27</v>
       </c>
       <c r="R139">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="S139">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="T139">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="U139">
-        <v>1.91</v>
+        <v>2.71</v>
       </c>
       <c r="V139">
+        <v>1.43</v>
+      </c>
+      <c r="W139">
+        <v>1.07</v>
+      </c>
+      <c r="X139">
+        <v>1.05</v>
+      </c>
+      <c r="Y139">
+        <v>1.26</v>
+      </c>
+      <c r="Z139">
+        <v>3.54</v>
+      </c>
+      <c r="AA139">
         <v>1.86</v>
       </c>
-      <c r="W139">
-        <v>1.18</v>
-      </c>
-      <c r="X139">
-        <v>1.01</v>
-      </c>
-      <c r="Y139">
-        <v>1.05</v>
-      </c>
-      <c r="Z139">
-        <v>6.7</v>
-      </c>
-      <c r="AA139">
-        <v>1.31</v>
-      </c>
       <c r="AB139">
-        <v>3.12</v>
+        <v>1.97</v>
       </c>
       <c r="AC139">
-        <v>1.93</v>
+        <v>2.85</v>
       </c>
       <c r="AD139">
-        <v>1.89</v>
+        <v>1.33</v>
       </c>
       <c r="AE139">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AF139">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG139">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK139">
-        <v>3.91</v>
+        <v>2.04</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
+        <v>2.7</v>
+      </c>
+      <c r="O142">
+        <v>3.5</v>
+      </c>
+      <c r="P142">
+        <v>2.23</v>
+      </c>
+      <c r="Q142">
+        <v>3.16</v>
+      </c>
+      <c r="R142">
+        <v>2.07</v>
+      </c>
+      <c r="S142">
+        <v>1.37</v>
+      </c>
+      <c r="T142">
+        <v>2.85</v>
+      </c>
+      <c r="U142">
+        <v>2.62</v>
+      </c>
+      <c r="V142">
+        <v>1.43</v>
+      </c>
+      <c r="W142">
+        <v>1.07</v>
+      </c>
+      <c r="X142">
+        <v>1.05</v>
+      </c>
+      <c r="Y142">
+        <v>1.26</v>
+      </c>
+      <c r="Z142">
+        <v>3.62</v>
+      </c>
+      <c r="AA142">
+        <v>1.76</v>
+      </c>
+      <c r="AB142">
         <v>1.97</v>
       </c>
-      <c r="O142">
-        <v>3.35</v>
-      </c>
-      <c r="P142">
-        <v>3.2</v>
-      </c>
-      <c r="Q142">
-        <v>2.55</v>
-      </c>
-      <c r="R142">
-        <v>2.25</v>
-      </c>
-      <c r="S142">
-        <v>1.33</v>
-      </c>
-      <c r="T142">
-        <v>3.2</v>
-      </c>
-      <c r="U142">
-        <v>2.53</v>
-      </c>
-      <c r="V142">
-        <v>1.45</v>
-      </c>
-      <c r="W142">
-        <v>1.06</v>
-      </c>
-      <c r="X142">
-        <v>1.01</v>
-      </c>
-      <c r="Y142">
-        <v>1.22</v>
-      </c>
-      <c r="Z142">
-        <v>3.7</v>
-      </c>
-      <c r="AA142">
-        <v>1.83</v>
-      </c>
-      <c r="AB142">
-        <v>1.93</v>
-      </c>
       <c r="AC142">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD142">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE142">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF142">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG142">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK142">
-        <v>1.77</v>
+        <v>1.31</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O143">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P143">
-        <v>2.23</v>
+        <v>2.87</v>
       </c>
       <c r="Q143">
-        <v>3.16</v>
+        <v>2.76</v>
       </c>
       <c r="R143">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S143">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T143">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="U143">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V143">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W143">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X143">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y143">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z143">
         <v>3.62</v>
       </c>
       <c r="AA143">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB143">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC143">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD143">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE143">
         <v>1.14</v>
       </c>
       <c r="AF143">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG143">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>1.24</v>
       </c>
       <c r="AK143">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="O144">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P144">
-        <v>3.94</v>
+        <v>3</v>
       </c>
       <c r="Q144">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="R144">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S144">
+        <v>1.38</v>
+      </c>
+      <c r="T144">
+        <v>2.75</v>
+      </c>
+      <c r="U144">
+        <v>2.88</v>
+      </c>
+      <c r="V144">
         <v>1.36</v>
       </c>
-      <c r="T144">
-        <v>2.89</v>
-      </c>
-      <c r="U144">
-        <v>2.69</v>
-      </c>
-      <c r="V144">
-        <v>1.43</v>
-      </c>
       <c r="W144">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X144">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="Z144">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA144">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AB144">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC144">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AD144">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE144">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF144">
         <v>1.75</v>
       </c>
       <c r="AG144">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK144">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,65 +23944,65 @@
         </is>
       </c>
       <c r="N145">
+        <v>1.85</v>
+      </c>
+      <c r="O145">
+        <v>3.7</v>
+      </c>
+      <c r="P145">
+        <v>3.94</v>
+      </c>
+      <c r="Q145">
+        <v>2.46</v>
+      </c>
+      <c r="R145">
         <v>2.3</v>
       </c>
-      <c r="O145">
-        <v>3.3</v>
-      </c>
-      <c r="P145">
-        <v>2.87</v>
-      </c>
-      <c r="Q145">
-        <v>2.76</v>
-      </c>
-      <c r="R145">
-        <v>2.2</v>
-      </c>
       <c r="S145">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T145">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="U145">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="V145">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W145">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X145">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z145">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="AA145">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB145">
+        <v>1.95</v>
+      </c>
+      <c r="AC145">
+        <v>3.1</v>
+      </c>
+      <c r="AD145">
+        <v>1.32</v>
+      </c>
+      <c r="AE145">
+        <v>1.08</v>
+      </c>
+      <c r="AF145">
+        <v>1.75</v>
+      </c>
+      <c r="AG145">
         <v>2</v>
       </c>
-      <c r="AC145">
-        <v>2.85</v>
-      </c>
-      <c r="AD145">
-        <v>1.37</v>
-      </c>
-      <c r="AE145">
-        <v>1.14</v>
-      </c>
-      <c r="AF145">
-        <v>1.62</v>
-      </c>
-      <c r="AG145">
-        <v>2.15</v>
-      </c>
       <c r="AH145" t="inlineStr">
         <is>
           <t>[]</t>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK145">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,65 +24107,65 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="O146">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P146">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q146">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="R146">
+        <v>2.25</v>
+      </c>
+      <c r="S146">
+        <v>1.33</v>
+      </c>
+      <c r="T146">
+        <v>3.2</v>
+      </c>
+      <c r="U146">
+        <v>2.53</v>
+      </c>
+      <c r="V146">
+        <v>1.45</v>
+      </c>
+      <c r="W146">
+        <v>1.06</v>
+      </c>
+      <c r="X146">
+        <v>1.01</v>
+      </c>
+      <c r="Y146">
+        <v>1.22</v>
+      </c>
+      <c r="Z146">
+        <v>3.7</v>
+      </c>
+      <c r="AA146">
+        <v>1.83</v>
+      </c>
+      <c r="AB146">
+        <v>1.93</v>
+      </c>
+      <c r="AC146">
+        <v>2.85</v>
+      </c>
+      <c r="AD146">
+        <v>1.33</v>
+      </c>
+      <c r="AE146">
+        <v>1.09</v>
+      </c>
+      <c r="AF146">
+        <v>1.67</v>
+      </c>
+      <c r="AG146">
         <v>2.1</v>
       </c>
-      <c r="S146">
-        <v>1.38</v>
-      </c>
-      <c r="T146">
-        <v>2.75</v>
-      </c>
-      <c r="U146">
-        <v>2.88</v>
-      </c>
-      <c r="V146">
-        <v>1.36</v>
-      </c>
-      <c r="W146">
-        <v>1.08</v>
-      </c>
-      <c r="X146">
-        <v>1.02</v>
-      </c>
-      <c r="Y146">
-        <v>1.31</v>
-      </c>
-      <c r="Z146">
-        <v>3.08</v>
-      </c>
-      <c r="AA146">
-        <v>1.99</v>
-      </c>
-      <c r="AB146">
-        <v>1.9</v>
-      </c>
-      <c r="AC146">
-        <v>3.6</v>
-      </c>
-      <c r="AD146">
-        <v>1.29</v>
-      </c>
-      <c r="AE146">
-        <v>1.06</v>
-      </c>
-      <c r="AF146">
-        <v>1.75</v>
-      </c>
-      <c r="AG146">
-        <v>1.97</v>
-      </c>
       <c r="AH146" t="inlineStr">
         <is>
           <t>[]</t>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK146">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,80 +26389,80 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="O160">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="P160">
+        <v>7</v>
+      </c>
+      <c r="Q160">
+        <v>1.85</v>
+      </c>
+      <c r="R160">
+        <v>2.25</v>
+      </c>
+      <c r="S160">
+        <v>1.29</v>
+      </c>
+      <c r="T160">
+        <v>3.1</v>
+      </c>
+      <c r="U160">
+        <v>2.39</v>
+      </c>
+      <c r="V160">
+        <v>1.5</v>
+      </c>
+      <c r="W160">
+        <v>1.09</v>
+      </c>
+      <c r="X160">
+        <v>1.04</v>
+      </c>
+      <c r="Y160">
+        <v>1.2</v>
+      </c>
+      <c r="Z160">
         <v>3.9</v>
       </c>
-      <c r="Q160">
-        <v>2.25</v>
-      </c>
-      <c r="R160">
-        <v>2.2</v>
-      </c>
-      <c r="S160">
-        <v>1.33</v>
-      </c>
-      <c r="T160">
-        <v>3</v>
-      </c>
-      <c r="U160">
-        <v>2.75</v>
-      </c>
-      <c r="V160">
-        <v>1.4</v>
-      </c>
-      <c r="W160">
+      <c r="AA160">
+        <v>1.66</v>
+      </c>
+      <c r="AB160">
+        <v>2.15</v>
+      </c>
+      <c r="AC160">
+        <v>2.62</v>
+      </c>
+      <c r="AD160">
+        <v>1.45</v>
+      </c>
+      <c r="AE160">
+        <v>1.14</v>
+      </c>
+      <c r="AF160">
+        <v>1.85</v>
+      </c>
+      <c r="AG160">
+        <v>1.83</v>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ160">
         <v>1.08</v>
       </c>
-      <c r="X160">
-        <v>1.02</v>
-      </c>
-      <c r="Y160">
-        <v>1.25</v>
-      </c>
-      <c r="Z160">
-        <v>3.6</v>
-      </c>
-      <c r="AA160">
-        <v>1.85</v>
-      </c>
-      <c r="AB160">
-        <v>1.84</v>
-      </c>
-      <c r="AC160">
-        <v>3.05</v>
-      </c>
-      <c r="AD160">
-        <v>1.3</v>
-      </c>
-      <c r="AE160">
-        <v>1.07</v>
-      </c>
-      <c r="AF160">
-        <v>1.77</v>
-      </c>
-      <c r="AG160">
-        <v>1.87</v>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ160">
-        <v>1.22</v>
-      </c>
       <c r="AK160">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="O161">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="P161">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="Q161">
-        <v>1.85</v>
+        <v>2.86</v>
       </c>
       <c r="R161">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S161">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T161">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U161">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="V161">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W161">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X161">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y161">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z161">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA161">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AB161">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AC161">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="AD161">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AE161">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF161">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG161">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AK161">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
+        <v>1.73</v>
+      </c>
+      <c r="O162">
+        <v>3.6</v>
+      </c>
+      <c r="P162">
+        <v>3.9</v>
+      </c>
+      <c r="Q162">
         <v>2.25</v>
       </c>
-      <c r="O162">
-        <v>3.3</v>
-      </c>
-      <c r="P162">
-        <v>2.7</v>
-      </c>
-      <c r="Q162">
-        <v>2.86</v>
-      </c>
       <c r="R162">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S162">
         <v>1.33</v>
       </c>
       <c r="T162">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U162">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V162">
         <v>1.4</v>
       </c>
       <c r="W162">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X162">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z162">
         <v>3.6</v>
       </c>
       <c r="AA162">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB162">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AC162">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="AD162">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE162">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF162">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG162">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK162">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S164">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T164">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U164">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V164">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W164">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X164">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z164">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AA164">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC164">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD164">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AK164">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O243">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P243">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T256">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X256">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE256">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF256">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AG256">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -45795,55 +45795,55 @@
         <v>0</v>
       </c>
       <c r="Q279">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R279">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T279">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V279">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W279">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y279">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z279">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC279">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD279">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AE279">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF279">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG279">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK279">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G340">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G341">

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.42</v>
+        <v>4.84</v>
       </c>
       <c r="O5">
-        <v>3.08</v>
+        <v>4.22</v>
       </c>
       <c r="P5">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="Q5">
         <v>4.6</v>
       </c>
       <c r="R5">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="S5">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>2.57</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AB5">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AC5">
-        <v>4.35</v>
+        <v>2.56</v>
       </c>
       <c r="AD5">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="AE5">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AF5">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="AG5">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>2.23</v>
       </c>
       <c r="AK5">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.84</v>
+        <v>3.42</v>
       </c>
       <c r="O6">
-        <v>4.22</v>
+        <v>3.08</v>
       </c>
       <c r="P6">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="Q6">
         <v>4.6</v>
       </c>
       <c r="R6">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="S6">
+        <v>1.48</v>
+      </c>
+      <c r="T6">
+        <v>2.38</v>
+      </c>
+      <c r="U6">
+        <v>3.2</v>
+      </c>
+      <c r="V6">
+        <v>1.3</v>
+      </c>
+      <c r="W6">
+        <v>1.06</v>
+      </c>
+      <c r="X6">
+        <v>1.04</v>
+      </c>
+      <c r="Y6">
+        <v>1.4</v>
+      </c>
+      <c r="Z6">
+        <v>2.57</v>
+      </c>
+      <c r="AA6">
+        <v>2.4</v>
+      </c>
+      <c r="AB6">
+        <v>1.53</v>
+      </c>
+      <c r="AC6">
+        <v>4.35</v>
+      </c>
+      <c r="AD6">
+        <v>1.19</v>
+      </c>
+      <c r="AE6">
+        <v>1.01</v>
+      </c>
+      <c r="AF6">
+        <v>2.06</v>
+      </c>
+      <c r="AG6">
+        <v>1.7</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.3</v>
+      </c>
+      <c r="AK6">
         <v>1.25</v>
-      </c>
-      <c r="T6">
-        <v>3.5</v>
-      </c>
-      <c r="U6">
-        <v>2.2</v>
-      </c>
-      <c r="V6">
-        <v>1.6</v>
-      </c>
-      <c r="W6">
-        <v>1.14</v>
-      </c>
-      <c r="X6">
-        <v>1.03</v>
-      </c>
-      <c r="Y6">
-        <v>1.14</v>
-      </c>
-      <c r="Z6">
-        <v>4.5</v>
-      </c>
-      <c r="AA6">
-        <v>1.6</v>
-      </c>
-      <c r="AB6">
-        <v>2.25</v>
-      </c>
-      <c r="AC6">
-        <v>2.56</v>
-      </c>
-      <c r="AD6">
-        <v>1.52</v>
-      </c>
-      <c r="AE6">
-        <v>1.2</v>
-      </c>
-      <c r="AF6">
-        <v>1.6</v>
-      </c>
-      <c r="AG6">
-        <v>2.2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>2.23</v>
-      </c>
-      <c r="AK6">
-        <v>1.18</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="O15">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
-        <v>4.35</v>
+        <v>2.6</v>
       </c>
       <c r="Q15">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="R15">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="S15">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>3.68</v>
+        <v>2.38</v>
       </c>
       <c r="V15">
+        <v>1.53</v>
+      </c>
+      <c r="W15">
+        <v>1.09</v>
+      </c>
+      <c r="X15">
+        <v>1.03</v>
+      </c>
+      <c r="Y15">
+        <v>1.15</v>
+      </c>
+      <c r="Z15">
+        <v>3.8</v>
+      </c>
+      <c r="AA15">
+        <v>1.61</v>
+      </c>
+      <c r="AB15">
+        <v>2.28</v>
+      </c>
+      <c r="AC15">
+        <v>2.43</v>
+      </c>
+      <c r="AD15">
+        <v>1.44</v>
+      </c>
+      <c r="AE15">
+        <v>1.14</v>
+      </c>
+      <c r="AF15">
+        <v>1.55</v>
+      </c>
+      <c r="AG15">
+        <v>2.12</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.25</v>
       </c>
-      <c r="W15">
-        <v>1.04</v>
-      </c>
-      <c r="X15">
-        <v>1.06</v>
-      </c>
-      <c r="Y15">
-        <v>1.53</v>
-      </c>
-      <c r="Z15">
-        <v>2.34</v>
-      </c>
-      <c r="AA15">
-        <v>2.56</v>
-      </c>
-      <c r="AB15">
-        <v>1.4</v>
-      </c>
-      <c r="AC15">
-        <v>5.28</v>
-      </c>
-      <c r="AD15">
-        <v>1.14</v>
-      </c>
-      <c r="AE15">
-        <v>1.02</v>
-      </c>
-      <c r="AF15">
-        <v>2.1</v>
-      </c>
-      <c r="AG15">
-        <v>1.57</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.28</v>
-      </c>
       <c r="AK15">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="O16">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="P16">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
-        <v>2.69</v>
+        <v>3.45</v>
       </c>
       <c r="R16">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="S16">
+        <v>1.46</v>
+      </c>
+      <c r="T16">
+        <v>2.5</v>
+      </c>
+      <c r="U16">
+        <v>3.1</v>
+      </c>
+      <c r="V16">
         <v>1.28</v>
       </c>
-      <c r="T16">
-        <v>3.25</v>
-      </c>
-      <c r="U16">
-        <v>2.38</v>
-      </c>
-      <c r="V16">
-        <v>1.53</v>
-      </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AA16">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AC16">
-        <v>2.43</v>
+        <v>3.65</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AE16">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AG16">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK16">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G29">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="O41">
         <v>3.75</v>
       </c>
       <c r="P41">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="Q41">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="R41">
         <v>2.36</v>
       </c>
       <c r="S41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T41">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U41">
         <v>2.15</v>
       </c>
       <c r="V41">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W41">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA41">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB41">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC41">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AD41">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AE41">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF41">
+        <v>1.4</v>
+      </c>
+      <c r="AG41">
+        <v>2.63</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.44</v>
       </c>
-      <c r="AG41">
-        <v>2.4</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.25</v>
-      </c>
       <c r="AK41">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="Q42">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="R42">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="S42">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T42">
         <v>4</v>
       </c>
       <c r="U42">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="V42">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W42">
         <v>1.17</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z42">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA42">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB42">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC42">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD42">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AE42">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF42">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG42">
         <v>2.63</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.18</v>
+        <v>2.26</v>
       </c>
       <c r="O43">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P43">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="Q43">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="S43">
         <v>1.22</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U43">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="V43">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W43">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA43">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AB43">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AC43">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AD43">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AE43">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AF43">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,61 +8296,61 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.25</v>
+        <v>1.47</v>
       </c>
       <c r="O49">
+        <v>4.4</v>
+      </c>
+      <c r="P49">
+        <v>6.1</v>
+      </c>
+      <c r="Q49">
+        <v>2</v>
+      </c>
+      <c r="R49">
+        <v>2.38</v>
+      </c>
+      <c r="S49">
+        <v>1.3</v>
+      </c>
+      <c r="T49">
         <v>3.3</v>
       </c>
-      <c r="P49">
-        <v>3.1</v>
-      </c>
-      <c r="Q49">
-        <v>2.6</v>
-      </c>
-      <c r="R49">
-        <v>2.03</v>
-      </c>
-      <c r="S49">
-        <v>1.41</v>
-      </c>
-      <c r="T49">
-        <v>2.81</v>
-      </c>
       <c r="U49">
-        <v>2.95</v>
+        <v>2.53</v>
       </c>
       <c r="V49">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="W49">
         <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z49">
-        <v>3.08</v>
+        <v>3.95</v>
       </c>
       <c r="AA49">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AB49">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="AC49">
-        <v>3.6</v>
+        <v>2.71</v>
       </c>
       <c r="AD49">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE49">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG49">
         <v>1.9</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,61 +8459,61 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.47</v>
+        <v>2.25</v>
       </c>
       <c r="O50">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="U50">
-        <v>2.53</v>
+        <v>2.95</v>
       </c>
       <c r="V50">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W50">
         <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z50">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="AA50">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AB50">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="AC50">
-        <v>2.71</v>
+        <v>3.6</v>
       </c>
       <c r="AD50">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AE50">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG50">
         <v>1.9</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="O55">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P55">
+        <v>3.55</v>
+      </c>
+      <c r="Q55">
         <v>2.25</v>
       </c>
-      <c r="Q55">
-        <v>3.35</v>
-      </c>
       <c r="R55">
+        <v>2.4</v>
+      </c>
+      <c r="S55">
+        <v>1.27</v>
+      </c>
+      <c r="T55">
+        <v>3.4</v>
+      </c>
+      <c r="U55">
         <v>2.18</v>
       </c>
-      <c r="S55">
-        <v>1.34</v>
-      </c>
-      <c r="T55">
-        <v>2.91</v>
-      </c>
-      <c r="U55">
-        <v>2.41</v>
-      </c>
       <c r="V55">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z55">
-        <v>3.82</v>
+        <v>4.9</v>
       </c>
       <c r="AA55">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB55">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC55">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AD55">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE55">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF55">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG55">
         <v>2.25</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AK55">
-        <v>1.35</v>
+        <v>1.97</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,61 +9437,61 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O56">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>3.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S56">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="T56">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U56">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="V56">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z56">
-        <v>4.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA56">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB56">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC56">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="AD56">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE56">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF56">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG56">
         <v>2.25</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AK56">
-        <v>1.97</v>
+        <v>1.35</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="O80">
+        <v>3.05</v>
+      </c>
+      <c r="P80">
         <v>3</v>
       </c>
-      <c r="P80">
-        <v>2.45</v>
-      </c>
       <c r="Q80">
-        <v>3.67</v>
+        <v>2.9</v>
       </c>
       <c r="R80">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S80">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T80">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U80">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V80">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W80">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z80">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="AA80">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AB80">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC80">
-        <v>3.93</v>
+        <v>3.69</v>
       </c>
       <c r="AD80">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE80">
         <v>1.03</v>
       </c>
       <c r="AF80">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG80">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK80">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R81">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S81">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T81">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U81">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V81">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W81">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y81">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z81">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA81">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC81">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AD81">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG81">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK81">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="O83">
         <v>3</v>
       </c>
       <c r="P83">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q83">
-        <v>2.98</v>
+        <v>3.67</v>
       </c>
       <c r="R83">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="S83">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U83">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="V83">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W83">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z83">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AA83">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AB83">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC83">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="AD83">
         <v>1.19</v>
       </c>
       <c r="AE83">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AK83">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O128">
-        <v>3.51</v>
+        <v>3.35</v>
       </c>
       <c r="P128">
-        <v>2.45</v>
+        <v>3.06</v>
       </c>
       <c r="Q128">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="R128">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="S128">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="T128">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U128">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="V128">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W128">
         <v>1.08</v>
       </c>
       <c r="X128">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y128">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z128">
-        <v>3.86</v>
+        <v>2.93</v>
       </c>
       <c r="AA128">
-        <v>1.71</v>
+        <v>2.01</v>
       </c>
       <c r="AB128">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC128">
-        <v>2.74</v>
+        <v>3.38</v>
       </c>
       <c r="AD128">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AE128">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AF128">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AG128">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK128">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O129">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P129">
-        <v>3.06</v>
+        <v>2.86</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
       </c>
       <c r="R129">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S129">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="T129">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U129">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="V129">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W129">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X129">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y129">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z129">
-        <v>2.93</v>
+        <v>3.54</v>
       </c>
       <c r="AA129">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AB129">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC129">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AD129">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE129">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF129">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AG129">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK129">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="O130">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P130">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="Q130">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R130">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S130">
+        <v>1.44</v>
+      </c>
+      <c r="T130">
+        <v>2.5</v>
+      </c>
+      <c r="U130">
+        <v>3.1</v>
+      </c>
+      <c r="V130">
         <v>1.32</v>
       </c>
-      <c r="T130">
+      <c r="W130">
+        <v>1.04</v>
+      </c>
+      <c r="X130">
+        <v>1.05</v>
+      </c>
+      <c r="Y130">
+        <v>1.35</v>
+      </c>
+      <c r="Z130">
         <v>3</v>
       </c>
-      <c r="U130">
-        <v>2.59</v>
-      </c>
-      <c r="V130">
-        <v>1.48</v>
-      </c>
-      <c r="W130">
-        <v>1.11</v>
-      </c>
-      <c r="X130">
-        <v>1</v>
-      </c>
-      <c r="Y130">
+      <c r="AA130">
+        <v>2.16</v>
+      </c>
+      <c r="AB130">
+        <v>1.71</v>
+      </c>
+      <c r="AC130">
+        <v>3.95</v>
+      </c>
+      <c r="AD130">
         <v>1.22</v>
       </c>
-      <c r="Z130">
-        <v>3.54</v>
-      </c>
-      <c r="AA130">
-        <v>1.78</v>
-      </c>
-      <c r="AB130">
-        <v>2</v>
-      </c>
-      <c r="AC130">
-        <v>3</v>
-      </c>
-      <c r="AD130">
-        <v>1.35</v>
-      </c>
       <c r="AE130">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF130">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AG130">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK130">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,80 +21662,80 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="O131">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P131">
-        <v>2.93</v>
+        <v>3.98</v>
       </c>
       <c r="Q131">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R131">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S131">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T131">
-        <v>2.5</v>
+        <v>3.21</v>
       </c>
       <c r="U131">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="V131">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="W131">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X131">
         <v>1.05</v>
       </c>
       <c r="Y131">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Z131">
+        <v>3.62</v>
+      </c>
+      <c r="AA131">
+        <v>1.82</v>
+      </c>
+      <c r="AB131">
+        <v>1.98</v>
+      </c>
+      <c r="AC131">
         <v>3</v>
       </c>
-      <c r="AA131">
-        <v>2.16</v>
-      </c>
-      <c r="AB131">
-        <v>1.71</v>
-      </c>
-      <c r="AC131">
-        <v>3.95</v>
-      </c>
       <c r="AD131">
+        <v>1.32</v>
+      </c>
+      <c r="AE131">
+        <v>1.14</v>
+      </c>
+      <c r="AF131">
+        <v>1.7</v>
+      </c>
+      <c r="AG131">
+        <v>2.05</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ131">
         <v>1.22</v>
       </c>
-      <c r="AE131">
-        <v>1.03</v>
-      </c>
-      <c r="AF131">
-        <v>1.83</v>
-      </c>
-      <c r="AG131">
-        <v>1.91</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>1.3</v>
-      </c>
       <c r="AK131">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.84</v>
+        <v>3.9</v>
       </c>
       <c r="O132">
+        <v>3.78</v>
+      </c>
+      <c r="P132">
+        <v>1.95</v>
+      </c>
+      <c r="Q132">
+        <v>4.35</v>
+      </c>
+      <c r="R132">
+        <v>2.21</v>
+      </c>
+      <c r="S132">
+        <v>1.28</v>
+      </c>
+      <c r="T132">
         <v>3.5</v>
       </c>
-      <c r="P132">
-        <v>3.98</v>
-      </c>
-      <c r="Q132">
-        <v>2.4</v>
-      </c>
-      <c r="R132">
-        <v>2.2</v>
-      </c>
-      <c r="S132">
-        <v>1.33</v>
-      </c>
-      <c r="T132">
-        <v>3.21</v>
-      </c>
       <c r="U132">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="V132">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="W132">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X132">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z132">
-        <v>3.62</v>
+        <v>4.5</v>
       </c>
       <c r="AA132">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AB132">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="AC132">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AD132">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AE132">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF132">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG132">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="AK132">
-        <v>1.85</v>
+        <v>1.24</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="O133">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="P133">
-        <v>1.95</v>
+        <v>3.02</v>
       </c>
       <c r="Q133">
-        <v>4.35</v>
+        <v>2.53</v>
       </c>
       <c r="R133">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="S133">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="T133">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="U133">
-        <v>2.39</v>
+        <v>2.94</v>
       </c>
       <c r="V133">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="W133">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y133">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="Z133">
-        <v>4.5</v>
+        <v>3.22</v>
       </c>
       <c r="AA133">
-        <v>1.62</v>
+        <v>1.99</v>
       </c>
       <c r="AB133">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="AC133">
-        <v>2.43</v>
+        <v>3.35</v>
       </c>
       <c r="AD133">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AE133">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF133">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG133">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AK133">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="O134">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P134">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="Q134">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="R134">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S134">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T134">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="U134">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="V134">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W134">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y134">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z134">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="AA134">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AB134">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC134">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="AD134">
         <v>1.26</v>
       </c>
       <c r="AE134">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF134">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG134">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,80 +22314,80 @@
         </is>
       </c>
       <c r="N135">
+        <v>2.5</v>
+      </c>
+      <c r="O135">
+        <v>3.51</v>
+      </c>
+      <c r="P135">
         <v>2.45</v>
       </c>
-      <c r="O135">
-        <v>3.22</v>
-      </c>
-      <c r="P135">
-        <v>2.87</v>
-      </c>
       <c r="Q135">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R135">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="S135">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T135">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U135">
-        <v>2.95</v>
+        <v>2.52</v>
       </c>
       <c r="V135">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W135">
         <v>1.08</v>
       </c>
       <c r="X135">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z135">
-        <v>3.35</v>
+        <v>3.86</v>
       </c>
       <c r="AA135">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AB135">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC135">
-        <v>3.54</v>
+        <v>2.74</v>
       </c>
       <c r="AD135">
+        <v>1.45</v>
+      </c>
+      <c r="AE135">
+        <v>1.18</v>
+      </c>
+      <c r="AF135">
+        <v>1.55</v>
+      </c>
+      <c r="AG135">
+        <v>2.26</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
         <v>1.26</v>
       </c>
-      <c r="AE135">
-        <v>1.06</v>
-      </c>
-      <c r="AF135">
-        <v>1.76</v>
-      </c>
-      <c r="AG135">
-        <v>1.96</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>1.3</v>
-      </c>
       <c r="AK135">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O141">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P141">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="Q141">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="R141">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S141">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T141">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U141">
         <v>2.6</v>
       </c>
       <c r="V141">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W141">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X141">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y141">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z141">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="AA141">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB141">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC141">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD141">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE141">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF141">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG141">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK141">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="O142">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P142">
-        <v>2.23</v>
+        <v>3.94</v>
       </c>
       <c r="Q142">
-        <v>3.16</v>
+        <v>2.46</v>
       </c>
       <c r="R142">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="S142">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T142">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U142">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="V142">
         <v>1.43</v>
       </c>
       <c r="W142">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X142">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y142">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z142">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="AA142">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB142">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC142">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD142">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE142">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF142">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG142">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK142">
-        <v>1.31</v>
+        <v>1.88</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="O143">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P143">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q143">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="R143">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S143">
         <v>1.33</v>
       </c>
       <c r="T143">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U143">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V143">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W143">
         <v>1.06</v>
       </c>
       <c r="X143">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z143">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA143">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB143">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC143">
         <v>2.85</v>
       </c>
       <c r="AD143">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE143">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF143">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG143">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK143">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="O145">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>3.94</v>
+        <v>2.23</v>
       </c>
       <c r="Q145">
-        <v>2.46</v>
+        <v>3.16</v>
       </c>
       <c r="R145">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="S145">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T145">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U145">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V145">
         <v>1.43</v>
       </c>
       <c r="W145">
+        <v>1.07</v>
+      </c>
+      <c r="X145">
         <v>1.05</v>
       </c>
-      <c r="X145">
-        <v>1.01</v>
-      </c>
       <c r="Y145">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z145">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="AA145">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB145">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC145">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD145">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE145">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF145">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK145">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,58 +24107,58 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="O146">
         <v>3.35</v>
       </c>
       <c r="P146">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q146">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="R146">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S146">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T146">
         <v>3.2</v>
       </c>
       <c r="U146">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="V146">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W146">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z146">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA146">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB146">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC146">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AD146">
         <v>1.33</v>
       </c>
       <c r="AE146">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF146">
         <v>1.67</v>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK146">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AL146">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.84</v>
+        <v>3.42</v>
       </c>
       <c r="O5">
-        <v>4.22</v>
+        <v>3.08</v>
       </c>
       <c r="P5">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="Q5">
         <v>4.6</v>
       </c>
       <c r="R5">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="S5">
+        <v>1.48</v>
+      </c>
+      <c r="T5">
+        <v>2.38</v>
+      </c>
+      <c r="U5">
+        <v>3.2</v>
+      </c>
+      <c r="V5">
+        <v>1.3</v>
+      </c>
+      <c r="W5">
+        <v>1.06</v>
+      </c>
+      <c r="X5">
+        <v>1.04</v>
+      </c>
+      <c r="Y5">
+        <v>1.4</v>
+      </c>
+      <c r="Z5">
+        <v>2.57</v>
+      </c>
+      <c r="AA5">
+        <v>2.4</v>
+      </c>
+      <c r="AB5">
+        <v>1.53</v>
+      </c>
+      <c r="AC5">
+        <v>4.35</v>
+      </c>
+      <c r="AD5">
+        <v>1.19</v>
+      </c>
+      <c r="AE5">
+        <v>1.01</v>
+      </c>
+      <c r="AF5">
+        <v>2.06</v>
+      </c>
+      <c r="AG5">
+        <v>1.7</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.3</v>
+      </c>
+      <c r="AK5">
         <v>1.25</v>
-      </c>
-      <c r="T5">
-        <v>3.5</v>
-      </c>
-      <c r="U5">
-        <v>2.2</v>
-      </c>
-      <c r="V5">
-        <v>1.6</v>
-      </c>
-      <c r="W5">
-        <v>1.14</v>
-      </c>
-      <c r="X5">
-        <v>1.03</v>
-      </c>
-      <c r="Y5">
-        <v>1.14</v>
-      </c>
-      <c r="Z5">
-        <v>4.5</v>
-      </c>
-      <c r="AA5">
-        <v>1.6</v>
-      </c>
-      <c r="AB5">
-        <v>2.25</v>
-      </c>
-      <c r="AC5">
-        <v>2.56</v>
-      </c>
-      <c r="AD5">
-        <v>1.52</v>
-      </c>
-      <c r="AE5">
-        <v>1.2</v>
-      </c>
-      <c r="AF5">
-        <v>1.6</v>
-      </c>
-      <c r="AG5">
-        <v>2.2</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>2.23</v>
-      </c>
-      <c r="AK5">
-        <v>1.18</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.42</v>
+        <v>4.84</v>
       </c>
       <c r="O6">
-        <v>3.08</v>
+        <v>4.22</v>
       </c>
       <c r="P6">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="Q6">
         <v>4.6</v>
       </c>
       <c r="R6">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="S6">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="U6">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="V6">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>2.57</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AB6">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AC6">
-        <v>4.35</v>
+        <v>2.56</v>
       </c>
       <c r="AD6">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AF6">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>2.23</v>
       </c>
       <c r="AK6">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="O15">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="P15">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>2.69</v>
+        <v>3.45</v>
       </c>
       <c r="R15">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="S15">
+        <v>1.46</v>
+      </c>
+      <c r="T15">
+        <v>2.5</v>
+      </c>
+      <c r="U15">
+        <v>3.1</v>
+      </c>
+      <c r="V15">
         <v>1.28</v>
       </c>
-      <c r="T15">
-        <v>3.25</v>
-      </c>
-      <c r="U15">
-        <v>2.38</v>
-      </c>
-      <c r="V15">
-        <v>1.53</v>
-      </c>
       <c r="W15">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AA15">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AC15">
-        <v>2.43</v>
+        <v>3.65</v>
       </c>
       <c r="AD15">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AE15">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AF15">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AG15">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.33</v>
+        <v>3.94</v>
       </c>
       <c r="O22">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>2.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q22">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="R22">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="T22">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U22">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="V22">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Z22">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="AA22">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>4.75</v>
+        <v>4.03</v>
       </c>
       <c r="AD22">
+        <v>1.2</v>
+      </c>
+      <c r="AE22">
+        <v>1.07</v>
+      </c>
+      <c r="AF22">
+        <v>1.91</v>
+      </c>
+      <c r="AG22">
+        <v>1.75</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.29</v>
+      </c>
+      <c r="AK22">
         <v>1.18</v>
-      </c>
-      <c r="AE22">
-        <v>1.01</v>
-      </c>
-      <c r="AF22">
-        <v>2.03</v>
-      </c>
-      <c r="AG22">
-        <v>1.67</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.36</v>
-      </c>
-      <c r="AK22">
-        <v>1.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="O23">
-        <v>4.15</v>
+        <v>3.08</v>
       </c>
       <c r="P23">
-        <v>5.05</v>
+        <v>2.78</v>
       </c>
       <c r="Q23">
-        <v>2.07</v>
+        <v>3.2</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="S23">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="T23">
-        <v>2.89</v>
+        <v>2.55</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="V23">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
+        <v>1.1</v>
+      </c>
+      <c r="Y23">
+        <v>1.5</v>
+      </c>
+      <c r="Z23">
+        <v>2.55</v>
+      </c>
+      <c r="AA23">
+        <v>2.5</v>
+      </c>
+      <c r="AB23">
+        <v>1.5</v>
+      </c>
+      <c r="AC23">
+        <v>4.75</v>
+      </c>
+      <c r="AD23">
+        <v>1.18</v>
+      </c>
+      <c r="AE23">
         <v>1.01</v>
       </c>
-      <c r="Y23">
-        <v>1.16</v>
-      </c>
-      <c r="Z23">
-        <v>4.75</v>
-      </c>
-      <c r="AA23">
-        <v>1.6</v>
-      </c>
-      <c r="AB23">
-        <v>2.3</v>
-      </c>
-      <c r="AC23">
-        <v>2.38</v>
-      </c>
-      <c r="AD23">
+      <c r="AF23">
+        <v>2.03</v>
+      </c>
+      <c r="AG23">
+        <v>1.67</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.36</v>
+      </c>
+      <c r="AK23">
         <v>1.45</v>
-      </c>
-      <c r="AE23">
-        <v>1.2</v>
-      </c>
-      <c r="AF23">
-        <v>1.62</v>
-      </c>
-      <c r="AG23">
-        <v>2.11</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.2</v>
-      </c>
-      <c r="AK23">
-        <v>2.18</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.94</v>
+        <v>1.55</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="P24">
-        <v>1.75</v>
+        <v>5.05</v>
       </c>
       <c r="Q24">
-        <v>5.25</v>
+        <v>2.07</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="T24">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="U24">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="W24">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>2.85</v>
+        <v>4.75</v>
       </c>
       <c r="AA24">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="AC24">
-        <v>4.03</v>
+        <v>2.38</v>
       </c>
       <c r="AD24">
+        <v>1.45</v>
+      </c>
+      <c r="AE24">
         <v>1.2</v>
       </c>
-      <c r="AE24">
-        <v>1.07</v>
-      </c>
       <c r="AF24">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
-        <v>1.18</v>
+        <v>2.18</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>3.35</v>
+        <v>2.06</v>
       </c>
       <c r="Q31">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="R31">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U31">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="V31">
         <v>1.36</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
         <v>1.29</v>
       </c>
       <c r="Z31">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA31">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AB31">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC31">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="AD31">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE31">
         <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.1</v>
+        <v>1.94</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
+        <v>3.35</v>
+      </c>
+      <c r="Q33">
+        <v>2.62</v>
+      </c>
+      <c r="R33">
         <v>2.06</v>
       </c>
-      <c r="Q33">
-        <v>3.9</v>
-      </c>
-      <c r="R33">
-        <v>2.07</v>
-      </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="V33">
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y33">
         <v>1.29</v>
       </c>
       <c r="Z33">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AA33">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC33">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
         <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG33">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="O50">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="P50">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Q50">
+        <v>2.23</v>
+      </c>
+      <c r="R50">
+        <v>2.13</v>
+      </c>
+      <c r="S50">
+        <v>1.33</v>
+      </c>
+      <c r="T50">
+        <v>3.2</v>
+      </c>
+      <c r="U50">
         <v>2.6</v>
       </c>
-      <c r="R50">
-        <v>2.03</v>
-      </c>
-      <c r="S50">
-        <v>1.41</v>
-      </c>
-      <c r="T50">
-        <v>2.81</v>
-      </c>
-      <c r="U50">
-        <v>2.95</v>
-      </c>
       <c r="V50">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
         <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="AA50">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="AD50">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="O51">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q51">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="R51">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S51">
+        <v>1.41</v>
+      </c>
+      <c r="T51">
+        <v>2.81</v>
+      </c>
+      <c r="U51">
+        <v>2.95</v>
+      </c>
+      <c r="V51">
         <v>1.33</v>
-      </c>
-      <c r="T51">
-        <v>3.2</v>
-      </c>
-      <c r="U51">
-        <v>2.6</v>
-      </c>
-      <c r="V51">
-        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
+        <v>1.28</v>
+      </c>
+      <c r="Z51">
+        <v>3.08</v>
+      </c>
+      <c r="AA51">
+        <v>2.02</v>
+      </c>
+      <c r="AB51">
+        <v>1.69</v>
+      </c>
+      <c r="AC51">
+        <v>3.6</v>
+      </c>
+      <c r="AD51">
         <v>1.22</v>
       </c>
-      <c r="Z51">
-        <v>3.54</v>
-      </c>
-      <c r="AA51">
+      <c r="AE51">
+        <v>1.07</v>
+      </c>
+      <c r="AF51">
         <v>1.8</v>
       </c>
-      <c r="AB51">
-        <v>2</v>
-      </c>
-      <c r="AC51">
-        <v>3.07</v>
-      </c>
-      <c r="AD51">
-        <v>1.32</v>
-      </c>
-      <c r="AE51">
-        <v>1.08</v>
-      </c>
-      <c r="AF51">
-        <v>1.73</v>
-      </c>
       <c r="AG51">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O55">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>3.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="R55">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S55">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="T55">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U55">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="V55">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z55">
-        <v>4.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA55">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB55">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC55">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="AD55">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE55">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF55">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG55">
         <v>2.25</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AK55">
-        <v>1.97</v>
+        <v>1.35</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,61 +9437,61 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P56">
+        <v>3.55</v>
+      </c>
+      <c r="Q56">
         <v>2.25</v>
       </c>
-      <c r="Q56">
-        <v>3.35</v>
-      </c>
       <c r="R56">
+        <v>2.4</v>
+      </c>
+      <c r="S56">
+        <v>1.27</v>
+      </c>
+      <c r="T56">
+        <v>3.4</v>
+      </c>
+      <c r="U56">
         <v>2.18</v>
       </c>
-      <c r="S56">
-        <v>1.34</v>
-      </c>
-      <c r="T56">
-        <v>2.91</v>
-      </c>
-      <c r="U56">
-        <v>2.41</v>
-      </c>
       <c r="V56">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W56">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
-        <v>3.82</v>
+        <v>4.9</v>
       </c>
       <c r="AA56">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB56">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC56">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AD56">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE56">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF56">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG56">
         <v>2.25</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AK56">
-        <v>1.35</v>
+        <v>1.97</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="O82">
         <v>3</v>
       </c>
       <c r="P82">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q82">
-        <v>2.98</v>
+        <v>3.67</v>
       </c>
       <c r="R82">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="S82">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T82">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U82">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="V82">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W82">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z82">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AA82">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AB82">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC82">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="AD82">
         <v>1.19</v>
       </c>
       <c r="AE82">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF82">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG82">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AK82">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S83">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T83">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U83">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="V83">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W83">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y83">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z83">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA83">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC83">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG83">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK83">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O112">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P112">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q112">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R112">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="S112">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T112">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="U112">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="V112">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W112">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z112">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="AA112">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AB112">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC112">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="AD112">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE112">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF112">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG112">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.2</v>
+        <v>1.66</v>
       </c>
       <c r="O113">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P113">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="Q113">
-        <v>3.6</v>
+        <v>2.24</v>
       </c>
       <c r="R113">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="S113">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T113">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U113">
-        <v>2.6</v>
+        <v>3.01</v>
       </c>
       <c r="V113">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W113">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X113">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z113">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="AA113">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AB113">
+        <v>1.74</v>
+      </c>
+      <c r="AC113">
+        <v>3.53</v>
+      </c>
+      <c r="AD113">
+        <v>1.24</v>
+      </c>
+      <c r="AE113">
+        <v>1.05</v>
+      </c>
+      <c r="AF113">
         <v>1.89</v>
       </c>
-      <c r="AC113">
-        <v>2.92</v>
-      </c>
-      <c r="AD113">
-        <v>1.31</v>
-      </c>
-      <c r="AE113">
-        <v>1.09</v>
-      </c>
-      <c r="AF113">
-        <v>1.67</v>
-      </c>
       <c r="AG113">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK113">
-        <v>1.26</v>
+        <v>2.02</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.66</v>
+        <v>3.5</v>
       </c>
       <c r="O114">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="P114">
-        <v>4.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q114">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="R114">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="S114">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T114">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="U114">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="V114">
         <v>1.36</v>
       </c>
       <c r="W114">
+        <v>1.05</v>
+      </c>
+      <c r="X114">
+        <v>1.03</v>
+      </c>
+      <c r="Y114">
+        <v>1.33</v>
+      </c>
+      <c r="Z114">
+        <v>3.17</v>
+      </c>
+      <c r="AA114">
+        <v>2</v>
+      </c>
+      <c r="AB114">
+        <v>1.77</v>
+      </c>
+      <c r="AC114">
+        <v>3.45</v>
+      </c>
+      <c r="AD114">
+        <v>1.25</v>
+      </c>
+      <c r="AE114">
         <v>1.06</v>
       </c>
-      <c r="X114">
-        <v>1.02</v>
-      </c>
-      <c r="Y114">
-        <v>1.32</v>
-      </c>
-      <c r="Z114">
-        <v>3.22</v>
-      </c>
-      <c r="AA114">
-        <v>1.98</v>
-      </c>
-      <c r="AB114">
-        <v>1.74</v>
-      </c>
-      <c r="AC114">
-        <v>3.53</v>
-      </c>
-      <c r="AD114">
-        <v>1.24</v>
-      </c>
-      <c r="AE114">
-        <v>1.05</v>
-      </c>
       <c r="AF114">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AG114">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>2.02</v>
+        <v>1.19</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,65 +23292,65 @@
         </is>
       </c>
       <c r="N141">
+        <v>1.85</v>
+      </c>
+      <c r="O141">
+        <v>3.7</v>
+      </c>
+      <c r="P141">
+        <v>3.94</v>
+      </c>
+      <c r="Q141">
+        <v>2.46</v>
+      </c>
+      <c r="R141">
         <v>2.3</v>
       </c>
-      <c r="O141">
-        <v>3.3</v>
-      </c>
-      <c r="P141">
-        <v>2.87</v>
-      </c>
-      <c r="Q141">
-        <v>2.76</v>
-      </c>
-      <c r="R141">
-        <v>2.2</v>
-      </c>
       <c r="S141">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T141">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="U141">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="V141">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W141">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X141">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z141">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="AA141">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB141">
+        <v>1.95</v>
+      </c>
+      <c r="AC141">
+        <v>3.1</v>
+      </c>
+      <c r="AD141">
+        <v>1.32</v>
+      </c>
+      <c r="AE141">
+        <v>1.08</v>
+      </c>
+      <c r="AF141">
+        <v>1.75</v>
+      </c>
+      <c r="AG141">
         <v>2</v>
       </c>
-      <c r="AC141">
-        <v>2.85</v>
-      </c>
-      <c r="AD141">
-        <v>1.37</v>
-      </c>
-      <c r="AE141">
-        <v>1.14</v>
-      </c>
-      <c r="AF141">
-        <v>1.62</v>
-      </c>
-      <c r="AG141">
-        <v>2.15</v>
-      </c>
       <c r="AH141" t="inlineStr">
         <is>
           <t>[]</t>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK141">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="O142">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P142">
-        <v>3.94</v>
+        <v>3.2</v>
       </c>
       <c r="Q142">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="R142">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S142">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T142">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="U142">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="V142">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W142">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X142">
         <v>1.01</v>
       </c>
       <c r="Y142">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z142">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA142">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB142">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC142">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AD142">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE142">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF142">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG142">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK142">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,80 +23618,80 @@
         </is>
       </c>
       <c r="N143">
+        <v>2.45</v>
+      </c>
+      <c r="O143">
+        <v>3.25</v>
+      </c>
+      <c r="P143">
+        <v>3</v>
+      </c>
+      <c r="Q143">
+        <v>2.88</v>
+      </c>
+      <c r="R143">
+        <v>2.1</v>
+      </c>
+      <c r="S143">
+        <v>1.38</v>
+      </c>
+      <c r="T143">
+        <v>2.75</v>
+      </c>
+      <c r="U143">
+        <v>2.88</v>
+      </c>
+      <c r="V143">
+        <v>1.36</v>
+      </c>
+      <c r="W143">
+        <v>1.08</v>
+      </c>
+      <c r="X143">
+        <v>1.02</v>
+      </c>
+      <c r="Y143">
+        <v>1.31</v>
+      </c>
+      <c r="Z143">
+        <v>3.08</v>
+      </c>
+      <c r="AA143">
+        <v>1.99</v>
+      </c>
+      <c r="AB143">
+        <v>1.9</v>
+      </c>
+      <c r="AC143">
+        <v>3.6</v>
+      </c>
+      <c r="AD143">
+        <v>1.29</v>
+      </c>
+      <c r="AE143">
+        <v>1.06</v>
+      </c>
+      <c r="AF143">
+        <v>1.75</v>
+      </c>
+      <c r="AG143">
         <v>1.97</v>
       </c>
-      <c r="O143">
-        <v>3.35</v>
-      </c>
-      <c r="P143">
-        <v>3.2</v>
-      </c>
-      <c r="Q143">
-        <v>2.55</v>
-      </c>
-      <c r="R143">
-        <v>2.25</v>
-      </c>
-      <c r="S143">
-        <v>1.33</v>
-      </c>
-      <c r="T143">
-        <v>3.2</v>
-      </c>
-      <c r="U143">
-        <v>2.53</v>
-      </c>
-      <c r="V143">
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ143">
+        <v>1.31</v>
+      </c>
+      <c r="AK143">
         <v>1.45</v>
-      </c>
-      <c r="W143">
-        <v>1.06</v>
-      </c>
-      <c r="X143">
-        <v>1.01</v>
-      </c>
-      <c r="Y143">
-        <v>1.22</v>
-      </c>
-      <c r="Z143">
-        <v>3.7</v>
-      </c>
-      <c r="AA143">
-        <v>1.83</v>
-      </c>
-      <c r="AB143">
-        <v>1.93</v>
-      </c>
-      <c r="AC143">
-        <v>2.85</v>
-      </c>
-      <c r="AD143">
-        <v>1.33</v>
-      </c>
-      <c r="AE143">
-        <v>1.09</v>
-      </c>
-      <c r="AF143">
-        <v>1.67</v>
-      </c>
-      <c r="AG143">
-        <v>2.1</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ143">
-        <v>1.28</v>
-      </c>
-      <c r="AK143">
-        <v>1.77</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O144">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P144">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="Q144">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="R144">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S144">
+        <v>1.37</v>
+      </c>
+      <c r="T144">
+        <v>2.85</v>
+      </c>
+      <c r="U144">
+        <v>2.62</v>
+      </c>
+      <c r="V144">
+        <v>1.43</v>
+      </c>
+      <c r="W144">
+        <v>1.07</v>
+      </c>
+      <c r="X144">
+        <v>1.05</v>
+      </c>
+      <c r="Y144">
+        <v>1.26</v>
+      </c>
+      <c r="Z144">
+        <v>3.62</v>
+      </c>
+      <c r="AA144">
+        <v>1.76</v>
+      </c>
+      <c r="AB144">
+        <v>1.97</v>
+      </c>
+      <c r="AC144">
+        <v>2.8</v>
+      </c>
+      <c r="AD144">
         <v>1.38</v>
       </c>
-      <c r="T144">
-        <v>2.75</v>
-      </c>
-      <c r="U144">
-        <v>2.88</v>
-      </c>
-      <c r="V144">
-        <v>1.36</v>
-      </c>
-      <c r="W144">
-        <v>1.08</v>
-      </c>
-      <c r="X144">
-        <v>1.02</v>
-      </c>
-      <c r="Y144">
+      <c r="AE144">
+        <v>1.14</v>
+      </c>
+      <c r="AF144">
+        <v>1.6</v>
+      </c>
+      <c r="AG144">
+        <v>2.18</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
+        <v>1.24</v>
+      </c>
+      <c r="AK144">
         <v>1.31</v>
-      </c>
-      <c r="Z144">
-        <v>3.08</v>
-      </c>
-      <c r="AA144">
-        <v>1.99</v>
-      </c>
-      <c r="AB144">
-        <v>1.9</v>
-      </c>
-      <c r="AC144">
-        <v>3.6</v>
-      </c>
-      <c r="AD144">
-        <v>1.29</v>
-      </c>
-      <c r="AE144">
-        <v>1.06</v>
-      </c>
-      <c r="AF144">
-        <v>1.75</v>
-      </c>
-      <c r="AG144">
-        <v>1.97</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.31</v>
-      </c>
-      <c r="AK144">
-        <v>1.45</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="O145">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P145">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="Q145">
-        <v>3.16</v>
+        <v>2.69</v>
       </c>
       <c r="R145">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="S145">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T145">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U145">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V145">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W145">
         <v>1.07</v>
       </c>
       <c r="X145">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z145">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="AA145">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB145">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC145">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD145">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE145">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG145">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK145">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O146">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P146">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="Q146">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="R146">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S146">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T146">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U146">
         <v>2.6</v>
       </c>
       <c r="V146">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W146">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X146">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z146">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="AA146">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB146">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC146">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD146">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE146">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF146">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG146">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK146">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -34711,55 +34711,55 @@
         <v>0</v>
       </c>
       <c r="Q211">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R211">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S211">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T211">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U211">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V211">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W211">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X211">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y211">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z211">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA211">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD211">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE211">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF211">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG211">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK211">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q279">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R279">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S279">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="T279">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U279">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V279">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W279">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X279">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y279">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z279">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA279">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB279">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC279">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD279">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AE279">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF279">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG279">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AK279">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O280">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P280">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q280">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R280">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S280">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T280">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U280">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V280">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W280">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X280">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y280">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z280">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA280">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB280">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC280">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD280">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AE280">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF280">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG280">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK280">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL280">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="P20">
+        <v>3.68</v>
+      </c>
+      <c r="Q20">
+        <v>2.38</v>
+      </c>
+      <c r="R20">
+        <v>2.15</v>
+      </c>
+      <c r="S20">
+        <v>1.38</v>
+      </c>
+      <c r="T20">
+        <v>2.81</v>
+      </c>
+      <c r="U20">
         <v>2.77</v>
       </c>
-      <c r="Q20">
-        <v>3.04</v>
-      </c>
-      <c r="R20">
-        <v>2.1</v>
-      </c>
-      <c r="S20">
-        <v>1.41</v>
-      </c>
-      <c r="T20">
-        <v>2.53</v>
-      </c>
-      <c r="U20">
-        <v>3.09</v>
-      </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z20">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AA20">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>3.6</v>
+        <v>3.29</v>
       </c>
       <c r="AD20">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE20">
         <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG20">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.82</v>
+        <v>3.94</v>
       </c>
       <c r="O21">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>3.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>5.25</v>
       </c>
       <c r="R21">
+        <v>2</v>
+      </c>
+      <c r="S21">
+        <v>1.43</v>
+      </c>
+      <c r="T21">
+        <v>2.5</v>
+      </c>
+      <c r="U21">
+        <v>3.1</v>
+      </c>
+      <c r="V21">
+        <v>1.32</v>
+      </c>
+      <c r="W21">
+        <v>1.02</v>
+      </c>
+      <c r="X21">
+        <v>1.04</v>
+      </c>
+      <c r="Y21">
+        <v>1.38</v>
+      </c>
+      <c r="Z21">
+        <v>2.85</v>
+      </c>
+      <c r="AA21">
         <v>2.15</v>
       </c>
-      <c r="S21">
-        <v>1.38</v>
-      </c>
-      <c r="T21">
-        <v>2.81</v>
-      </c>
-      <c r="U21">
-        <v>2.77</v>
-      </c>
-      <c r="V21">
-        <v>1.39</v>
-      </c>
-      <c r="W21">
-        <v>1.07</v>
-      </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>1.29</v>
-      </c>
-      <c r="Z21">
-        <v>3.24</v>
-      </c>
-      <c r="AA21">
-        <v>1.94</v>
-      </c>
       <c r="AB21">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AC21">
-        <v>3.29</v>
+        <v>4.03</v>
       </c>
       <c r="AD21">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE21">
         <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AG21">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.92</v>
+        <v>1.18</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.94</v>
+        <v>2.33</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="P22">
-        <v>1.75</v>
+        <v>2.78</v>
       </c>
       <c r="Q22">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="T22">
+        <v>2.55</v>
+      </c>
+      <c r="U22">
+        <v>3.6</v>
+      </c>
+      <c r="V22">
+        <v>1.25</v>
+      </c>
+      <c r="W22">
+        <v>1.01</v>
+      </c>
+      <c r="X22">
+        <v>1.1</v>
+      </c>
+      <c r="Y22">
+        <v>1.5</v>
+      </c>
+      <c r="Z22">
+        <v>2.55</v>
+      </c>
+      <c r="AA22">
         <v>2.5</v>
       </c>
-      <c r="U22">
-        <v>3.1</v>
-      </c>
-      <c r="V22">
-        <v>1.32</v>
-      </c>
-      <c r="W22">
-        <v>1.02</v>
-      </c>
-      <c r="X22">
-        <v>1.04</v>
-      </c>
-      <c r="Y22">
-        <v>1.38</v>
-      </c>
-      <c r="Z22">
-        <v>2.85</v>
-      </c>
-      <c r="AA22">
-        <v>2.15</v>
-      </c>
       <c r="AB22">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AC22">
-        <v>4.03</v>
+        <v>4.75</v>
       </c>
       <c r="AD22">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AG22">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK22">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="O23">
-        <v>3.08</v>
+        <v>4.15</v>
       </c>
       <c r="P23">
-        <v>2.78</v>
+        <v>5.05</v>
       </c>
       <c r="Q23">
-        <v>3.2</v>
+        <v>2.07</v>
       </c>
       <c r="R23">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="U23">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="W23">
+        <v>1.09</v>
+      </c>
+      <c r="X23">
         <v>1.01</v>
       </c>
-      <c r="X23">
-        <v>1.1</v>
-      </c>
       <c r="Y23">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA23">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB23">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC23">
-        <v>4.75</v>
+        <v>2.38</v>
       </c>
       <c r="AD23">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AE23">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>1.67</v>
+        <v>2.11</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.55</v>
+        <v>2.28</v>
       </c>
       <c r="O24">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>5.05</v>
+        <v>2.77</v>
       </c>
       <c r="Q24">
-        <v>2.07</v>
+        <v>3.04</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
+        <v>1.41</v>
+      </c>
+      <c r="T24">
+        <v>2.53</v>
+      </c>
+      <c r="U24">
+        <v>3.09</v>
+      </c>
+      <c r="V24">
         <v>1.34</v>
       </c>
-      <c r="T24">
-        <v>2.89</v>
-      </c>
-      <c r="U24">
-        <v>2.3</v>
-      </c>
-      <c r="V24">
-        <v>1.56</v>
-      </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="Z24">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="AD24">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AG24">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AK24">
-        <v>2.18</v>
+        <v>1.54</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,16 +5525,16 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.68</v>
+        <v>1.94</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="Q32">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="R32">
         <v>2.06</v>
@@ -5543,46 +5543,46 @@
         <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="V32">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
         <v>1.06</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z32">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="AA32">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB32">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AC32">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AD32">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AG32">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.94</v>
+        <v>2.68</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="Q33">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="R33">
         <v>2.06</v>
@@ -5706,46 +5706,46 @@
         <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U33">
-        <v>3.01</v>
+        <v>2.82</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
         <v>1.06</v>
       </c>
       <c r="Y33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="AA33">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB33">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC33">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AD33">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE33">
         <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AK33">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="O50">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="R50">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S50">
+        <v>1.41</v>
+      </c>
+      <c r="T50">
+        <v>2.81</v>
+      </c>
+      <c r="U50">
+        <v>2.95</v>
+      </c>
+      <c r="V50">
         <v>1.33</v>
-      </c>
-      <c r="T50">
-        <v>3.2</v>
-      </c>
-      <c r="U50">
-        <v>2.6</v>
-      </c>
-      <c r="V50">
-        <v>1.44</v>
       </c>
       <c r="W50">
         <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
+        <v>1.28</v>
+      </c>
+      <c r="Z50">
+        <v>3.08</v>
+      </c>
+      <c r="AA50">
+        <v>2.02</v>
+      </c>
+      <c r="AB50">
+        <v>1.69</v>
+      </c>
+      <c r="AC50">
+        <v>3.6</v>
+      </c>
+      <c r="AD50">
         <v>1.22</v>
       </c>
-      <c r="Z50">
-        <v>3.54</v>
-      </c>
-      <c r="AA50">
+      <c r="AE50">
+        <v>1.07</v>
+      </c>
+      <c r="AF50">
         <v>1.8</v>
       </c>
-      <c r="AB50">
-        <v>2</v>
-      </c>
-      <c r="AC50">
-        <v>3.07</v>
-      </c>
-      <c r="AD50">
-        <v>1.32</v>
-      </c>
-      <c r="AE50">
-        <v>1.08</v>
-      </c>
-      <c r="AF50">
-        <v>1.73</v>
-      </c>
       <c r="AG50">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="P51">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Q51">
+        <v>2.23</v>
+      </c>
+      <c r="R51">
+        <v>2.13</v>
+      </c>
+      <c r="S51">
+        <v>1.33</v>
+      </c>
+      <c r="T51">
+        <v>3.2</v>
+      </c>
+      <c r="U51">
         <v>2.6</v>
       </c>
-      <c r="R51">
-        <v>2.03</v>
-      </c>
-      <c r="S51">
-        <v>1.41</v>
-      </c>
-      <c r="T51">
-        <v>2.81</v>
-      </c>
-      <c r="U51">
-        <v>2.95</v>
-      </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="AA51">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AC51">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="AD51">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG51">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -11402,10 +11402,10 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W68">
         <v>0</v>
@@ -11426,31 +11426,31 @@
         <v>0</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE68">
         <v>0</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -13847,16 +13847,16 @@
         <v>0</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U83">
         <v>0</v>
@@ -13871,31 +13871,31 @@
         <v>0</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE83">
         <v>0</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.55</v>
+        <v>1.49</v>
       </c>
       <c r="O94">
-        <v>3.15</v>
+        <v>4.55</v>
       </c>
       <c r="P94">
-        <v>2.55</v>
+        <v>4.85</v>
       </c>
       <c r="Q94">
-        <v>3.05</v>
+        <v>1.82</v>
       </c>
       <c r="R94">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S94">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="T94">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="U94">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="V94">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="W94">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z94">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="AA94">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AB94">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="AC94">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD94">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AE94">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF94">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG94">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AK94">
-        <v>1.44</v>
+        <v>2.45</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.49</v>
+        <v>2.95</v>
       </c>
       <c r="O95">
-        <v>4.55</v>
+        <v>3.3</v>
       </c>
       <c r="P95">
-        <v>4.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q95">
-        <v>1.82</v>
+        <v>3.54</v>
       </c>
       <c r="R95">
+        <v>2.13</v>
+      </c>
+      <c r="S95">
+        <v>1.32</v>
+      </c>
+      <c r="T95">
+        <v>3.25</v>
+      </c>
+      <c r="U95">
+        <v>2.3</v>
+      </c>
+      <c r="V95">
+        <v>1.47</v>
+      </c>
+      <c r="W95">
+        <v>1.11</v>
+      </c>
+      <c r="X95">
+        <v>1.01</v>
+      </c>
+      <c r="Y95">
+        <v>1.19</v>
+      </c>
+      <c r="Z95">
+        <v>3.8</v>
+      </c>
+      <c r="AA95">
+        <v>1.64</v>
+      </c>
+      <c r="AB95">
+        <v>2.02</v>
+      </c>
+      <c r="AC95">
         <v>2.6</v>
       </c>
-      <c r="S95">
-        <v>1.22</v>
-      </c>
-      <c r="T95">
-        <v>3.8</v>
-      </c>
-      <c r="U95">
-        <v>2.18</v>
-      </c>
-      <c r="V95">
-        <v>1.6</v>
-      </c>
-      <c r="W95">
-        <v>1.17</v>
-      </c>
-      <c r="X95">
-        <v>1.02</v>
-      </c>
-      <c r="Y95">
-        <v>1.1</v>
-      </c>
-      <c r="Z95">
-        <v>5</v>
-      </c>
-      <c r="AA95">
-        <v>1.5</v>
-      </c>
-      <c r="AB95">
-        <v>2.28</v>
-      </c>
-      <c r="AC95">
-        <v>2.25</v>
-      </c>
       <c r="AD95">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AE95">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF95">
         <v>1.57</v>
       </c>
       <c r="AG95">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="AK95">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="O96">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P96">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q96">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="R96">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="S96">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T96">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U96">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="V96">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W96">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X96">
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z96">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA96">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="AB96">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AC96">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD96">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE96">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF96">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AG96">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AK96">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -19063,55 +19063,55 @@
         <v>0</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19226,55 +19226,55 @@
         <v>2.11</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,80 +23455,80 @@
         </is>
       </c>
       <c r="N142">
+        <v>2.45</v>
+      </c>
+      <c r="O142">
+        <v>3.25</v>
+      </c>
+      <c r="P142">
+        <v>3</v>
+      </c>
+      <c r="Q142">
+        <v>2.88</v>
+      </c>
+      <c r="R142">
+        <v>2.1</v>
+      </c>
+      <c r="S142">
+        <v>1.38</v>
+      </c>
+      <c r="T142">
+        <v>2.75</v>
+      </c>
+      <c r="U142">
+        <v>2.88</v>
+      </c>
+      <c r="V142">
+        <v>1.36</v>
+      </c>
+      <c r="W142">
+        <v>1.08</v>
+      </c>
+      <c r="X142">
+        <v>1.02</v>
+      </c>
+      <c r="Y142">
+        <v>1.31</v>
+      </c>
+      <c r="Z142">
+        <v>3.08</v>
+      </c>
+      <c r="AA142">
+        <v>1.99</v>
+      </c>
+      <c r="AB142">
+        <v>1.9</v>
+      </c>
+      <c r="AC142">
+        <v>3.6</v>
+      </c>
+      <c r="AD142">
+        <v>1.29</v>
+      </c>
+      <c r="AE142">
+        <v>1.06</v>
+      </c>
+      <c r="AF142">
+        <v>1.75</v>
+      </c>
+      <c r="AG142">
         <v>1.97</v>
       </c>
-      <c r="O142">
-        <v>3.35</v>
-      </c>
-      <c r="P142">
-        <v>3.2</v>
-      </c>
-      <c r="Q142">
-        <v>2.55</v>
-      </c>
-      <c r="R142">
-        <v>2.25</v>
-      </c>
-      <c r="S142">
-        <v>1.33</v>
-      </c>
-      <c r="T142">
-        <v>3.2</v>
-      </c>
-      <c r="U142">
-        <v>2.53</v>
-      </c>
-      <c r="V142">
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ142">
+        <v>1.31</v>
+      </c>
+      <c r="AK142">
         <v>1.45</v>
-      </c>
-      <c r="W142">
-        <v>1.06</v>
-      </c>
-      <c r="X142">
-        <v>1.01</v>
-      </c>
-      <c r="Y142">
-        <v>1.22</v>
-      </c>
-      <c r="Z142">
-        <v>3.7</v>
-      </c>
-      <c r="AA142">
-        <v>1.83</v>
-      </c>
-      <c r="AB142">
-        <v>1.93</v>
-      </c>
-      <c r="AC142">
-        <v>2.85</v>
-      </c>
-      <c r="AD142">
-        <v>1.33</v>
-      </c>
-      <c r="AE142">
-        <v>1.09</v>
-      </c>
-      <c r="AF142">
-        <v>1.67</v>
-      </c>
-      <c r="AG142">
-        <v>2.1</v>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ142">
-        <v>1.28</v>
-      </c>
-      <c r="AK142">
-        <v>1.77</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,65 +23618,65 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="O143">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P143">
+        <v>2.88</v>
+      </c>
+      <c r="Q143">
+        <v>2.69</v>
+      </c>
+      <c r="R143">
+        <v>2.11</v>
+      </c>
+      <c r="S143">
+        <v>1.3</v>
+      </c>
+      <c r="T143">
+        <v>3.2</v>
+      </c>
+      <c r="U143">
+        <v>2.6</v>
+      </c>
+      <c r="V143">
+        <v>1.44</v>
+      </c>
+      <c r="W143">
+        <v>1.07</v>
+      </c>
+      <c r="X143">
+        <v>1.03</v>
+      </c>
+      <c r="Y143">
+        <v>1.25</v>
+      </c>
+      <c r="Z143">
+        <v>3.65</v>
+      </c>
+      <c r="AA143">
+        <v>1.8</v>
+      </c>
+      <c r="AB143">
+        <v>1.98</v>
+      </c>
+      <c r="AC143">
         <v>3</v>
       </c>
-      <c r="Q143">
-        <v>2.88</v>
-      </c>
-      <c r="R143">
+      <c r="AD143">
+        <v>1.33</v>
+      </c>
+      <c r="AE143">
+        <v>1.1</v>
+      </c>
+      <c r="AF143">
+        <v>1.67</v>
+      </c>
+      <c r="AG143">
         <v>2.1</v>
       </c>
-      <c r="S143">
-        <v>1.38</v>
-      </c>
-      <c r="T143">
-        <v>2.75</v>
-      </c>
-      <c r="U143">
-        <v>2.88</v>
-      </c>
-      <c r="V143">
-        <v>1.36</v>
-      </c>
-      <c r="W143">
-        <v>1.08</v>
-      </c>
-      <c r="X143">
-        <v>1.02</v>
-      </c>
-      <c r="Y143">
-        <v>1.31</v>
-      </c>
-      <c r="Z143">
-        <v>3.08</v>
-      </c>
-      <c r="AA143">
-        <v>1.99</v>
-      </c>
-      <c r="AB143">
-        <v>1.9</v>
-      </c>
-      <c r="AC143">
-        <v>3.6</v>
-      </c>
-      <c r="AD143">
-        <v>1.29</v>
-      </c>
-      <c r="AE143">
-        <v>1.06</v>
-      </c>
-      <c r="AF143">
-        <v>1.75</v>
-      </c>
-      <c r="AG143">
-        <v>1.97</v>
-      </c>
       <c r="AH143" t="inlineStr">
         <is>
           <t>[]</t>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK143">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P144">
-        <v>2.23</v>
+        <v>2.87</v>
       </c>
       <c r="Q144">
-        <v>3.16</v>
+        <v>2.76</v>
       </c>
       <c r="R144">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S144">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="U144">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V144">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W144">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X144">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z144">
         <v>3.62</v>
       </c>
       <c r="AA144">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB144">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC144">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD144">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE144">
         <v>1.14</v>
       </c>
       <c r="AF144">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG144">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>1.24</v>
       </c>
       <c r="AK144">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="O145">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="Q145">
-        <v>2.69</v>
+        <v>3.16</v>
       </c>
       <c r="R145">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="S145">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T145">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U145">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V145">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W145">
         <v>1.07</v>
       </c>
       <c r="X145">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y145">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z145">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="AA145">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB145">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC145">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD145">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE145">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF145">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK145">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="O146">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P146">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q146">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="R146">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S146">
         <v>1.33</v>
       </c>
       <c r="T146">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U146">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V146">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W146">
         <v>1.06</v>
       </c>
       <c r="X146">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z146">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA146">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB146">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC146">
         <v>2.85</v>
       </c>
       <c r="AD146">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE146">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF146">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG146">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK146">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -26235,55 +26235,55 @@
         <v>2.45</v>
       </c>
       <c r="Q159">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R159">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S159">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T159">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U159">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V159">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W159">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X159">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y159">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z159">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC159">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD159">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE159">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF159">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG159">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK159">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G188">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G189">
@@ -32755,10 +32755,10 @@
         <v>2.15</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S199">
         <v>0</v>
@@ -32767,10 +32767,10 @@
         <v>0</v>
       </c>
       <c r="U199">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V199">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W199">
         <v>0</v>
@@ -32779,31 +32779,31 @@
         <v>0</v>
       </c>
       <c r="Y199">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z199">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA199">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB199">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC199">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD199">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE199">
         <v>0</v>
       </c>
       <c r="AF199">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG199">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK199">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32918,10 +32918,10 @@
         <v>0</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -32930,10 +32930,10 @@
         <v>0</v>
       </c>
       <c r="U200">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V200">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W200">
         <v>0</v>
@@ -32942,31 +32942,31 @@
         <v>0</v>
       </c>
       <c r="Y200">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z200">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA200">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB200">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC200">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD200">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE200">
         <v>0</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG200">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK200">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -35843,64 +35843,64 @@
         </is>
       </c>
       <c r="N218">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O218">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S218">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T218">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U218">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V218">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W218">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X218">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y218">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z218">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA218">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB218">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC218">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD218">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG218">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK218">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T219">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U219">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V219">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W219">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X219">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y219">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z219">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA219">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB219">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC219">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="AD219">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF219">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG219">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK219">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O223">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q223">
         <v>3.08</v>
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39112,55 +39112,55 @@
         <v>0</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -40244,64 +40244,64 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q245">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R245">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S245">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T245">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U245">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V245">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W245">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X245">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y245">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z245">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA245">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB245">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC245">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD245">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE245">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF245">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG245">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK245">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40579,55 +40579,55 @@
         <v>0</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S247">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T247">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U247">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V247">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W247">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X247">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y247">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z247">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC247">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD247">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG247">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK247">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -41059,64 +41059,64 @@
         </is>
       </c>
       <c r="N250">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O250">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S250">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T250">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U250">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V250">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W250">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y250">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z250">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA250">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB250">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC250">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD250">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE250">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF250">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG250">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK250">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41222,64 +41222,64 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S251">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T251">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U251">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V251">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W251">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y251">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z251">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA251">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB251">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC251">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD251">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK251">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41394,55 +41394,55 @@
         <v>0</v>
       </c>
       <c r="Q252">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R252">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S252">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T252">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U252">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V252">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W252">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X252">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z252">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA252">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB252">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC252">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD252">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE252">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF252">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG252">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK252">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41548,64 +41548,64 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41711,64 +41711,64 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q254">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R254">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S254">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T254">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U254">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V254">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W254">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X254">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y254">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z254">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA254">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB254">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC254">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD254">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE254">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF254">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG254">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK254">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41874,64 +41874,64 @@
         </is>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O255">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P255">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T255">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X255">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE255">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF255">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG255">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK255">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42363,64 +42363,64 @@
         </is>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O258">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P258">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q258">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R258">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S258">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T258">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U258">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V258">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W258">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X258">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y258">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z258">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC258">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD258">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE258">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF258">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG258">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK258">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42698,16 +42698,16 @@
         <v>0</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T260">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U260">
         <v>0</v>
@@ -42722,31 +42722,31 @@
         <v>0</v>
       </c>
       <c r="Y260">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z260">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC260">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD260">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE260">
         <v>0</v>
       </c>
       <c r="AF260">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG260">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK260">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,64 +43015,64 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z262">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG262">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,64 +43178,64 @@
         </is>
       </c>
       <c r="N263">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O263">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P263">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q263">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R263">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S263">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T263">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U263">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V263">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W263">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X263">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y263">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z263">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AA263">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB263">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC263">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD263">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE263">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF263">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG263">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK263">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q264">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R264">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S264">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T264">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U264">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V264">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W264">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X264">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y264">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z264">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC264">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AD264">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE264">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF264">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG264">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK264">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43504,64 +43504,64 @@
         </is>
       </c>
       <c r="N265">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O265">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P265">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q265">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R265">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S265">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T265">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U265">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V265">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W265">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X265">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y265">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z265">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA265">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB265">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC265">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD265">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE265">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF265">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG265">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK265">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q266">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R266">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S266">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T266">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U266">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V266">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W266">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X266">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y266">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z266">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA266">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB266">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC266">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD266">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE266">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF266">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG266">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK266">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q269">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R269">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S269">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T269">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U269">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V269">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W269">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X269">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y269">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z269">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC269">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD269">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE269">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF269">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG269">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK269">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,64 +44319,64 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q270">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R270">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T270">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V270">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W270">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X270">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y270">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z270">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA270">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB270">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC270">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD270">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE270">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF270">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG270">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK270">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P271">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE271">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G273">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G274">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G275">
@@ -45306,55 +45306,55 @@
         <v>0</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G277">
@@ -45469,55 +45469,55 @@
         <v>0</v>
       </c>
       <c r="Q277">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R277">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S277">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T277">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U277">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V277">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W277">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X277">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y277">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z277">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA277">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB277">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC277">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD277">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE277">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF277">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG277">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK277">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G278">
@@ -45632,55 +45632,55 @@
         <v>0</v>
       </c>
       <c r="Q278">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R278">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S278">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T278">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U278">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V278">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W278">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X278">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y278">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z278">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA278">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB278">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC278">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD278">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE278">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF278">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG278">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK278">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G281">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G282">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G283">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G284">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q285">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S285">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T285">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U285">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V285">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W285">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X285">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y285">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z285">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC285">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD285">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE285">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG285">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK285">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O287">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P287">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q287">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R287">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S287">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T287">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V287">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W287">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X287">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y287">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z287">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA287">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB287">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC287">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD287">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE287">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF287">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG287">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK287">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q288">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R288">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T288">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U288">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V288">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W288">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X288">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC288">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD288">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE288">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF288">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG288">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK288">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q289">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R289">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S289">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T289">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U289">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V289">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W289">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X289">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z289">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC289">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD289">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE289">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF289">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG289">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK289">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47579,64 +47579,64 @@
         </is>
       </c>
       <c r="N290">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O290">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P290">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R290">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T290">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U290">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V290">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W290">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X290">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC290">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AD290">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE290">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG290">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK290">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O304">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P304">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49900,10 +49900,10 @@
         <v>0</v>
       </c>
       <c r="AA304">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB304">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC304">
         <v>0</v>
@@ -50033,55 +50033,55 @@
         <v>0</v>
       </c>
       <c r="Q305">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R305">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S305">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T305">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U305">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V305">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W305">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X305">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y305">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z305">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC305">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD305">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE305">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF305">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG305">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK305">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G312">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G313">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G314">
@@ -53447,64 +53447,64 @@
         </is>
       </c>
       <c r="N326">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O326">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P326">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q326">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R326">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S326">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T326">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U326">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V326">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W326">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X326">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y326">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z326">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA326">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB326">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC326">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="AD326">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE326">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF326">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG326">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK326">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G340">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G341">

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="O50">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="R50">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S50">
+        <v>1.41</v>
+      </c>
+      <c r="T50">
+        <v>2.81</v>
+      </c>
+      <c r="U50">
+        <v>2.95</v>
+      </c>
+      <c r="V50">
         <v>1.33</v>
-      </c>
-      <c r="T50">
-        <v>3.2</v>
-      </c>
-      <c r="U50">
-        <v>2.6</v>
-      </c>
-      <c r="V50">
-        <v>1.44</v>
       </c>
       <c r="W50">
         <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
+        <v>1.28</v>
+      </c>
+      <c r="Z50">
+        <v>3.08</v>
+      </c>
+      <c r="AA50">
+        <v>2.02</v>
+      </c>
+      <c r="AB50">
+        <v>1.69</v>
+      </c>
+      <c r="AC50">
+        <v>3.6</v>
+      </c>
+      <c r="AD50">
         <v>1.22</v>
       </c>
-      <c r="Z50">
-        <v>3.54</v>
-      </c>
-      <c r="AA50">
+      <c r="AE50">
+        <v>1.07</v>
+      </c>
+      <c r="AF50">
         <v>1.8</v>
       </c>
-      <c r="AB50">
-        <v>2</v>
-      </c>
-      <c r="AC50">
-        <v>3.07</v>
-      </c>
-      <c r="AD50">
-        <v>1.32</v>
-      </c>
-      <c r="AE50">
-        <v>1.08</v>
-      </c>
-      <c r="AF50">
-        <v>1.73</v>
-      </c>
       <c r="AG50">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="P51">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Q51">
+        <v>2.23</v>
+      </c>
+      <c r="R51">
+        <v>2.13</v>
+      </c>
+      <c r="S51">
+        <v>1.33</v>
+      </c>
+      <c r="T51">
+        <v>3.2</v>
+      </c>
+      <c r="U51">
         <v>2.6</v>
       </c>
-      <c r="R51">
-        <v>2.03</v>
-      </c>
-      <c r="S51">
-        <v>1.41</v>
-      </c>
-      <c r="T51">
-        <v>2.81</v>
-      </c>
-      <c r="U51">
-        <v>2.95</v>
-      </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="AA51">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AC51">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="AD51">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG51">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="O55">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P55">
+        <v>3.55</v>
+      </c>
+      <c r="Q55">
         <v>2.25</v>
       </c>
-      <c r="Q55">
-        <v>3.35</v>
-      </c>
       <c r="R55">
+        <v>2.4</v>
+      </c>
+      <c r="S55">
+        <v>1.27</v>
+      </c>
+      <c r="T55">
+        <v>3.4</v>
+      </c>
+      <c r="U55">
         <v>2.18</v>
       </c>
-      <c r="S55">
-        <v>1.34</v>
-      </c>
-      <c r="T55">
-        <v>2.91</v>
-      </c>
-      <c r="U55">
-        <v>2.41</v>
-      </c>
       <c r="V55">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z55">
-        <v>3.82</v>
+        <v>4.9</v>
       </c>
       <c r="AA55">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB55">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC55">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AD55">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE55">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF55">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG55">
         <v>2.25</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AK55">
-        <v>1.35</v>
+        <v>1.97</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,61 +9437,61 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O56">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>3.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S56">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="T56">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U56">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="V56">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z56">
-        <v>4.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA56">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB56">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC56">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="AD56">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE56">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF56">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG56">
         <v>2.25</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AK56">
-        <v>1.97</v>
+        <v>1.35</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.47</v>
+        <v>1.52</v>
       </c>
       <c r="O97">
-        <v>3.56</v>
+        <v>4.45</v>
       </c>
       <c r="P97">
-        <v>2.72</v>
+        <v>5.25</v>
       </c>
       <c r="Q97">
-        <v>3.06</v>
+        <v>2.11</v>
       </c>
       <c r="R97">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="S97">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T97">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U97">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="V97">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W97">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z97">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA97">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AB97">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AC97">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="AD97">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AE97">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AF97">
         <v>1.53</v>
       </c>
       <c r="AG97">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK97">
-        <v>1.51</v>
+        <v>2.33</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.52</v>
+        <v>2.57</v>
       </c>
       <c r="O98">
-        <v>4.45</v>
+        <v>3.65</v>
       </c>
       <c r="P98">
-        <v>5.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q98">
-        <v>2.11</v>
+        <v>3.45</v>
       </c>
       <c r="R98">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="S98">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T98">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U98">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="V98">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W98">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z98">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA98">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AB98">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="AC98">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AD98">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AE98">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AF98">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG98">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK98">
-        <v>2.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="O99">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="P99">
-        <v>2.23</v>
+        <v>2.72</v>
       </c>
       <c r="Q99">
-        <v>3.45</v>
+        <v>3.06</v>
       </c>
       <c r="R99">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="S99">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U99">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V99">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="W99">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X99">
         <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z99">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA99">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AB99">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AC99">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="AD99">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AE99">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF99">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AG99">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK99">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
+        <v>5.4</v>
+      </c>
+      <c r="O100">
+        <v>4.64</v>
+      </c>
+      <c r="P100">
+        <v>1.54</v>
+      </c>
+      <c r="Q100">
+        <v>4</v>
+      </c>
+      <c r="R100">
+        <v>2.82</v>
+      </c>
+      <c r="S100">
+        <v>1.22</v>
+      </c>
+      <c r="T100">
+        <v>4.05</v>
+      </c>
+      <c r="U100">
+        <v>2.19</v>
+      </c>
+      <c r="V100">
         <v>1.7</v>
       </c>
-      <c r="O100">
-        <v>3.9</v>
-      </c>
-      <c r="P100">
-        <v>4.5</v>
-      </c>
-      <c r="Q100">
-        <v>2.24</v>
-      </c>
-      <c r="R100">
-        <v>2.2</v>
-      </c>
-      <c r="S100">
-        <v>1.3</v>
-      </c>
-      <c r="T100">
-        <v>3.36</v>
-      </c>
-      <c r="U100">
-        <v>2.45</v>
-      </c>
-      <c r="V100">
-        <v>1.54</v>
-      </c>
       <c r="W100">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z100">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AA100">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="AB100">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="AC100">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="AD100">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AE100">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AF100">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG100">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.19</v>
+        <v>2.53</v>
       </c>
       <c r="AK100">
-        <v>2.21</v>
+        <v>1.15</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="O101">
-        <v>4.64</v>
+        <v>3.9</v>
       </c>
       <c r="P101">
+        <v>4.5</v>
+      </c>
+      <c r="Q101">
+        <v>2.24</v>
+      </c>
+      <c r="R101">
+        <v>2.2</v>
+      </c>
+      <c r="S101">
+        <v>1.3</v>
+      </c>
+      <c r="T101">
+        <v>3.36</v>
+      </c>
+      <c r="U101">
+        <v>2.45</v>
+      </c>
+      <c r="V101">
         <v>1.54</v>
       </c>
-      <c r="Q101">
-        <v>4</v>
-      </c>
-      <c r="R101">
-        <v>2.82</v>
-      </c>
-      <c r="S101">
-        <v>1.22</v>
-      </c>
-      <c r="T101">
-        <v>4.05</v>
-      </c>
-      <c r="U101">
-        <v>2.19</v>
-      </c>
-      <c r="V101">
-        <v>1.7</v>
-      </c>
       <c r="W101">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
+        <v>1.18</v>
+      </c>
+      <c r="Z101">
+        <v>4.2</v>
+      </c>
+      <c r="AA101">
+        <v>1.69</v>
+      </c>
+      <c r="AB101">
+        <v>2.24</v>
+      </c>
+      <c r="AC101">
+        <v>2.63</v>
+      </c>
+      <c r="AD101">
+        <v>1.43</v>
+      </c>
+      <c r="AE101">
         <v>1.13</v>
       </c>
-      <c r="Z101">
-        <v>5.6</v>
-      </c>
-      <c r="AA101">
-        <v>1.43</v>
-      </c>
-      <c r="AB101">
-        <v>2.7</v>
-      </c>
-      <c r="AC101">
-        <v>2.27</v>
-      </c>
-      <c r="AD101">
-        <v>1.74</v>
-      </c>
-      <c r="AE101">
-        <v>1.25</v>
-      </c>
       <c r="AF101">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>2.53</v>
+        <v>1.19</v>
       </c>
       <c r="AK101">
-        <v>1.15</v>
+        <v>2.21</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="O135">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P135">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="Q135">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R135">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S135">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T135">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U135">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V135">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W135">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
         <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z135">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AA135">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="AB135">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AC135">
-        <v>3.95</v>
+        <v>3.54</v>
       </c>
       <c r="AD135">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE135">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF135">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG135">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>1.3</v>
       </c>
       <c r="AK135">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="O136">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P136">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="Q136">
+        <v>2.8</v>
+      </c>
+      <c r="R136">
+        <v>2.05</v>
+      </c>
+      <c r="S136">
+        <v>1.44</v>
+      </c>
+      <c r="T136">
+        <v>2.5</v>
+      </c>
+      <c r="U136">
         <v>3.1</v>
       </c>
-      <c r="R136">
-        <v>2.1</v>
-      </c>
-      <c r="S136">
-        <v>1.36</v>
-      </c>
-      <c r="T136">
-        <v>2.88</v>
-      </c>
-      <c r="U136">
-        <v>2.95</v>
-      </c>
       <c r="V136">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W136">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X136">
         <v>1.05</v>
       </c>
       <c r="Y136">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z136">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AA136">
+        <v>2.16</v>
+      </c>
+      <c r="AB136">
+        <v>1.71</v>
+      </c>
+      <c r="AC136">
+        <v>3.95</v>
+      </c>
+      <c r="AD136">
+        <v>1.22</v>
+      </c>
+      <c r="AE136">
+        <v>1.03</v>
+      </c>
+      <c r="AF136">
+        <v>1.83</v>
+      </c>
+      <c r="AG136">
         <v>1.91</v>
-      </c>
-      <c r="AB136">
-        <v>1.9</v>
-      </c>
-      <c r="AC136">
-        <v>3.54</v>
-      </c>
-      <c r="AD136">
-        <v>1.26</v>
-      </c>
-      <c r="AE136">
-        <v>1.06</v>
-      </c>
-      <c r="AF136">
-        <v>1.76</v>
-      </c>
-      <c r="AG136">
-        <v>1.96</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>1.3</v>
       </c>
       <c r="AK136">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="P144">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="Q144">
-        <v>3.16</v>
+        <v>2.54</v>
       </c>
       <c r="R144">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="S144">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="T144">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U144">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="V144">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W144">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X144">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z144">
-        <v>3.62</v>
+        <v>2.94</v>
       </c>
       <c r="AA144">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AB144">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="AC144">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD144">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE144">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF144">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AG144">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK144">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,58 +23944,58 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="O145">
         <v>3.35</v>
       </c>
       <c r="P145">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q145">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="R145">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S145">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T145">
         <v>3.2</v>
       </c>
       <c r="U145">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="V145">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W145">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z145">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA145">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB145">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC145">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AD145">
         <v>1.33</v>
       </c>
       <c r="AE145">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
         <v>1.67</v>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK145">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="O146">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P146">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="Q146">
-        <v>2.69</v>
+        <v>3.16</v>
       </c>
       <c r="R146">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="S146">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T146">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U146">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V146">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W146">
         <v>1.07</v>
       </c>
       <c r="X146">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y146">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z146">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="AA146">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB146">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC146">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD146">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE146">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF146">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG146">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK146">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,65 +24270,65 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O147">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="P147">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q147">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="R147">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="S147">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T147">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U147">
-        <v>3.04</v>
+        <v>2.53</v>
       </c>
       <c r="V147">
+        <v>1.45</v>
+      </c>
+      <c r="W147">
+        <v>1.06</v>
+      </c>
+      <c r="X147">
+        <v>1.01</v>
+      </c>
+      <c r="Y147">
+        <v>1.22</v>
+      </c>
+      <c r="Z147">
+        <v>3.7</v>
+      </c>
+      <c r="AA147">
+        <v>1.83</v>
+      </c>
+      <c r="AB147">
+        <v>1.93</v>
+      </c>
+      <c r="AC147">
+        <v>2.85</v>
+      </c>
+      <c r="AD147">
         <v>1.33</v>
       </c>
-      <c r="W147">
-        <v>1.03</v>
-      </c>
-      <c r="X147">
-        <v>1.02</v>
-      </c>
-      <c r="Y147">
-        <v>1.35</v>
-      </c>
-      <c r="Z147">
-        <v>2.94</v>
-      </c>
-      <c r="AA147">
+      <c r="AE147">
+        <v>1.09</v>
+      </c>
+      <c r="AF147">
+        <v>1.67</v>
+      </c>
+      <c r="AG147">
         <v>2.1</v>
       </c>
-      <c r="AB147">
-        <v>1.71</v>
-      </c>
-      <c r="AC147">
-        <v>3.75</v>
-      </c>
-      <c r="AD147">
-        <v>1.21</v>
-      </c>
-      <c r="AE147">
-        <v>1.04</v>
-      </c>
-      <c r="AF147">
-        <v>1.82</v>
-      </c>
-      <c r="AG147">
-        <v>1.85</v>
-      </c>
       <c r="AH147" t="inlineStr">
         <is>
           <t>[]</t>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK147">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G204">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.62</v>
+        <v>2.21</v>
       </c>
       <c r="O222">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="P222">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="Q222">
-        <v>2.18</v>
+        <v>2.86</v>
       </c>
       <c r="R222">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="S222">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T222">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U222">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="V222">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W222">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X222">
+        <v>1.03</v>
+      </c>
+      <c r="Y222">
+        <v>1.29</v>
+      </c>
+      <c r="Z222">
+        <v>3.22</v>
+      </c>
+      <c r="AA222">
+        <v>2.09</v>
+      </c>
+      <c r="AB222">
+        <v>1.8</v>
+      </c>
+      <c r="AC222">
+        <v>3.44</v>
+      </c>
+      <c r="AD222">
+        <v>1.26</v>
+      </c>
+      <c r="AE222">
         <v>1.04</v>
       </c>
-      <c r="Y222">
-        <v>1.23</v>
-      </c>
-      <c r="Z222">
-        <v>3.9</v>
-      </c>
-      <c r="AA222">
-        <v>1.8</v>
-      </c>
-      <c r="AB222">
-        <v>1.96</v>
-      </c>
-      <c r="AC222">
-        <v>3.1</v>
-      </c>
-      <c r="AD222">
-        <v>1.36</v>
-      </c>
-      <c r="AE222">
-        <v>1.1</v>
-      </c>
       <c r="AF222">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG222">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK222">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.21</v>
+        <v>1.62</v>
       </c>
       <c r="O223">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="P223">
+        <v>5</v>
+      </c>
+      <c r="Q223">
+        <v>2.18</v>
+      </c>
+      <c r="R223">
+        <v>2.42</v>
+      </c>
+      <c r="S223">
+        <v>1.35</v>
+      </c>
+      <c r="T223">
         <v>3.1</v>
       </c>
-      <c r="Q223">
-        <v>2.86</v>
-      </c>
-      <c r="R223">
-        <v>2.24</v>
-      </c>
-      <c r="S223">
-        <v>1.4</v>
-      </c>
-      <c r="T223">
-        <v>2.75</v>
-      </c>
       <c r="U223">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="V223">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W223">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X223">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y223">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z223">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="AA223">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AB223">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AC223">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AD223">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE223">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF223">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG223">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK223">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G267">
@@ -43839,16 +43839,16 @@
         <v>0</v>
       </c>
       <c r="Q267">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R267">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S267">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T267">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U267">
         <v>0</v>
@@ -43863,31 +43863,31 @@
         <v>0</v>
       </c>
       <c r="Y267">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z267">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA267">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB267">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC267">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD267">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE267">
         <v>0</v>
       </c>
       <c r="AF267">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG267">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK267">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G268">
@@ -44002,16 +44002,16 @@
         <v>0</v>
       </c>
       <c r="Q268">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R268">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S268">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T268">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U268">
         <v>0</v>
@@ -44026,31 +44026,31 @@
         <v>0</v>
       </c>
       <c r="Y268">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z268">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA268">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB268">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC268">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD268">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE268">
         <v>0</v>
       </c>
       <c r="AF268">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG268">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK268">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="O273">
         <v>3.4</v>
       </c>
       <c r="P273">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q273">
-        <v>2.56</v>
+        <v>3.32</v>
       </c>
       <c r="R273">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="S273">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T273">
+        <v>2.85</v>
+      </c>
+      <c r="U273">
         <v>2.88</v>
       </c>
-      <c r="U273">
-        <v>3.08</v>
-      </c>
       <c r="V273">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W273">
+        <v>1.08</v>
+      </c>
+      <c r="X273">
+        <v>1.03</v>
+      </c>
+      <c r="Y273">
+        <v>1.3</v>
+      </c>
+      <c r="Z273">
+        <v>3.35</v>
+      </c>
+      <c r="AA273">
+        <v>1.96</v>
+      </c>
+      <c r="AB273">
+        <v>1.91</v>
+      </c>
+      <c r="AC273">
+        <v>3.45</v>
+      </c>
+      <c r="AD273">
+        <v>1.28</v>
+      </c>
+      <c r="AE273">
         <v>1.07</v>
       </c>
-      <c r="X273">
-        <v>1.02</v>
-      </c>
-      <c r="Y273">
-        <v>1.35</v>
-      </c>
-      <c r="Z273">
-        <v>3.1</v>
-      </c>
-      <c r="AA273">
-        <v>2.12</v>
-      </c>
-      <c r="AB273">
-        <v>1.65</v>
-      </c>
-      <c r="AC273">
-        <v>3.56</v>
-      </c>
-      <c r="AD273">
-        <v>1.24</v>
-      </c>
-      <c r="AE273">
-        <v>1.05</v>
-      </c>
       <c r="AF273">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG273">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>1.25</v>
       </c>
       <c r="AK273">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="O274">
         <v>3.4</v>
       </c>
       <c r="P274">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="Q274">
-        <v>3.32</v>
+        <v>2.56</v>
       </c>
       <c r="R274">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="S274">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T274">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U274">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="V274">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="W274">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X274">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y274">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z274">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AA274">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AB274">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AC274">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="AD274">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE274">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF274">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG274">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>1.25</v>
       </c>
       <c r="AK274">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="O288">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P288">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q288">
-        <v>3.74</v>
+        <v>3.36</v>
       </c>
       <c r="R288">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="S288">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="T288">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="U288">
-        <v>4.15</v>
+        <v>4.65</v>
       </c>
       <c r="V288">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="W288">
+        <v>1.02</v>
+      </c>
+      <c r="X288">
+        <v>1.14</v>
+      </c>
+      <c r="Y288">
+        <v>1.83</v>
+      </c>
+      <c r="Z288">
+        <v>1.87</v>
+      </c>
+      <c r="AA288">
+        <v>3.42</v>
+      </c>
+      <c r="AB288">
+        <v>1.23</v>
+      </c>
+      <c r="AC288">
+        <v>7.4</v>
+      </c>
+      <c r="AD288">
         <v>1.03</v>
       </c>
-      <c r="X288">
-        <v>1.11</v>
-      </c>
-      <c r="Y288">
-        <v>1.69</v>
-      </c>
-      <c r="Z288">
-        <v>2.18</v>
-      </c>
-      <c r="AA288">
-        <v>3.4</v>
-      </c>
-      <c r="AB288">
-        <v>1.33</v>
-      </c>
-      <c r="AC288">
-        <v>6.2</v>
-      </c>
-      <c r="AD288">
-        <v>1.06</v>
-      </c>
       <c r="AE288">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF288">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="AG288">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AK288">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,80 +47416,80 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="O289">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P289">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q289">
-        <v>3.36</v>
+        <v>3.74</v>
       </c>
       <c r="R289">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="S289">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="T289">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="U289">
-        <v>4.65</v>
+        <v>4.15</v>
       </c>
       <c r="V289">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="W289">
+        <v>1.03</v>
+      </c>
+      <c r="X289">
+        <v>1.11</v>
+      </c>
+      <c r="Y289">
+        <v>1.69</v>
+      </c>
+      <c r="Z289">
+        <v>2.18</v>
+      </c>
+      <c r="AA289">
+        <v>3.4</v>
+      </c>
+      <c r="AB289">
+        <v>1.33</v>
+      </c>
+      <c r="AC289">
+        <v>6.2</v>
+      </c>
+      <c r="AD289">
+        <v>1.06</v>
+      </c>
+      <c r="AE289">
         <v>1.02</v>
       </c>
-      <c r="X289">
-        <v>1.14</v>
-      </c>
-      <c r="Y289">
-        <v>1.83</v>
-      </c>
-      <c r="Z289">
-        <v>1.87</v>
-      </c>
-      <c r="AA289">
-        <v>3.42</v>
-      </c>
-      <c r="AB289">
-        <v>1.23</v>
-      </c>
-      <c r="AC289">
-        <v>7.4</v>
-      </c>
-      <c r="AD289">
-        <v>1.03</v>
-      </c>
-      <c r="AE289">
-        <v>1.01</v>
-      </c>
       <c r="AF289">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AG289">
+        <v>1.51</v>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ289">
         <v>1.4</v>
       </c>
-      <c r="AH289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ289">
-        <v>1.37</v>
-      </c>
       <c r="AK289">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G299">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G300">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G301">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G302">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G303">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G305">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,65 +53610,65 @@
         </is>
       </c>
       <c r="N327">
+        <v>1.4</v>
+      </c>
+      <c r="O327">
+        <v>5.7</v>
+      </c>
+      <c r="P327">
+        <v>5.65</v>
+      </c>
+      <c r="Q327">
+        <v>1.75</v>
+      </c>
+      <c r="R327">
+        <v>2.88</v>
+      </c>
+      <c r="S327">
+        <v>1.14</v>
+      </c>
+      <c r="T327">
+        <v>4.9</v>
+      </c>
+      <c r="U327">
+        <v>1.82</v>
+      </c>
+      <c r="V327">
+        <v>1.93</v>
+      </c>
+      <c r="W327">
+        <v>1.28</v>
+      </c>
+      <c r="X327">
+        <v>0</v>
+      </c>
+      <c r="Y327">
+        <v>1.08</v>
+      </c>
+      <c r="Z327">
+        <v>8.5</v>
+      </c>
+      <c r="AA327">
+        <v>1.24</v>
+      </c>
+      <c r="AB327">
+        <v>3.38</v>
+      </c>
+      <c r="AC327">
+        <v>1.7</v>
+      </c>
+      <c r="AD327">
+        <v>2.05</v>
+      </c>
+      <c r="AE327">
+        <v>1.42</v>
+      </c>
+      <c r="AF327">
+        <v>1.4</v>
+      </c>
+      <c r="AG327">
         <v>2.85</v>
       </c>
-      <c r="O327">
-        <v>4</v>
-      </c>
-      <c r="P327">
-        <v>2.15</v>
-      </c>
-      <c r="Q327">
-        <v>3.42</v>
-      </c>
-      <c r="R327">
-        <v>2.48</v>
-      </c>
-      <c r="S327">
-        <v>1.2</v>
-      </c>
-      <c r="T327">
-        <v>3.75</v>
-      </c>
-      <c r="U327">
-        <v>2.04</v>
-      </c>
-      <c r="V327">
-        <v>1.73</v>
-      </c>
-      <c r="W327">
-        <v>1.2</v>
-      </c>
-      <c r="X327">
-        <v>0</v>
-      </c>
-      <c r="Y327">
-        <v>1.1</v>
-      </c>
-      <c r="Z327">
-        <v>6.4</v>
-      </c>
-      <c r="AA327">
-        <v>1.38</v>
-      </c>
-      <c r="AB327">
-        <v>2.75</v>
-      </c>
-      <c r="AC327">
-        <v>1.96</v>
-      </c>
-      <c r="AD327">
-        <v>1.79</v>
-      </c>
-      <c r="AE327">
-        <v>1.33</v>
-      </c>
-      <c r="AF327">
-        <v>1.35</v>
-      </c>
-      <c r="AG327">
-        <v>2.9</v>
-      </c>
       <c r="AH327" t="inlineStr">
         <is>
           <t>[]</t>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK327">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G329">
@@ -53936,80 +53936,80 @@
         </is>
       </c>
       <c r="N329">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="O329">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="P329">
-        <v>5.65</v>
+        <v>2.15</v>
       </c>
       <c r="Q329">
-        <v>1.75</v>
+        <v>3.42</v>
       </c>
       <c r="R329">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="S329">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T329">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="U329">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="V329">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="W329">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X329">
         <v>0</v>
       </c>
       <c r="Y329">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z329">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="AA329">
+        <v>1.38</v>
+      </c>
+      <c r="AB329">
+        <v>2.75</v>
+      </c>
+      <c r="AC329">
+        <v>1.96</v>
+      </c>
+      <c r="AD329">
+        <v>1.79</v>
+      </c>
+      <c r="AE329">
+        <v>1.33</v>
+      </c>
+      <c r="AF329">
+        <v>1.35</v>
+      </c>
+      <c r="AG329">
+        <v>2.9</v>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ329">
         <v>1.24</v>
       </c>
-      <c r="AB329">
-        <v>3.38</v>
-      </c>
-      <c r="AC329">
-        <v>1.7</v>
-      </c>
-      <c r="AD329">
-        <v>2.05</v>
-      </c>
-      <c r="AE329">
-        <v>1.42</v>
-      </c>
-      <c r="AF329">
-        <v>1.4</v>
-      </c>
-      <c r="AG329">
-        <v>2.85</v>
-      </c>
-      <c r="AH329" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI329" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ329">
-        <v>1.13</v>
-      </c>
       <c r="AK329">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="AL329">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -6512,40 +6512,40 @@
         <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="R38">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U38">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V38">
         <v>1.57</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA38">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC38">
         <v>2.28</v>
@@ -6557,10 +6557,10 @@
         <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>2.7</v>
       </c>
       <c r="Q39">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R39">
         <v>2.28</v>
@@ -6687,10 +6687,10 @@
         <v>2.84</v>
       </c>
       <c r="U39">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="V39">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W39">
         <v>1.06</v>
@@ -6705,19 +6705,19 @@
         <v>3.48</v>
       </c>
       <c r="AA39">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB39">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC39">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="AD39">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE39">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
         <v>1.63</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
         <v>1.5</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="O50">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="P50">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Q50">
+        <v>2.23</v>
+      </c>
+      <c r="R50">
+        <v>2.13</v>
+      </c>
+      <c r="S50">
+        <v>1.33</v>
+      </c>
+      <c r="T50">
+        <v>3.2</v>
+      </c>
+      <c r="U50">
         <v>2.6</v>
       </c>
-      <c r="R50">
-        <v>2.03</v>
-      </c>
-      <c r="S50">
-        <v>1.41</v>
-      </c>
-      <c r="T50">
-        <v>2.81</v>
-      </c>
-      <c r="U50">
-        <v>2.95</v>
-      </c>
       <c r="V50">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
         <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="AA50">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="AD50">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG50">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="O51">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q51">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="R51">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S51">
+        <v>1.41</v>
+      </c>
+      <c r="T51">
+        <v>2.81</v>
+      </c>
+      <c r="U51">
+        <v>2.95</v>
+      </c>
+      <c r="V51">
         <v>1.33</v>
-      </c>
-      <c r="T51">
-        <v>3.2</v>
-      </c>
-      <c r="U51">
-        <v>2.6</v>
-      </c>
-      <c r="V51">
-        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
+        <v>1.28</v>
+      </c>
+      <c r="Z51">
+        <v>3.08</v>
+      </c>
+      <c r="AA51">
+        <v>2.02</v>
+      </c>
+      <c r="AB51">
+        <v>1.69</v>
+      </c>
+      <c r="AC51">
+        <v>3.6</v>
+      </c>
+      <c r="AD51">
         <v>1.22</v>
       </c>
-      <c r="Z51">
-        <v>3.54</v>
-      </c>
-      <c r="AA51">
+      <c r="AE51">
+        <v>1.07</v>
+      </c>
+      <c r="AF51">
         <v>1.8</v>
       </c>
-      <c r="AB51">
-        <v>2</v>
-      </c>
-      <c r="AC51">
-        <v>3.07</v>
-      </c>
-      <c r="AD51">
-        <v>1.32</v>
-      </c>
-      <c r="AE51">
-        <v>1.08</v>
-      </c>
-      <c r="AF51">
-        <v>1.73</v>
-      </c>
       <c r="AG51">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O55">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>3.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="R55">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S55">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="T55">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U55">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="V55">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z55">
-        <v>4.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA55">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB55">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC55">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="AD55">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE55">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF55">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG55">
         <v>2.25</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AK55">
-        <v>1.97</v>
+        <v>1.35</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,61 +9437,61 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P56">
+        <v>3.55</v>
+      </c>
+      <c r="Q56">
         <v>2.25</v>
       </c>
-      <c r="Q56">
-        <v>3.35</v>
-      </c>
       <c r="R56">
+        <v>2.4</v>
+      </c>
+      <c r="S56">
+        <v>1.27</v>
+      </c>
+      <c r="T56">
+        <v>3.4</v>
+      </c>
+      <c r="U56">
         <v>2.18</v>
       </c>
-      <c r="S56">
-        <v>1.34</v>
-      </c>
-      <c r="T56">
-        <v>2.91</v>
-      </c>
-      <c r="U56">
-        <v>2.41</v>
-      </c>
       <c r="V56">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W56">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
-        <v>3.82</v>
+        <v>4.9</v>
       </c>
       <c r="AA56">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB56">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC56">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="AD56">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE56">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF56">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG56">
         <v>2.25</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AK56">
-        <v>1.35</v>
+        <v>1.97</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -12057,13 +12057,13 @@
         <v>2.5</v>
       </c>
       <c r="R72">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S72">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T72">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U72">
         <v>3</v>
@@ -12118,7 +12118,7 @@
         <v>1.36</v>
       </c>
       <c r="AK72">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -14327,61 +14327,61 @@
         </is>
       </c>
       <c r="N86">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O86">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P86">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q86">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="R86">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S86">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T86">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="U86">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V86">
         <v>1.53</v>
       </c>
       <c r="W86">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y86">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z86">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA86">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB86">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AC86">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD86">
         <v>1.44</v>
       </c>
       <c r="AE86">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF86">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG86">
         <v>2.48</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK86">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15314,46 +15314,46 @@
         <v>2.11</v>
       </c>
       <c r="Q92">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="R92">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="S92">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T92">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U92">
         <v>2.73</v>
       </c>
       <c r="V92">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W92">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
         <v>1.26</v>
       </c>
       <c r="Z92">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA92">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB92">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AC92">
         <v>3.3</v>
       </c>
       <c r="AD92">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE92">
         <v>1.07</v>
@@ -15362,7 +15362,7 @@
         <v>1.75</v>
       </c>
       <c r="AG92">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="AK92">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15631,19 +15631,19 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="O94">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="P94">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="Q94">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="R94">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="S94">
         <v>1.22</v>
@@ -15652,13 +15652,13 @@
         <v>3.8</v>
       </c>
       <c r="U94">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V94">
         <v>1.6</v>
       </c>
       <c r="W94">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X94">
         <v>1.02</v>
@@ -15673,22 +15673,22 @@
         <v>1.5</v>
       </c>
       <c r="AB94">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AC94">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD94">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE94">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF94">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG94">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK94">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,46 +15803,46 @@
         <v>2.2</v>
       </c>
       <c r="Q95">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="R95">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T95">
         <v>3.25</v>
       </c>
       <c r="U95">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V95">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W95">
         <v>1.11</v>
       </c>
       <c r="X95">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y95">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z95">
-        <v>3.8</v>
+        <v>4.07</v>
       </c>
       <c r="AA95">
         <v>1.64</v>
       </c>
       <c r="AB95">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC95">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AD95">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE95">
         <v>1.12</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AK95">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15966,19 +15966,19 @@
         <v>2.55</v>
       </c>
       <c r="Q96">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="R96">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="S96">
         <v>1.37</v>
       </c>
       <c r="T96">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U96">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="V96">
         <v>1.39</v>
@@ -15993,41 +15993,41 @@
         <v>1.21</v>
       </c>
       <c r="Z96">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA96">
         <v>1.94</v>
       </c>
       <c r="AB96">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AC96">
         <v>2.75</v>
       </c>
       <c r="AD96">
+        <v>1.31</v>
+      </c>
+      <c r="AE96">
+        <v>1.11</v>
+      </c>
+      <c r="AF96">
+        <v>1.67</v>
+      </c>
+      <c r="AG96">
+        <v>2.03</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
         <v>1.35</v>
-      </c>
-      <c r="AE96">
-        <v>1.07</v>
-      </c>
-      <c r="AF96">
-        <v>1.68</v>
-      </c>
-      <c r="AG96">
-        <v>2.04</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.4</v>
       </c>
       <c r="AK96">
         <v>1.44</v>
@@ -16120,19 +16120,19 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="O97">
-        <v>4.45</v>
+        <v>4.66</v>
       </c>
       <c r="P97">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q97">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="R97">
-        <v>2.63</v>
+        <v>2.37</v>
       </c>
       <c r="S97">
         <v>1.2</v>
@@ -16141,34 +16141,34 @@
         <v>4</v>
       </c>
       <c r="U97">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V97">
         <v>1.67</v>
       </c>
       <c r="W97">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X97">
         <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z97">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="AA97">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB97">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="AC97">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AD97">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AE97">
         <v>1.28</v>
@@ -16177,7 +16177,7 @@
         <v>1.53</v>
       </c>
       <c r="AG97">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16283,49 +16283,49 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.57</v>
+        <v>2.96</v>
       </c>
       <c r="O98">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P98">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="Q98">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="R98">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S98">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T98">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U98">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="V98">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="W98">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
         <v>1.18</v>
       </c>
       <c r="Z98">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA98">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB98">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AC98">
         <v>2.27</v>
@@ -16334,10 +16334,10 @@
         <v>1.6</v>
       </c>
       <c r="AE98">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF98">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG98">
         <v>2.6</v>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK98">
         <v>1.36</v>
@@ -16449,16 +16449,16 @@
         <v>2.47</v>
       </c>
       <c r="O99">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P99">
         <v>2.72</v>
       </c>
       <c r="Q99">
-        <v>3.06</v>
+        <v>2.71</v>
       </c>
       <c r="R99">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="S99">
         <v>1.33</v>
@@ -16467,16 +16467,16 @@
         <v>3.3</v>
       </c>
       <c r="U99">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V99">
         <v>1.5</v>
       </c>
       <c r="W99">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y99">
         <v>1.2</v>
@@ -16497,10 +16497,10 @@
         <v>1.44</v>
       </c>
       <c r="AE99">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF99">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG99">
         <v>2.3</v>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK99">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>5.4</v>
+        <v>1.71</v>
       </c>
       <c r="O100">
-        <v>4.64</v>
+        <v>4.07</v>
       </c>
       <c r="P100">
-        <v>1.54</v>
+        <v>4.81</v>
       </c>
       <c r="Q100">
-        <v>4</v>
+        <v>2.31</v>
       </c>
       <c r="R100">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="S100">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T100">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="U100">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="V100">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="W100">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X100">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y100">
+        <v>1.18</v>
+      </c>
+      <c r="Z100">
+        <v>4.2</v>
+      </c>
+      <c r="AA100">
+        <v>1.74</v>
+      </c>
+      <c r="AB100">
+        <v>2.27</v>
+      </c>
+      <c r="AC100">
+        <v>2.58</v>
+      </c>
+      <c r="AD100">
+        <v>1.43</v>
+      </c>
+      <c r="AE100">
         <v>1.13</v>
       </c>
-      <c r="Z100">
-        <v>5.6</v>
-      </c>
-      <c r="AA100">
-        <v>1.43</v>
-      </c>
-      <c r="AB100">
-        <v>2.7</v>
-      </c>
-      <c r="AC100">
-        <v>2.27</v>
-      </c>
-      <c r="AD100">
-        <v>1.74</v>
-      </c>
-      <c r="AE100">
-        <v>1.25</v>
-      </c>
       <c r="AF100">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG100">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>2.53</v>
+        <v>1.14</v>
       </c>
       <c r="AK100">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="O101">
-        <v>3.9</v>
+        <v>4.35</v>
       </c>
       <c r="P101">
-        <v>4.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q101">
-        <v>2.24</v>
+        <v>5</v>
       </c>
       <c r="R101">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S101">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T101">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="U101">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="V101">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="W101">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z101">
-        <v>4.2</v>
+        <v>5.45</v>
       </c>
       <c r="AA101">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AB101">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="AC101">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="AD101">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AE101">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AF101">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG101">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>2.21</v>
+        <v>1.17</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17424,40 +17424,40 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q105">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="R105">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S105">
         <v>1.25</v>
       </c>
       <c r="T105">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="U105">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V105">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W105">
         <v>1.14</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z105">
         <v>4.5</v>
@@ -17469,19 +17469,19 @@
         <v>2.27</v>
       </c>
       <c r="AC105">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AD105">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AE105">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF105">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG105">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.16</v>
       </c>
       <c r="AK105">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="O135">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P135">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="Q135">
+        <v>2.8</v>
+      </c>
+      <c r="R135">
+        <v>2.05</v>
+      </c>
+      <c r="S135">
+        <v>1.44</v>
+      </c>
+      <c r="T135">
+        <v>2.5</v>
+      </c>
+      <c r="U135">
         <v>3.1</v>
       </c>
-      <c r="R135">
-        <v>2.1</v>
-      </c>
-      <c r="S135">
-        <v>1.36</v>
-      </c>
-      <c r="T135">
-        <v>2.88</v>
-      </c>
-      <c r="U135">
-        <v>2.95</v>
-      </c>
       <c r="V135">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W135">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X135">
         <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z135">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AA135">
+        <v>2.16</v>
+      </c>
+      <c r="AB135">
+        <v>1.71</v>
+      </c>
+      <c r="AC135">
+        <v>3.95</v>
+      </c>
+      <c r="AD135">
+        <v>1.22</v>
+      </c>
+      <c r="AE135">
+        <v>1.03</v>
+      </c>
+      <c r="AF135">
+        <v>1.83</v>
+      </c>
+      <c r="AG135">
         <v>1.91</v>
-      </c>
-      <c r="AB135">
-        <v>1.9</v>
-      </c>
-      <c r="AC135">
-        <v>3.54</v>
-      </c>
-      <c r="AD135">
-        <v>1.26</v>
-      </c>
-      <c r="AE135">
-        <v>1.06</v>
-      </c>
-      <c r="AF135">
-        <v>1.76</v>
-      </c>
-      <c r="AG135">
-        <v>1.96</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>1.3</v>
       </c>
       <c r="AK135">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="O136">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P136">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="Q136">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R136">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T136">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U136">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V136">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W136">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X136">
         <v>1.05</v>
       </c>
       <c r="Y136">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z136">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AA136">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="AB136">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AC136">
-        <v>3.95</v>
+        <v>3.54</v>
       </c>
       <c r="AD136">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE136">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF136">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG136">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>1.3</v>
       </c>
       <c r="AK136">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="O146">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P146">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="Q146">
-        <v>3.16</v>
+        <v>2.55</v>
       </c>
       <c r="R146">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S146">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T146">
+        <v>3.2</v>
+      </c>
+      <c r="U146">
+        <v>2.53</v>
+      </c>
+      <c r="V146">
+        <v>1.45</v>
+      </c>
+      <c r="W146">
+        <v>1.06</v>
+      </c>
+      <c r="X146">
+        <v>1.01</v>
+      </c>
+      <c r="Y146">
+        <v>1.22</v>
+      </c>
+      <c r="Z146">
+        <v>3.7</v>
+      </c>
+      <c r="AA146">
+        <v>1.83</v>
+      </c>
+      <c r="AB146">
+        <v>1.93</v>
+      </c>
+      <c r="AC146">
         <v>2.85</v>
       </c>
-      <c r="U146">
-        <v>2.62</v>
-      </c>
-      <c r="V146">
-        <v>1.43</v>
-      </c>
-      <c r="W146">
-        <v>1.07</v>
-      </c>
-      <c r="X146">
-        <v>1.05</v>
-      </c>
-      <c r="Y146">
-        <v>1.26</v>
-      </c>
-      <c r="Z146">
-        <v>3.62</v>
-      </c>
-      <c r="AA146">
-        <v>1.76</v>
-      </c>
-      <c r="AB146">
-        <v>1.97</v>
-      </c>
-      <c r="AC146">
-        <v>2.8</v>
-      </c>
       <c r="AD146">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE146">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF146">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG146">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK146">
-        <v>1.31</v>
+        <v>1.77</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
+        <v>2.7</v>
+      </c>
+      <c r="O147">
+        <v>3.5</v>
+      </c>
+      <c r="P147">
+        <v>2.23</v>
+      </c>
+      <c r="Q147">
+        <v>3.16</v>
+      </c>
+      <c r="R147">
+        <v>2.07</v>
+      </c>
+      <c r="S147">
+        <v>1.37</v>
+      </c>
+      <c r="T147">
+        <v>2.85</v>
+      </c>
+      <c r="U147">
+        <v>2.62</v>
+      </c>
+      <c r="V147">
+        <v>1.43</v>
+      </c>
+      <c r="W147">
+        <v>1.07</v>
+      </c>
+      <c r="X147">
+        <v>1.05</v>
+      </c>
+      <c r="Y147">
+        <v>1.26</v>
+      </c>
+      <c r="Z147">
+        <v>3.62</v>
+      </c>
+      <c r="AA147">
+        <v>1.76</v>
+      </c>
+      <c r="AB147">
         <v>1.97</v>
       </c>
-      <c r="O147">
-        <v>3.35</v>
-      </c>
-      <c r="P147">
-        <v>3.2</v>
-      </c>
-      <c r="Q147">
-        <v>2.55</v>
-      </c>
-      <c r="R147">
-        <v>2.25</v>
-      </c>
-      <c r="S147">
-        <v>1.33</v>
-      </c>
-      <c r="T147">
-        <v>3.2</v>
-      </c>
-      <c r="U147">
-        <v>2.53</v>
-      </c>
-      <c r="V147">
-        <v>1.45</v>
-      </c>
-      <c r="W147">
-        <v>1.06</v>
-      </c>
-      <c r="X147">
-        <v>1.01</v>
-      </c>
-      <c r="Y147">
-        <v>1.22</v>
-      </c>
-      <c r="Z147">
-        <v>3.7</v>
-      </c>
-      <c r="AA147">
-        <v>1.83</v>
-      </c>
-      <c r="AB147">
-        <v>1.93</v>
-      </c>
       <c r="AC147">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD147">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE147">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF147">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG147">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK147">
-        <v>1.77</v>
+        <v>1.31</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24961,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC151">
         <v>0</v>
@@ -26063,19 +26063,19 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O158">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P158">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="Q158">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R158">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="S158">
         <v>1.15</v>
@@ -26084,10 +26084,10 @@
         <v>4.33</v>
       </c>
       <c r="U158">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V158">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="W158">
         <v>1.18</v>
@@ -26096,31 +26096,31 @@
         <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Z158">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA158">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AB158">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AC158">
         <v>1.87</v>
       </c>
       <c r="AD158">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AE158">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AF158">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AG158">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK158">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O165">
+        <v>3.65</v>
+      </c>
+      <c r="P165">
+        <v>1.94</v>
+      </c>
+      <c r="Q165">
         <v>3.6</v>
       </c>
-      <c r="P165">
-        <v>1.97</v>
-      </c>
-      <c r="Q165">
-        <v>3.78</v>
-      </c>
       <c r="R165">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S165">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T165">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U165">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V165">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W165">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X165">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y165">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z165">
-        <v>4.53</v>
+        <v>4.3</v>
       </c>
       <c r="AA165">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB165">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC165">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AD165">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AE165">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF165">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG165">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="AK165">
         <v>1.28</v>
@@ -28182,25 +28182,25 @@
         </is>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O171">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q171">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R171">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S171">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T171">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U171">
         <v>2.4</v>
@@ -28209,28 +28209,28 @@
         <v>1.43</v>
       </c>
       <c r="W171">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X171">
         <v>1.02</v>
       </c>
       <c r="Y171">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z171">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AA171">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AB171">
         <v>1.75</v>
       </c>
       <c r="AC171">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD171">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE171">
         <v>1.13</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="Q172">
         <v>1.76</v>
@@ -28360,16 +28360,16 @@
         <v>2.12</v>
       </c>
       <c r="S172">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T172">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U172">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="V172">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W172">
         <v>1.06</v>
@@ -28393,16 +28393,16 @@
         <v>2.6</v>
       </c>
       <c r="AD172">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AE172">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF172">
         <v>1.88</v>
       </c>
       <c r="AG172">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK172">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>6.62</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G194">
@@ -33739,10 +33739,10 @@
         <v>2.23</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U205">
         <v>2.5</v>
@@ -33751,10 +33751,10 @@
         <v>1.4</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y205">
         <v>1.24</v>
@@ -33775,7 +33775,7 @@
         <v>1.3</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF205">
         <v>1.68</v>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q206">
         <v>3.25</v>
@@ -33902,10 +33902,10 @@
         <v>2.17</v>
       </c>
       <c r="S206">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T206">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U206">
         <v>2.55</v>
@@ -33914,10 +33914,10 @@
         <v>1.38</v>
       </c>
       <c r="W206">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X206">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y206">
         <v>1.26</v>
@@ -33938,7 +33938,7 @@
         <v>1.29</v>
       </c>
       <c r="AE206">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF206">
         <v>1.66</v>
@@ -34904,10 +34904,10 @@
         <v>0</v>
       </c>
       <c r="AA212">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB212">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC212">
         <v>0</v>
@@ -35719,10 +35719,10 @@
         <v>0</v>
       </c>
       <c r="AA217">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB217">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC217">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q219">
         <v>1.76</v>
@@ -43851,16 +43851,16 @@
         <v>2.75</v>
       </c>
       <c r="U267">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V267">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W267">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y267">
         <v>1.25</v>
@@ -43881,7 +43881,7 @@
         <v>1.28</v>
       </c>
       <c r="AE267">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF267">
         <v>1.7</v>
@@ -45336,10 +45336,10 @@
         <v>0</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC276">
         <v>0</v>
@@ -45499,10 +45499,10 @@
         <v>0</v>
       </c>
       <c r="AA277">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB277">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC277">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G305">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G306">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G307">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G308">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
-        <v>1.4</v>
+        <v>2.37</v>
       </c>
       <c r="O327">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="P327">
-        <v>5.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q327">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="R327">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="S327">
+        <v>1.3</v>
+      </c>
+      <c r="T327">
+        <v>3.3</v>
+      </c>
+      <c r="U327">
+        <v>2.36</v>
+      </c>
+      <c r="V327">
+        <v>1.52</v>
+      </c>
+      <c r="W327">
+        <v>1.11</v>
+      </c>
+      <c r="X327">
+        <v>1.01</v>
+      </c>
+      <c r="Y327">
+        <v>1.18</v>
+      </c>
+      <c r="Z327">
+        <v>4.5</v>
+      </c>
+      <c r="AA327">
+        <v>1.68</v>
+      </c>
+      <c r="AB327">
+        <v>2.21</v>
+      </c>
+      <c r="AC327">
+        <v>2.63</v>
+      </c>
+      <c r="AD327">
+        <v>1.43</v>
+      </c>
+      <c r="AE327">
         <v>1.14</v>
       </c>
-      <c r="T327">
-        <v>4.9</v>
-      </c>
-      <c r="U327">
-        <v>1.82</v>
-      </c>
-      <c r="V327">
-        <v>1.93</v>
-      </c>
-      <c r="W327">
-        <v>1.28</v>
-      </c>
-      <c r="X327">
-        <v>0</v>
-      </c>
-      <c r="Y327">
-        <v>1.08</v>
-      </c>
-      <c r="Z327">
-        <v>8.5</v>
-      </c>
-      <c r="AA327">
-        <v>1.24</v>
-      </c>
-      <c r="AB327">
-        <v>3.38</v>
-      </c>
-      <c r="AC327">
-        <v>1.7</v>
-      </c>
-      <c r="AD327">
-        <v>2.05</v>
-      </c>
-      <c r="AE327">
-        <v>1.42</v>
-      </c>
       <c r="AF327">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG327">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AK327">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G328">
@@ -53773,64 +53773,64 @@
         </is>
       </c>
       <c r="N328">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="O328">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P328">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q328">
+        <v>3.42</v>
+      </c>
+      <c r="R328">
+        <v>2.48</v>
+      </c>
+      <c r="S328">
+        <v>1.2</v>
+      </c>
+      <c r="T328">
+        <v>3.75</v>
+      </c>
+      <c r="U328">
+        <v>2.04</v>
+      </c>
+      <c r="V328">
+        <v>1.73</v>
+      </c>
+      <c r="W328">
+        <v>1.2</v>
+      </c>
+      <c r="X328">
+        <v>0</v>
+      </c>
+      <c r="Y328">
+        <v>1.1</v>
+      </c>
+      <c r="Z328">
+        <v>6.4</v>
+      </c>
+      <c r="AA328">
+        <v>1.38</v>
+      </c>
+      <c r="AB328">
         <v>2.75</v>
       </c>
-      <c r="R328">
-        <v>2.23</v>
-      </c>
-      <c r="S328">
-        <v>1.3</v>
-      </c>
-      <c r="T328">
-        <v>3.3</v>
-      </c>
-      <c r="U328">
-        <v>2.36</v>
-      </c>
-      <c r="V328">
-        <v>1.52</v>
-      </c>
-      <c r="W328">
-        <v>1.11</v>
-      </c>
-      <c r="X328">
-        <v>1.01</v>
-      </c>
-      <c r="Y328">
-        <v>1.18</v>
-      </c>
-      <c r="Z328">
-        <v>4.5</v>
-      </c>
-      <c r="AA328">
-        <v>1.68</v>
-      </c>
-      <c r="AB328">
-        <v>2.21</v>
-      </c>
       <c r="AC328">
-        <v>2.63</v>
+        <v>1.96</v>
       </c>
       <c r="AD328">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AE328">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AF328">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AG328">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK328">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G329">
@@ -53936,65 +53936,65 @@
         </is>
       </c>
       <c r="N329">
+        <v>1.4</v>
+      </c>
+      <c r="O329">
+        <v>5.7</v>
+      </c>
+      <c r="P329">
+        <v>5.65</v>
+      </c>
+      <c r="Q329">
+        <v>1.75</v>
+      </c>
+      <c r="R329">
+        <v>2.88</v>
+      </c>
+      <c r="S329">
+        <v>1.14</v>
+      </c>
+      <c r="T329">
+        <v>4.9</v>
+      </c>
+      <c r="U329">
+        <v>1.82</v>
+      </c>
+      <c r="V329">
+        <v>1.93</v>
+      </c>
+      <c r="W329">
+        <v>1.28</v>
+      </c>
+      <c r="X329">
+        <v>0</v>
+      </c>
+      <c r="Y329">
+        <v>1.08</v>
+      </c>
+      <c r="Z329">
+        <v>8.5</v>
+      </c>
+      <c r="AA329">
+        <v>1.24</v>
+      </c>
+      <c r="AB329">
+        <v>3.38</v>
+      </c>
+      <c r="AC329">
+        <v>1.7</v>
+      </c>
+      <c r="AD329">
+        <v>2.05</v>
+      </c>
+      <c r="AE329">
+        <v>1.42</v>
+      </c>
+      <c r="AF329">
+        <v>1.4</v>
+      </c>
+      <c r="AG329">
         <v>2.85</v>
       </c>
-      <c r="O329">
-        <v>4</v>
-      </c>
-      <c r="P329">
-        <v>2.15</v>
-      </c>
-      <c r="Q329">
-        <v>3.42</v>
-      </c>
-      <c r="R329">
-        <v>2.48</v>
-      </c>
-      <c r="S329">
-        <v>1.2</v>
-      </c>
-      <c r="T329">
-        <v>3.75</v>
-      </c>
-      <c r="U329">
-        <v>2.04</v>
-      </c>
-      <c r="V329">
-        <v>1.73</v>
-      </c>
-      <c r="W329">
-        <v>1.2</v>
-      </c>
-      <c r="X329">
-        <v>0</v>
-      </c>
-      <c r="Y329">
-        <v>1.1</v>
-      </c>
-      <c r="Z329">
-        <v>6.4</v>
-      </c>
-      <c r="AA329">
-        <v>1.38</v>
-      </c>
-      <c r="AB329">
-        <v>2.75</v>
-      </c>
-      <c r="AC329">
-        <v>1.96</v>
-      </c>
-      <c r="AD329">
-        <v>1.79</v>
-      </c>
-      <c r="AE329">
-        <v>1.33</v>
-      </c>
-      <c r="AF329">
-        <v>1.35</v>
-      </c>
-      <c r="AG329">
-        <v>2.9</v>
-      </c>
       <c r="AH329" t="inlineStr">
         <is>
           <t>[]</t>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK329">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,80 +55403,80 @@
         </is>
       </c>
       <c r="N338">
-        <v>6.25</v>
+        <v>1.66</v>
       </c>
       <c r="O338">
-        <v>5.55</v>
+        <v>3.9</v>
       </c>
       <c r="P338">
-        <v>1.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q338">
-        <v>6</v>
+        <v>2.16</v>
       </c>
       <c r="R338">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="S338">
+        <v>1.22</v>
+      </c>
+      <c r="T338">
+        <v>3.8</v>
+      </c>
+      <c r="U338">
+        <v>2.16</v>
+      </c>
+      <c r="V338">
+        <v>1.65</v>
+      </c>
+      <c r="W338">
+        <v>1.15</v>
+      </c>
+      <c r="X338">
+        <v>0</v>
+      </c>
+      <c r="Y338">
+        <v>1.13</v>
+      </c>
+      <c r="Z338">
+        <v>5.53</v>
+      </c>
+      <c r="AA338">
+        <v>1.45</v>
+      </c>
+      <c r="AB338">
+        <v>2.63</v>
+      </c>
+      <c r="AC338">
+        <v>2.11</v>
+      </c>
+      <c r="AD338">
+        <v>1.63</v>
+      </c>
+      <c r="AE338">
+        <v>1.23</v>
+      </c>
+      <c r="AF338">
+        <v>1.47</v>
+      </c>
+      <c r="AG338">
+        <v>2.45</v>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI338" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ338">
         <v>1.2</v>
       </c>
-      <c r="T338">
-        <v>4</v>
-      </c>
-      <c r="U338">
-        <v>1.95</v>
-      </c>
-      <c r="V338">
-        <v>1.72</v>
-      </c>
-      <c r="W338">
-        <v>1.18</v>
-      </c>
-      <c r="X338">
-        <v>0</v>
-      </c>
-      <c r="Y338">
-        <v>1.07</v>
-      </c>
-      <c r="Z338">
-        <v>6.5</v>
-      </c>
-      <c r="AA338">
-        <v>1.44</v>
-      </c>
-      <c r="AB338">
-        <v>2.7</v>
-      </c>
-      <c r="AC338">
-        <v>1.92</v>
-      </c>
-      <c r="AD338">
-        <v>1.7</v>
-      </c>
-      <c r="AE338">
-        <v>1.3</v>
-      </c>
-      <c r="AF338">
-        <v>1.55</v>
-      </c>
-      <c r="AG338">
-        <v>2.3</v>
-      </c>
-      <c r="AH338" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI338" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ338">
-        <v>2.7</v>
-      </c>
       <c r="AK338">
-        <v>1.12</v>
+        <v>2.1</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,34 +55566,34 @@
         </is>
       </c>
       <c r="N339">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O339">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P339">
-        <v>4.32</v>
+        <v>3.8</v>
       </c>
       <c r="Q339">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="R339">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S339">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T339">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U339">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="V339">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W339">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X339">
         <v>0</v>
@@ -55602,28 +55602,28 @@
         <v>1.13</v>
       </c>
       <c r="Z339">
-        <v>5.53</v>
+        <v>6.03</v>
       </c>
       <c r="AA339">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB339">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AC339">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AD339">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE339">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AF339">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG339">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK339">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,80 +55729,80 @@
         </is>
       </c>
       <c r="N340">
-        <v>1.73</v>
+        <v>6.25</v>
       </c>
       <c r="O340">
-        <v>4.05</v>
+        <v>5.55</v>
       </c>
       <c r="P340">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q340">
-        <v>2.27</v>
+        <v>6</v>
       </c>
       <c r="R340">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="S340">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T340">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U340">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V340">
+        <v>1.72</v>
+      </c>
+      <c r="W340">
+        <v>1.18</v>
+      </c>
+      <c r="X340">
+        <v>0</v>
+      </c>
+      <c r="Y340">
+        <v>1.07</v>
+      </c>
+      <c r="Z340">
+        <v>6.5</v>
+      </c>
+      <c r="AA340">
+        <v>1.44</v>
+      </c>
+      <c r="AB340">
+        <v>2.7</v>
+      </c>
+      <c r="AC340">
+        <v>1.92</v>
+      </c>
+      <c r="AD340">
         <v>1.7</v>
       </c>
-      <c r="W340">
-        <v>1.17</v>
-      </c>
-      <c r="X340">
-        <v>0</v>
-      </c>
-      <c r="Y340">
-        <v>1.13</v>
-      </c>
-      <c r="Z340">
-        <v>6.03</v>
-      </c>
-      <c r="AA340">
-        <v>1.4</v>
-      </c>
-      <c r="AB340">
-        <v>2.81</v>
-      </c>
-      <c r="AC340">
-        <v>2.16</v>
-      </c>
-      <c r="AD340">
-        <v>1.66</v>
-      </c>
       <c r="AE340">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF340">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG340">
+        <v>2.3</v>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI340" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ340">
         <v>2.7</v>
       </c>
-      <c r="AH340" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI340" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ340">
-        <v>1.25</v>
-      </c>
       <c r="AK340">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="AL340">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="O50">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S50">
+        <v>1.4</v>
+      </c>
+      <c r="T50">
+        <v>2.81</v>
+      </c>
+      <c r="U50">
+        <v>2.99</v>
+      </c>
+      <c r="V50">
         <v>1.35</v>
-      </c>
-      <c r="T50">
-        <v>2.94</v>
-      </c>
-      <c r="U50">
-        <v>2.7</v>
-      </c>
-      <c r="V50">
-        <v>1.4</v>
       </c>
       <c r="W50">
         <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y50">
+        <v>1.32</v>
+      </c>
+      <c r="Z50">
+        <v>3.2</v>
+      </c>
+      <c r="AA50">
+        <v>2.2</v>
+      </c>
+      <c r="AB50">
+        <v>1.69</v>
+      </c>
+      <c r="AC50">
+        <v>3.6</v>
+      </c>
+      <c r="AD50">
         <v>1.22</v>
       </c>
-      <c r="Z50">
-        <v>3.7</v>
-      </c>
-      <c r="AA50">
-        <v>1.83</v>
-      </c>
-      <c r="AB50">
-        <v>1.92</v>
-      </c>
-      <c r="AC50">
-        <v>3.1</v>
-      </c>
-      <c r="AD50">
-        <v>1.33</v>
-      </c>
       <c r="AE50">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF50">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG50">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK50">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
+        <v>1.72</v>
+      </c>
+      <c r="O51">
+        <v>3.78</v>
+      </c>
+      <c r="P51">
+        <v>4.35</v>
+      </c>
+      <c r="Q51">
         <v>2.25</v>
       </c>
-      <c r="O51">
-        <v>3.3</v>
-      </c>
-      <c r="P51">
-        <v>3.1</v>
-      </c>
-      <c r="Q51">
-        <v>2.89</v>
-      </c>
       <c r="R51">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
+        <v>1.35</v>
+      </c>
+      <c r="T51">
+        <v>2.94</v>
+      </c>
+      <c r="U51">
+        <v>2.7</v>
+      </c>
+      <c r="V51">
         <v>1.4</v>
-      </c>
-      <c r="T51">
-        <v>2.81</v>
-      </c>
-      <c r="U51">
-        <v>2.99</v>
-      </c>
-      <c r="V51">
-        <v>1.35</v>
       </c>
       <c r="W51">
         <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA51">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB51">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="AC51">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD51">
+        <v>1.33</v>
+      </c>
+      <c r="AE51">
+        <v>1.1</v>
+      </c>
+      <c r="AF51">
+        <v>1.75</v>
+      </c>
+      <c r="AG51">
+        <v>1.94</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.22</v>
       </c>
-      <c r="AE51">
-        <v>1.03</v>
-      </c>
-      <c r="AF51">
-        <v>1.78</v>
-      </c>
-      <c r="AG51">
-        <v>1.9</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.28</v>
-      </c>
       <c r="AK51">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="O121">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P121">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="Q121">
-        <v>2.4</v>
+        <v>3.21</v>
       </c>
       <c r="R121">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S121">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T121">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="U121">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="V121">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W121">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X121">
         <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z121">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="AA121">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AB121">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AC121">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD121">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE121">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF121">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG121">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="O122">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P122">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q122">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R122">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S122">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T122">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="U122">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V122">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W122">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z122">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA122">
         <v>1.95</v>
       </c>
       <c r="AB122">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC122">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD122">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE122">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF122">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AG122">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK122">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,80 +20358,80 @@
         </is>
       </c>
       <c r="N123">
+        <v>1.95</v>
+      </c>
+      <c r="O123">
+        <v>3.45</v>
+      </c>
+      <c r="P123">
+        <v>3.85</v>
+      </c>
+      <c r="Q123">
         <v>2.4</v>
       </c>
-      <c r="O123">
-        <v>3.25</v>
-      </c>
-      <c r="P123">
-        <v>2.6</v>
-      </c>
-      <c r="Q123">
-        <v>3.21</v>
-      </c>
       <c r="R123">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S123">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T123">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U123">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="V123">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W123">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X123">
         <v>1.03</v>
       </c>
       <c r="Y123">
+        <v>1.27</v>
+      </c>
+      <c r="Z123">
+        <v>3.58</v>
+      </c>
+      <c r="AA123">
+        <v>1.88</v>
+      </c>
+      <c r="AB123">
+        <v>1.88</v>
+      </c>
+      <c r="AC123">
+        <v>3.2</v>
+      </c>
+      <c r="AD123">
         <v>1.33</v>
       </c>
-      <c r="Z123">
-        <v>3.36</v>
-      </c>
-      <c r="AA123">
-        <v>1.99</v>
-      </c>
-      <c r="AB123">
+      <c r="AE123">
+        <v>1.07</v>
+      </c>
+      <c r="AF123">
+        <v>1.72</v>
+      </c>
+      <c r="AG123">
+        <v>1.95</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ123">
+        <v>1.22</v>
+      </c>
+      <c r="AK123">
         <v>1.74</v>
-      </c>
-      <c r="AC123">
-        <v>3.34</v>
-      </c>
-      <c r="AD123">
-        <v>1.24</v>
-      </c>
-      <c r="AE123">
-        <v>1.06</v>
-      </c>
-      <c r="AF123">
-        <v>1.73</v>
-      </c>
-      <c r="AG123">
-        <v>1.97</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>1.25</v>
-      </c>
-      <c r="AK123">
-        <v>1.48</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="O125">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P125">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q125">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R125">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S125">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T125">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="U125">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V125">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W125">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y125">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z125">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA125">
         <v>1.95</v>
       </c>
       <c r="AB125">
+        <v>1.75</v>
+      </c>
+      <c r="AC125">
+        <v>3.6</v>
+      </c>
+      <c r="AD125">
+        <v>1.28</v>
+      </c>
+      <c r="AE125">
+        <v>1.09</v>
+      </c>
+      <c r="AF125">
         <v>1.83</v>
       </c>
-      <c r="AC125">
-        <v>3.2</v>
-      </c>
-      <c r="AD125">
-        <v>1.27</v>
-      </c>
-      <c r="AE125">
-        <v>1.07</v>
-      </c>
-      <c r="AF125">
-        <v>1.71</v>
-      </c>
       <c r="AG125">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK125">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,22 +22314,22 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="O135">
         <v>3.2</v>
       </c>
       <c r="P135">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="Q135">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="R135">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S135">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T135">
         <v>2.75</v>
@@ -22338,40 +22338,40 @@
         <v>2.95</v>
       </c>
       <c r="V135">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W135">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y135">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z135">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="AA135">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB135">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="AC135">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD135">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE135">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF135">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG135">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK135">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,22 +22477,22 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="O136">
         <v>3.2</v>
       </c>
       <c r="P136">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q136">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="R136">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S136">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T136">
         <v>2.75</v>
@@ -22501,40 +22501,40 @@
         <v>2.95</v>
       </c>
       <c r="V136">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W136">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X136">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z136">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="AA136">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AB136">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AC136">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD136">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG136">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK136">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.35</v>
+        <v>1.2</v>
       </c>
       <c r="O138">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="P138">
-        <v>2.65</v>
+        <v>11</v>
       </c>
       <c r="Q138">
-        <v>2.88</v>
+        <v>1.55</v>
       </c>
       <c r="R138">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="S138">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="T138">
-        <v>2.99</v>
+        <v>4.2</v>
       </c>
       <c r="U138">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="V138">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="W138">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X138">
         <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="Z138">
-        <v>3.62</v>
+        <v>6.7</v>
       </c>
       <c r="AA138">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="AB138">
-        <v>2.06</v>
+        <v>3.12</v>
       </c>
       <c r="AC138">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="AD138">
-        <v>1.41</v>
+        <v>1.89</v>
       </c>
       <c r="AE138">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AF138">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AG138">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK138">
-        <v>1.53</v>
+        <v>4.25</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="O139">
-        <v>6.5</v>
+        <v>3.72</v>
       </c>
       <c r="P139">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="Q139">
-        <v>1.55</v>
+        <v>2.27</v>
       </c>
       <c r="R139">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="S139">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="T139">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="U139">
-        <v>1.92</v>
+        <v>2.53</v>
       </c>
       <c r="V139">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="W139">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X139">
         <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="Z139">
-        <v>6.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA139">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="AB139">
-        <v>3.12</v>
+        <v>1.97</v>
       </c>
       <c r="AC139">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AD139">
-        <v>1.89</v>
+        <v>1.34</v>
       </c>
       <c r="AE139">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF139">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG139">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK139">
-        <v>4.25</v>
+        <v>2.11</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O140">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="P140">
-        <v>4.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q140">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="R140">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="S140">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T140">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U140">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="V140">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W140">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X140">
         <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z140">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA140">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB140">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AC140">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD140">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE140">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF140">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG140">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK140">
-        <v>2.11</v>
+        <v>1.53</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="O145">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>3.59</v>
+        <v>2.47</v>
       </c>
       <c r="Q145">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="R145">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S145">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T145">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U145">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="V145">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W145">
         <v>1.06</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y145">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z145">
-        <v>3.52</v>
+        <v>3.89</v>
       </c>
       <c r="AA145">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB145">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC145">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="AD145">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE145">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK145">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,52 +24107,52 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O146">
         <v>3.5</v>
       </c>
       <c r="P146">
+        <v>2.9</v>
+      </c>
+      <c r="Q146">
+        <v>2.69</v>
+      </c>
+      <c r="R146">
+        <v>2.25</v>
+      </c>
+      <c r="S146">
+        <v>1.34</v>
+      </c>
+      <c r="T146">
+        <v>2.82</v>
+      </c>
+      <c r="U146">
         <v>2.47</v>
-      </c>
-      <c r="Q146">
-        <v>3.3</v>
-      </c>
-      <c r="R146">
-        <v>2.07</v>
-      </c>
-      <c r="S146">
-        <v>1.33</v>
-      </c>
-      <c r="T146">
-        <v>3.18</v>
-      </c>
-      <c r="U146">
-        <v>2.45</v>
       </c>
       <c r="V146">
         <v>1.48</v>
       </c>
       <c r="W146">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X146">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y146">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z146">
-        <v>3.89</v>
+        <v>3.75</v>
       </c>
       <c r="AA146">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB146">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AC146">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
       <c r="AD146">
         <v>1.34</v>
@@ -24164,7 +24164,7 @@
         <v>1.6</v>
       </c>
       <c r="AG146">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK146">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="O147">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P147">
-        <v>2.9</v>
+        <v>3.59</v>
       </c>
       <c r="Q147">
+        <v>2.36</v>
+      </c>
+      <c r="R147">
+        <v>2.12</v>
+      </c>
+      <c r="S147">
+        <v>1.3</v>
+      </c>
+      <c r="T147">
+        <v>3.2</v>
+      </c>
+      <c r="U147">
         <v>2.69</v>
       </c>
-      <c r="R147">
-        <v>2.25</v>
-      </c>
-      <c r="S147">
-        <v>1.34</v>
-      </c>
-      <c r="T147">
-        <v>2.82</v>
-      </c>
-      <c r="U147">
-        <v>2.47</v>
-      </c>
       <c r="V147">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W147">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X147">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y147">
         <v>1.22</v>
       </c>
       <c r="Z147">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="AA147">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AB147">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC147">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="AD147">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE147">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF147">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG147">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK147">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.75</v>
+        <v>2.24</v>
       </c>
       <c r="O155">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="P155">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="Q155">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R155">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S155">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T155">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U155">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V155">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W155">
         <v>1.07</v>
       </c>
       <c r="X155">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y155">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z155">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="AA155">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB155">
         <v>1.65</v>
       </c>
       <c r="AC155">
-        <v>4.25</v>
+        <v>3.65</v>
       </c>
       <c r="AD155">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE155">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF155">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG155">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK155">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="O156">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P156">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="Q156">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R156">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S156">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U156">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V156">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W156">
         <v>1.07</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z156">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AA156">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB156">
         <v>1.65</v>
       </c>
       <c r="AC156">
-        <v>3.65</v>
+        <v>4.25</v>
       </c>
       <c r="AD156">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE156">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AF156">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG156">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK156">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -27421,10 +27421,10 @@
         <v>1.11</v>
       </c>
       <c r="AF166">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG166">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G204">
@@ -38291,58 +38291,58 @@
         <v>1.86</v>
       </c>
       <c r="O233">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="P233">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q233">
         <v>2.26</v>
       </c>
       <c r="R233">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S233">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T233">
-        <v>3.23</v>
+        <v>2.98</v>
       </c>
       <c r="U233">
         <v>2.7</v>
       </c>
       <c r="V233">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W233">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X233">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y233">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z233">
         <v>3.64</v>
       </c>
       <c r="AA233">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB233">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AC233">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AD233">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE233">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF233">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG233">
         <v>2.05</v>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK233">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="O272">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P272">
-        <v>3.61</v>
+        <v>2.5</v>
       </c>
       <c r="Q272">
-        <v>2.4</v>
+        <v>3.32</v>
       </c>
       <c r="R272">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S272">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T272">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U272">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V272">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W272">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X272">
         <v>1.03</v>
       </c>
       <c r="Y272">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z272">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="AA272">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB272">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC272">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD272">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE272">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF272">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG272">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK272">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="O273">
         <v>3.4</v>
       </c>
       <c r="P273">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="Q273">
-        <v>3.32</v>
+        <v>2.56</v>
       </c>
       <c r="R273">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="S273">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T273">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U273">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="V273">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="W273">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X273">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y273">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z273">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AA273">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AB273">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AC273">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="AD273">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE273">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF273">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG273">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>1.25</v>
       </c>
       <c r="AK273">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,80 +44971,80 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O274">
+        <v>3.35</v>
+      </c>
+      <c r="P274">
+        <v>3.61</v>
+      </c>
+      <c r="Q274">
+        <v>2.4</v>
+      </c>
+      <c r="R274">
+        <v>2.12</v>
+      </c>
+      <c r="S274">
+        <v>1.37</v>
+      </c>
+      <c r="T274">
+        <v>2.8</v>
+      </c>
+      <c r="U274">
+        <v>2.8</v>
+      </c>
+      <c r="V274">
+        <v>1.38</v>
+      </c>
+      <c r="W274">
+        <v>1.05</v>
+      </c>
+      <c r="X274">
+        <v>1.03</v>
+      </c>
+      <c r="Y274">
+        <v>1.33</v>
+      </c>
+      <c r="Z274">
+        <v>2.96</v>
+      </c>
+      <c r="AA274">
+        <v>1.94</v>
+      </c>
+      <c r="AB274">
+        <v>1.87</v>
+      </c>
+      <c r="AC274">
         <v>3.4</v>
       </c>
-      <c r="P274">
-        <v>3.48</v>
-      </c>
-      <c r="Q274">
-        <v>2.56</v>
-      </c>
-      <c r="R274">
-        <v>2.06</v>
-      </c>
-      <c r="S274">
-        <v>1.36</v>
-      </c>
-      <c r="T274">
-        <v>2.88</v>
-      </c>
-      <c r="U274">
-        <v>3.08</v>
-      </c>
-      <c r="V274">
-        <v>1.33</v>
-      </c>
-      <c r="W274">
-        <v>1.07</v>
-      </c>
-      <c r="X274">
-        <v>1.02</v>
-      </c>
-      <c r="Y274">
-        <v>1.35</v>
-      </c>
-      <c r="Z274">
-        <v>3.1</v>
-      </c>
-      <c r="AA274">
-        <v>2.12</v>
-      </c>
-      <c r="AB274">
-        <v>1.65</v>
-      </c>
-      <c r="AC274">
-        <v>3.56</v>
-      </c>
       <c r="AD274">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE274">
         <v>1.05</v>
       </c>
       <c r="AF274">
+        <v>1.85</v>
+      </c>
+      <c r="AG274">
+        <v>1.85</v>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ274">
+        <v>1.32</v>
+      </c>
+      <c r="AK274">
         <v>1.87</v>
-      </c>
-      <c r="AG274">
-        <v>1.87</v>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ274">
-        <v>1.25</v>
-      </c>
-      <c r="AK274">
-        <v>1.91</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O288">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P288">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q288">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="R288">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S288">
         <v>1.7</v>
       </c>
       <c r="T288">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U288">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="V288">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="W288">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X288">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y288">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="Z288">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AA288">
         <v>3.4</v>
       </c>
       <c r="AB288">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC288">
-        <v>6.95</v>
+        <v>6.2</v>
       </c>
       <c r="AD288">
         <v>1.06</v>
       </c>
       <c r="AE288">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF288">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AG288">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK288">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O289">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P289">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q289">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="R289">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S289">
         <v>1.7</v>
       </c>
       <c r="T289">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U289">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="V289">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W289">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X289">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y289">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="Z289">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="AA289">
         <v>3.4</v>
       </c>
       <c r="AB289">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC289">
-        <v>6.2</v>
+        <v>6.95</v>
       </c>
       <c r="AD289">
         <v>1.06</v>
       </c>
       <c r="AE289">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF289">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="AG289">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK289">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G290">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G292">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,28 +55240,28 @@
         </is>
       </c>
       <c r="N337">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="O337">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P337">
-        <v>3.8</v>
+        <v>4.32</v>
       </c>
       <c r="Q337">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="R337">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S337">
         <v>1.22</v>
       </c>
       <c r="T337">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U337">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V337">
         <v>1.65</v>
@@ -55270,34 +55270,34 @@
         <v>1.15</v>
       </c>
       <c r="X337">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y337">
         <v>1.13</v>
       </c>
       <c r="Z337">
-        <v>5.75</v>
+        <v>5.53</v>
       </c>
       <c r="AA337">
+        <v>1.45</v>
+      </c>
+      <c r="AB337">
+        <v>2.63</v>
+      </c>
+      <c r="AC337">
+        <v>2.11</v>
+      </c>
+      <c r="AD337">
+        <v>1.63</v>
+      </c>
+      <c r="AE337">
+        <v>1.23</v>
+      </c>
+      <c r="AF337">
         <v>1.47</v>
       </c>
-      <c r="AB337">
-        <v>2.67</v>
-      </c>
-      <c r="AC337">
-        <v>2.14</v>
-      </c>
-      <c r="AD337">
-        <v>1.68</v>
-      </c>
-      <c r="AE337">
-        <v>1.29</v>
-      </c>
-      <c r="AF337">
-        <v>1.41</v>
-      </c>
       <c r="AG337">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AH337" t="inlineStr">
         <is>
@@ -55310,10 +55310,10 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK337">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,64 +55403,64 @@
         </is>
       </c>
       <c r="N338">
-        <v>1.66</v>
+        <v>6.25</v>
       </c>
       <c r="O338">
-        <v>3.9</v>
+        <v>5.55</v>
       </c>
       <c r="P338">
-        <v>4.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q338">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="R338">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="S338">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T338">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U338">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="V338">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="W338">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X338">
         <v>0</v>
       </c>
       <c r="Y338">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z338">
-        <v>5.53</v>
+        <v>6.5</v>
       </c>
       <c r="AA338">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB338">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC338">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="AD338">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AE338">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF338">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AG338">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55473,10 +55473,10 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="AK338">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,64 +55566,64 @@
         </is>
       </c>
       <c r="N339">
-        <v>6.25</v>
+        <v>1.81</v>
       </c>
       <c r="O339">
-        <v>5.55</v>
+        <v>4</v>
       </c>
       <c r="P339">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q339">
-        <v>6</v>
+        <v>2.23</v>
       </c>
       <c r="R339">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="S339">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T339">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U339">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="V339">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="W339">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X339">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y339">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z339">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA339">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB339">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AC339">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="AD339">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE339">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF339">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AG339">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>2.7</v>
+        <v>1.23</v>
       </c>
       <c r="AK339">
-        <v>1.12</v>
+        <v>1.98</v>
       </c>
       <c r="AL339">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O48">
         <v>3.7</v>
       </c>
       <c r="P48">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -8160,7 +8160,7 @@
         <v>1.8</v>
       </c>
       <c r="W48">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X48">
         <v>1</v>
@@ -8169,13 +8169,13 @@
         <v>1.06</v>
       </c>
       <c r="Z48">
-        <v>7</v>
+        <v>6.05</v>
       </c>
       <c r="AA48">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AB48">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AC48">
         <v>1.86</v>
@@ -8190,7 +8190,7 @@
         <v>1.31</v>
       </c>
       <c r="AG48">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.43</v>
       </c>
       <c r="AK48">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="O55">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P55">
-        <v>3.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="R55">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="S55">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T55">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="U55">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="V55">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z55">
-        <v>4.45</v>
+        <v>3.55</v>
       </c>
       <c r="AA55">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB55">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AC55">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="AD55">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE55">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF55">
         <v>1.55</v>
       </c>
       <c r="AG55">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AK55">
-        <v>1.97</v>
+        <v>1.3</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="O56">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q56">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="R56">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="S56">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="U56">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="V56">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W56">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z56">
-        <v>3.55</v>
+        <v>4.45</v>
       </c>
       <c r="AA56">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB56">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AC56">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="AD56">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE56">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF56">
         <v>1.55</v>
       </c>
       <c r="AG56">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AK56">
-        <v>1.3</v>
+        <v>1.97</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G87">
@@ -14499,10 +14499,10 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="R87">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="U87">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="V87">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="W87">
         <v>0</v>
@@ -14529,25 +14529,25 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AB87">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="AC87">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AD87">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AE87">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AF87">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG87">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>2.55</v>
+        <v>1.06</v>
       </c>
       <c r="AK87">
-        <v>1.06</v>
+        <v>3.7</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G88">
@@ -14662,55 +14662,55 @@
         <v>0</v>
       </c>
       <c r="Q88">
+        <v>5.8</v>
+      </c>
+      <c r="R88">
+        <v>2.63</v>
+      </c>
+      <c r="S88">
+        <v>0</v>
+      </c>
+      <c r="T88">
+        <v>0</v>
+      </c>
+      <c r="U88">
+        <v>2.12</v>
+      </c>
+      <c r="V88">
+        <v>1.55</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
+      <c r="X88">
+        <v>0</v>
+      </c>
+      <c r="Y88">
+        <v>0</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+      <c r="AA88">
         <v>1.5</v>
       </c>
-      <c r="R88">
-        <v>3.1</v>
-      </c>
-      <c r="S88">
-        <v>0</v>
-      </c>
-      <c r="T88">
-        <v>0</v>
-      </c>
-      <c r="U88">
-        <v>1.84</v>
-      </c>
-      <c r="V88">
-        <v>1.75</v>
-      </c>
-      <c r="W88">
-        <v>0</v>
-      </c>
-      <c r="X88">
-        <v>0</v>
-      </c>
-      <c r="Y88">
-        <v>0</v>
-      </c>
-      <c r="Z88">
-        <v>0</v>
-      </c>
-      <c r="AA88">
-        <v>1.34</v>
-      </c>
       <c r="AB88">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="AC88">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD88">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AE88">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AF88">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AG88">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
+        <v>2.55</v>
+      </c>
+      <c r="AK88">
         <v>1.06</v>
-      </c>
-      <c r="AK88">
-        <v>3.7</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O89">
-        <v>4.6</v>
+        <v>3.94</v>
       </c>
       <c r="P89">
         <v>5</v>
       </c>
       <c r="Q89">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="R89">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="S89">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="T89">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="U89">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="V89">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="W89">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z89">
-        <v>5.59</v>
+        <v>3.78</v>
       </c>
       <c r="AA89">
-        <v>1.46</v>
+        <v>1.86</v>
       </c>
       <c r="AB89">
-        <v>2.68</v>
+        <v>1.96</v>
       </c>
       <c r="AC89">
-        <v>2.13</v>
+        <v>2.89</v>
       </c>
       <c r="AD89">
-        <v>1.69</v>
+        <v>1.32</v>
       </c>
       <c r="AE89">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AF89">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="AG89">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK89">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O90">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="P90">
         <v>5</v>
       </c>
       <c r="Q90">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="R90">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="S90">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="T90">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="U90">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="V90">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="W90">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z90">
-        <v>3.78</v>
+        <v>5.59</v>
       </c>
       <c r="AA90">
-        <v>1.86</v>
+        <v>1.46</v>
       </c>
       <c r="AB90">
-        <v>1.96</v>
+        <v>2.68</v>
       </c>
       <c r="AC90">
-        <v>2.89</v>
+        <v>2.13</v>
       </c>
       <c r="AD90">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AF90">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="AG90">
-        <v>1.86</v>
+        <v>2.32</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK90">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="O121">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P121">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q121">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="R121">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S121">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T121">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U121">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V121">
         <v>1.38</v>
       </c>
       <c r="W121">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X121">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z121">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AA121">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB121">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC121">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD121">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE121">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF121">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG121">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK121">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,28 +20195,28 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="O122">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P122">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q122">
+        <v>2.38</v>
+      </c>
+      <c r="R122">
+        <v>2.08</v>
+      </c>
+      <c r="S122">
+        <v>1.4</v>
+      </c>
+      <c r="T122">
+        <v>2.75</v>
+      </c>
+      <c r="U122">
         <v>2.88</v>
-      </c>
-      <c r="R122">
-        <v>2.2</v>
-      </c>
-      <c r="S122">
-        <v>1.41</v>
-      </c>
-      <c r="T122">
-        <v>2.62</v>
-      </c>
-      <c r="U122">
-        <v>2.7</v>
       </c>
       <c r="V122">
         <v>1.38</v>
@@ -20225,34 +20225,34 @@
         <v>1.05</v>
       </c>
       <c r="X122">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y122">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z122">
         <v>3.25</v>
       </c>
       <c r="AA122">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB122">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC122">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AD122">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE122">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF122">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AG122">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK122">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
+        <v>1.93</v>
+      </c>
+      <c r="O123">
+        <v>3.4</v>
+      </c>
+      <c r="P123">
+        <v>3.8</v>
+      </c>
+      <c r="Q123">
+        <v>2.5</v>
+      </c>
+      <c r="R123">
+        <v>2.06</v>
+      </c>
+      <c r="S123">
+        <v>1.43</v>
+      </c>
+      <c r="T123">
+        <v>2.84</v>
+      </c>
+      <c r="U123">
+        <v>2.77</v>
+      </c>
+      <c r="V123">
+        <v>1.37</v>
+      </c>
+      <c r="W123">
+        <v>1.03</v>
+      </c>
+      <c r="X123">
+        <v>1.06</v>
+      </c>
+      <c r="Y123">
+        <v>1.29</v>
+      </c>
+      <c r="Z123">
+        <v>3.1</v>
+      </c>
+      <c r="AA123">
         <v>1.95</v>
       </c>
-      <c r="O123">
-        <v>3.45</v>
-      </c>
-      <c r="P123">
-        <v>3.85</v>
-      </c>
-      <c r="Q123">
-        <v>2.4</v>
-      </c>
-      <c r="R123">
-        <v>2.08</v>
-      </c>
-      <c r="S123">
-        <v>1.33</v>
-      </c>
-      <c r="T123">
-        <v>3.05</v>
-      </c>
-      <c r="U123">
-        <v>2.79</v>
-      </c>
-      <c r="V123">
-        <v>1.4</v>
-      </c>
-      <c r="W123">
-        <v>1.04</v>
-      </c>
-      <c r="X123">
-        <v>1.03</v>
-      </c>
-      <c r="Y123">
-        <v>1.27</v>
-      </c>
-      <c r="Z123">
-        <v>3.58</v>
-      </c>
-      <c r="AA123">
-        <v>1.88</v>
-      </c>
       <c r="AB123">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AC123">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD123">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE123">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF123">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG123">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK123">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="O124">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P124">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q124">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="R124">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S124">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T124">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="U124">
+        <v>2.9</v>
+      </c>
+      <c r="V124">
+        <v>1.35</v>
+      </c>
+      <c r="W124">
+        <v>1.03</v>
+      </c>
+      <c r="X124">
+        <v>1.03</v>
+      </c>
+      <c r="Y124">
+        <v>1.38</v>
+      </c>
+      <c r="Z124">
         <v>2.88</v>
       </c>
-      <c r="V124">
-        <v>1.38</v>
-      </c>
-      <c r="W124">
-        <v>1.05</v>
-      </c>
-      <c r="X124">
-        <v>1.06</v>
-      </c>
-      <c r="Y124">
-        <v>1.3</v>
-      </c>
-      <c r="Z124">
-        <v>3.25</v>
-      </c>
       <c r="AA124">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB124">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC124">
-        <v>3.55</v>
+        <v>3.83</v>
       </c>
       <c r="AD124">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE124">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF124">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG124">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK124">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="O125">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P125">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q125">
-        <v>2.5</v>
+        <v>3.21</v>
       </c>
       <c r="R125">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S125">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T125">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U125">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V125">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
+        <v>1.03</v>
+      </c>
+      <c r="Y125">
+        <v>1.33</v>
+      </c>
+      <c r="Z125">
+        <v>3.36</v>
+      </c>
+      <c r="AA125">
+        <v>1.99</v>
+      </c>
+      <c r="AB125">
+        <v>1.74</v>
+      </c>
+      <c r="AC125">
+        <v>3.34</v>
+      </c>
+      <c r="AD125">
+        <v>1.24</v>
+      </c>
+      <c r="AE125">
         <v>1.06</v>
       </c>
-      <c r="Y125">
-        <v>1.29</v>
-      </c>
-      <c r="Z125">
-        <v>3.1</v>
-      </c>
-      <c r="AA125">
-        <v>1.95</v>
-      </c>
-      <c r="AB125">
-        <v>1.75</v>
-      </c>
-      <c r="AC125">
-        <v>3.6</v>
-      </c>
-      <c r="AD125">
-        <v>1.28</v>
-      </c>
-      <c r="AE125">
-        <v>1.09</v>
-      </c>
       <c r="AF125">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG125">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK125">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="O126">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P126">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="Q126">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="R126">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="S126">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T126">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="U126">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="V126">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W126">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X126">
         <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="Z126">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="AA126">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AB126">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC126">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="AD126">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AE126">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF126">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG126">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK126">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21179,7 +21179,7 @@
         <v>3.4</v>
       </c>
       <c r="P128">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q128">
         <v>2.94</v>
@@ -21212,19 +21212,19 @@
         <v>4.15</v>
       </c>
       <c r="AA128">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB128">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC128">
         <v>2.52</v>
       </c>
       <c r="AD128">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE128">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF128">
         <v>1.52</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,22 +22314,22 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="O135">
         <v>3.2</v>
       </c>
       <c r="P135">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q135">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="R135">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S135">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T135">
         <v>2.75</v>
@@ -22338,40 +22338,40 @@
         <v>2.95</v>
       </c>
       <c r="V135">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W135">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X135">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z135">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="AA135">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AB135">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AC135">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD135">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE135">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF135">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG135">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK135">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,22 +22477,22 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="O136">
         <v>3.2</v>
       </c>
       <c r="P136">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="Q136">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="R136">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S136">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T136">
         <v>2.75</v>
@@ -22501,40 +22501,40 @@
         <v>2.95</v>
       </c>
       <c r="V136">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W136">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y136">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z136">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="AA136">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB136">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="AC136">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD136">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE136">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG136">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK136">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="O138">
-        <v>6.5</v>
+        <v>3.72</v>
       </c>
       <c r="P138">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="Q138">
-        <v>1.55</v>
+        <v>2.27</v>
       </c>
       <c r="R138">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="S138">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="T138">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="U138">
-        <v>1.92</v>
+        <v>2.53</v>
       </c>
       <c r="V138">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="W138">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X138">
         <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="Z138">
-        <v>6.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA138">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="AB138">
-        <v>3.12</v>
+        <v>1.97</v>
       </c>
       <c r="AC138">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AD138">
-        <v>1.89</v>
+        <v>1.34</v>
       </c>
       <c r="AE138">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF138">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG138">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK138">
-        <v>4.25</v>
+        <v>2.11</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="O139">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="P139">
-        <v>4.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q139">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="R139">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="S139">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T139">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U139">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="V139">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W139">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X139">
         <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z139">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA139">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB139">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AC139">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD139">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE139">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF139">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG139">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK139">
-        <v>2.11</v>
+        <v>1.53</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.35</v>
+        <v>1.2</v>
       </c>
       <c r="O140">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="P140">
-        <v>2.65</v>
+        <v>11</v>
       </c>
       <c r="Q140">
-        <v>2.88</v>
+        <v>1.55</v>
       </c>
       <c r="R140">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="S140">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="T140">
-        <v>2.99</v>
+        <v>4.2</v>
       </c>
       <c r="U140">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="V140">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="W140">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X140">
         <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="Z140">
-        <v>3.62</v>
+        <v>6.7</v>
       </c>
       <c r="AA140">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="AB140">
-        <v>2.06</v>
+        <v>3.12</v>
       </c>
       <c r="AC140">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="AD140">
-        <v>1.41</v>
+        <v>1.89</v>
       </c>
       <c r="AE140">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AF140">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AG140">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK140">
-        <v>1.53</v>
+        <v>4.25</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="O146">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P146">
-        <v>2.9</v>
+        <v>3.59</v>
       </c>
       <c r="Q146">
+        <v>2.36</v>
+      </c>
+      <c r="R146">
+        <v>2.12</v>
+      </c>
+      <c r="S146">
+        <v>1.3</v>
+      </c>
+      <c r="T146">
+        <v>3.2</v>
+      </c>
+      <c r="U146">
         <v>2.69</v>
       </c>
-      <c r="R146">
-        <v>2.25</v>
-      </c>
-      <c r="S146">
-        <v>1.34</v>
-      </c>
-      <c r="T146">
-        <v>2.82</v>
-      </c>
-      <c r="U146">
-        <v>2.47</v>
-      </c>
       <c r="V146">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W146">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X146">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
         <v>1.22</v>
       </c>
       <c r="Z146">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="AA146">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AB146">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC146">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="AD146">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE146">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF146">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG146">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK146">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="O147">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P147">
-        <v>3.59</v>
+        <v>2.9</v>
       </c>
       <c r="Q147">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="R147">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S147">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T147">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U147">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="V147">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W147">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X147">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y147">
         <v>1.22</v>
       </c>
       <c r="Z147">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="AA147">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB147">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC147">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="AD147">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE147">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF147">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG147">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK147">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,80 +32583,80 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O198">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P198">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q198">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R198">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="S198">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T198">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U198">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="V198">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="W198">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X198">
         <v>1.02</v>
       </c>
       <c r="Y198">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z198">
-        <v>4.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA198">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB198">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC198">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AD198">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AE198">
+        <v>1.28</v>
+      </c>
+      <c r="AF198">
+        <v>1.41</v>
+      </c>
+      <c r="AG198">
+        <v>2.69</v>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ198">
         <v>1.18</v>
       </c>
-      <c r="AF198">
-        <v>1.5</v>
-      </c>
-      <c r="AG198">
-        <v>2.4</v>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ198">
-        <v>1.26</v>
-      </c>
       <c r="AK198">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O199">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P199">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q199">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R199">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="S199">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T199">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U199">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="V199">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="W199">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X199">
         <v>1.02</v>
       </c>
       <c r="Y199">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z199">
-        <v>5.45</v>
+        <v>4.75</v>
       </c>
       <c r="AA199">
+        <v>1.53</v>
+      </c>
+      <c r="AB199">
+        <v>2.4</v>
+      </c>
+      <c r="AC199">
+        <v>2.35</v>
+      </c>
+      <c r="AD199">
+        <v>1.57</v>
+      </c>
+      <c r="AE199">
+        <v>1.18</v>
+      </c>
+      <c r="AF199">
         <v>1.5</v>
       </c>
-      <c r="AB199">
-        <v>2.5</v>
-      </c>
-      <c r="AC199">
-        <v>2.1</v>
-      </c>
-      <c r="AD199">
-        <v>1.71</v>
-      </c>
-      <c r="AE199">
-        <v>1.28</v>
-      </c>
-      <c r="AF199">
-        <v>1.41</v>
-      </c>
       <c r="AG199">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK199">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G204">
@@ -41243,7 +41243,7 @@
         <v>2.2</v>
       </c>
       <c r="U251">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="V251">
         <v>1.2</v>
@@ -41252,34 +41252,34 @@
         <v>1.04</v>
       </c>
       <c r="X251">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y251">
         <v>1.45</v>
       </c>
       <c r="Z251">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AA251">
         <v>2.69</v>
       </c>
       <c r="AB251">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AC251">
         <v>5.65</v>
       </c>
       <c r="AD251">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE251">
         <v>1.03</v>
       </c>
       <c r="AF251">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AG251">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41720,28 +41720,28 @@
         <v>0</v>
       </c>
       <c r="Q254">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R254">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S254">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T254">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U254">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V254">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W254">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X254">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y254">
         <v>1.19</v>
@@ -41750,25 +41750,25 @@
         <v>3.95</v>
       </c>
       <c r="AA254">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AB254">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC254">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AD254">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE254">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF254">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG254">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK254">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -42698,55 +42698,55 @@
         <v>1.79</v>
       </c>
       <c r="Q260">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="R260">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="S260">
+        <v>1.36</v>
+      </c>
+      <c r="T260">
+        <v>2.75</v>
+      </c>
+      <c r="U260">
+        <v>2.77</v>
+      </c>
+      <c r="V260">
         <v>1.38</v>
-      </c>
-      <c r="T260">
-        <v>2.77</v>
-      </c>
-      <c r="U260">
-        <v>2.69</v>
-      </c>
-      <c r="V260">
-        <v>1.4</v>
       </c>
       <c r="W260">
         <v>1.08</v>
       </c>
       <c r="X260">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y260">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z260">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="AA260">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB260">
         <v>1.85</v>
       </c>
       <c r="AC260">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="AD260">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE260">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF260">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG260">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>1.23</v>
       </c>
       <c r="AK260">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -43350,10 +43350,10 @@
         <v>5.57</v>
       </c>
       <c r="Q264">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="R264">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S264">
         <v>1.58</v>
@@ -43365,7 +43365,7 @@
         <v>3.6</v>
       </c>
       <c r="V264">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W264">
         <v>1.01</v>
@@ -43383,19 +43383,19 @@
         <v>2.87</v>
       </c>
       <c r="AB264">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AC264">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="AD264">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE264">
         <v>1.03</v>
       </c>
       <c r="AF264">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AG264">
         <v>1.46</v>
@@ -43414,7 +43414,7 @@
         <v>1.14</v>
       </c>
       <c r="AK264">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -47265,13 +47265,13 @@
         <v>3.74</v>
       </c>
       <c r="R288">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S288">
         <v>1.7</v>
       </c>
       <c r="T288">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="U288">
         <v>4.2</v>
@@ -47292,7 +47292,7 @@
         <v>2.18</v>
       </c>
       <c r="AA288">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AB288">
         <v>1.3</v>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK288">
         <v>1.38</v>
@@ -47434,13 +47434,13 @@
         <v>1.7</v>
       </c>
       <c r="T289">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U289">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="V289">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="W289">
         <v>1.02</v>
@@ -47455,10 +47455,10 @@
         <v>1.93</v>
       </c>
       <c r="AA289">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB289">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC289">
         <v>6.95</v>
@@ -47470,7 +47470,7 @@
         <v>1.01</v>
       </c>
       <c r="AF289">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG289">
         <v>1.44</v>
@@ -51328,31 +51328,31 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q313">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="R313">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S313">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T313">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="U313">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="V313">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W313">
         <v>1.04</v>
@@ -51361,28 +51361,28 @@
         <v>1.03</v>
       </c>
       <c r="Y313">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z313">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA313">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB313">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC313">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="AD313">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE313">
         <v>1.03</v>
       </c>
       <c r="AF313">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG313">
         <v>1.8</v>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AK313">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51980,64 +51980,64 @@
         </is>
       </c>
       <c r="N317">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O317">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P317">
+        <v>3.7</v>
+      </c>
+      <c r="Q317">
+        <v>2.91</v>
+      </c>
+      <c r="R317">
+        <v>1.93</v>
+      </c>
+      <c r="S317">
+        <v>1.55</v>
+      </c>
+      <c r="T317">
+        <v>2.32</v>
+      </c>
+      <c r="U317">
         <v>3.6</v>
-      </c>
-      <c r="Q317">
-        <v>2.8</v>
-      </c>
-      <c r="R317">
-        <v>1.84</v>
-      </c>
-      <c r="S317">
-        <v>1.6</v>
-      </c>
-      <c r="T317">
-        <v>2.23</v>
-      </c>
-      <c r="U317">
-        <v>3.55</v>
       </c>
       <c r="V317">
         <v>1.25</v>
       </c>
       <c r="W317">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X317">
         <v>1.08</v>
       </c>
       <c r="Y317">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="Z317">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="AA317">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AB317">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AC317">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AD317">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE317">
         <v>1.03</v>
       </c>
       <c r="AF317">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AG317">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK317">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL317">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -10427,10 +10427,10 @@
         <v>1.73</v>
       </c>
       <c r="R62">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="S62">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T62">
         <v>3.9</v>
@@ -10454,10 +10454,10 @@
         <v>5.35</v>
       </c>
       <c r="AA62">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AB62">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AC62">
         <v>2.04</v>
@@ -10466,13 +10466,13 @@
         <v>1.69</v>
       </c>
       <c r="AE62">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF62">
         <v>1.64</v>
       </c>
       <c r="AG62">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.1</v>
       </c>
       <c r="AK62">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,7 +10587,7 @@
         <v>2.9</v>
       </c>
       <c r="Q63">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R63">
         <v>2.36</v>
@@ -10599,13 +10599,13 @@
         <v>3.5</v>
       </c>
       <c r="U63">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V63">
         <v>1.67</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X63">
         <v>1.01</v>
@@ -10617,25 +10617,25 @@
         <v>5.1</v>
       </c>
       <c r="AA63">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB63">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC63">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AD63">
         <v>1.65</v>
       </c>
       <c r="AE63">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF63">
         <v>1.4</v>
       </c>
       <c r="AG63">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AK63">
         <v>1.67</v>
@@ -10747,28 +10747,28 @@
         <v>3.5</v>
       </c>
       <c r="P64">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q64">
         <v>3.32</v>
       </c>
       <c r="R64">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S64">
         <v>1.22</v>
       </c>
       <c r="T64">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U64">
         <v>2.2</v>
       </c>
       <c r="V64">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W64">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
         <v>1.02</v>
@@ -10783,13 +10783,13 @@
         <v>1.47</v>
       </c>
       <c r="AB64">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AC64">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD64">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AE64">
         <v>1.19</v>
@@ -10798,7 +10798,7 @@
         <v>1.44</v>
       </c>
       <c r="AG64">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK64">
         <v>1.36</v>
@@ -10907,16 +10907,16 @@
         <v>2.65</v>
       </c>
       <c r="O65">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="P65">
         <v>2.35</v>
       </c>
       <c r="Q65">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="R65">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S65">
         <v>1.22</v>
@@ -10925,13 +10925,13 @@
         <v>3.5</v>
       </c>
       <c r="U65">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V65">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W65">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
         <v>1.03</v>
@@ -10943,10 +10943,10 @@
         <v>5</v>
       </c>
       <c r="AA65">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AB65">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC65">
         <v>2.35</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AK65">
         <v>1.38</v>
@@ -11076,13 +11076,13 @@
         <v>4.8</v>
       </c>
       <c r="Q66">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R66">
         <v>2.51</v>
       </c>
       <c r="S66">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T66">
         <v>4</v>
@@ -11094,19 +11094,19 @@
         <v>1.65</v>
       </c>
       <c r="W66">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z66">
         <v>5.5</v>
       </c>
       <c r="AA66">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB66">
         <v>2.7</v>
@@ -11118,7 +11118,7 @@
         <v>1.7</v>
       </c>
       <c r="AE66">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AF66">
         <v>1.52</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="O92">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P92">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="Q92">
         <v>4</v>
@@ -15320,16 +15320,16 @@
         <v>2.13</v>
       </c>
       <c r="S92">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="T92">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U92">
         <v>2.73</v>
       </c>
       <c r="V92">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W92">
         <v>1.04</v>
@@ -15341,19 +15341,19 @@
         <v>1.26</v>
       </c>
       <c r="Z92">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA92">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB92">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC92">
         <v>3.3</v>
       </c>
       <c r="AD92">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE92">
         <v>1.07</v>
@@ -15631,19 +15631,19 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O94">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="P94">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="Q94">
         <v>1.89</v>
       </c>
       <c r="R94">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="S94">
         <v>1.22</v>
@@ -15667,28 +15667,28 @@
         <v>1.1</v>
       </c>
       <c r="Z94">
-        <v>5</v>
+        <v>5.23</v>
       </c>
       <c r="AA94">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB94">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC94">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AD94">
         <v>1.56</v>
       </c>
       <c r="AE94">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF94">
         <v>1.6</v>
       </c>
       <c r="AG94">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AK94">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15797,13 +15797,13 @@
         <v>2.95</v>
       </c>
       <c r="O95">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P95">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q95">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="R95">
         <v>2.3</v>
@@ -15815,7 +15815,7 @@
         <v>3.25</v>
       </c>
       <c r="U95">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V95">
         <v>1.44</v>
@@ -15824,13 +15824,13 @@
         <v>1.11</v>
       </c>
       <c r="X95">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
         <v>1.22</v>
       </c>
       <c r="Z95">
-        <v>4.07</v>
+        <v>3.78</v>
       </c>
       <c r="AA95">
         <v>1.64</v>
@@ -15839,10 +15839,10 @@
         <v>2.07</v>
       </c>
       <c r="AC95">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD95">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE95">
         <v>1.12</v>
@@ -15957,19 +15957,19 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="O96">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P96">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="Q96">
         <v>3.24</v>
       </c>
       <c r="R96">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S96">
         <v>1.37</v>
@@ -15990,10 +15990,10 @@
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z96">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA96">
         <v>1.94</v>
@@ -16002,19 +16002,19 @@
         <v>1.84</v>
       </c>
       <c r="AC96">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="AD96">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE96">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF96">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG96">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK96">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16123,13 +16123,13 @@
         <v>1.55</v>
       </c>
       <c r="O97">
-        <v>4.66</v>
+        <v>4.6</v>
       </c>
       <c r="P97">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="Q97">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="R97">
         <v>2.37</v>
@@ -16144,7 +16144,7 @@
         <v>2.12</v>
       </c>
       <c r="V97">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W97">
         <v>1.18</v>
@@ -16159,25 +16159,25 @@
         <v>5.2</v>
       </c>
       <c r="AA97">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AB97">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AC97">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD97">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AE97">
         <v>1.28</v>
       </c>
       <c r="AF97">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG97">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16286,10 +16286,10 @@
         <v>2.96</v>
       </c>
       <c r="O98">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="P98">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q98">
         <v>3.12</v>
@@ -16298,16 +16298,16 @@
         <v>2.29</v>
       </c>
       <c r="S98">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T98">
         <v>3.8</v>
       </c>
       <c r="U98">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="V98">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W98">
         <v>1.14</v>
@@ -16319,7 +16319,7 @@
         <v>1.18</v>
       </c>
       <c r="Z98">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA98">
         <v>1.54</v>
@@ -16334,13 +16334,13 @@
         <v>1.6</v>
       </c>
       <c r="AE98">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF98">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG98">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK98">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16449,10 +16449,10 @@
         <v>1.71</v>
       </c>
       <c r="O99">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="P99">
-        <v>4.81</v>
+        <v>4.5</v>
       </c>
       <c r="Q99">
         <v>2.31</v>
@@ -16461,43 +16461,43 @@
         <v>2.3</v>
       </c>
       <c r="S99">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T99">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U99">
         <v>2.46</v>
       </c>
       <c r="V99">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W99">
         <v>1.11</v>
       </c>
       <c r="X99">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z99">
         <v>4.2</v>
       </c>
       <c r="AA99">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AB99">
         <v>2.27</v>
       </c>
       <c r="AC99">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD99">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE99">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF99">
         <v>1.66</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK99">
         <v>2.1</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>4.6</v>
+        <v>2.46</v>
       </c>
       <c r="O100">
-        <v>4.35</v>
+        <v>3.55</v>
       </c>
       <c r="P100">
-        <v>1.57</v>
+        <v>2.72</v>
       </c>
       <c r="Q100">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="R100">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S100">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T100">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U100">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V100">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="W100">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z100">
-        <v>5.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA100">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AB100">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC100">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="AD100">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AE100">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF100">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG100">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK100">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.47</v>
+        <v>4.6</v>
       </c>
       <c r="O101">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P101">
-        <v>2.72</v>
+        <v>1.54</v>
       </c>
       <c r="Q101">
-        <v>2.71</v>
+        <v>4</v>
       </c>
       <c r="R101">
+        <v>2.6</v>
+      </c>
+      <c r="S101">
+        <v>1.22</v>
+      </c>
+      <c r="T101">
+        <v>4.05</v>
+      </c>
+      <c r="U101">
         <v>2.19</v>
       </c>
-      <c r="S101">
-        <v>1.33</v>
-      </c>
-      <c r="T101">
-        <v>3.3</v>
-      </c>
-      <c r="U101">
-        <v>2.34</v>
-      </c>
       <c r="V101">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="W101">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z101">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA101">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AB101">
+        <v>2.6</v>
+      </c>
+      <c r="AC101">
         <v>2.15</v>
       </c>
-      <c r="AC101">
-        <v>2.7</v>
-      </c>
       <c r="AD101">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AE101">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AF101">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG101">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17433,10 +17433,10 @@
         <v>4.75</v>
       </c>
       <c r="Q105">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R105">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S105">
         <v>1.25</v>
@@ -17448,19 +17448,19 @@
         <v>2.25</v>
       </c>
       <c r="V105">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W105">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z105">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA105">
         <v>1.56</v>
@@ -17472,7 +17472,7 @@
         <v>2.48</v>
       </c>
       <c r="AD105">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE105">
         <v>1.17</v>
@@ -17497,7 +17497,7 @@
         <v>1.16</v>
       </c>
       <c r="AK105">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="O122">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P122">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q122">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="R122">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="S122">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T122">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="U122">
+        <v>2.9</v>
+      </c>
+      <c r="V122">
+        <v>1.35</v>
+      </c>
+      <c r="W122">
+        <v>1.03</v>
+      </c>
+      <c r="X122">
+        <v>1.03</v>
+      </c>
+      <c r="Y122">
+        <v>1.38</v>
+      </c>
+      <c r="Z122">
         <v>2.88</v>
       </c>
-      <c r="V122">
-        <v>1.38</v>
-      </c>
-      <c r="W122">
-        <v>1.05</v>
-      </c>
-      <c r="X122">
-        <v>1.06</v>
-      </c>
-      <c r="Y122">
-        <v>1.3</v>
-      </c>
-      <c r="Z122">
-        <v>3.25</v>
-      </c>
       <c r="AA122">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB122">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC122">
-        <v>3.55</v>
+        <v>3.83</v>
       </c>
       <c r="AD122">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE122">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF122">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG122">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK122">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,65 +20358,65 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O123">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P123">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q123">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R123">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S123">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T123">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="U123">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="V123">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W123">
+        <v>1.04</v>
+      </c>
+      <c r="X123">
         <v>1.03</v>
       </c>
-      <c r="X123">
-        <v>1.06</v>
-      </c>
       <c r="Y123">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z123">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA123">
+        <v>1.88</v>
+      </c>
+      <c r="AB123">
+        <v>1.88</v>
+      </c>
+      <c r="AC123">
+        <v>3.2</v>
+      </c>
+      <c r="AD123">
+        <v>1.33</v>
+      </c>
+      <c r="AE123">
+        <v>1.07</v>
+      </c>
+      <c r="AF123">
+        <v>1.72</v>
+      </c>
+      <c r="AG123">
         <v>1.95</v>
       </c>
-      <c r="AB123">
-        <v>1.75</v>
-      </c>
-      <c r="AC123">
-        <v>3.6</v>
-      </c>
-      <c r="AD123">
-        <v>1.28</v>
-      </c>
-      <c r="AE123">
-        <v>1.09</v>
-      </c>
-      <c r="AF123">
-        <v>1.83</v>
-      </c>
-      <c r="AG123">
-        <v>1.85</v>
-      </c>
       <c r="AH123" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK123">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="O124">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P124">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q124">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="R124">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="S124">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T124">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U124">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V124">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W124">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X124">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y124">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z124">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AA124">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB124">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC124">
-        <v>3.83</v>
+        <v>3.55</v>
       </c>
       <c r="AD124">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE124">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF124">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG124">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK124">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="O125">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P125">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q125">
-        <v>3.21</v>
+        <v>2.5</v>
       </c>
       <c r="R125">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S125">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T125">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="U125">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V125">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y125">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z125">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="AA125">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB125">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC125">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD125">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE125">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF125">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG125">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK125">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="O126">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P126">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="Q126">
-        <v>2.4</v>
+        <v>3.21</v>
       </c>
       <c r="R126">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S126">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T126">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="U126">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="V126">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W126">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
         <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z126">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="AA126">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AB126">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AC126">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD126">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE126">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF126">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG126">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK126">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,22 +22314,22 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="O135">
         <v>3.2</v>
       </c>
       <c r="P135">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="Q135">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="R135">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S135">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T135">
         <v>2.75</v>
@@ -22338,40 +22338,40 @@
         <v>2.95</v>
       </c>
       <c r="V135">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W135">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y135">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z135">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="AA135">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB135">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="AC135">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD135">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE135">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF135">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG135">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK135">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,22 +22477,22 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="O136">
         <v>3.2</v>
       </c>
       <c r="P136">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q136">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="R136">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S136">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T136">
         <v>2.75</v>
@@ -22501,40 +22501,40 @@
         <v>2.95</v>
       </c>
       <c r="V136">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W136">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X136">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z136">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="AA136">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AB136">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AC136">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD136">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG136">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK136">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.35</v>
+        <v>1.2</v>
       </c>
       <c r="O139">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="P139">
-        <v>2.65</v>
+        <v>11</v>
       </c>
       <c r="Q139">
-        <v>2.88</v>
+        <v>1.55</v>
       </c>
       <c r="R139">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="S139">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="T139">
-        <v>2.99</v>
+        <v>4.2</v>
       </c>
       <c r="U139">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="V139">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="W139">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X139">
         <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="Z139">
-        <v>3.62</v>
+        <v>6.7</v>
       </c>
       <c r="AA139">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="AB139">
-        <v>2.06</v>
+        <v>3.12</v>
       </c>
       <c r="AC139">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="AD139">
-        <v>1.41</v>
+        <v>1.89</v>
       </c>
       <c r="AE139">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AF139">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AG139">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK139">
-        <v>1.53</v>
+        <v>4.25</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>1.2</v>
+        <v>2.35</v>
       </c>
       <c r="O140">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="P140">
-        <v>11</v>
+        <v>2.65</v>
       </c>
       <c r="Q140">
-        <v>1.55</v>
+        <v>2.88</v>
       </c>
       <c r="R140">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="S140">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="T140">
-        <v>4.2</v>
+        <v>2.99</v>
       </c>
       <c r="U140">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="V140">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="W140">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X140">
         <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="Z140">
-        <v>6.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA140">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="AB140">
-        <v>3.12</v>
+        <v>2.06</v>
       </c>
       <c r="AC140">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
       <c r="AD140">
-        <v>1.89</v>
+        <v>1.41</v>
       </c>
       <c r="AE140">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AF140">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AG140">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK140">
-        <v>4.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -25248,19 +25248,19 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="O153">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P153">
         <v>2.25</v>
       </c>
       <c r="Q153">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="R153">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S153">
         <v>1.23</v>
@@ -25269,28 +25269,28 @@
         <v>3.42</v>
       </c>
       <c r="U153">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="V153">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W153">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X153">
         <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z153">
-        <v>5.09</v>
+        <v>4.95</v>
       </c>
       <c r="AA153">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AB153">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC153">
         <v>2.3</v>
@@ -25299,7 +25299,7 @@
         <v>1.59</v>
       </c>
       <c r="AE153">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF153">
         <v>1.44</v>
@@ -25321,7 +25321,7 @@
         <v>1.51</v>
       </c>
       <c r="AK153">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25903,31 +25903,31 @@
         <v>2.25</v>
       </c>
       <c r="O157">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="P157">
         <v>2.45</v>
       </c>
       <c r="Q157">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="R157">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S157">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T157">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U157">
         <v>2.2</v>
       </c>
       <c r="V157">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W157">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X157">
         <v>1.03</v>
@@ -25936,28 +25936,28 @@
         <v>1.16</v>
       </c>
       <c r="Z157">
-        <v>5.37</v>
+        <v>5.19</v>
       </c>
       <c r="AA157">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB157">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AC157">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AD157">
         <v>1.65</v>
       </c>
       <c r="AE157">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF157">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AG157">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.25</v>
       </c>
       <c r="AK157">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26063,19 +26063,19 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O158">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P158">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="Q158">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R158">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S158">
         <v>1.15</v>
@@ -26096,28 +26096,28 @@
         <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z158">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA158">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB158">
         <v>3.04</v>
       </c>
       <c r="AC158">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD158">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AE158">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AF158">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG158">
         <v>3.14</v>
@@ -26392,25 +26392,25 @@
         <v>2.7</v>
       </c>
       <c r="O160">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P160">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q160">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="R160">
         <v>1.99</v>
       </c>
       <c r="S160">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T160">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="U160">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="V160">
         <v>1.33</v>
@@ -26428,25 +26428,25 @@
         <v>2.85</v>
       </c>
       <c r="AA160">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB160">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AC160">
         <v>3.54</v>
       </c>
       <c r="AD160">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE160">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF160">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG160">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK160">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -30301,65 +30301,65 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O184">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="P184">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="Q184">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="R184">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="S184">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="T184">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="U184">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V184">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="W184">
         <v>1.02</v>
       </c>
       <c r="X184">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y184">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="Z184">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="AA184">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AB184">
+        <v>1.45</v>
+      </c>
+      <c r="AC184">
+        <v>5.1</v>
+      </c>
+      <c r="AD184">
+        <v>1.1</v>
+      </c>
+      <c r="AE184">
+        <v>1.04</v>
+      </c>
+      <c r="AF184">
+        <v>2.08</v>
+      </c>
+      <c r="AG184">
         <v>1.63</v>
       </c>
-      <c r="AC184">
-        <v>3.96</v>
-      </c>
-      <c r="AD184">
-        <v>1.17</v>
-      </c>
-      <c r="AE184">
-        <v>1.02</v>
-      </c>
-      <c r="AF184">
-        <v>1.92</v>
-      </c>
-      <c r="AG184">
-        <v>1.79</v>
-      </c>
       <c r="AH184" t="inlineStr">
         <is>
           <t>[]</t>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK184">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -32094,80 +32094,80 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O195">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P195">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q195">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="R195">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S195">
         <v>1.42</v>
       </c>
       <c r="T195">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U195">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="V195">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W195">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X195">
         <v>1.04</v>
       </c>
       <c r="Y195">
+        <v>1.35</v>
+      </c>
+      <c r="Z195">
+        <v>2.94</v>
+      </c>
+      <c r="AA195">
+        <v>2.01</v>
+      </c>
+      <c r="AB195">
+        <v>1.77</v>
+      </c>
+      <c r="AC195">
+        <v>3.52</v>
+      </c>
+      <c r="AD195">
+        <v>1.23</v>
+      </c>
+      <c r="AE195">
+        <v>1.05</v>
+      </c>
+      <c r="AF195">
+        <v>1.86</v>
+      </c>
+      <c r="AG195">
+        <v>1.81</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ195">
         <v>1.3</v>
       </c>
-      <c r="Z195">
-        <v>3.25</v>
-      </c>
-      <c r="AA195">
-        <v>1.96</v>
-      </c>
-      <c r="AB195">
-        <v>1.72</v>
-      </c>
-      <c r="AC195">
-        <v>3.6</v>
-      </c>
-      <c r="AD195">
-        <v>1.25</v>
-      </c>
-      <c r="AE195">
-        <v>1.06</v>
-      </c>
-      <c r="AF195">
-        <v>1.81</v>
-      </c>
-      <c r="AG195">
-        <v>1.87</v>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ195">
-        <v>1.25</v>
-      </c>
       <c r="AK195">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -33727,16 +33727,16 @@
         <v>2.9</v>
       </c>
       <c r="O205">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P205">
         <v>2.15</v>
       </c>
       <c r="Q205">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="R205">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S205">
         <v>1.34</v>
@@ -33751,28 +33751,28 @@
         <v>1.38</v>
       </c>
       <c r="W205">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X205">
         <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z205">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="AA205">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AB205">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AC205">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD205">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE205">
         <v>1.09</v>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK205">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33887,19 +33887,19 @@
         </is>
       </c>
       <c r="N206">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="O206">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P206">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q206">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R206">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="S206">
         <v>1.33</v>
@@ -33908,10 +33908,10 @@
         <v>3</v>
       </c>
       <c r="U206">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V206">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W206">
         <v>1.05</v>
@@ -33923,25 +33923,25 @@
         <v>1.24</v>
       </c>
       <c r="Z206">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AA206">
+        <v>1.83</v>
+      </c>
+      <c r="AB206">
         <v>1.8</v>
       </c>
-      <c r="AB206">
-        <v>1.83</v>
-      </c>
       <c r="AC206">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AD206">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE206">
         <v>1.07</v>
       </c>
       <c r="AF206">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG206">
         <v>2</v>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AK206">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34056,7 +34056,7 @@
         <v>3.2</v>
       </c>
       <c r="P207">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34385,56 +34385,56 @@
         <v>3.26</v>
       </c>
       <c r="Q209">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R209">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S209">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T209">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U209">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V209">
         <v>1.36</v>
       </c>
       <c r="W209">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X209">
         <v>1</v>
       </c>
       <c r="Y209">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z209">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA209">
+        <v>2</v>
+      </c>
+      <c r="AB209">
+        <v>1.77</v>
+      </c>
+      <c r="AC209">
+        <v>3.34</v>
+      </c>
+      <c r="AD209">
+        <v>1.24</v>
+      </c>
+      <c r="AE209">
+        <v>1.04</v>
+      </c>
+      <c r="AF209">
+        <v>1.76</v>
+      </c>
+      <c r="AG209">
         <v>1.96</v>
       </c>
-      <c r="AB209">
-        <v>1.8</v>
-      </c>
-      <c r="AC209">
-        <v>3.28</v>
-      </c>
-      <c r="AD209">
-        <v>1.25</v>
-      </c>
-      <c r="AE209">
-        <v>1.05</v>
-      </c>
-      <c r="AF209">
-        <v>1.74</v>
-      </c>
-      <c r="AG209">
-        <v>1.95</v>
-      </c>
       <c r="AH209" t="inlineStr">
         <is>
           <t>[]</t>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK209">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="O212">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P212">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O217">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P217">
-        <v>3.95</v>
+        <v>3.36</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -36006,25 +36006,25 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="O219">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="P219">
         <v>6.4</v>
       </c>
       <c r="Q219">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R219">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="S219">
         <v>1.22</v>
       </c>
       <c r="T219">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U219">
         <v>2.15</v>
@@ -36042,10 +36042,10 @@
         <v>1.1</v>
       </c>
       <c r="Z219">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA219">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AB219">
         <v>2.59</v>
@@ -36060,7 +36060,7 @@
         <v>1.22</v>
       </c>
       <c r="AF219">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG219">
         <v>2</v>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK219">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36169,16 +36169,16 @@
         </is>
       </c>
       <c r="N220">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="O220">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P220">
         <v>2.9</v>
       </c>
       <c r="Q220">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R220">
         <v>2.12</v>
@@ -36193,25 +36193,25 @@
         <v>2.56</v>
       </c>
       <c r="V220">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W220">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X220">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y220">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z220">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="AA220">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB220">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC220">
         <v>2.78</v>
@@ -36242,7 +36242,7 @@
         <v>1.24</v>
       </c>
       <c r="AK220">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36332,22 +36332,22 @@
         </is>
       </c>
       <c r="N221">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O221">
         <v>3.18</v>
       </c>
       <c r="P221">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="Q221">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="R221">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="S221">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="T221">
         <v>2.53</v>
@@ -36365,28 +36365,28 @@
         <v>1.05</v>
       </c>
       <c r="Y221">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z221">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA221">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB221">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC221">
         <v>4.1</v>
       </c>
       <c r="AD221">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE221">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF221">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AG221">
         <v>1.83</v>
@@ -36405,7 +36405,7 @@
         <v>1.38</v>
       </c>
       <c r="AK221">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36498,46 +36498,46 @@
         <v>2.21</v>
       </c>
       <c r="O222">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P222">
         <v>3.1</v>
       </c>
       <c r="Q222">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R222">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="S222">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T222">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U222">
         <v>3</v>
       </c>
       <c r="V222">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W222">
         <v>1.05</v>
       </c>
       <c r="X222">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y222">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z222">
         <v>3.22</v>
       </c>
       <c r="AA222">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AB222">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC222">
         <v>3.44</v>
@@ -36549,10 +36549,10 @@
         <v>1.04</v>
       </c>
       <c r="AF222">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG222">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK222">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36658,19 +36658,19 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="O223">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P223">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q223">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="R223">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S223">
         <v>1.35</v>
@@ -36679,43 +36679,43 @@
         <v>3.1</v>
       </c>
       <c r="U223">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="V223">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W223">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X223">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z223">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA223">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB223">
         <v>1.96</v>
       </c>
       <c r="AC223">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AD223">
         <v>1.36</v>
       </c>
       <c r="AE223">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF223">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG223">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK223">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36824,61 +36824,61 @@
         <v>1.31</v>
       </c>
       <c r="O224">
-        <v>5.45</v>
+        <v>5.05</v>
       </c>
       <c r="P224">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="Q224">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R224">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="S224">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T224">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="U224">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="V224">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W224">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X224">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y224">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z224">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA224">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB224">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AC224">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AD224">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AE224">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF224">
         <v>1.8</v>
       </c>
       <c r="AG224">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK224">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36984,31 +36984,31 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="O225">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="P225">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="Q225">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R225">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="S225">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T225">
         <v>4.5</v>
       </c>
       <c r="U225">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V225">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W225">
         <v>1.17</v>
@@ -37017,22 +37017,22 @@
         <v>1.01</v>
       </c>
       <c r="Y225">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z225">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="AA225">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB225">
         <v>2.87</v>
       </c>
       <c r="AC225">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AD225">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AE225">
         <v>1.35</v>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK225">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37150,10 +37150,10 @@
         <v>2.14</v>
       </c>
       <c r="O226">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P226">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q226">
         <v>2.74</v>
@@ -37162,16 +37162,16 @@
         <v>2.07</v>
       </c>
       <c r="S226">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T226">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="U226">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="V226">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W226">
         <v>1.04</v>
@@ -37183,16 +37183,16 @@
         <v>1.34</v>
       </c>
       <c r="Z226">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AA226">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB226">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC226">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD226">
         <v>1.25</v>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK226">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37310,58 +37310,58 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O227">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="P227">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q227">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="R227">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="S227">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T227">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U227">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="V227">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W227">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X227">
         <v>1.04</v>
       </c>
       <c r="Y227">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z227">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="AA227">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AB227">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC227">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="AD227">
         <v>1.18</v>
       </c>
       <c r="AE227">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF227">
         <v>1.99</v>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK227">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37799,31 +37799,31 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="O230">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P230">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="Q230">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="R230">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="S230">
+        <v>1.38</v>
+      </c>
+      <c r="T230">
+        <v>2.81</v>
+      </c>
+      <c r="U230">
+        <v>2.88</v>
+      </c>
+      <c r="V230">
         <v>1.39</v>
-      </c>
-      <c r="T230">
-        <v>2.77</v>
-      </c>
-      <c r="U230">
-        <v>2.81</v>
-      </c>
-      <c r="V230">
-        <v>1.38</v>
       </c>
       <c r="W230">
         <v>1.05</v>
@@ -37832,31 +37832,31 @@
         <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z230">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AA230">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AB230">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AC230">
-        <v>3.18</v>
+        <v>3.45</v>
       </c>
       <c r="AD230">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE230">
         <v>1.07</v>
       </c>
       <c r="AF230">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG230">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK230">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37965,49 +37965,49 @@
         <v>2.3</v>
       </c>
       <c r="O231">
+        <v>2.87</v>
+      </c>
+      <c r="P231">
+        <v>2.9</v>
+      </c>
+      <c r="Q231">
         <v>3</v>
       </c>
-      <c r="P231">
-        <v>2.95</v>
-      </c>
-      <c r="Q231">
-        <v>3.08</v>
-      </c>
       <c r="R231">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S231">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="T231">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="U231">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V231">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W231">
         <v>1.01</v>
       </c>
       <c r="X231">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y231">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Z231">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="AA231">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AB231">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC231">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD231">
         <v>1.16</v>
@@ -38016,10 +38016,10 @@
         <v>1.01</v>
       </c>
       <c r="AF231">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AG231">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>3.4</v>
       </c>
       <c r="R241">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S241">
         <v>1.33</v>
@@ -39613,10 +39613,10 @@
         <v>2.84</v>
       </c>
       <c r="U241">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V241">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W241">
         <v>1.08</v>
@@ -39625,28 +39625,28 @@
         <v>1.01</v>
       </c>
       <c r="Y241">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z241">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA241">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AB241">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC241">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD241">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE241">
         <v>1.07</v>
       </c>
       <c r="AF241">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG241">
         <v>2.02</v>
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AK241">
         <v>1.4</v>
@@ -42689,25 +42689,25 @@
         </is>
       </c>
       <c r="N260">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O260">
         <v>3.4</v>
       </c>
       <c r="P260">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Q260">
         <v>4.8</v>
       </c>
       <c r="R260">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S260">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T260">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U260">
         <v>2.77</v>
@@ -42716,7 +42716,7 @@
         <v>1.38</v>
       </c>
       <c r="W260">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X260">
         <v>1.02</v>
@@ -42728,7 +42728,7 @@
         <v>3.08</v>
       </c>
       <c r="AA260">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB260">
         <v>1.85</v>
@@ -42737,16 +42737,16 @@
         <v>3.5</v>
       </c>
       <c r="AD260">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE260">
         <v>1.1</v>
       </c>
       <c r="AF260">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG260">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>1.23</v>
       </c>
       <c r="AK260">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42852,34 +42852,34 @@
         </is>
       </c>
       <c r="N261">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="O261">
         <v>4.8</v>
       </c>
       <c r="P261">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q261">
         <v>1.85</v>
       </c>
       <c r="R261">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="S261">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T261">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U261">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="V261">
         <v>1.51</v>
       </c>
       <c r="W261">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X261">
         <v>1.04</v>
@@ -42888,7 +42888,7 @@
         <v>1.2</v>
       </c>
       <c r="Z261">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA261">
         <v>1.66</v>
@@ -42906,7 +42906,7 @@
         <v>1.14</v>
       </c>
       <c r="AF261">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG261">
         <v>1.87</v>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AK261">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43015,31 +43015,31 @@
         </is>
       </c>
       <c r="N262">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="O262">
         <v>3.45</v>
       </c>
       <c r="P262">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Q262">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="R262">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S262">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T262">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U262">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="V262">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W262">
         <v>1.08</v>
@@ -43048,31 +43048,31 @@
         <v>1.02</v>
       </c>
       <c r="Y262">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z262">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA262">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB262">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC262">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AD262">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE262">
         <v>1.09</v>
       </c>
       <c r="AF262">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG262">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AK262">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43504,64 +43504,64 @@
         </is>
       </c>
       <c r="N265">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="O265">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="P265">
+        <v>3.26</v>
+      </c>
+      <c r="Q265">
+        <v>2.92</v>
+      </c>
+      <c r="R265">
+        <v>2.05</v>
+      </c>
+      <c r="S265">
+        <v>1.51</v>
+      </c>
+      <c r="T265">
+        <v>2.39</v>
+      </c>
+      <c r="U265">
         <v>3.4</v>
       </c>
-      <c r="Q265">
-        <v>2.73</v>
-      </c>
-      <c r="R265">
+      <c r="V265">
+        <v>1.27</v>
+      </c>
+      <c r="W265">
+        <v>1.01</v>
+      </c>
+      <c r="X265">
+        <v>1.05</v>
+      </c>
+      <c r="Y265">
+        <v>1.42</v>
+      </c>
+      <c r="Z265">
+        <v>2.51</v>
+      </c>
+      <c r="AA265">
+        <v>2.3</v>
+      </c>
+      <c r="AB265">
+        <v>1.55</v>
+      </c>
+      <c r="AC265">
+        <v>4.33</v>
+      </c>
+      <c r="AD265">
+        <v>1.15</v>
+      </c>
+      <c r="AE265">
+        <v>1.01</v>
+      </c>
+      <c r="AF265">
         <v>2.01</v>
       </c>
-      <c r="S265">
-        <v>1.45</v>
-      </c>
-      <c r="T265">
-        <v>2.56</v>
-      </c>
-      <c r="U265">
-        <v>3.15</v>
-      </c>
-      <c r="V265">
-        <v>1.31</v>
-      </c>
-      <c r="W265">
-        <v>1.03</v>
-      </c>
-      <c r="X265">
-        <v>1.03</v>
-      </c>
-      <c r="Y265">
-        <v>1.35</v>
-      </c>
-      <c r="Z265">
-        <v>2.76</v>
-      </c>
-      <c r="AA265">
-        <v>2.19</v>
-      </c>
-      <c r="AB265">
-        <v>1.65</v>
-      </c>
-      <c r="AC265">
-        <v>3.82</v>
-      </c>
-      <c r="AD265">
-        <v>1.19</v>
-      </c>
-      <c r="AE265">
-        <v>1.03</v>
-      </c>
-      <c r="AF265">
-        <v>1.89</v>
-      </c>
       <c r="AG265">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK265">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43830,25 +43830,25 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q267">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="R267">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S267">
         <v>1.33</v>
       </c>
       <c r="T267">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U267">
         <v>2.75</v>
@@ -43857,34 +43857,34 @@
         <v>1.4</v>
       </c>
       <c r="W267">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X267">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y267">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z267">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA267">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AB267">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AC267">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD267">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE267">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF267">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG267">
         <v>1.96</v>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK267">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>3.51</v>
+        <v>2.83</v>
       </c>
       <c r="O269">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P269">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -45134,31 +45134,31 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O275">
-        <v>6.75</v>
+        <v>6.2</v>
       </c>
       <c r="P275">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q275">
         <v>1.6</v>
       </c>
       <c r="R275">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="S275">
         <v>1.29</v>
       </c>
       <c r="T275">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U275">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V275">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W275">
         <v>1.1</v>
@@ -45167,22 +45167,22 @@
         <v>1.04</v>
       </c>
       <c r="Y275">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z275">
         <v>4.33</v>
       </c>
       <c r="AA275">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB275">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="AC275">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD275">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE275">
         <v>1.14</v>
@@ -45191,7 +45191,7 @@
         <v>2.3</v>
       </c>
       <c r="AG275">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>1.14</v>
       </c>
       <c r="AK275">
-        <v>4.2</v>
+        <v>4.52</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="O276">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="P276">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="O277">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P277">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45623,7 +45623,7 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O278">
         <v>3.1</v>
@@ -45638,16 +45638,16 @@
         <v>1.97</v>
       </c>
       <c r="S278">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T278">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="U278">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="V278">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W278">
         <v>1.03</v>
@@ -45668,19 +45668,19 @@
         <v>1.65</v>
       </c>
       <c r="AC278">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD278">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE278">
         <v>1.04</v>
       </c>
       <c r="AF278">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG278">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK278">
         <v>1.47</v>
@@ -45786,31 +45786,31 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="O279">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P279">
         <v>2.4</v>
       </c>
       <c r="Q279">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="R279">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S279">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T279">
         <v>2.44</v>
       </c>
       <c r="U279">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="V279">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W279">
         <v>1.02</v>
@@ -45822,28 +45822,28 @@
         <v>1.37</v>
       </c>
       <c r="Z279">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AA279">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AB279">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC279">
-        <v>3.94</v>
+        <v>4.73</v>
       </c>
       <c r="AD279">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE279">
         <v>1.03</v>
       </c>
       <c r="AF279">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AG279">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK279">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45949,25 +45949,25 @@
         </is>
       </c>
       <c r="N280">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="O280">
         <v>3.1</v>
       </c>
       <c r="P280">
-        <v>3.7</v>
+        <v>4.04</v>
       </c>
       <c r="Q280">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="R280">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="S280">
         <v>1.5</v>
       </c>
       <c r="T280">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U280">
         <v>3.34</v>
@@ -45976,31 +45976,31 @@
         <v>1.28</v>
       </c>
       <c r="W280">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X280">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y280">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="Z280">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="AA280">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AB280">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AC280">
         <v>4.25</v>
       </c>
       <c r="AD280">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE280">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF280">
         <v>2.1</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,16 +47253,16 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O288">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P288">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q288">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="R288">
         <v>1.75</v>
@@ -47271,46 +47271,46 @@
         <v>1.7</v>
       </c>
       <c r="T288">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="U288">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="V288">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W288">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X288">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y288">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="Z288">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="AA288">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="AB288">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC288">
-        <v>6.2</v>
+        <v>6.95</v>
       </c>
       <c r="AD288">
         <v>1.06</v>
       </c>
       <c r="AE288">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF288">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG288">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK288">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,16 +47416,16 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O289">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P289">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q289">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="R289">
         <v>1.75</v>
@@ -47434,46 +47434,46 @@
         <v>1.7</v>
       </c>
       <c r="T289">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="U289">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="V289">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W289">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X289">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y289">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="Z289">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AA289">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="AB289">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC289">
-        <v>6.95</v>
+        <v>6.2</v>
       </c>
       <c r="AD289">
         <v>1.06</v>
       </c>
       <c r="AE289">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF289">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG289">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK289">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -48394,22 +48394,22 @@
         </is>
       </c>
       <c r="N295">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="O295">
         <v>4.4</v>
       </c>
       <c r="P295">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Q295">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R295">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="S295">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T295">
         <v>4</v>
@@ -48421,7 +48421,7 @@
         <v>1.73</v>
       </c>
       <c r="W295">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X295">
         <v>1.01</v>
@@ -48430,22 +48430,22 @@
         <v>1.13</v>
       </c>
       <c r="Z295">
-        <v>6.2</v>
+        <v>5.95</v>
       </c>
       <c r="AA295">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB295">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AC295">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AD295">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE295">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF295">
         <v>1.43</v>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.17</v>
+        <v>2.16</v>
       </c>
       <c r="AK295">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48720,64 +48720,64 @@
         </is>
       </c>
       <c r="N297">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O297">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P297">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="Q297">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="R297">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S297">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T297">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U297">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V297">
         <v>1.4</v>
       </c>
       <c r="W297">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X297">
         <v>1.01</v>
       </c>
       <c r="Y297">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z297">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA297">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB297">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC297">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="AD297">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE297">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF297">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG297">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK297">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AL297">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O28">
         <v>3.5</v>
@@ -4882,7 +4882,7 @@
         <v>3.5</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R28">
         <v>2.27</v>
@@ -4906,19 +4906,19 @@
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
         <v>4.1</v>
       </c>
       <c r="AA28">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
         <v>2.07</v>
       </c>
       <c r="AC28">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AD28">
         <v>1.4</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
         <v>3.1</v>
@@ -5045,28 +5045,28 @@
         <v>2.45</v>
       </c>
       <c r="Q29">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
         <v>2.05</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
         <v>2.88</v>
       </c>
       <c r="U29">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="V29">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
+        <v>1.06</v>
+      </c>
+      <c r="X29">
         <v>1.02</v>
-      </c>
-      <c r="X29">
-        <v>1</v>
       </c>
       <c r="Y29">
         <v>1.28</v>
@@ -5078,22 +5078,22 @@
         <v>2.03</v>
       </c>
       <c r="AB29">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AC29">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="AD29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG29">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AK29">
         <v>1.43</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.57</v>
       </c>
       <c r="P41">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>3.77</v>
       </c>
       <c r="R41">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T41">
         <v>4</v>
       </c>
       <c r="U41">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="V41">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z41">
         <v>5</v>
       </c>
       <c r="AA41">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB41">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AC41">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AD41">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE41">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF41">
         <v>1.4</v>
       </c>
       <c r="AG41">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK41">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
-        <v>3.57</v>
+        <v>3.65</v>
       </c>
       <c r="P42">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q42">
-        <v>3.77</v>
+        <v>2.46</v>
       </c>
       <c r="R42">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
         <v>1.22</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="V42">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
         <v>5</v>
       </c>
       <c r="AA42">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB42">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="AC42">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AD42">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AE42">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF42">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,28 +7318,28 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O43">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P43">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q43">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U43">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V43">
         <v>1.6</v>
@@ -7348,7 +7348,7 @@
         <v>1.13</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
         <v>1.16</v>
@@ -7357,25 +7357,25 @@
         <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AB43">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="AC43">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AD43">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE43">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="O50">
-        <v>3.28</v>
+        <v>3.61</v>
       </c>
       <c r="P50">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="Q50">
+        <v>2.25</v>
+      </c>
+      <c r="R50">
+        <v>2.25</v>
+      </c>
+      <c r="S50">
+        <v>1.37</v>
+      </c>
+      <c r="T50">
+        <v>2.78</v>
+      </c>
+      <c r="U50">
+        <v>2.65</v>
+      </c>
+      <c r="V50">
+        <v>1.44</v>
+      </c>
+      <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
+        <v>1.02</v>
+      </c>
+      <c r="Y50">
+        <v>1.22</v>
+      </c>
+      <c r="Z50">
+        <v>3.82</v>
+      </c>
+      <c r="AA50">
+        <v>1.82</v>
+      </c>
+      <c r="AB50">
+        <v>1.95</v>
+      </c>
+      <c r="AC50">
         <v>2.89</v>
       </c>
-      <c r="R50">
-        <v>2.03</v>
-      </c>
-      <c r="S50">
-        <v>1.4</v>
-      </c>
-      <c r="T50">
-        <v>2.81</v>
-      </c>
-      <c r="U50">
-        <v>2.99</v>
-      </c>
-      <c r="V50">
-        <v>1.35</v>
-      </c>
-      <c r="W50">
-        <v>1.02</v>
-      </c>
-      <c r="X50">
-        <v>1.06</v>
-      </c>
-      <c r="Y50">
-        <v>1.32</v>
-      </c>
-      <c r="Z50">
-        <v>3.2</v>
-      </c>
-      <c r="AA50">
-        <v>2.1</v>
-      </c>
-      <c r="AB50">
-        <v>1.69</v>
-      </c>
-      <c r="AC50">
-        <v>3.54</v>
-      </c>
       <c r="AD50">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="O51">
-        <v>3.61</v>
+        <v>3.28</v>
       </c>
       <c r="P51">
-        <v>4.5</v>
+        <v>2.82</v>
       </c>
       <c r="Q51">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S51">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="U51">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z51">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="AA51">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AC51">
-        <v>2.89</v>
+        <v>3.54</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O114">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P114">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q114">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="R114">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S114">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T114">
         <v>2.82</v>
       </c>
       <c r="U114">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V114">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W114">
+        <v>1.04</v>
+      </c>
+      <c r="X114">
+        <v>1.02</v>
+      </c>
+      <c r="Y114">
+        <v>1.29</v>
+      </c>
+      <c r="Z114">
+        <v>3.25</v>
+      </c>
+      <c r="AA114">
+        <v>2.03</v>
+      </c>
+      <c r="AB114">
+        <v>1.76</v>
+      </c>
+      <c r="AC114">
+        <v>3.34</v>
+      </c>
+      <c r="AD114">
+        <v>1.25</v>
+      </c>
+      <c r="AE114">
         <v>1.06</v>
       </c>
-      <c r="X114">
-        <v>1.03</v>
-      </c>
-      <c r="Y114">
-        <v>1.24</v>
-      </c>
-      <c r="Z114">
-        <v>3.42</v>
-      </c>
-      <c r="AA114">
-        <v>1.85</v>
-      </c>
-      <c r="AB114">
-        <v>1.95</v>
-      </c>
-      <c r="AC114">
-        <v>2.92</v>
-      </c>
-      <c r="AD114">
-        <v>1.3</v>
-      </c>
-      <c r="AE114">
-        <v>1.07</v>
-      </c>
       <c r="AF114">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AG114">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AK114">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,49 +19054,49 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="O115">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P115">
-        <v>1.91</v>
+        <v>4.4</v>
       </c>
       <c r="Q115">
-        <v>4.4</v>
+        <v>2.25</v>
       </c>
       <c r="R115">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="S115">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T115">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="U115">
         <v>2.88</v>
       </c>
       <c r="V115">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W115">
         <v>1.04</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z115">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AA115">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB115">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC115">
         <v>3.34</v>
@@ -19108,10 +19108,10 @@
         <v>1.06</v>
       </c>
       <c r="AF115">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AG115">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AK115">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="O116">
         <v>3.4</v>
       </c>
       <c r="P116">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="Q116">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="R116">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="S116">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T116">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="U116">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V116">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W116">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X116">
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Z116">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="AA116">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AB116">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC116">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="AD116">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE116">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF116">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AG116">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AK116">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,80 +20195,80 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="O122">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P122">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q122">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="R122">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="S122">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T122">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="U122">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="V122">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W122">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X122">
         <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z122">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="AA122">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB122">
+        <v>1.66</v>
+      </c>
+      <c r="AC122">
+        <v>3.58</v>
+      </c>
+      <c r="AD122">
+        <v>1.21</v>
+      </c>
+      <c r="AE122">
+        <v>1.04</v>
+      </c>
+      <c r="AF122">
+        <v>1.83</v>
+      </c>
+      <c r="AG122">
         <v>1.88</v>
       </c>
-      <c r="AC122">
-        <v>3.2</v>
-      </c>
-      <c r="AD122">
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ122">
         <v>1.33</v>
       </c>
-      <c r="AE122">
-        <v>1.12</v>
-      </c>
-      <c r="AF122">
-        <v>1.72</v>
-      </c>
-      <c r="AG122">
-        <v>2</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>1.23</v>
-      </c>
       <c r="AK122">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="O123">
         <v>3.5</v>
       </c>
       <c r="P123">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q123">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R123">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T123">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="U123">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="V123">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W123">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X123">
         <v>1.06</v>
       </c>
       <c r="Y123">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z123">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA123">
         <v>1.95</v>
       </c>
       <c r="AB123">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC123">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AD123">
         <v>1.28</v>
       </c>
       <c r="AE123">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF123">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG123">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK123">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
+        <v>2.4</v>
+      </c>
+      <c r="O124">
+        <v>3.15</v>
+      </c>
+      <c r="P124">
         <v>2.6</v>
       </c>
-      <c r="O124">
-        <v>3.1</v>
-      </c>
-      <c r="P124">
-        <v>2.7</v>
-      </c>
       <c r="Q124">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="R124">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S124">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T124">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="U124">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="V124">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W124">
         <v>1.03</v>
       </c>
       <c r="X124">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z124">
-        <v>2.88</v>
+        <v>3.36</v>
       </c>
       <c r="AA124">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB124">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC124">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD124">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE124">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF124">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG124">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK124">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="O125">
         <v>3.5</v>
       </c>
       <c r="P125">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q125">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R125">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S125">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T125">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="U125">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="V125">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W125">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X125">
         <v>1.06</v>
       </c>
       <c r="Y125">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z125">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA125">
         <v>1.95</v>
       </c>
       <c r="AB125">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC125">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="AD125">
         <v>1.28</v>
       </c>
       <c r="AE125">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF125">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG125">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK125">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,65 +21010,65 @@
         </is>
       </c>
       <c r="N127">
+        <v>1.86</v>
+      </c>
+      <c r="O127">
+        <v>3.35</v>
+      </c>
+      <c r="P127">
+        <v>3.6</v>
+      </c>
+      <c r="Q127">
         <v>2.4</v>
       </c>
-      <c r="O127">
-        <v>3.15</v>
-      </c>
-      <c r="P127">
-        <v>2.6</v>
-      </c>
-      <c r="Q127">
-        <v>3.21</v>
-      </c>
       <c r="R127">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S127">
         <v>1.36</v>
       </c>
       <c r="T127">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="U127">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="V127">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W127">
+        <v>1.04</v>
+      </c>
+      <c r="X127">
         <v>1.03</v>
-      </c>
-      <c r="X127">
-        <v>1.01</v>
       </c>
       <c r="Y127">
         <v>1.27</v>
       </c>
       <c r="Z127">
-        <v>3.36</v>
+        <v>3.55</v>
       </c>
       <c r="AA127">
+        <v>1.9</v>
+      </c>
+      <c r="AB127">
+        <v>1.88</v>
+      </c>
+      <c r="AC127">
+        <v>3.2</v>
+      </c>
+      <c r="AD127">
+        <v>1.33</v>
+      </c>
+      <c r="AE127">
+        <v>1.12</v>
+      </c>
+      <c r="AF127">
+        <v>1.72</v>
+      </c>
+      <c r="AG127">
         <v>2</v>
       </c>
-      <c r="AB127">
-        <v>1.8</v>
-      </c>
-      <c r="AC127">
-        <v>3.34</v>
-      </c>
-      <c r="AD127">
-        <v>1.24</v>
-      </c>
-      <c r="AE127">
-        <v>1.06</v>
-      </c>
-      <c r="AF127">
-        <v>1.73</v>
-      </c>
-      <c r="AG127">
-        <v>1.98</v>
-      </c>
       <c r="AH127" t="inlineStr">
         <is>
           <t>[]</t>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK127">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.33</v>
+        <v>1.17</v>
       </c>
       <c r="O140">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="P140">
-        <v>2.7</v>
+        <v>9.6</v>
       </c>
       <c r="Q140">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="R140">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="S140">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="T140">
-        <v>2.99</v>
+        <v>4.4</v>
       </c>
       <c r="U140">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="V140">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="W140">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X140">
         <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="Z140">
-        <v>3.62</v>
+        <v>6.7</v>
       </c>
       <c r="AA140">
+        <v>1.4</v>
+      </c>
+      <c r="AB140">
+        <v>3.12</v>
+      </c>
+      <c r="AC140">
+        <v>1.93</v>
+      </c>
+      <c r="AD140">
+        <v>1.89</v>
+      </c>
+      <c r="AE140">
+        <v>1.36</v>
+      </c>
+      <c r="AF140">
         <v>1.77</v>
       </c>
-      <c r="AB140">
-        <v>2.01</v>
-      </c>
-      <c r="AC140">
-        <v>2.72</v>
-      </c>
-      <c r="AD140">
-        <v>1.41</v>
-      </c>
-      <c r="AE140">
-        <v>1.11</v>
-      </c>
-      <c r="AF140">
-        <v>1.58</v>
-      </c>
       <c r="AG140">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AK140">
-        <v>1.53</v>
+        <v>4.25</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.17</v>
+        <v>2.33</v>
       </c>
       <c r="O141">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="P141">
-        <v>9.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q141">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="R141">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="S141">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="T141">
-        <v>4.4</v>
+        <v>2.99</v>
       </c>
       <c r="U141">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="V141">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="W141">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="X141">
         <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="Z141">
-        <v>6.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA141">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AB141">
-        <v>3.12</v>
+        <v>2.01</v>
       </c>
       <c r="AC141">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
       <c r="AD141">
-        <v>1.89</v>
+        <v>1.41</v>
       </c>
       <c r="AE141">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF141">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AG141">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AK141">
-        <v>4.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="O144">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="P144">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q144">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="R144">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S144">
+        <v>1.36</v>
+      </c>
+      <c r="T144">
+        <v>2.63</v>
+      </c>
+      <c r="U144">
+        <v>2.86</v>
+      </c>
+      <c r="V144">
         <v>1.33</v>
       </c>
-      <c r="T144">
-        <v>3.04</v>
-      </c>
-      <c r="U144">
-        <v>2.62</v>
-      </c>
-      <c r="V144">
-        <v>1.43</v>
-      </c>
       <c r="W144">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X144">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y144">
+        <v>1.31</v>
+      </c>
+      <c r="Z144">
+        <v>3.14</v>
+      </c>
+      <c r="AA144">
+        <v>2.02</v>
+      </c>
+      <c r="AB144">
+        <v>1.7</v>
+      </c>
+      <c r="AC144">
+        <v>3.9</v>
+      </c>
+      <c r="AD144">
         <v>1.21</v>
       </c>
-      <c r="Z144">
-        <v>3.62</v>
-      </c>
-      <c r="AA144">
-        <v>1.78</v>
-      </c>
-      <c r="AB144">
-        <v>1.98</v>
-      </c>
-      <c r="AC144">
-        <v>2.85</v>
-      </c>
-      <c r="AD144">
-        <v>1.33</v>
-      </c>
       <c r="AE144">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF144">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG144">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK144">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,80 +23944,80 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="O145">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q145">
-        <v>2.86</v>
+        <v>3.16</v>
       </c>
       <c r="R145">
+        <v>2.1</v>
+      </c>
+      <c r="S145">
+        <v>1.33</v>
+      </c>
+      <c r="T145">
+        <v>2.81</v>
+      </c>
+      <c r="U145">
+        <v>2.62</v>
+      </c>
+      <c r="V145">
+        <v>1.45</v>
+      </c>
+      <c r="W145">
+        <v>1.07</v>
+      </c>
+      <c r="X145">
+        <v>1.01</v>
+      </c>
+      <c r="Y145">
+        <v>1.25</v>
+      </c>
+      <c r="Z145">
+        <v>3.89</v>
+      </c>
+      <c r="AA145">
+        <v>1.76</v>
+      </c>
+      <c r="AB145">
         <v>2</v>
       </c>
-      <c r="S145">
-        <v>1.36</v>
-      </c>
-      <c r="T145">
-        <v>2.63</v>
-      </c>
-      <c r="U145">
-        <v>2.86</v>
-      </c>
-      <c r="V145">
-        <v>1.33</v>
-      </c>
-      <c r="W145">
-        <v>1.02</v>
-      </c>
-      <c r="X145">
-        <v>1.03</v>
-      </c>
-      <c r="Y145">
+      <c r="AC145">
+        <v>2.79</v>
+      </c>
+      <c r="AD145">
+        <v>1.34</v>
+      </c>
+      <c r="AE145">
+        <v>1.09</v>
+      </c>
+      <c r="AF145">
+        <v>1.6</v>
+      </c>
+      <c r="AG145">
+        <v>2.18</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ145">
         <v>1.31</v>
       </c>
-      <c r="Z145">
-        <v>3.14</v>
-      </c>
-      <c r="AA145">
-        <v>2.02</v>
-      </c>
-      <c r="AB145">
-        <v>1.7</v>
-      </c>
-      <c r="AC145">
-        <v>3.9</v>
-      </c>
-      <c r="AD145">
-        <v>1.21</v>
-      </c>
-      <c r="AE145">
-        <v>1.04</v>
-      </c>
-      <c r="AF145">
-        <v>1.83</v>
-      </c>
-      <c r="AG145">
-        <v>1.87</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ145">
-        <v>1.32</v>
-      </c>
       <c r="AK145">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,80 +24107,80 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="O146">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P146">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q146">
-        <v>3.16</v>
+        <v>2.36</v>
       </c>
       <c r="R146">
         <v>2.1</v>
       </c>
       <c r="S146">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T146">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="U146">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="V146">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W146">
         <v>1.07</v>
       </c>
       <c r="X146">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y146">
+        <v>1.22</v>
+      </c>
+      <c r="Z146">
+        <v>3.9</v>
+      </c>
+      <c r="AA146">
+        <v>1.78</v>
+      </c>
+      <c r="AB146">
+        <v>1.98</v>
+      </c>
+      <c r="AC146">
+        <v>2.8</v>
+      </c>
+      <c r="AD146">
+        <v>1.39</v>
+      </c>
+      <c r="AE146">
+        <v>1.1</v>
+      </c>
+      <c r="AF146">
+        <v>1.68</v>
+      </c>
+      <c r="AG146">
+        <v>2.06</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ146">
         <v>1.25</v>
       </c>
-      <c r="Z146">
-        <v>3.89</v>
-      </c>
-      <c r="AA146">
-        <v>1.76</v>
-      </c>
-      <c r="AB146">
-        <v>2</v>
-      </c>
-      <c r="AC146">
-        <v>2.79</v>
-      </c>
-      <c r="AD146">
-        <v>1.34</v>
-      </c>
-      <c r="AE146">
-        <v>1.09</v>
-      </c>
-      <c r="AF146">
-        <v>1.6</v>
-      </c>
-      <c r="AG146">
-        <v>2.18</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>1.31</v>
-      </c>
       <c r="AK146">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,43 +24433,43 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="O148">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P148">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q148">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
       <c r="R148">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S148">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T148">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U148">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="V148">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W148">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X148">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y148">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z148">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="AA148">
         <v>1.78</v>
@@ -24478,19 +24478,19 @@
         <v>1.98</v>
       </c>
       <c r="AC148">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD148">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE148">
         <v>1.1</v>
       </c>
       <c r="AF148">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG148">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK148">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,65 +37962,65 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="O231">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="P231">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="Q231">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="R231">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="S231">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T231">
-        <v>2.81</v>
+        <v>2.41</v>
       </c>
       <c r="U231">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="V231">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W231">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X231">
+        <v>1.04</v>
+      </c>
+      <c r="Y231">
+        <v>1.45</v>
+      </c>
+      <c r="Z231">
+        <v>2.48</v>
+      </c>
+      <c r="AA231">
+        <v>2.29</v>
+      </c>
+      <c r="AB231">
+        <v>1.61</v>
+      </c>
+      <c r="AC231">
+        <v>4.2</v>
+      </c>
+      <c r="AD231">
+        <v>1.16</v>
+      </c>
+      <c r="AE231">
         <v>1.01</v>
       </c>
-      <c r="Y231">
-        <v>1.29</v>
-      </c>
-      <c r="Z231">
-        <v>3.4</v>
-      </c>
-      <c r="AA231">
-        <v>1.89</v>
-      </c>
-      <c r="AB231">
-        <v>1.78</v>
-      </c>
-      <c r="AC231">
-        <v>3.45</v>
-      </c>
-      <c r="AD231">
-        <v>1.3</v>
-      </c>
-      <c r="AE231">
-        <v>1.07</v>
-      </c>
       <c r="AF231">
+        <v>1.93</v>
+      </c>
+      <c r="AG231">
         <v>1.75</v>
       </c>
-      <c r="AG231">
-        <v>1.95</v>
-      </c>
       <c r="AH231" t="inlineStr">
         <is>
           <t>[]</t>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK231">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,64 +38125,64 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="O232">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="P232">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="Q232">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R232">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="S232">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="T232">
-        <v>2.41</v>
+        <v>2.81</v>
       </c>
       <c r="U232">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="V232">
+        <v>1.39</v>
+      </c>
+      <c r="W232">
+        <v>1.05</v>
+      </c>
+      <c r="X232">
+        <v>1.01</v>
+      </c>
+      <c r="Y232">
         <v>1.29</v>
       </c>
-      <c r="W232">
-        <v>1.01</v>
-      </c>
-      <c r="X232">
-        <v>1.04</v>
-      </c>
-      <c r="Y232">
-        <v>1.45</v>
-      </c>
       <c r="Z232">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="AA232">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="AB232">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AC232">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD232">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE232">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF232">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AG232">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK232">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AL232">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="P4">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="Q4">
         <v>2.9</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U4">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="V4">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA4">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB4">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC4">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD4">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
         <v>1.44</v>
@@ -4879,13 +4879,13 @@
         <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S28">
         <v>1.36</v>
@@ -4903,7 +4903,7 @@
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>1.3</v>
@@ -4912,13 +4912,13 @@
         <v>3.1</v>
       </c>
       <c r="AA28">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AD28">
         <v>1.28</v>
@@ -4927,10 +4927,10 @@
         <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,40 +5036,40 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q29">
         <v>2.45</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
         <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
         <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
         <v>4.1</v>
@@ -5081,16 +5081,16 @@
         <v>2.07</v>
       </c>
       <c r="AC29">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="AD29">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
         <v>1.13</v>
       </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG29">
         <v>2.15</v>
@@ -5109,7 +5109,7 @@
         <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,46 +5208,46 @@
         <v>3.33</v>
       </c>
       <c r="Q30">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R30">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U30">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V30">
         <v>1.39</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA30">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB30">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC30">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AD30">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AE30">
         <v>1.07</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK30">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,25 +5365,25 @@
         <v>3.05</v>
       </c>
       <c r="O31">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="R31">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="S31">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="U31">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V31">
         <v>1.36</v>
@@ -5401,22 +5401,22 @@
         <v>3.28</v>
       </c>
       <c r="AA31">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB31">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AC31">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="AD31">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE31">
         <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG31">
         <v>1.98</v>
@@ -5435,7 +5435,7 @@
         <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,61 +5525,61 @@
         </is>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="O32">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q32">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="R32">
         <v>2.16</v>
       </c>
       <c r="S32">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
         <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="V32">
         <v>1.36</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
         <v>1.06</v>
       </c>
       <c r="Y32">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="AA32">
         <v>2</v>
       </c>
       <c r="AB32">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC32">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD32">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG32">
         <v>1.97</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O33">
         <v>3.2</v>
       </c>
       <c r="P33">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q33">
         <v>3.75</v>
@@ -5709,43 +5709,43 @@
         <v>2.91</v>
       </c>
       <c r="U33">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
         <v>1.06</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z33">
         <v>3.2</v>
       </c>
       <c r="AA33">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB33">
         <v>1.78</v>
       </c>
       <c r="AC33">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD33">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5851,37 +5851,37 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="O34">
         <v>3.3</v>
       </c>
       <c r="P34">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="Q34">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R34">
         <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y34">
         <v>1.3</v>
@@ -5890,7 +5890,7 @@
         <v>3.25</v>
       </c>
       <c r="AA34">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB34">
         <v>1.8</v>
@@ -5899,7 +5899,7 @@
         <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
         <v>1.1</v>
@@ -5908,7 +5908,7 @@
         <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="O35">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P35">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="Q35">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="R35">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="S35">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T35">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="U35">
         <v>1.8</v>
       </c>
       <c r="V35">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="W35">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA35">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB35">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AC35">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AD35">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AE35">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AF35">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AG35">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.43</v>
+        <v>2.25</v>
       </c>
       <c r="O41">
         <v>3.7</v>
       </c>
       <c r="P41">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q41">
-        <v>3.6</v>
+        <v>2.46</v>
       </c>
       <c r="R41">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="U41">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V41">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W41">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
         <v>1.02</v>
@@ -7028,28 +7028,28 @@
         <v>1.12</v>
       </c>
       <c r="Z41">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AA41">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC41">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AD41">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE41">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AK41">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q42">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="R42">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T42">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U42">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="V42">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W42">
         <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA42">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB42">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AC42">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AD42">
         <v>1.61</v>
       </c>
       <c r="AE42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF42">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG42">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AK42">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,55 +7318,55 @@
         </is>
       </c>
       <c r="N43">
+        <v>3.43</v>
+      </c>
+      <c r="O43">
+        <v>3.7</v>
+      </c>
+      <c r="P43">
+        <v>1.85</v>
+      </c>
+      <c r="Q43">
+        <v>3.6</v>
+      </c>
+      <c r="R43">
+        <v>2.38</v>
+      </c>
+      <c r="S43">
+        <v>1.2</v>
+      </c>
+      <c r="T43">
+        <v>3.66</v>
+      </c>
+      <c r="U43">
+        <v>2.1</v>
+      </c>
+      <c r="V43">
+        <v>1.65</v>
+      </c>
+      <c r="W43">
+        <v>1.17</v>
+      </c>
+      <c r="X43">
+        <v>1.02</v>
+      </c>
+      <c r="Y43">
+        <v>1.12</v>
+      </c>
+      <c r="Z43">
+        <v>5</v>
+      </c>
+      <c r="AA43">
+        <v>1.45</v>
+      </c>
+      <c r="AB43">
         <v>2.5</v>
       </c>
-      <c r="O43">
-        <v>3.75</v>
-      </c>
-      <c r="P43">
-        <v>2.55</v>
-      </c>
-      <c r="Q43">
-        <v>2.8</v>
-      </c>
-      <c r="R43">
-        <v>2.48</v>
-      </c>
-      <c r="S43">
-        <v>1.22</v>
-      </c>
-      <c r="T43">
-        <v>3.8</v>
-      </c>
-      <c r="U43">
-        <v>2.13</v>
-      </c>
-      <c r="V43">
-        <v>1.6</v>
-      </c>
-      <c r="W43">
-        <v>1.13</v>
-      </c>
-      <c r="X43">
-        <v>1.03</v>
-      </c>
-      <c r="Y43">
-        <v>1.16</v>
-      </c>
-      <c r="Z43">
-        <v>4.8</v>
-      </c>
-      <c r="AA43">
-        <v>1.47</v>
-      </c>
-      <c r="AB43">
-        <v>2.43</v>
-      </c>
       <c r="AC43">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AD43">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE43">
         <v>1.22</v>
@@ -7375,7 +7375,7 @@
         <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AK43">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.27</v>
+        <v>1.73</v>
       </c>
       <c r="O50">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
-        <v>2.89</v>
+        <v>2.13</v>
       </c>
       <c r="R50">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
         <v>2.81</v>
       </c>
       <c r="U50">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
         <v>1.02</v>
       </c>
-      <c r="X50">
-        <v>1.04</v>
-      </c>
       <c r="Y50">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="AA50">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>3.55</v>
+        <v>2.82</v>
       </c>
       <c r="AD50">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE50">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="O51">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="P51">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q51">
-        <v>2.13</v>
+        <v>2.89</v>
       </c>
       <c r="R51">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
         <v>2.81</v>
       </c>
       <c r="U51">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
+        <v>1.35</v>
+      </c>
+      <c r="Z51">
+        <v>3.25</v>
+      </c>
+      <c r="AA51">
+        <v>2.2</v>
+      </c>
+      <c r="AB51">
+        <v>1.7</v>
+      </c>
+      <c r="AC51">
+        <v>3.55</v>
+      </c>
+      <c r="AD51">
         <v>1.22</v>
       </c>
-      <c r="Z51">
-        <v>3.54</v>
-      </c>
-      <c r="AA51">
-        <v>1.8</v>
-      </c>
-      <c r="AB51">
-        <v>2</v>
-      </c>
-      <c r="AC51">
-        <v>2.82</v>
-      </c>
-      <c r="AD51">
-        <v>1.32</v>
-      </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG51">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK51">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="O57">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P57">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="Q57">
         <v>1.62</v>
@@ -9621,10 +9621,10 @@
         <v>4.8</v>
       </c>
       <c r="U57">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="V57">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="W57">
         <v>1.2</v>
@@ -9633,31 +9633,31 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>6.15</v>
+        <v>6.62</v>
       </c>
       <c r="AA57">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB57">
         <v>3.14</v>
       </c>
       <c r="AC57">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AD57">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AE57">
         <v>1.33</v>
       </c>
       <c r="AF57">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG57">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="O58">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="P58">
-        <v>3.92</v>
+        <v>5.25</v>
       </c>
       <c r="Q58">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R58">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S58">
         <v>1.35</v>
       </c>
       <c r="T58">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U58">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="V58">
         <v>1.41</v>
       </c>
       <c r="W58">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X58">
         <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z58">
         <v>3.7</v>
       </c>
       <c r="AA58">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB58">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC58">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AD58">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE58">
         <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG58">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK58">
         <v>2.3</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,34 +10415,34 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="O62">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P62">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q62">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="R62">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="S62">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="T62">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="U62">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V62">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W62">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.02</v>
@@ -10451,28 +10451,28 @@
         <v>1.11</v>
       </c>
       <c r="Z62">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA62">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB62">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC62">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AD62">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE62">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF62">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AG62">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK62">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="O63">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P63">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q63">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="R63">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S63">
         <v>1.21</v>
@@ -10599,13 +10599,13 @@
         <v>3.58</v>
       </c>
       <c r="U63">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="V63">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X63">
         <v>1.02</v>
@@ -10614,16 +10614,16 @@
         <v>1.11</v>
       </c>
       <c r="Z63">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA63">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB63">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AC63">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AD63">
         <v>1.58</v>
@@ -10632,10 +10632,10 @@
         <v>1.24</v>
       </c>
       <c r="AF63">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AG63">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.19</v>
       </c>
       <c r="AK63">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="O64">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P64">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q64">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R64">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="S64">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="T64">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="U64">
-        <v>2.18</v>
+        <v>2.59</v>
       </c>
       <c r="V64">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="W64">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
+        <v>1.18</v>
+      </c>
+      <c r="Z64">
+        <v>3.84</v>
+      </c>
+      <c r="AA64">
+        <v>1.67</v>
+      </c>
+      <c r="AB64">
+        <v>1.98</v>
+      </c>
+      <c r="AC64">
+        <v>2.76</v>
+      </c>
+      <c r="AD64">
+        <v>1.39</v>
+      </c>
+      <c r="AE64">
         <v>1.11</v>
       </c>
-      <c r="Z64">
-        <v>4.95</v>
-      </c>
-      <c r="AA64">
-        <v>1.45</v>
-      </c>
-      <c r="AB64">
-        <v>2.41</v>
-      </c>
-      <c r="AC64">
-        <v>2.28</v>
-      </c>
-      <c r="AD64">
-        <v>1.58</v>
-      </c>
-      <c r="AE64">
-        <v>1.24</v>
-      </c>
       <c r="AF64">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AG64">
-        <v>2.59</v>
+        <v>2.23</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK64">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.61</v>
+        <v>1.4</v>
       </c>
       <c r="O65">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="P65">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q65">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="R65">
         <v>2.31</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T65">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U65">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="V65">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W65">
         <v>1.07</v>
@@ -10937,31 +10937,31 @@
         <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z65">
-        <v>3.84</v>
+        <v>4.15</v>
       </c>
       <c r="AA65">
+        <v>1.64</v>
+      </c>
+      <c r="AB65">
+        <v>2.3</v>
+      </c>
+      <c r="AC65">
+        <v>2.56</v>
+      </c>
+      <c r="AD65">
+        <v>1.4</v>
+      </c>
+      <c r="AE65">
+        <v>1.13</v>
+      </c>
+      <c r="AF65">
         <v>1.67</v>
       </c>
-      <c r="AB65">
-        <v>1.98</v>
-      </c>
-      <c r="AC65">
-        <v>2.76</v>
-      </c>
-      <c r="AD65">
-        <v>1.39</v>
-      </c>
-      <c r="AE65">
-        <v>1.11</v>
-      </c>
-      <c r="AF65">
-        <v>1.57</v>
-      </c>
       <c r="AG65">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK65">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O66">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P66">
         <v>5.5</v>
       </c>
       <c r="Q66">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R66">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="S66">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T66">
-        <v>3.25</v>
+        <v>3.82</v>
       </c>
       <c r="U66">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V66">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z66">
-        <v>4.15</v>
+        <v>4.9</v>
       </c>
       <c r="AA66">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AB66">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AC66">
-        <v>2.56</v>
+        <v>2.23</v>
       </c>
       <c r="AD66">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AE66">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF66">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG66">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK66">
         <v>2.5</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q76">
-        <v>2.4</v>
+        <v>3.56</v>
       </c>
       <c r="R76">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S76">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="T76">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="U76">
-        <v>3.46</v>
+        <v>2.96</v>
       </c>
       <c r="V76">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="W76">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X76">
+        <v>1.01</v>
+      </c>
+      <c r="Y76">
+        <v>1.31</v>
+      </c>
+      <c r="Z76">
+        <v>2.92</v>
+      </c>
+      <c r="AA76">
+        <v>2.04</v>
+      </c>
+      <c r="AB76">
+        <v>1.69</v>
+      </c>
+      <c r="AC76">
+        <v>3.58</v>
+      </c>
+      <c r="AD76">
+        <v>1.21</v>
+      </c>
+      <c r="AE76">
         <v>1.04</v>
       </c>
-      <c r="Y76">
-        <v>1.44</v>
-      </c>
-      <c r="Z76">
-        <v>2.65</v>
-      </c>
-      <c r="AA76">
-        <v>2.45</v>
-      </c>
-      <c r="AB76">
-        <v>1.53</v>
-      </c>
-      <c r="AC76">
-        <v>4.64</v>
-      </c>
-      <c r="AD76">
-        <v>1.12</v>
-      </c>
-      <c r="AE76">
-        <v>1.01</v>
-      </c>
       <c r="AF76">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AG76">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.1</v>
+        <v>1.46</v>
       </c>
       <c r="AK76">
-        <v>1.98</v>
+        <v>1.35</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,37 +12860,37 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P77">
-        <v>2.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q77">
-        <v>3.56</v>
+        <v>3.85</v>
       </c>
       <c r="R77">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="S77">
         <v>1.41</v>
       </c>
       <c r="T77">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="U77">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="V77">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
         <v>1.03</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
         <v>1.31</v>
@@ -12902,22 +12902,22 @@
         <v>2.04</v>
       </c>
       <c r="AB77">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC77">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AD77">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE77">
         <v>1.04</v>
       </c>
       <c r="AF77">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG77">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q78">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="R78">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="S78">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="T78">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="U78">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V78">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W78">
+        <v>1.03</v>
+      </c>
+      <c r="X78">
         <v>1.01</v>
       </c>
-      <c r="X78">
-        <v>1.05</v>
-      </c>
       <c r="Y78">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z78">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AA78">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AB78">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AC78">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AD78">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF78">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AG78">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK78">
         <v>1.53</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q79">
-        <v>3.85</v>
+        <v>2.8</v>
       </c>
       <c r="R79">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S79">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T79">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U79">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="V79">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
         <v>1.03</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA79">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AB79">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC79">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE79">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF79">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK79">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="R80">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="S80">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T80">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="U80">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V80">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W80">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X80">
+        <v>1.05</v>
+      </c>
+      <c r="Y80">
+        <v>1.38</v>
+      </c>
+      <c r="Z80">
+        <v>2.62</v>
+      </c>
+      <c r="AA80">
+        <v>2.27</v>
+      </c>
+      <c r="AB80">
+        <v>1.59</v>
+      </c>
+      <c r="AC80">
+        <v>4.2</v>
+      </c>
+      <c r="AD80">
+        <v>1.15</v>
+      </c>
+      <c r="AE80">
         <v>1.01</v>
       </c>
-      <c r="Y80">
-        <v>1.31</v>
-      </c>
-      <c r="Z80">
-        <v>2.92</v>
-      </c>
-      <c r="AA80">
-        <v>2.1</v>
-      </c>
-      <c r="AB80">
-        <v>1.7</v>
-      </c>
-      <c r="AC80">
-        <v>3.58</v>
-      </c>
-      <c r="AD80">
-        <v>1.25</v>
-      </c>
-      <c r="AE80">
-        <v>1.03</v>
-      </c>
       <c r="AF80">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AG80">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK80">
         <v>1.53</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="R81">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S81">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T81">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U81">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="V81">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="W81">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X81">
+        <v>1.04</v>
+      </c>
+      <c r="Y81">
+        <v>1.44</v>
+      </c>
+      <c r="Z81">
+        <v>2.65</v>
+      </c>
+      <c r="AA81">
+        <v>2.45</v>
+      </c>
+      <c r="AB81">
+        <v>1.53</v>
+      </c>
+      <c r="AC81">
+        <v>4.64</v>
+      </c>
+      <c r="AD81">
+        <v>1.12</v>
+      </c>
+      <c r="AE81">
         <v>1.01</v>
       </c>
-      <c r="Y81">
-        <v>1.31</v>
-      </c>
-      <c r="Z81">
-        <v>3.08</v>
-      </c>
-      <c r="AA81">
-        <v>2.14</v>
-      </c>
-      <c r="AB81">
-        <v>1.66</v>
-      </c>
-      <c r="AC81">
-        <v>3.8</v>
-      </c>
-      <c r="AD81">
-        <v>1.19</v>
-      </c>
-      <c r="AE81">
-        <v>1.02</v>
-      </c>
       <c r="AF81">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="AG81">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK81">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q82">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S82">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T82">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U82">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="V82">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W82">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z82">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA82">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AB82">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AC82">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="AD82">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AE82">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF82">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG82">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14816,16 +14816,16 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O89">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P89">
         <v>5</v>
       </c>
       <c r="Q89">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="R89">
         <v>2.39</v>
@@ -14834,7 +14834,7 @@
         <v>1.3</v>
       </c>
       <c r="T89">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="U89">
         <v>2.6</v>
@@ -14846,10 +14846,10 @@
         <v>1.07</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z89">
         <v>3.78</v>
@@ -14861,16 +14861,16 @@
         <v>1.96</v>
       </c>
       <c r="AC89">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="AD89">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE89">
         <v>1.08</v>
       </c>
       <c r="AF89">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG89">
         <v>1.86</v>
@@ -14979,25 +14979,25 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O90">
         <v>4.6</v>
       </c>
       <c r="P90">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Q90">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="R90">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S90">
         <v>1.21</v>
       </c>
       <c r="T90">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U90">
         <v>2.14</v>
@@ -15024,19 +15024,19 @@
         <v>2.68</v>
       </c>
       <c r="AC90">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AD90">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE90">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF90">
         <v>1.54</v>
       </c>
       <c r="AG90">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>4.66</v>
+        <v>2.33</v>
       </c>
       <c r="O100">
-        <v>4.62</v>
+        <v>3.62</v>
       </c>
       <c r="P100">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="Q100">
-        <v>5</v>
+        <v>2.98</v>
       </c>
       <c r="R100">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S100">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="T100">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U100">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V100">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W100">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z100">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA100">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB100">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AC100">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AD100">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AE100">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AF100">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG100">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,65 +16772,65 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.33</v>
+        <v>4.66</v>
       </c>
       <c r="O101">
-        <v>3.62</v>
+        <v>4.62</v>
       </c>
       <c r="P101">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="Q101">
-        <v>2.98</v>
+        <v>5</v>
       </c>
       <c r="R101">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S101">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T101">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U101">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="V101">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="W101">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z101">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA101">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB101">
+        <v>2.55</v>
+      </c>
+      <c r="AC101">
         <v>2.2</v>
       </c>
-      <c r="AC101">
+      <c r="AD101">
+        <v>1.68</v>
+      </c>
+      <c r="AE101">
+        <v>1.24</v>
+      </c>
+      <c r="AF101">
+        <v>1.57</v>
+      </c>
+      <c r="AG101">
         <v>2.63</v>
       </c>
-      <c r="AD101">
-        <v>1.54</v>
-      </c>
-      <c r="AE101">
-        <v>1.15</v>
-      </c>
-      <c r="AF101">
-        <v>1.6</v>
-      </c>
-      <c r="AG101">
-        <v>2.33</v>
-      </c>
       <c r="AH101" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK101">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="O122">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P122">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="Q122">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="R122">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T122">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="U122">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V122">
         <v>1.4</v>
       </c>
       <c r="W122">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X122">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
+        <v>1.27</v>
+      </c>
+      <c r="Z122">
+        <v>3.42</v>
+      </c>
+      <c r="AA122">
+        <v>1.84</v>
+      </c>
+      <c r="AB122">
+        <v>1.87</v>
+      </c>
+      <c r="AC122">
+        <v>3.05</v>
+      </c>
+      <c r="AD122">
         <v>1.33</v>
       </c>
-      <c r="Z122">
-        <v>3.35</v>
-      </c>
-      <c r="AA122">
-        <v>1.92</v>
-      </c>
-      <c r="AB122">
-        <v>1.76</v>
-      </c>
-      <c r="AC122">
-        <v>3.35</v>
-      </c>
-      <c r="AD122">
-        <v>1.27</v>
-      </c>
       <c r="AE122">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF122">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG122">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK122">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="O123">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P123">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q123">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R123">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T123">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="U123">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="V123">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W123">
         <v>1.05</v>
       </c>
       <c r="X123">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z123">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA123">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB123">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AC123">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD123">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE123">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF123">
         <v>1.83</v>
       </c>
       <c r="AG123">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK123">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O124">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P124">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q124">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R124">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S124">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T124">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="U124">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="V124">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W124">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X124">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y124">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z124">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA124">
         <v>1.84</v>
       </c>
       <c r="AB124">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AC124">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD124">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE124">
         <v>1.06</v>
       </c>
       <c r="AF124">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG124">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK124">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="O125">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P125">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q125">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R125">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S125">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T125">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="U125">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="V125">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W125">
         <v>1.05</v>
       </c>
       <c r="X125">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y125">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z125">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="AA125">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB125">
         <v>1.76</v>
       </c>
       <c r="AC125">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AD125">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE125">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF125">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AG125">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK125">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O128">
         <v>3.7</v>
       </c>
       <c r="P128">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="Q128">
         <v>2.99</v>
@@ -21191,13 +21191,13 @@
         <v>1.18</v>
       </c>
       <c r="T128">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="U128">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="V128">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W128">
         <v>1.2</v>
@@ -21206,7 +21206,7 @@
         <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z128">
         <v>6.84</v>
@@ -21215,7 +21215,7 @@
         <v>1.31</v>
       </c>
       <c r="AB128">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="AC128">
         <v>1.91</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.34</v>
+        <v>1.65</v>
       </c>
       <c r="O164">
+        <v>3.6</v>
+      </c>
+      <c r="P164">
+        <v>4.75</v>
+      </c>
+      <c r="Q164">
+        <v>2.2</v>
+      </c>
+      <c r="R164">
+        <v>2.19</v>
+      </c>
+      <c r="S164">
+        <v>1.3</v>
+      </c>
+      <c r="T164">
+        <v>3.2</v>
+      </c>
+      <c r="U164">
+        <v>2.6</v>
+      </c>
+      <c r="V164">
+        <v>1.42</v>
+      </c>
+      <c r="W164">
+        <v>1.06</v>
+      </c>
+      <c r="X164">
+        <v>1</v>
+      </c>
+      <c r="Y164">
+        <v>1.29</v>
+      </c>
+      <c r="Z164">
         <v>3.4</v>
       </c>
-      <c r="P164">
-        <v>2.7</v>
-      </c>
-      <c r="Q164">
-        <v>2.88</v>
-      </c>
-      <c r="R164">
-        <v>2.24</v>
-      </c>
-      <c r="S164">
-        <v>1.35</v>
-      </c>
-      <c r="T164">
-        <v>3</v>
-      </c>
-      <c r="U164">
-        <v>2.75</v>
-      </c>
-      <c r="V164">
-        <v>1.4</v>
-      </c>
-      <c r="W164">
-        <v>1.1</v>
-      </c>
-      <c r="X164">
-        <v>1.02</v>
-      </c>
-      <c r="Y164">
-        <v>1.27</v>
-      </c>
-      <c r="Z164">
-        <v>3.74</v>
-      </c>
       <c r="AA164">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB164">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AC164">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD164">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE164">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF164">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AG164">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AK164">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="O165">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P165">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q165">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="R165">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="S165">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T165">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U165">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V165">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W165">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X165">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y165">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z165">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="AA165">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB165">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AC165">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD165">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE165">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF165">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AG165">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK165">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27699,7 +27699,7 @@
         <v>3.36</v>
       </c>
       <c r="P168">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Q168">
         <v>3.9</v>
@@ -27720,13 +27720,13 @@
         <v>1.41</v>
       </c>
       <c r="W168">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X168">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y168">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z168">
         <v>3.4</v>
@@ -27735,19 +27735,19 @@
         <v>1.99</v>
       </c>
       <c r="AB168">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC168">
-        <v>3.05</v>
+        <v>3.44</v>
       </c>
       <c r="AD168">
         <v>1.28</v>
       </c>
       <c r="AE168">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF168">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG168">
         <v>2</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="O179">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="P179">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q179">
         <v>3.65</v>
@@ -29513,7 +29513,7 @@
         <v>1.41</v>
       </c>
       <c r="W179">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X179">
         <v>1.05</v>
@@ -29525,16 +29525,16 @@
         <v>3.6</v>
       </c>
       <c r="AA179">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB179">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC179">
         <v>2.94</v>
       </c>
       <c r="AD179">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE179">
         <v>1.07</v>
@@ -29559,7 +29559,7 @@
         <v>1.72</v>
       </c>
       <c r="AK179">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="O194">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P194">
-        <v>5.23</v>
+        <v>3.3</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G195">
@@ -32097,10 +32097,10 @@
         <v>2.15</v>
       </c>
       <c r="O195">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P195">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="O196">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P196">
-        <v>3.24</v>
+        <v>5.23</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -33235,10 +33235,10 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="O202">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="P202">
         <v>7</v>
@@ -33253,7 +33253,7 @@
         <v>1.13</v>
       </c>
       <c r="T202">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="U202">
         <v>1.78</v>
@@ -33268,7 +33268,7 @@
         <v>1.01</v>
       </c>
       <c r="Y202">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z202">
         <v>7.5</v>
@@ -33277,13 +33277,13 @@
         <v>1.28</v>
       </c>
       <c r="AB202">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AC202">
         <v>1.65</v>
       </c>
       <c r="AD202">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AE202">
         <v>1.52</v>
@@ -33292,7 +33292,7 @@
         <v>1.5</v>
       </c>
       <c r="AG202">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>1.11</v>
       </c>
       <c r="AK202">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -35363,55 +35363,55 @@
         <v>0</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S215">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T215">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U215">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V215">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W215">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X215">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y215">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z215">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA215">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD215">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG215">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK215">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,80 +38125,80 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O232">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="P232">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q232">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="R232">
+        <v>2.1</v>
+      </c>
+      <c r="S232">
+        <v>1.38</v>
+      </c>
+      <c r="T232">
+        <v>2.7</v>
+      </c>
+      <c r="U232">
+        <v>2.77</v>
+      </c>
+      <c r="V232">
+        <v>1.39</v>
+      </c>
+      <c r="W232">
+        <v>1.05</v>
+      </c>
+      <c r="X232">
+        <v>1.01</v>
+      </c>
+      <c r="Y232">
+        <v>1.29</v>
+      </c>
+      <c r="Z232">
+        <v>3.4</v>
+      </c>
+      <c r="AA232">
         <v>2.02</v>
       </c>
-      <c r="S232">
-        <v>1.5</v>
-      </c>
-      <c r="T232">
-        <v>2.5</v>
-      </c>
-      <c r="U232">
-        <v>3.3</v>
-      </c>
-      <c r="V232">
-        <v>1.25</v>
-      </c>
-      <c r="W232">
-        <v>1.04</v>
-      </c>
-      <c r="X232">
-        <v>1.04</v>
-      </c>
-      <c r="Y232">
-        <v>1.45</v>
-      </c>
-      <c r="Z232">
-        <v>2.5</v>
-      </c>
-      <c r="AA232">
-        <v>2.4</v>
-      </c>
       <c r="AB232">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AC232">
-        <v>4.83</v>
+        <v>3.52</v>
       </c>
       <c r="AD232">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE232">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF232">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AG232">
+        <v>1.95</v>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ232">
+        <v>1.28</v>
+      </c>
+      <c r="AK232">
         <v>1.75</v>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ232">
-        <v>1.35</v>
-      </c>
-      <c r="AK232">
-        <v>1.57</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,65 +38288,65 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="O233">
+        <v>2.87</v>
+      </c>
+      <c r="P233">
+        <v>2.9</v>
+      </c>
+      <c r="Q233">
+        <v>3.1</v>
+      </c>
+      <c r="R233">
+        <v>2.02</v>
+      </c>
+      <c r="S233">
+        <v>1.5</v>
+      </c>
+      <c r="T233">
+        <v>2.5</v>
+      </c>
+      <c r="U233">
         <v>3.3</v>
       </c>
-      <c r="P233">
-        <v>3.6</v>
-      </c>
-      <c r="Q233">
-        <v>2.67</v>
-      </c>
-      <c r="R233">
-        <v>2.1</v>
-      </c>
-      <c r="S233">
-        <v>1.38</v>
-      </c>
-      <c r="T233">
-        <v>2.7</v>
-      </c>
-      <c r="U233">
-        <v>2.77</v>
-      </c>
       <c r="V233">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="W233">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X233">
+        <v>1.04</v>
+      </c>
+      <c r="Y233">
+        <v>1.45</v>
+      </c>
+      <c r="Z233">
+        <v>2.5</v>
+      </c>
+      <c r="AA233">
+        <v>2.4</v>
+      </c>
+      <c r="AB233">
+        <v>1.61</v>
+      </c>
+      <c r="AC233">
+        <v>4.83</v>
+      </c>
+      <c r="AD233">
+        <v>1.16</v>
+      </c>
+      <c r="AE233">
         <v>1.01</v>
       </c>
-      <c r="Y233">
-        <v>1.29</v>
-      </c>
-      <c r="Z233">
-        <v>3.4</v>
-      </c>
-      <c r="AA233">
-        <v>2.02</v>
-      </c>
-      <c r="AB233">
-        <v>1.83</v>
-      </c>
-      <c r="AC233">
-        <v>3.52</v>
-      </c>
-      <c r="AD233">
-        <v>1.3</v>
-      </c>
-      <c r="AE233">
-        <v>1.07</v>
-      </c>
       <c r="AF233">
+        <v>1.93</v>
+      </c>
+      <c r="AG233">
         <v>1.75</v>
       </c>
-      <c r="AG233">
-        <v>1.95</v>
-      </c>
       <c r="AH233" t="inlineStr">
         <is>
           <t>[]</t>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK233">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="O234">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P234">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q234">
         <v>2.05</v>
@@ -38469,34 +38469,34 @@
         <v>1.17</v>
       </c>
       <c r="T234">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="U234">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="V234">
         <v>1.74</v>
       </c>
       <c r="W234">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X234">
         <v>1.01</v>
       </c>
       <c r="Y234">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z234">
-        <v>5.73</v>
+        <v>5.45</v>
       </c>
       <c r="AA234">
         <v>1.42</v>
       </c>
       <c r="AB234">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AC234">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD234">
         <v>1.79</v>
@@ -38505,10 +38505,10 @@
         <v>1.3</v>
       </c>
       <c r="AF234">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG234">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>1.22</v>
       </c>
       <c r="AK234">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38641,28 +38641,28 @@
         <v>1.42</v>
       </c>
       <c r="W235">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X235">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y235">
         <v>1.27</v>
       </c>
       <c r="Z235">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="AA235">
         <v>1.83</v>
       </c>
       <c r="AB235">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AC235">
         <v>3.1</v>
       </c>
       <c r="AD235">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE235">
         <v>1.11</v>
@@ -41222,64 +41222,64 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S251">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T251">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U251">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V251">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W251">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X251">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y251">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z251">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA251">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB251">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC251">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD251">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK251">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41551,22 +41551,22 @@
         <v>2.1</v>
       </c>
       <c r="O253">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P253">
         <v>3.5</v>
       </c>
       <c r="Q253">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="R253">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="S253">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T253">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U253">
         <v>3.72</v>
@@ -41581,13 +41581,13 @@
         <v>1.12</v>
       </c>
       <c r="Y253">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Z253">
         <v>2.33</v>
       </c>
       <c r="AA253">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="AB253">
         <v>1.44</v>
@@ -41596,16 +41596,16 @@
         <v>5.65</v>
       </c>
       <c r="AD253">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AE253">
         <v>1.03</v>
       </c>
       <c r="AF253">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AG253">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -42037,25 +42037,25 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O256">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P256">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q256">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R256">
-        <v>2.24</v>
+        <v>2.43</v>
       </c>
       <c r="S256">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T256">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U256">
         <v>2.45</v>
@@ -42064,28 +42064,28 @@
         <v>1.48</v>
       </c>
       <c r="W256">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X256">
         <v>1.01</v>
       </c>
       <c r="Y256">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z256">
         <v>3.95</v>
       </c>
       <c r="AA256">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB256">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC256">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD256">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE256">
         <v>1.12</v>
@@ -42094,7 +42094,7 @@
         <v>1.7</v>
       </c>
       <c r="AG256">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK256">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -43676,7 +43676,7 @@
         <v>5</v>
       </c>
       <c r="Q266">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R266">
         <v>1.86</v>
@@ -43691,13 +43691,13 @@
         <v>3.6</v>
       </c>
       <c r="V266">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W266">
         <v>1.03</v>
       </c>
       <c r="X266">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y266">
         <v>1.57</v>
@@ -43712,10 +43712,10 @@
         <v>1.41</v>
       </c>
       <c r="AC266">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="AD266">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE266">
         <v>1.03</v>
@@ -43740,7 +43740,7 @@
         <v>1.14</v>
       </c>
       <c r="AK266">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="O269">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P269">
-        <v>5.25</v>
+        <v>2.87</v>
       </c>
       <c r="Q269">
-        <v>2.02</v>
+        <v>2.91</v>
       </c>
       <c r="R269">
         <v>2.2</v>
       </c>
       <c r="S269">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T269">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U269">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V269">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W269">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X269">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y269">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z269">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="AA269">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB269">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC269">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="AD269">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE269">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF269">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG269">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AK269">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,64 +44319,64 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="O270">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P270">
-        <v>2.87</v>
+        <v>5.25</v>
       </c>
       <c r="Q270">
-        <v>2.91</v>
+        <v>2.02</v>
       </c>
       <c r="R270">
         <v>2.2</v>
       </c>
       <c r="S270">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T270">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U270">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V270">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W270">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X270">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y270">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z270">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="AA270">
+        <v>1.84</v>
+      </c>
+      <c r="AB270">
+        <v>1.86</v>
+      </c>
+      <c r="AC270">
+        <v>3.08</v>
+      </c>
+      <c r="AD270">
+        <v>1.28</v>
+      </c>
+      <c r="AE270">
+        <v>1.06</v>
+      </c>
+      <c r="AF270">
         <v>1.95</v>
       </c>
-      <c r="AB270">
-        <v>1.85</v>
-      </c>
-      <c r="AC270">
-        <v>3.31</v>
-      </c>
-      <c r="AD270">
-        <v>1.3</v>
-      </c>
-      <c r="AE270">
-        <v>1.07</v>
-      </c>
-      <c r="AF270">
-        <v>1.7</v>
-      </c>
       <c r="AG270">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AK270">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -46447,55 +46447,55 @@
         <v>0</v>
       </c>
       <c r="Q283">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R283">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S283">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T283">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U283">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V283">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W283">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y283">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z283">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC283">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD283">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE283">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF283">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG283">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK283">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G288">
@@ -47262,71 +47262,71 @@
         <v>0</v>
       </c>
       <c r="Q288">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R288">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="S288">
+        <v>1.29</v>
+      </c>
+      <c r="T288">
+        <v>2.96</v>
+      </c>
+      <c r="U288">
+        <v>2.62</v>
+      </c>
+      <c r="V288">
         <v>1.4</v>
       </c>
-      <c r="T288">
-        <v>2.62</v>
-      </c>
-      <c r="U288">
-        <v>3</v>
-      </c>
-      <c r="V288">
-        <v>1.32</v>
-      </c>
       <c r="W288">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X288">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y288">
+        <v>1.2</v>
+      </c>
+      <c r="Z288">
+        <v>3.58</v>
+      </c>
+      <c r="AA288">
+        <v>1.85</v>
+      </c>
+      <c r="AB288">
+        <v>1.95</v>
+      </c>
+      <c r="AC288">
+        <v>2.65</v>
+      </c>
+      <c r="AD288">
+        <v>1.38</v>
+      </c>
+      <c r="AE288">
+        <v>1.08</v>
+      </c>
+      <c r="AF288">
+        <v>1.6</v>
+      </c>
+      <c r="AG288">
+        <v>2.15</v>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ288">
+        <v>1.25</v>
+      </c>
+      <c r="AK288">
         <v>1.3</v>
-      </c>
-      <c r="Z288">
-        <v>2.97</v>
-      </c>
-      <c r="AA288">
-        <v>2.1</v>
-      </c>
-      <c r="AB288">
-        <v>1.7</v>
-      </c>
-      <c r="AC288">
-        <v>3.58</v>
-      </c>
-      <c r="AD288">
-        <v>1.21</v>
-      </c>
-      <c r="AE288">
-        <v>1.03</v>
-      </c>
-      <c r="AF288">
-        <v>1.77</v>
-      </c>
-      <c r="AG288">
-        <v>1.85</v>
-      </c>
-      <c r="AH288" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI288" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ288">
-        <v>1.4</v>
-      </c>
-      <c r="AK288">
-        <v>1.48</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G289">
@@ -47425,71 +47425,71 @@
         <v>0</v>
       </c>
       <c r="Q289">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R289">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="S289">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T289">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="U289">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V289">
+        <v>1.32</v>
+      </c>
+      <c r="W289">
+        <v>1.02</v>
+      </c>
+      <c r="X289">
+        <v>1</v>
+      </c>
+      <c r="Y289">
+        <v>1.3</v>
+      </c>
+      <c r="Z289">
+        <v>2.97</v>
+      </c>
+      <c r="AA289">
+        <v>2.1</v>
+      </c>
+      <c r="AB289">
+        <v>1.7</v>
+      </c>
+      <c r="AC289">
+        <v>3.58</v>
+      </c>
+      <c r="AD289">
+        <v>1.21</v>
+      </c>
+      <c r="AE289">
+        <v>1.03</v>
+      </c>
+      <c r="AF289">
+        <v>1.77</v>
+      </c>
+      <c r="AG289">
+        <v>1.85</v>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ289">
         <v>1.4</v>
       </c>
-      <c r="W289">
-        <v>1.05</v>
-      </c>
-      <c r="X289">
-        <v>1.05</v>
-      </c>
-      <c r="Y289">
-        <v>1.2</v>
-      </c>
-      <c r="Z289">
-        <v>3.58</v>
-      </c>
-      <c r="AA289">
-        <v>1.85</v>
-      </c>
-      <c r="AB289">
-        <v>1.95</v>
-      </c>
-      <c r="AC289">
-        <v>2.65</v>
-      </c>
-      <c r="AD289">
-        <v>1.38</v>
-      </c>
-      <c r="AE289">
-        <v>1.08</v>
-      </c>
-      <c r="AF289">
-        <v>1.6</v>
-      </c>
-      <c r="AG289">
-        <v>2.15</v>
-      </c>
-      <c r="AH289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ289">
-        <v>1.25</v>
-      </c>
       <c r="AK289">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47579,19 +47579,19 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O290">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P290">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q290">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="R290">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S290">
         <v>1.7</v>
@@ -47618,7 +47618,7 @@
         <v>1.92</v>
       </c>
       <c r="AA290">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="AB290">
         <v>1.28</v>
@@ -47742,7 +47742,7 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O291">
         <v>2.7</v>
@@ -47754,7 +47754,7 @@
         <v>3.74</v>
       </c>
       <c r="R291">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="S291">
         <v>1.67</v>
@@ -47763,10 +47763,10 @@
         <v>2.07</v>
       </c>
       <c r="U291">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="V291">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W291">
         <v>1.03</v>
@@ -47775,7 +47775,7 @@
         <v>1.11</v>
       </c>
       <c r="Y291">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="Z291">
         <v>2.18</v>
@@ -47784,7 +47784,7 @@
         <v>2.97</v>
       </c>
       <c r="AB291">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC291">
         <v>6.2</v>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK291">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -49218,13 +49218,13 @@
         <v>2.09</v>
       </c>
       <c r="Q300">
-        <v>4.26</v>
+        <v>4.15</v>
       </c>
       <c r="R300">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S300">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T300">
         <v>2.85</v>
@@ -49233,7 +49233,7 @@
         <v>2.88</v>
       </c>
       <c r="V300">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W300">
         <v>1.06</v>
@@ -49245,13 +49245,13 @@
         <v>1.26</v>
       </c>
       <c r="Z300">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA300">
         <v>1.98</v>
       </c>
       <c r="AB300">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC300">
         <v>3.4</v>
@@ -49279,7 +49279,7 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AK300">
         <v>1.33</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G302">
@@ -49544,55 +49544,55 @@
         <v>0</v>
       </c>
       <c r="Q302">
-        <v>2.67</v>
+        <v>3.08</v>
       </c>
       <c r="R302">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="S302">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T302">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U302">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="V302">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W302">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X302">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y302">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z302">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AA302">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AB302">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AC302">
-        <v>4.05</v>
+        <v>3.42</v>
       </c>
       <c r="AD302">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE302">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF302">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AG302">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49608,7 +49608,7 @@
         <v>1.27</v>
       </c>
       <c r="AK302">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G303">
@@ -49707,55 +49707,55 @@
         <v>0</v>
       </c>
       <c r="Q303">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="R303">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="S303">
+        <v>1.45</v>
+      </c>
+      <c r="T303">
+        <v>2.44</v>
+      </c>
+      <c r="U303">
+        <v>3.28</v>
+      </c>
+      <c r="V303">
+        <v>1.26</v>
+      </c>
+      <c r="W303">
+        <v>1.03</v>
+      </c>
+      <c r="X303">
+        <v>1.02</v>
+      </c>
+      <c r="Y303">
         <v>1.38</v>
       </c>
-      <c r="T303">
-        <v>2.67</v>
-      </c>
-      <c r="U303">
-        <v>2.71</v>
-      </c>
-      <c r="V303">
-        <v>1.37</v>
-      </c>
-      <c r="W303">
-        <v>1.07</v>
-      </c>
-      <c r="X303">
+      <c r="Z303">
+        <v>2.8</v>
+      </c>
+      <c r="AA303">
+        <v>2.23</v>
+      </c>
+      <c r="AB303">
+        <v>1.56</v>
+      </c>
+      <c r="AC303">
+        <v>4.2</v>
+      </c>
+      <c r="AD303">
+        <v>1.15</v>
+      </c>
+      <c r="AE303">
         <v>1.01</v>
       </c>
-      <c r="Y303">
-        <v>1.25</v>
-      </c>
-      <c r="Z303">
-        <v>3.28</v>
-      </c>
-      <c r="AA303">
-        <v>1.86</v>
-      </c>
-      <c r="AB303">
-        <v>1.81</v>
-      </c>
-      <c r="AC303">
-        <v>3.05</v>
-      </c>
-      <c r="AD303">
-        <v>1.28</v>
-      </c>
-      <c r="AE303">
-        <v>1.08</v>
-      </c>
       <c r="AF303">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AG303">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK303">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G304">
@@ -49870,55 +49870,55 @@
         <v>0</v>
       </c>
       <c r="Q304">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="R304">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="S304">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T304">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U304">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="V304">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W304">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X304">
+        <v>1.03</v>
+      </c>
+      <c r="Y304">
+        <v>1.37</v>
+      </c>
+      <c r="Z304">
+        <v>2.66</v>
+      </c>
+      <c r="AA304">
+        <v>2.23</v>
+      </c>
+      <c r="AB304">
+        <v>1.57</v>
+      </c>
+      <c r="AC304">
+        <v>4.15</v>
+      </c>
+      <c r="AD304">
+        <v>1.16</v>
+      </c>
+      <c r="AE304">
         <v>1.01</v>
       </c>
-      <c r="Y304">
-        <v>1.29</v>
-      </c>
-      <c r="Z304">
-        <v>3</v>
-      </c>
-      <c r="AA304">
-        <v>2</v>
-      </c>
-      <c r="AB304">
-        <v>1.71</v>
-      </c>
-      <c r="AC304">
-        <v>3.42</v>
-      </c>
-      <c r="AD304">
-        <v>1.23</v>
-      </c>
-      <c r="AE304">
-        <v>1.04</v>
-      </c>
       <c r="AF304">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AG304">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK304">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G305">
@@ -50033,55 +50033,55 @@
         <v>0</v>
       </c>
       <c r="Q305">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="R305">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="S305">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T305">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="U305">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V305">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W305">
         <v>1.03</v>
       </c>
       <c r="X305">
+        <v>1.04</v>
+      </c>
+      <c r="Y305">
+        <v>1.4</v>
+      </c>
+      <c r="Z305">
+        <v>2.56</v>
+      </c>
+      <c r="AA305">
+        <v>2.27</v>
+      </c>
+      <c r="AB305">
+        <v>1.55</v>
+      </c>
+      <c r="AC305">
+        <v>4.15</v>
+      </c>
+      <c r="AD305">
+        <v>1.16</v>
+      </c>
+      <c r="AE305">
         <v>1.02</v>
       </c>
-      <c r="Y305">
-        <v>1.38</v>
-      </c>
-      <c r="Z305">
-        <v>2.8</v>
-      </c>
-      <c r="AA305">
-        <v>2.23</v>
-      </c>
-      <c r="AB305">
-        <v>1.56</v>
-      </c>
-      <c r="AC305">
-        <v>4.2</v>
-      </c>
-      <c r="AD305">
-        <v>1.15</v>
-      </c>
-      <c r="AE305">
-        <v>1.01</v>
-      </c>
       <c r="AF305">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AG305">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK305">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P306">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="Q306">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R306">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="S306">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="T306">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U306">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V306">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W306">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X306">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y306">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z306">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA306">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AB306">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC306">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AD306">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE306">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF306">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AG306">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK306">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G307">
@@ -50359,10 +50359,10 @@
         <v>0</v>
       </c>
       <c r="Q307">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="R307">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S307">
         <v>1.45</v>
@@ -50383,31 +50383,31 @@
         <v>1.03</v>
       </c>
       <c r="Y307">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z307">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AA307">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AB307">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC307">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD307">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE307">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF307">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG307">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK307">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G309">
@@ -50685,55 +50685,55 @@
         <v>0</v>
       </c>
       <c r="Q309">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="R309">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="S309">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="T309">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="U309">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="V309">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="W309">
+        <v>1.01</v>
+      </c>
+      <c r="X309">
+        <v>1.05</v>
+      </c>
+      <c r="Y309">
+        <v>1.49</v>
+      </c>
+      <c r="Z309">
+        <v>2.41</v>
+      </c>
+      <c r="AA309">
+        <v>2.49</v>
+      </c>
+      <c r="AB309">
+        <v>1.42</v>
+      </c>
+      <c r="AC309">
+        <v>4.95</v>
+      </c>
+      <c r="AD309">
+        <v>1.11</v>
+      </c>
+      <c r="AE309">
         <v>1.03</v>
       </c>
-      <c r="X309">
-        <v>1.04</v>
-      </c>
-      <c r="Y309">
-        <v>1.4</v>
-      </c>
-      <c r="Z309">
-        <v>2.56</v>
-      </c>
-      <c r="AA309">
-        <v>2.27</v>
-      </c>
-      <c r="AB309">
-        <v>1.55</v>
-      </c>
-      <c r="AC309">
-        <v>4.15</v>
-      </c>
-      <c r="AD309">
-        <v>1.16</v>
-      </c>
-      <c r="AE309">
-        <v>1.02</v>
-      </c>
       <c r="AF309">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="AG309">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK309">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O310">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P310">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="Q310">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R310">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T310">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U310">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V310">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W310">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X310">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y310">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z310">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC310">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD310">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF310">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG310">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK310">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51165,49 +51165,49 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O312">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P312">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q312">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="R312">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S312">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T312">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="U312">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="V312">
         <v>1.61</v>
       </c>
       <c r="W312">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X312">
         <v>1.01</v>
       </c>
       <c r="Y312">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z312">
-        <v>4.8</v>
+        <v>5.11</v>
       </c>
       <c r="AA312">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AB312">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AC312">
         <v>2.45</v>
@@ -51219,10 +51219,10 @@
         <v>1.24</v>
       </c>
       <c r="AF312">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG312">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK312">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51343,7 +51343,7 @@
         <v>2.04</v>
       </c>
       <c r="S313">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T313">
         <v>2.7</v>
@@ -51367,13 +51367,13 @@
         <v>3.05</v>
       </c>
       <c r="AA313">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB313">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC313">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD313">
         <v>1.22</v>
@@ -51385,7 +51385,7 @@
         <v>1.78</v>
       </c>
       <c r="AG313">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AK313">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51491,13 +51491,13 @@
         </is>
       </c>
       <c r="N314">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="O314">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P314">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="Q314">
         <v>0</v>
@@ -51654,19 +51654,19 @@
         </is>
       </c>
       <c r="N315">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O315">
         <v>3.05</v>
       </c>
       <c r="P315">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q315">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R315">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S315">
         <v>1.46</v>
@@ -51678,31 +51678,31 @@
         <v>3.08</v>
       </c>
       <c r="V315">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W315">
         <v>1.04</v>
       </c>
       <c r="X315">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y315">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z315">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA315">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB315">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC315">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="AD315">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE315">
         <v>1.03</v>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="AK315">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O316">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P316">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q316">
         <v>0</v>
@@ -51980,7 +51980,7 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="O317">
         <v>3.6</v>
@@ -51998,46 +51998,46 @@
         <v>1.41</v>
       </c>
       <c r="T317">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U317">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="V317">
         <v>1.36</v>
       </c>
       <c r="W317">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X317">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y317">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z317">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AA317">
         <v>2.05</v>
       </c>
       <c r="AB317">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC317">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AD317">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE317">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF317">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG317">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AK317">
         <v>2.1</v>
@@ -52641,25 +52641,25 @@
         <v>0</v>
       </c>
       <c r="Q321">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="R321">
         <v>1.99</v>
       </c>
       <c r="S321">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T321">
         <v>2.81</v>
       </c>
       <c r="U321">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="V321">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W321">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X321">
         <v>1.04</v>
@@ -52671,16 +52671,16 @@
         <v>3.15</v>
       </c>
       <c r="AA321">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AB321">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC321">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="AD321">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE321">
         <v>1.05</v>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AK321">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52804,19 +52804,19 @@
         <v>0</v>
       </c>
       <c r="Q322">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R322">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="S322">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T322">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U322">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="V322">
         <v>1.45</v>
@@ -52828,7 +52828,7 @@
         <v>1.01</v>
       </c>
       <c r="Y322">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z322">
         <v>3.88</v>
@@ -52846,10 +52846,10 @@
         <v>1.35</v>
       </c>
       <c r="AE322">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF322">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG322">
         <v>2.12</v>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK322">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52958,31 +52958,31 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O323">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P323">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q323">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R323">
         <v>2.4</v>
       </c>
       <c r="S323">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T323">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U323">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V323">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W323">
         <v>1.12</v>
@@ -52991,31 +52991,31 @@
         <v>1.01</v>
       </c>
       <c r="Y323">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z323">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="AA323">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB323">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="AC323">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AD323">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE323">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AF323">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG323">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>1.17</v>
       </c>
       <c r="AK323">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53127,22 +53127,22 @@
         <v>3.65</v>
       </c>
       <c r="P324">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q324">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R324">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="S324">
         <v>1.29</v>
       </c>
       <c r="T324">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U324">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="V324">
         <v>1.5</v>
@@ -53154,16 +53154,16 @@
         <v>1</v>
       </c>
       <c r="Y324">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z324">
         <v>3.9</v>
       </c>
       <c r="AA324">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB324">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AC324">
         <v>2.82</v>
@@ -53175,10 +53175,10 @@
         <v>1.13</v>
       </c>
       <c r="AF324">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG324">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53305,10 +53305,10 @@
         <v>3.2</v>
       </c>
       <c r="U325">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V325">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W325">
         <v>1.08</v>
@@ -53320,13 +53320,13 @@
         <v>1.17</v>
       </c>
       <c r="Z325">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="AA325">
         <v>1.65</v>
       </c>
       <c r="AB325">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC325">
         <v>2.59</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK325">
         <v>1.4</v>
@@ -53447,13 +53447,13 @@
         </is>
       </c>
       <c r="N326">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O326">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P326">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q326">
         <v>0</v>
@@ -53610,13 +53610,13 @@
         </is>
       </c>
       <c r="N327">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O327">
-        <v>4.02</v>
+        <v>3.55</v>
       </c>
       <c r="P327">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q327">
         <v>2.8</v>
@@ -53625,49 +53625,49 @@
         <v>2.3</v>
       </c>
       <c r="S327">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T327">
         <v>3.45</v>
       </c>
       <c r="U327">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V327">
         <v>1.57</v>
       </c>
       <c r="W327">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X327">
         <v>1.01</v>
       </c>
       <c r="Y327">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z327">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="AA327">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB327">
+        <v>2.25</v>
+      </c>
+      <c r="AC327">
         <v>2.3</v>
       </c>
-      <c r="AC327">
-        <v>2.31</v>
-      </c>
       <c r="AD327">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE327">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF327">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG327">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK327">
         <v>1.6</v>
@@ -53773,13 +53773,13 @@
         </is>
       </c>
       <c r="N328">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O328">
         <v>3.5</v>
       </c>
       <c r="P328">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q328">
         <v>3.45</v>
@@ -53788,7 +53788,7 @@
         <v>2.28</v>
       </c>
       <c r="S328">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T328">
         <v>3.3</v>
@@ -53797,7 +53797,7 @@
         <v>2.41</v>
       </c>
       <c r="V328">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W328">
         <v>1.11</v>
@@ -53809,28 +53809,28 @@
         <v>1.18</v>
       </c>
       <c r="Z328">
-        <v>4.69</v>
+        <v>4.6</v>
       </c>
       <c r="AA328">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB328">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC328">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AD328">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE328">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF328">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG328">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AK328">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53936,49 +53936,49 @@
         </is>
       </c>
       <c r="N329">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="O329">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="P329">
         <v>2.5</v>
       </c>
       <c r="Q329">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R329">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S329">
         <v>1.3</v>
       </c>
       <c r="T329">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U329">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V329">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W329">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X329">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y329">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z329">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="AA329">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB329">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AC329">
         <v>2.63</v>
@@ -53987,13 +53987,13 @@
         <v>1.44</v>
       </c>
       <c r="AE329">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF329">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG329">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AK329">
         <v>1.5</v>
@@ -54099,34 +54099,34 @@
         </is>
       </c>
       <c r="N330">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O330">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="P330">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q330">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="R330">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="S330">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T330">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U330">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V330">
         <v>1.73</v>
       </c>
       <c r="W330">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X330">
         <v>0</v>
@@ -54138,7 +54138,7 @@
         <v>6.4</v>
       </c>
       <c r="AA330">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AB330">
         <v>2.84</v>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK330">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54262,64 +54262,64 @@
         </is>
       </c>
       <c r="N331">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O331">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="P331">
         <v>6.1</v>
       </c>
       <c r="Q331">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="R331">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="S331">
         <v>1.14</v>
       </c>
       <c r="T331">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="U331">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="V331">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="W331">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X331">
         <v>0</v>
       </c>
       <c r="Y331">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z331">
         <v>9</v>
       </c>
       <c r="AA331">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AB331">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AC331">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AD331">
         <v>2.14</v>
       </c>
       <c r="AE331">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AF331">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG331">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AH331" t="inlineStr">
         <is>
@@ -54332,10 +54332,10 @@
         </is>
       </c>
       <c r="AJ331">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK331">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AL331">
         <v>0</v>
@@ -54591,10 +54591,10 @@
         <v>1.96</v>
       </c>
       <c r="O333">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P333">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q333">
         <v>2.57</v>
@@ -54603,16 +54603,16 @@
         <v>2.2</v>
       </c>
       <c r="S333">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T333">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U333">
         <v>2.5</v>
       </c>
       <c r="V333">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W333">
         <v>1.1</v>
@@ -54621,31 +54621,31 @@
         <v>1.04</v>
       </c>
       <c r="Y333">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z333">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="AA333">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AB333">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC333">
         <v>2.88</v>
       </c>
       <c r="AD333">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE333">
         <v>1.08</v>
       </c>
       <c r="AF333">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG333">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH333" t="inlineStr">
         <is>
@@ -54658,7 +54658,7 @@
         </is>
       </c>
       <c r="AJ333">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK333">
         <v>1.7</v>
@@ -54763,7 +54763,7 @@
         <v>2.25</v>
       </c>
       <c r="R334">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="S334">
         <v>1.35</v>
@@ -54778,7 +54778,7 @@
         <v>1.41</v>
       </c>
       <c r="W334">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X334">
         <v>1</v>
@@ -54790,25 +54790,25 @@
         <v>3.34</v>
       </c>
       <c r="AA334">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB334">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC334">
         <v>2.97</v>
       </c>
       <c r="AD334">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE334">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF334">
         <v>1.75</v>
       </c>
       <c r="AG334">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH334" t="inlineStr">
         <is>
@@ -54821,10 +54821,10 @@
         </is>
       </c>
       <c r="AJ334">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK334">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AL334">
         <v>0</v>
@@ -55083,10 +55083,10 @@
         <v>3</v>
       </c>
       <c r="P336">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q336">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="R336">
         <v>2</v>
@@ -55098,7 +55098,7 @@
         <v>2.46</v>
       </c>
       <c r="U336">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="V336">
         <v>1.25</v>
@@ -55116,25 +55116,25 @@
         <v>2.49</v>
       </c>
       <c r="AA336">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AB336">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC336">
-        <v>4.39</v>
+        <v>4.67</v>
       </c>
       <c r="AD336">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE336">
         <v>1.01</v>
       </c>
       <c r="AF336">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG336">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>1.33</v>
       </c>
       <c r="AK336">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55249,7 +55249,7 @@
         <v>0</v>
       </c>
       <c r="Q337">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="R337">
         <v>2.15</v>
@@ -55258,25 +55258,25 @@
         <v>1.42</v>
       </c>
       <c r="T337">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U337">
         <v>2.85</v>
       </c>
       <c r="V337">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W337">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X337">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y337">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z337">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA337">
         <v>2.09</v>
@@ -55291,13 +55291,13 @@
         <v>1.28</v>
       </c>
       <c r="AE337">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF337">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG337">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AH337" t="inlineStr">
         <is>
@@ -55412,40 +55412,40 @@
         <v>2.4</v>
       </c>
       <c r="Q338">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="R338">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="S338">
         <v>1.39</v>
       </c>
       <c r="T338">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U338">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V338">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W338">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X338">
         <v>1.02</v>
       </c>
       <c r="Y338">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z338">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA338">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AB338">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC338">
         <v>3</v>
@@ -55460,7 +55460,7 @@
         <v>1.75</v>
       </c>
       <c r="AG338">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55566,19 +55566,19 @@
         </is>
       </c>
       <c r="N339">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="O339">
         <v>3.9</v>
       </c>
       <c r="P339">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q339">
         <v>2.15</v>
       </c>
       <c r="R339">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S339">
         <v>1.22</v>
@@ -55590,7 +55590,7 @@
         <v>2.18</v>
       </c>
       <c r="V339">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W339">
         <v>1.15</v>
@@ -55599,31 +55599,31 @@
         <v>0</v>
       </c>
       <c r="Y339">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z339">
         <v>5.5</v>
       </c>
       <c r="AA339">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AB339">
         <v>2.55</v>
       </c>
       <c r="AC339">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AD339">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE339">
         <v>1.26</v>
       </c>
       <c r="AF339">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG339">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK339">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,64 +55729,64 @@
         </is>
       </c>
       <c r="N340">
-        <v>6</v>
+        <v>1.78</v>
       </c>
       <c r="O340">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="P340">
-        <v>1.43</v>
+        <v>3.7</v>
       </c>
       <c r="Q340">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="R340">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="S340">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T340">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U340">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V340">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="W340">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X340">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y340">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z340">
-        <v>5.84</v>
+        <v>5.75</v>
       </c>
       <c r="AA340">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AB340">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC340">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AD340">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AE340">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF340">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AG340">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>2.7</v>
+        <v>1.22</v>
       </c>
       <c r="AK340">
-        <v>1.12</v>
+        <v>1.98</v>
       </c>
       <c r="AL340">
         <v>0</v>
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,64 +55892,64 @@
         </is>
       </c>
       <c r="N341">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O341">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P341">
         <v>3.7</v>
       </c>
       <c r="Q341">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R341">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="S341">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T341">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="U341">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V341">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W341">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X341">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y341">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z341">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA341">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AB341">
-        <v>2.39</v>
+        <v>2.79</v>
       </c>
       <c r="AC341">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AD341">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE341">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF341">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AG341">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AH341" t="inlineStr">
         <is>
@@ -55962,10 +55962,10 @@
         </is>
       </c>
       <c r="AJ341">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK341">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL341">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,34 +56055,34 @@
         </is>
       </c>
       <c r="N342">
-        <v>1.73</v>
+        <v>5.9</v>
       </c>
       <c r="O342">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="P342">
-        <v>3.78</v>
+        <v>1.4</v>
       </c>
       <c r="Q342">
-        <v>2.23</v>
+        <v>5.8</v>
       </c>
       <c r="R342">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S342">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T342">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U342">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V342">
         <v>1.7</v>
       </c>
       <c r="W342">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X342">
         <v>0</v>
@@ -56091,44 +56091,44 @@
         <v>1.13</v>
       </c>
       <c r="Z342">
-        <v>6</v>
+        <v>5.84</v>
       </c>
       <c r="AA342">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB342">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AC342">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AD342">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE342">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF342">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AG342">
+        <v>2.48</v>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ342">
         <v>2.7</v>
       </c>
-      <c r="AH342" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI342" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ342">
-        <v>1.25</v>
-      </c>
       <c r="AK342">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="AL342">
         <v>0</v>
@@ -56218,19 +56218,19 @@
         </is>
       </c>
       <c r="N343">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="O343">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="P343">
-        <v>8.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q343">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R343">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="S343">
         <v>1.22</v>
@@ -56239,13 +56239,13 @@
         <v>3.8</v>
       </c>
       <c r="U343">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="V343">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W343">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X343">
         <v>1.02</v>
@@ -56260,19 +56260,19 @@
         <v>1.46</v>
       </c>
       <c r="AB343">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AC343">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AD343">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE343">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF343">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG343">
         <v>1.8</v>
@@ -56288,10 +56288,10 @@
         </is>
       </c>
       <c r="AJ343">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AK343">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="AL343">
         <v>0</v>
@@ -56393,13 +56393,13 @@
         <v>2.1</v>
       </c>
       <c r="R344">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S344">
         <v>1.26</v>
       </c>
       <c r="T344">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="U344">
         <v>2.07</v>
@@ -56420,19 +56420,19 @@
         <v>4.5</v>
       </c>
       <c r="AA344">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB344">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AC344">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="AD344">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AE344">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF344">
         <v>1.55</v>
@@ -56451,7 +56451,7 @@
         </is>
       </c>
       <c r="AJ344">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK344">
         <v>1.95</v>
@@ -56553,10 +56553,10 @@
         <v>0</v>
       </c>
       <c r="Q345">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="R345">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S345">
         <v>1.3</v>
@@ -56565,25 +56565,25 @@
         <v>3.08</v>
       </c>
       <c r="U345">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V345">
         <v>1.47</v>
       </c>
       <c r="W345">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X345">
         <v>1</v>
       </c>
       <c r="Y345">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z345">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA345">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB345">
         <v>2.04</v>
@@ -56598,10 +56598,10 @@
         <v>1.12</v>
       </c>
       <c r="AF345">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG345">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AH345" t="inlineStr">
         <is>
@@ -56614,7 +56614,7 @@
         </is>
       </c>
       <c r="AJ345">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK345">
         <v>1.63</v>
@@ -56710,31 +56710,31 @@
         <v>1.85</v>
       </c>
       <c r="O346">
-        <v>4.14</v>
+        <v>3.6</v>
       </c>
       <c r="P346">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="Q346">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="R346">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S346">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T346">
         <v>3.6</v>
       </c>
       <c r="U346">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="V346">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W346">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X346">
         <v>1.03</v>
@@ -56746,16 +56746,16 @@
         <v>4.33</v>
       </c>
       <c r="AA346">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB346">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="AC346">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD346">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE346">
         <v>1.22</v>
@@ -56764,7 +56764,7 @@
         <v>1.5</v>
       </c>
       <c r="AG346">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AH346" t="inlineStr">
         <is>
@@ -56777,10 +56777,10 @@
         </is>
       </c>
       <c r="AJ346">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK346">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL346">
         <v>0</v>
@@ -56873,13 +56873,13 @@
         <v>3.55</v>
       </c>
       <c r="O347">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P347">
         <v>1.88</v>
       </c>
       <c r="Q347">
-        <v>4.36</v>
+        <v>3.6</v>
       </c>
       <c r="R347">
         <v>2.1</v>
@@ -56888,13 +56888,13 @@
         <v>1.35</v>
       </c>
       <c r="T347">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U347">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="V347">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W347">
         <v>1.03</v>
@@ -56912,13 +56912,13 @@
         <v>1.95</v>
       </c>
       <c r="AB347">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC347">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD347">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE347">
         <v>1.04</v>
@@ -56940,7 +56940,7 @@
         </is>
       </c>
       <c r="AJ347">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK347">
         <v>1.21</v>
@@ -57042,16 +57042,16 @@
         <v>3.45</v>
       </c>
       <c r="Q348">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R348">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S348">
         <v>1.32</v>
       </c>
       <c r="T348">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="U348">
         <v>2.44</v>
@@ -57060,37 +57060,37 @@
         <v>1.46</v>
       </c>
       <c r="W348">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X348">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y348">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z348">
         <v>3.95</v>
       </c>
       <c r="AA348">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AB348">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC348">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AD348">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE348">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF348">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG348">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AH348" t="inlineStr">
         <is>
@@ -57199,28 +57199,28 @@
         <v>3.1</v>
       </c>
       <c r="O349">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P349">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="Q349">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="R349">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="S349">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T349">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U349">
         <v>2.5</v>
       </c>
       <c r="V349">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W349">
         <v>1.11</v>
@@ -57229,31 +57229,31 @@
         <v>1.04</v>
       </c>
       <c r="Y349">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z349">
         <v>3.78</v>
       </c>
       <c r="AA349">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB349">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="AC349">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD349">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE349">
         <v>1.14</v>
       </c>
       <c r="AF349">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG349">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AH349" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>1.22</v>
       </c>
       <c r="AK349">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL349">
         <v>0</v>
@@ -57359,19 +57359,19 @@
         </is>
       </c>
       <c r="N350">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O350">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="P350">
         <v>3.4</v>
       </c>
       <c r="Q350">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="R350">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S350">
         <v>1.2</v>
@@ -57380,10 +57380,10 @@
         <v>4</v>
       </c>
       <c r="U350">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V350">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W350">
         <v>1.17</v>
@@ -57395,25 +57395,25 @@
         <v>1.11</v>
       </c>
       <c r="Z350">
-        <v>6.1</v>
+        <v>5.96</v>
       </c>
       <c r="AA350">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB350">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AC350">
         <v>2.05</v>
       </c>
       <c r="AD350">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE350">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF350">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG350">
         <v>2.7</v>
@@ -57429,10 +57429,10 @@
         </is>
       </c>
       <c r="AJ350">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK350">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AL350">
         <v>0</v>
@@ -57522,43 +57522,43 @@
         </is>
       </c>
       <c r="N351">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O351">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P351">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="Q351">
+        <v>1.93</v>
+      </c>
+      <c r="R351">
+        <v>2.55</v>
+      </c>
+      <c r="S351">
+        <v>1.2</v>
+      </c>
+      <c r="T351">
+        <v>3.85</v>
+      </c>
+      <c r="U351">
         <v>2.06</v>
-      </c>
-      <c r="R351">
-        <v>2.68</v>
-      </c>
-      <c r="S351">
-        <v>1.22</v>
-      </c>
-      <c r="T351">
-        <v>4.1</v>
-      </c>
-      <c r="U351">
-        <v>2.18</v>
       </c>
       <c r="V351">
         <v>1.65</v>
       </c>
       <c r="W351">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X351">
         <v>0</v>
       </c>
       <c r="Y351">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z351">
-        <v>5.47</v>
+        <v>5.8</v>
       </c>
       <c r="AA351">
         <v>1.47</v>
@@ -57570,13 +57570,13 @@
         <v>2.24</v>
       </c>
       <c r="AD351">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE351">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF351">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG351">
         <v>2.4</v>
@@ -57592,7 +57592,7 @@
         </is>
       </c>
       <c r="AJ351">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK351">
         <v>2.3</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="P17">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q17">
-        <v>2.69</v>
+        <v>3.72</v>
       </c>
       <c r="R17">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="S17">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="V17">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="Z17">
-        <v>4.3</v>
+        <v>2.86</v>
       </c>
       <c r="AA17">
-        <v>1.61</v>
+        <v>2.21</v>
       </c>
       <c r="AB17">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="AC17">
-        <v>2.6</v>
+        <v>4.15</v>
       </c>
       <c r="AD17">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AE17">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
+        <v>1.75</v>
+      </c>
+      <c r="AG17">
+        <v>1.8</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.5</v>
       </c>
-      <c r="AG17">
-        <v>2.38</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.37</v>
-      </c>
       <c r="AK17">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>2.56</v>
+        <v>3.6</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="R28">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC28">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q29">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA29">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AB29">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC29">
-        <v>2.68</v>
+        <v>3.55</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK29">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="O38">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P38">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="Q38">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S38">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="T38">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="U38">
-        <v>2.32</v>
+        <v>2.73</v>
       </c>
       <c r="V38">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W38">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="AA38">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AB38">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="AC38">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="AD38">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AE38">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="O39">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P39">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="Q39">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="R39">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T39">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="U39">
-        <v>2.73</v>
+        <v>2.32</v>
       </c>
       <c r="V39">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.13</v>
+      </c>
+      <c r="Z39">
+        <v>4.55</v>
+      </c>
+      <c r="AA39">
+        <v>1.66</v>
+      </c>
+      <c r="AB39">
+        <v>2.33</v>
+      </c>
+      <c r="AC39">
+        <v>2.43</v>
+      </c>
+      <c r="AD39">
+        <v>1.49</v>
+      </c>
+      <c r="AE39">
         <v>1.22</v>
       </c>
-      <c r="Z39">
-        <v>3.75</v>
-      </c>
-      <c r="AA39">
-        <v>1.86</v>
-      </c>
-      <c r="AB39">
-        <v>1.93</v>
-      </c>
-      <c r="AC39">
-        <v>3.1</v>
-      </c>
-      <c r="AD39">
-        <v>1.38</v>
-      </c>
-      <c r="AE39">
-        <v>1.09</v>
-      </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>2.11</v>
+        <v>2.43</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,55 +7155,55 @@
         </is>
       </c>
       <c r="N42">
+        <v>3.43</v>
+      </c>
+      <c r="O42">
+        <v>3.7</v>
+      </c>
+      <c r="P42">
+        <v>1.85</v>
+      </c>
+      <c r="Q42">
+        <v>3.6</v>
+      </c>
+      <c r="R42">
+        <v>2.38</v>
+      </c>
+      <c r="S42">
+        <v>1.2</v>
+      </c>
+      <c r="T42">
+        <v>3.66</v>
+      </c>
+      <c r="U42">
+        <v>2.1</v>
+      </c>
+      <c r="V42">
+        <v>1.65</v>
+      </c>
+      <c r="W42">
+        <v>1.17</v>
+      </c>
+      <c r="X42">
+        <v>1.02</v>
+      </c>
+      <c r="Y42">
+        <v>1.12</v>
+      </c>
+      <c r="Z42">
+        <v>5</v>
+      </c>
+      <c r="AA42">
+        <v>1.45</v>
+      </c>
+      <c r="AB42">
         <v>2.5</v>
       </c>
-      <c r="O42">
-        <v>3.75</v>
-      </c>
-      <c r="P42">
-        <v>2.55</v>
-      </c>
-      <c r="Q42">
-        <v>2.8</v>
-      </c>
-      <c r="R42">
-        <v>2.48</v>
-      </c>
-      <c r="S42">
-        <v>1.22</v>
-      </c>
-      <c r="T42">
-        <v>3.8</v>
-      </c>
-      <c r="U42">
-        <v>2.13</v>
-      </c>
-      <c r="V42">
-        <v>1.6</v>
-      </c>
-      <c r="W42">
-        <v>1.13</v>
-      </c>
-      <c r="X42">
-        <v>1.03</v>
-      </c>
-      <c r="Y42">
-        <v>1.16</v>
-      </c>
-      <c r="Z42">
-        <v>4.8</v>
-      </c>
-      <c r="AA42">
-        <v>1.47</v>
-      </c>
-      <c r="AB42">
-        <v>2.43</v>
-      </c>
       <c r="AC42">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AD42">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE42">
         <v>1.22</v>
@@ -7212,7 +7212,7 @@
         <v>1.4</v>
       </c>
       <c r="AG42">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,55 +7318,55 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.43</v>
+        <v>2.5</v>
       </c>
       <c r="O43">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P43">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="Q43">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="R43">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="S43">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="U43">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V43">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W43">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA43">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB43">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC43">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD43">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE43">
         <v>1.22</v>
@@ -7375,7 +7375,7 @@
         <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AK43">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,31 +10741,31 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.61</v>
+        <v>1.4</v>
       </c>
       <c r="O64">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="P64">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q64">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="R64">
         <v>2.31</v>
       </c>
       <c r="S64">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T64">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U64">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="V64">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W64">
         <v>1.07</v>
@@ -10774,31 +10774,31 @@
         <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z64">
-        <v>3.84</v>
+        <v>4.15</v>
       </c>
       <c r="AA64">
+        <v>1.64</v>
+      </c>
+      <c r="AB64">
+        <v>2.3</v>
+      </c>
+      <c r="AC64">
+        <v>2.56</v>
+      </c>
+      <c r="AD64">
+        <v>1.4</v>
+      </c>
+      <c r="AE64">
+        <v>1.13</v>
+      </c>
+      <c r="AF64">
         <v>1.67</v>
       </c>
-      <c r="AB64">
-        <v>1.98</v>
-      </c>
-      <c r="AC64">
-        <v>2.76</v>
-      </c>
-      <c r="AD64">
-        <v>1.39</v>
-      </c>
-      <c r="AE64">
-        <v>1.11</v>
-      </c>
-      <c r="AF64">
-        <v>1.57</v>
-      </c>
       <c r="AG64">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK64">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.4</v>
+        <v>2.61</v>
       </c>
       <c r="O65">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q65">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="R65">
         <v>2.31</v>
       </c>
       <c r="S65">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="U65">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="V65">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W65">
         <v>1.07</v>
@@ -10937,31 +10937,31 @@
         <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>4.15</v>
+        <v>3.84</v>
       </c>
       <c r="AA65">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB65">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AC65">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="AD65">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE65">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF65">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK65">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q81">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="R81">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S81">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T81">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="U81">
-        <v>3.46</v>
+        <v>2.9</v>
       </c>
       <c r="V81">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="W81">
+        <v>1.07</v>
+      </c>
+      <c r="X81">
+        <v>1.01</v>
+      </c>
+      <c r="Y81">
+        <v>1.31</v>
+      </c>
+      <c r="Z81">
+        <v>3.08</v>
+      </c>
+      <c r="AA81">
+        <v>2.14</v>
+      </c>
+      <c r="AB81">
+        <v>1.66</v>
+      </c>
+      <c r="AC81">
+        <v>3.8</v>
+      </c>
+      <c r="AD81">
+        <v>1.19</v>
+      </c>
+      <c r="AE81">
         <v>1.02</v>
       </c>
-      <c r="X81">
-        <v>1.04</v>
-      </c>
-      <c r="Y81">
-        <v>1.44</v>
-      </c>
-      <c r="Z81">
-        <v>2.65</v>
-      </c>
-      <c r="AA81">
-        <v>2.45</v>
-      </c>
-      <c r="AB81">
+      <c r="AF81">
+        <v>1.83</v>
+      </c>
+      <c r="AG81">
+        <v>1.85</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
+        <v>1.3</v>
+      </c>
+      <c r="AK81">
         <v>1.53</v>
-      </c>
-      <c r="AC81">
-        <v>4.64</v>
-      </c>
-      <c r="AD81">
-        <v>1.12</v>
-      </c>
-      <c r="AE81">
-        <v>1.01</v>
-      </c>
-      <c r="AF81">
-        <v>2.21</v>
-      </c>
-      <c r="AG81">
-        <v>1.58</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.1</v>
-      </c>
-      <c r="AK81">
-        <v>1.98</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="R82">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S82">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T82">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U82">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="V82">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="W82">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X82">
+        <v>1.04</v>
+      </c>
+      <c r="Y82">
+        <v>1.44</v>
+      </c>
+      <c r="Z82">
+        <v>2.65</v>
+      </c>
+      <c r="AA82">
+        <v>2.45</v>
+      </c>
+      <c r="AB82">
+        <v>1.53</v>
+      </c>
+      <c r="AC82">
+        <v>4.64</v>
+      </c>
+      <c r="AD82">
+        <v>1.12</v>
+      </c>
+      <c r="AE82">
         <v>1.01</v>
       </c>
-      <c r="Y82">
-        <v>1.31</v>
-      </c>
-      <c r="Z82">
-        <v>3.08</v>
-      </c>
-      <c r="AA82">
-        <v>2.14</v>
-      </c>
-      <c r="AB82">
-        <v>1.66</v>
-      </c>
-      <c r="AC82">
-        <v>3.8</v>
-      </c>
-      <c r="AD82">
-        <v>1.19</v>
-      </c>
-      <c r="AE82">
-        <v>1.02</v>
-      </c>
       <c r="AF82">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="AG82">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK82">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,65 +16609,65 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.33</v>
+        <v>4.66</v>
       </c>
       <c r="O100">
-        <v>3.62</v>
+        <v>4.62</v>
       </c>
       <c r="P100">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="Q100">
-        <v>2.98</v>
+        <v>5</v>
       </c>
       <c r="R100">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S100">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T100">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U100">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="V100">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="W100">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z100">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA100">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB100">
+        <v>2.55</v>
+      </c>
+      <c r="AC100">
         <v>2.2</v>
       </c>
-      <c r="AC100">
+      <c r="AD100">
+        <v>1.68</v>
+      </c>
+      <c r="AE100">
+        <v>1.24</v>
+      </c>
+      <c r="AF100">
+        <v>1.57</v>
+      </c>
+      <c r="AG100">
         <v>2.63</v>
       </c>
-      <c r="AD100">
-        <v>1.54</v>
-      </c>
-      <c r="AE100">
-        <v>1.15</v>
-      </c>
-      <c r="AF100">
-        <v>1.6</v>
-      </c>
-      <c r="AG100">
-        <v>2.33</v>
-      </c>
       <c r="AH100" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK100">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>4.66</v>
+        <v>2.33</v>
       </c>
       <c r="O101">
-        <v>4.62</v>
+        <v>3.62</v>
       </c>
       <c r="P101">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="Q101">
-        <v>5</v>
+        <v>2.98</v>
       </c>
       <c r="R101">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S101">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="T101">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U101">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V101">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W101">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA101">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB101">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AC101">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AD101">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AE101">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AF101">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG101">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,80 +20684,80 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O125">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P125">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Q125">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="R125">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S125">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T125">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="U125">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V125">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W125">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y125">
+        <v>1.38</v>
+      </c>
+      <c r="Z125">
+        <v>3</v>
+      </c>
+      <c r="AA125">
+        <v>2.15</v>
+      </c>
+      <c r="AB125">
+        <v>1.7</v>
+      </c>
+      <c r="AC125">
+        <v>3.58</v>
+      </c>
+      <c r="AD125">
+        <v>1.21</v>
+      </c>
+      <c r="AE125">
+        <v>1.07</v>
+      </c>
+      <c r="AF125">
+        <v>1.81</v>
+      </c>
+      <c r="AG125">
+        <v>1.9</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
         <v>1.33</v>
       </c>
-      <c r="Z125">
-        <v>3.35</v>
-      </c>
-      <c r="AA125">
-        <v>1.92</v>
-      </c>
-      <c r="AB125">
-        <v>1.76</v>
-      </c>
-      <c r="AC125">
-        <v>3.35</v>
-      </c>
-      <c r="AD125">
-        <v>1.27</v>
-      </c>
-      <c r="AE125">
-        <v>1.12</v>
-      </c>
-      <c r="AF125">
-        <v>1.71</v>
-      </c>
-      <c r="AG125">
-        <v>2</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.36</v>
-      </c>
       <c r="AK125">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O127">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P127">
+        <v>2.87</v>
+      </c>
+      <c r="Q127">
+        <v>2.88</v>
+      </c>
+      <c r="R127">
+        <v>2.04</v>
+      </c>
+      <c r="S127">
+        <v>1.41</v>
+      </c>
+      <c r="T127">
+        <v>2.62</v>
+      </c>
+      <c r="U127">
         <v>2.7</v>
       </c>
-      <c r="Q127">
-        <v>3.2</v>
-      </c>
-      <c r="R127">
-        <v>2.05</v>
-      </c>
-      <c r="S127">
-        <v>1.44</v>
-      </c>
-      <c r="T127">
-        <v>2.54</v>
-      </c>
-      <c r="U127">
-        <v>2.75</v>
-      </c>
       <c r="V127">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W127">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z127">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AA127">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB127">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC127">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="AD127">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE127">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF127">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AG127">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK127">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="O136">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P136">
-        <v>3.34</v>
+        <v>2.87</v>
       </c>
       <c r="Q136">
-        <v>2.56</v>
+        <v>2.95</v>
       </c>
       <c r="R136">
+        <v>2.1</v>
+      </c>
+      <c r="S136">
+        <v>1.36</v>
+      </c>
+      <c r="T136">
+        <v>2.8</v>
+      </c>
+      <c r="U136">
+        <v>2.89</v>
+      </c>
+      <c r="V136">
+        <v>1.34</v>
+      </c>
+      <c r="W136">
+        <v>1.04</v>
+      </c>
+      <c r="X136">
+        <v>1.04</v>
+      </c>
+      <c r="Y136">
+        <v>1.29</v>
+      </c>
+      <c r="Z136">
+        <v>2.95</v>
+      </c>
+      <c r="AA136">
         <v>2</v>
       </c>
-      <c r="S136">
-        <v>1.45</v>
-      </c>
-      <c r="T136">
-        <v>2.75</v>
-      </c>
-      <c r="U136">
-        <v>3.1</v>
-      </c>
-      <c r="V136">
-        <v>1.3</v>
-      </c>
-      <c r="W136">
-        <v>1.01</v>
-      </c>
-      <c r="X136">
-        <v>1.02</v>
-      </c>
-      <c r="Y136">
-        <v>1.32</v>
-      </c>
-      <c r="Z136">
-        <v>2.89</v>
-      </c>
-      <c r="AA136">
-        <v>2.13</v>
-      </c>
       <c r="AB136">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC136">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="AD136">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE136">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF136">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG136">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK136">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="O137">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P137">
-        <v>2.87</v>
+        <v>3.34</v>
       </c>
       <c r="Q137">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="R137">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S137">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T137">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U137">
+        <v>3.1</v>
+      </c>
+      <c r="V137">
+        <v>1.3</v>
+      </c>
+      <c r="W137">
+        <v>1.01</v>
+      </c>
+      <c r="X137">
+        <v>1.02</v>
+      </c>
+      <c r="Y137">
+        <v>1.32</v>
+      </c>
+      <c r="Z137">
         <v>2.89</v>
       </c>
-      <c r="V137">
-        <v>1.34</v>
-      </c>
-      <c r="W137">
-        <v>1.04</v>
-      </c>
-      <c r="X137">
-        <v>1.04</v>
-      </c>
-      <c r="Y137">
-        <v>1.29</v>
-      </c>
-      <c r="Z137">
-        <v>2.95</v>
-      </c>
       <c r="AA137">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AB137">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC137">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="AD137">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE137">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF137">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG137">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK137">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="O146">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="P146">
-        <v>3.9</v>
+        <v>2.67</v>
       </c>
       <c r="Q146">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="R146">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S146">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T146">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U146">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V146">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W146">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X146">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z146">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="AA146">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB146">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC146">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AD146">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE146">
         <v>1.1</v>
       </c>
       <c r="AF146">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG146">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AK146">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
+        <v>1.87</v>
+      </c>
+      <c r="O147">
+        <v>3.5</v>
+      </c>
+      <c r="P147">
+        <v>3.9</v>
+      </c>
+      <c r="Q147">
+        <v>2.38</v>
+      </c>
+      <c r="R147">
         <v>2.15</v>
       </c>
-      <c r="O147">
-        <v>3.6</v>
-      </c>
-      <c r="P147">
-        <v>2.9</v>
-      </c>
-      <c r="Q147">
-        <v>2.69</v>
-      </c>
-      <c r="R147">
-        <v>2.25</v>
-      </c>
       <c r="S147">
+        <v>1.29</v>
+      </c>
+      <c r="T147">
+        <v>3.3</v>
+      </c>
+      <c r="U147">
+        <v>2.5</v>
+      </c>
+      <c r="V147">
+        <v>1.43</v>
+      </c>
+      <c r="W147">
+        <v>1.07</v>
+      </c>
+      <c r="X147">
+        <v>1</v>
+      </c>
+      <c r="Y147">
+        <v>1.22</v>
+      </c>
+      <c r="Z147">
+        <v>3.75</v>
+      </c>
+      <c r="AA147">
+        <v>1.8</v>
+      </c>
+      <c r="AB147">
+        <v>1.93</v>
+      </c>
+      <c r="AC147">
+        <v>3</v>
+      </c>
+      <c r="AD147">
         <v>1.33</v>
-      </c>
-      <c r="T147">
-        <v>2.85</v>
-      </c>
-      <c r="U147">
-        <v>2.67</v>
-      </c>
-      <c r="V147">
-        <v>1.45</v>
-      </c>
-      <c r="W147">
-        <v>1.08</v>
-      </c>
-      <c r="X147">
-        <v>1.01</v>
-      </c>
-      <c r="Y147">
-        <v>1.21</v>
-      </c>
-      <c r="Z147">
-        <v>3.62</v>
-      </c>
-      <c r="AA147">
-        <v>1.77</v>
-      </c>
-      <c r="AB147">
-        <v>1.98</v>
-      </c>
-      <c r="AC147">
-        <v>2.99</v>
-      </c>
-      <c r="AD147">
-        <v>1.38</v>
       </c>
       <c r="AE147">
         <v>1.1</v>
       </c>
       <c r="AF147">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG147">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK147">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,52 +24433,52 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O148">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="P148">
+        <v>2.9</v>
+      </c>
+      <c r="Q148">
+        <v>2.69</v>
+      </c>
+      <c r="R148">
+        <v>2.25</v>
+      </c>
+      <c r="S148">
+        <v>1.33</v>
+      </c>
+      <c r="T148">
+        <v>2.85</v>
+      </c>
+      <c r="U148">
         <v>2.67</v>
       </c>
-      <c r="Q148">
-        <v>2.8</v>
-      </c>
-      <c r="R148">
-        <v>2.31</v>
-      </c>
-      <c r="S148">
-        <v>1.32</v>
-      </c>
-      <c r="T148">
-        <v>2.86</v>
-      </c>
-      <c r="U148">
-        <v>2.59</v>
-      </c>
       <c r="V148">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W148">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X148">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z148">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="AA148">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB148">
         <v>1.98</v>
       </c>
       <c r="AC148">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="AD148">
         <v>1.38</v>
@@ -24487,10 +24487,10 @@
         <v>1.1</v>
       </c>
       <c r="AF148">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG148">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK148">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O163">
         <v>4.2</v>
       </c>
       <c r="P163">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Q163">
         <v>1.87</v>
@@ -26902,16 +26902,16 @@
         <v>2.4</v>
       </c>
       <c r="V163">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W163">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X163">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y163">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z163">
         <v>3.9</v>
@@ -26920,13 +26920,13 @@
         <v>1.66</v>
       </c>
       <c r="AB163">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC163">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD163">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE163">
         <v>1.14</v>
@@ -26948,7 +26948,7 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK163">
         <v>2.62</v>
@@ -27041,31 +27041,31 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O164">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P164">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q164">
+        <v>2.18</v>
+      </c>
+      <c r="R164">
         <v>2.2</v>
       </c>
-      <c r="R164">
-        <v>2.19</v>
-      </c>
       <c r="S164">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T164">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U164">
         <v>2.6</v>
       </c>
       <c r="V164">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W164">
         <v>1.06</v>
@@ -27074,16 +27074,16 @@
         <v>1</v>
       </c>
       <c r="Y164">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z164">
         <v>3.4</v>
       </c>
       <c r="AA164">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB164">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC164">
         <v>3.05</v>
@@ -27114,7 +27114,7 @@
         <v>1.2</v>
       </c>
       <c r="AK164">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27213,16 +27213,16 @@
         <v>2.7</v>
       </c>
       <c r="Q165">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R165">
         <v>2.24</v>
       </c>
       <c r="S165">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T165">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U165">
         <v>2.75</v>
@@ -27237,7 +27237,7 @@
         <v>1.02</v>
       </c>
       <c r="Y165">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z165">
         <v>3.74</v>
@@ -27249,13 +27249,13 @@
         <v>1.79</v>
       </c>
       <c r="AC165">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD165">
         <v>1.35</v>
       </c>
       <c r="AE165">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF165">
         <v>1.59</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G288">
@@ -47262,71 +47262,71 @@
         <v>0</v>
       </c>
       <c r="Q288">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R288">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="S288">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T288">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="U288">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V288">
+        <v>1.32</v>
+      </c>
+      <c r="W288">
+        <v>1.02</v>
+      </c>
+      <c r="X288">
+        <v>1</v>
+      </c>
+      <c r="Y288">
+        <v>1.3</v>
+      </c>
+      <c r="Z288">
+        <v>2.97</v>
+      </c>
+      <c r="AA288">
+        <v>2.1</v>
+      </c>
+      <c r="AB288">
+        <v>1.7</v>
+      </c>
+      <c r="AC288">
+        <v>3.58</v>
+      </c>
+      <c r="AD288">
+        <v>1.21</v>
+      </c>
+      <c r="AE288">
+        <v>1.03</v>
+      </c>
+      <c r="AF288">
+        <v>1.77</v>
+      </c>
+      <c r="AG288">
+        <v>1.85</v>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ288">
         <v>1.4</v>
       </c>
-      <c r="W288">
-        <v>1.05</v>
-      </c>
-      <c r="X288">
-        <v>1.05</v>
-      </c>
-      <c r="Y288">
-        <v>1.2</v>
-      </c>
-      <c r="Z288">
-        <v>3.58</v>
-      </c>
-      <c r="AA288">
-        <v>1.85</v>
-      </c>
-      <c r="AB288">
-        <v>1.95</v>
-      </c>
-      <c r="AC288">
-        <v>2.65</v>
-      </c>
-      <c r="AD288">
-        <v>1.38</v>
-      </c>
-      <c r="AE288">
-        <v>1.08</v>
-      </c>
-      <c r="AF288">
-        <v>1.6</v>
-      </c>
-      <c r="AG288">
-        <v>2.15</v>
-      </c>
-      <c r="AH288" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI288" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ288">
-        <v>1.25</v>
-      </c>
       <c r="AK288">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G289">
@@ -47425,71 +47425,71 @@
         <v>0</v>
       </c>
       <c r="Q289">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R289">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="S289">
+        <v>1.29</v>
+      </c>
+      <c r="T289">
+        <v>2.96</v>
+      </c>
+      <c r="U289">
+        <v>2.62</v>
+      </c>
+      <c r="V289">
         <v>1.4</v>
       </c>
-      <c r="T289">
-        <v>2.62</v>
-      </c>
-      <c r="U289">
-        <v>3</v>
-      </c>
-      <c r="V289">
-        <v>1.32</v>
-      </c>
       <c r="W289">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X289">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y289">
+        <v>1.2</v>
+      </c>
+      <c r="Z289">
+        <v>3.58</v>
+      </c>
+      <c r="AA289">
+        <v>1.85</v>
+      </c>
+      <c r="AB289">
+        <v>1.95</v>
+      </c>
+      <c r="AC289">
+        <v>2.65</v>
+      </c>
+      <c r="AD289">
+        <v>1.38</v>
+      </c>
+      <c r="AE289">
+        <v>1.08</v>
+      </c>
+      <c r="AF289">
+        <v>1.6</v>
+      </c>
+      <c r="AG289">
+        <v>2.15</v>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ289">
+        <v>1.25</v>
+      </c>
+      <c r="AK289">
         <v>1.3</v>
-      </c>
-      <c r="Z289">
-        <v>2.97</v>
-      </c>
-      <c r="AA289">
-        <v>2.1</v>
-      </c>
-      <c r="AB289">
-        <v>1.7</v>
-      </c>
-      <c r="AC289">
-        <v>3.58</v>
-      </c>
-      <c r="AD289">
-        <v>1.21</v>
-      </c>
-      <c r="AE289">
-        <v>1.03</v>
-      </c>
-      <c r="AF289">
-        <v>1.77</v>
-      </c>
-      <c r="AG289">
-        <v>1.85</v>
-      </c>
-      <c r="AH289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ289">
-        <v>1.4</v>
-      </c>
-      <c r="AK289">
-        <v>1.48</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G301">
@@ -49381,55 +49381,55 @@
         <v>0</v>
       </c>
       <c r="Q301">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="R301">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S301">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T301">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U301">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="V301">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W301">
+        <v>1.05</v>
+      </c>
+      <c r="X301">
+        <v>1.01</v>
+      </c>
+      <c r="Y301">
+        <v>1.29</v>
+      </c>
+      <c r="Z301">
+        <v>3</v>
+      </c>
+      <c r="AA301">
+        <v>2</v>
+      </c>
+      <c r="AB301">
+        <v>1.71</v>
+      </c>
+      <c r="AC301">
+        <v>3.42</v>
+      </c>
+      <c r="AD301">
+        <v>1.23</v>
+      </c>
+      <c r="AE301">
         <v>1.04</v>
       </c>
-      <c r="X301">
-        <v>1.02</v>
-      </c>
-      <c r="Y301">
-        <v>1.34</v>
-      </c>
-      <c r="Z301">
-        <v>2.78</v>
-      </c>
-      <c r="AA301">
-        <v>2.15</v>
-      </c>
-      <c r="AB301">
-        <v>1.61</v>
-      </c>
-      <c r="AC301">
-        <v>3.9</v>
-      </c>
-      <c r="AD301">
-        <v>1.18</v>
-      </c>
-      <c r="AE301">
-        <v>1.02</v>
-      </c>
       <c r="AF301">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AG301">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>1.27</v>
       </c>
       <c r="AK301">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G302">
@@ -49544,55 +49544,55 @@
         <v>0</v>
       </c>
       <c r="Q302">
-        <v>3.08</v>
+        <v>2.69</v>
       </c>
       <c r="R302">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="S302">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T302">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U302">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="V302">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W302">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X302">
+        <v>1.02</v>
+      </c>
+      <c r="Y302">
+        <v>1.38</v>
+      </c>
+      <c r="Z302">
+        <v>2.8</v>
+      </c>
+      <c r="AA302">
+        <v>2.23</v>
+      </c>
+      <c r="AB302">
+        <v>1.56</v>
+      </c>
+      <c r="AC302">
+        <v>4.2</v>
+      </c>
+      <c r="AD302">
+        <v>1.15</v>
+      </c>
+      <c r="AE302">
         <v>1.01</v>
       </c>
-      <c r="Y302">
-        <v>1.29</v>
-      </c>
-      <c r="Z302">
-        <v>3</v>
-      </c>
-      <c r="AA302">
-        <v>2</v>
-      </c>
-      <c r="AB302">
-        <v>1.71</v>
-      </c>
-      <c r="AC302">
-        <v>3.42</v>
-      </c>
-      <c r="AD302">
-        <v>1.23</v>
-      </c>
-      <c r="AE302">
-        <v>1.04</v>
-      </c>
       <c r="AF302">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AG302">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49608,7 +49608,7 @@
         <v>1.27</v>
       </c>
       <c r="AK302">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G303">
@@ -49707,10 +49707,10 @@
         <v>0</v>
       </c>
       <c r="Q303">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="R303">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S303">
         <v>1.45</v>
@@ -49719,43 +49719,43 @@
         <v>2.44</v>
       </c>
       <c r="U303">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V303">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W303">
         <v>1.03</v>
       </c>
       <c r="X303">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y303">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z303">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AA303">
         <v>2.23</v>
       </c>
       <c r="AB303">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC303">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD303">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE303">
         <v>1.01</v>
       </c>
       <c r="AF303">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG303">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK303">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G304">
@@ -49870,16 +49870,16 @@
         <v>0</v>
       </c>
       <c r="Q304">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="R304">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="S304">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T304">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="U304">
         <v>3.2</v>
@@ -49891,19 +49891,19 @@
         <v>1.03</v>
       </c>
       <c r="X304">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y304">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z304">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="AA304">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AB304">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC304">
         <v>4.15</v>
@@ -49912,13 +49912,13 @@
         <v>1.16</v>
       </c>
       <c r="AE304">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF304">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AG304">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK304">
-        <v>1.49</v>
+        <v>2.35</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,64 +50024,64 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="Q305">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R305">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S305">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T305">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U305">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V305">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W305">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X305">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y305">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z305">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA305">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB305">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC305">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD305">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE305">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF305">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG305">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK305">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O306">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P306">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="Q306">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R306">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S306">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T306">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U306">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V306">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W306">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X306">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y306">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z306">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA306">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB306">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC306">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD306">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE306">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF306">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG306">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK306">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G307">
@@ -50359,55 +50359,55 @@
         <v>0</v>
       </c>
       <c r="Q307">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="R307">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="S307">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="T307">
-        <v>2.44</v>
+        <v>3.14</v>
       </c>
       <c r="U307">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="V307">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="W307">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X307">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y307">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z307">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="AA307">
-        <v>2.21</v>
+        <v>1.6</v>
       </c>
       <c r="AB307">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="AC307">
-        <v>4.05</v>
+        <v>2.46</v>
       </c>
       <c r="AD307">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AE307">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF307">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AG307">
-        <v>1.74</v>
+        <v>2.26</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK307">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G308">
@@ -50522,55 +50522,55 @@
         <v>0</v>
       </c>
       <c r="Q308">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="R308">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="S308">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="T308">
-        <v>3.14</v>
+        <v>2.28</v>
       </c>
       <c r="U308">
-        <v>2.34</v>
+        <v>3.58</v>
       </c>
       <c r="V308">
+        <v>1.21</v>
+      </c>
+      <c r="W308">
+        <v>1.01</v>
+      </c>
+      <c r="X308">
+        <v>1.05</v>
+      </c>
+      <c r="Y308">
         <v>1.49</v>
       </c>
-      <c r="W308">
+      <c r="Z308">
+        <v>2.41</v>
+      </c>
+      <c r="AA308">
+        <v>2.49</v>
+      </c>
+      <c r="AB308">
+        <v>1.42</v>
+      </c>
+      <c r="AC308">
+        <v>4.95</v>
+      </c>
+      <c r="AD308">
         <v>1.11</v>
       </c>
-      <c r="X308">
-        <v>1.02</v>
-      </c>
-      <c r="Y308">
-        <v>1.15</v>
-      </c>
-      <c r="Z308">
-        <v>4.25</v>
-      </c>
-      <c r="AA308">
-        <v>1.6</v>
-      </c>
-      <c r="AB308">
-        <v>2.12</v>
-      </c>
-      <c r="AC308">
-        <v>2.46</v>
-      </c>
-      <c r="AD308">
-        <v>1.43</v>
-      </c>
       <c r="AE308">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF308">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="AG308">
-        <v>2.26</v>
+        <v>1.58</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK308">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G309">
@@ -50685,55 +50685,55 @@
         <v>0</v>
       </c>
       <c r="Q309">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="R309">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="S309">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="T309">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="U309">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="V309">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="W309">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X309">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y309">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="Z309">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AA309">
-        <v>2.49</v>
+        <v>2.21</v>
       </c>
       <c r="AB309">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AC309">
-        <v>4.95</v>
+        <v>4.05</v>
       </c>
       <c r="AD309">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE309">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF309">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="AG309">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK309">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -52306,7 +52306,7 @@
         </is>
       </c>
       <c r="N319">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O319">
         <v>3</v>
@@ -52315,10 +52315,10 @@
         <v>3.5</v>
       </c>
       <c r="Q319">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="R319">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="S319">
         <v>1.56</v>
@@ -52333,7 +52333,7 @@
         <v>1.25</v>
       </c>
       <c r="W319">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X319">
         <v>1.07</v>
@@ -52342,10 +52342,10 @@
         <v>1.5</v>
       </c>
       <c r="Z319">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AA319">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AB319">
         <v>1.5</v>
@@ -52354,7 +52354,7 @@
         <v>4.45</v>
       </c>
       <c r="AD319">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE319">
         <v>1.01</v>
@@ -52379,7 +52379,7 @@
         <v>1.36</v>
       </c>
       <c r="AK319">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,34 +55892,34 @@
         </is>
       </c>
       <c r="N341">
-        <v>1.75</v>
+        <v>5.9</v>
       </c>
       <c r="O341">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="P341">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q341">
-        <v>2.25</v>
+        <v>5.8</v>
       </c>
       <c r="R341">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="S341">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T341">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="U341">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="V341">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W341">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X341">
         <v>0</v>
@@ -55928,44 +55928,44 @@
         <v>1.13</v>
       </c>
       <c r="Z341">
-        <v>5.6</v>
+        <v>5.84</v>
       </c>
       <c r="AA341">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB341">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AC341">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AD341">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AE341">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF341">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG341">
+        <v>2.48</v>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ341">
         <v>2.7</v>
       </c>
-      <c r="AH341" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI341" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ341">
-        <v>1.24</v>
-      </c>
       <c r="AK341">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="AL341">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,34 +56055,34 @@
         </is>
       </c>
       <c r="N342">
-        <v>5.9</v>
+        <v>1.75</v>
       </c>
       <c r="O342">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="P342">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q342">
-        <v>5.8</v>
+        <v>2.25</v>
       </c>
       <c r="R342">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="S342">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T342">
-        <v>4.33</v>
+        <v>3.88</v>
       </c>
       <c r="U342">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="V342">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W342">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X342">
         <v>0</v>
@@ -56091,29 +56091,29 @@
         <v>1.13</v>
       </c>
       <c r="Z342">
-        <v>5.84</v>
+        <v>5.6</v>
       </c>
       <c r="AA342">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AB342">
+        <v>2.79</v>
+      </c>
+      <c r="AC342">
+        <v>2.16</v>
+      </c>
+      <c r="AD342">
+        <v>1.67</v>
+      </c>
+      <c r="AE342">
+        <v>1.29</v>
+      </c>
+      <c r="AF342">
+        <v>1.4</v>
+      </c>
+      <c r="AG342">
         <v>2.7</v>
       </c>
-      <c r="AC342">
-        <v>1.92</v>
-      </c>
-      <c r="AD342">
-        <v>1.74</v>
-      </c>
-      <c r="AE342">
-        <v>1.3</v>
-      </c>
-      <c r="AF342">
-        <v>1.57</v>
-      </c>
-      <c r="AG342">
-        <v>2.48</v>
-      </c>
       <c r="AH342" t="inlineStr">
         <is>
           <t>[]</t>
@@ -56125,10 +56125,10 @@
         </is>
       </c>
       <c r="AJ342">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="AK342">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="AL342">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q28">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA28">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
-        <v>2.68</v>
+        <v>3.55</v>
       </c>
       <c r="AD28">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK28">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>2.56</v>
+        <v>3.6</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="R29">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA29">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AB29">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC29">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF29">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="P50">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
-        <v>2.13</v>
+        <v>2.89</v>
       </c>
       <c r="R50">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
         <v>2.81</v>
       </c>
       <c r="U50">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
+        <v>1.35</v>
+      </c>
+      <c r="Z50">
+        <v>3.25</v>
+      </c>
+      <c r="AA50">
+        <v>2.2</v>
+      </c>
+      <c r="AB50">
+        <v>1.7</v>
+      </c>
+      <c r="AC50">
+        <v>3.55</v>
+      </c>
+      <c r="AD50">
         <v>1.22</v>
       </c>
-      <c r="Z50">
-        <v>3.54</v>
-      </c>
-      <c r="AA50">
-        <v>1.8</v>
-      </c>
-      <c r="AB50">
-        <v>2</v>
-      </c>
-      <c r="AC50">
-        <v>2.82</v>
-      </c>
-      <c r="AD50">
-        <v>1.32</v>
-      </c>
       <c r="AE50">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF50">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG50">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.27</v>
+        <v>1.73</v>
       </c>
       <c r="O51">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="P51">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q51">
-        <v>2.89</v>
+        <v>2.13</v>
       </c>
       <c r="R51">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
         <v>2.81</v>
       </c>
       <c r="U51">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
+        <v>1.07</v>
+      </c>
+      <c r="X51">
         <v>1.02</v>
       </c>
-      <c r="X51">
-        <v>1.04</v>
-      </c>
       <c r="Y51">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="AA51">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC51">
-        <v>3.55</v>
+        <v>2.82</v>
       </c>
       <c r="AD51">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q82">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="R82">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S82">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T82">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="U82">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="V82">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W82">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X82">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z82">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="AA82">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB82">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC82">
-        <v>4.64</v>
+        <v>3.93</v>
       </c>
       <c r="AD82">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AE82">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF82">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AG82">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AK82">
-        <v>1.98</v>
+        <v>1.36</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="R83">
+        <v>2.05</v>
+      </c>
+      <c r="S83">
+        <v>1.51</v>
+      </c>
+      <c r="T83">
+        <v>2.48</v>
+      </c>
+      <c r="U83">
+        <v>3.46</v>
+      </c>
+      <c r="V83">
+        <v>1.24</v>
+      </c>
+      <c r="W83">
+        <v>1.02</v>
+      </c>
+      <c r="X83">
+        <v>1.04</v>
+      </c>
+      <c r="Y83">
+        <v>1.44</v>
+      </c>
+      <c r="Z83">
+        <v>2.65</v>
+      </c>
+      <c r="AA83">
+        <v>2.45</v>
+      </c>
+      <c r="AB83">
+        <v>1.53</v>
+      </c>
+      <c r="AC83">
+        <v>4.64</v>
+      </c>
+      <c r="AD83">
+        <v>1.12</v>
+      </c>
+      <c r="AE83">
+        <v>1.01</v>
+      </c>
+      <c r="AF83">
+        <v>2.21</v>
+      </c>
+      <c r="AG83">
+        <v>1.58</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.1</v>
+      </c>
+      <c r="AK83">
         <v>1.98</v>
-      </c>
-      <c r="S83">
-        <v>1.38</v>
-      </c>
-      <c r="T83">
-        <v>2.55</v>
-      </c>
-      <c r="U83">
-        <v>3.3</v>
-      </c>
-      <c r="V83">
-        <v>1.29</v>
-      </c>
-      <c r="W83">
-        <v>1.03</v>
-      </c>
-      <c r="X83">
-        <v>1.03</v>
-      </c>
-      <c r="Y83">
-        <v>1.35</v>
-      </c>
-      <c r="Z83">
-        <v>2.98</v>
-      </c>
-      <c r="AA83">
-        <v>2.2</v>
-      </c>
-      <c r="AB83">
-        <v>1.65</v>
-      </c>
-      <c r="AC83">
-        <v>3.93</v>
-      </c>
-      <c r="AD83">
-        <v>1.23</v>
-      </c>
-      <c r="AE83">
-        <v>1.03</v>
-      </c>
-      <c r="AF83">
-        <v>1.85</v>
-      </c>
-      <c r="AG83">
-        <v>1.84</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.28</v>
-      </c>
-      <c r="AK83">
-        <v>1.36</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>4.66</v>
+        <v>2.33</v>
       </c>
       <c r="O100">
-        <v>4.62</v>
+        <v>3.62</v>
       </c>
       <c r="P100">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="Q100">
-        <v>5</v>
+        <v>2.98</v>
       </c>
       <c r="R100">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S100">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="T100">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U100">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V100">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W100">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z100">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA100">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB100">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AC100">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AD100">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AE100">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AF100">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG100">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,65 +16772,65 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.33</v>
+        <v>4.66</v>
       </c>
       <c r="O101">
-        <v>3.62</v>
+        <v>4.62</v>
       </c>
       <c r="P101">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="Q101">
-        <v>2.98</v>
+        <v>5</v>
       </c>
       <c r="R101">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S101">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T101">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U101">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="V101">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="W101">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z101">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA101">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB101">
+        <v>2.55</v>
+      </c>
+      <c r="AC101">
         <v>2.2</v>
       </c>
-      <c r="AC101">
+      <c r="AD101">
+        <v>1.68</v>
+      </c>
+      <c r="AE101">
+        <v>1.24</v>
+      </c>
+      <c r="AF101">
+        <v>1.57</v>
+      </c>
+      <c r="AG101">
         <v>2.63</v>
       </c>
-      <c r="AD101">
-        <v>1.54</v>
-      </c>
-      <c r="AE101">
-        <v>1.15</v>
-      </c>
-      <c r="AF101">
-        <v>1.6</v>
-      </c>
-      <c r="AG101">
-        <v>2.33</v>
-      </c>
       <c r="AH101" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK101">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O122">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P122">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q122">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R122">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S122">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T122">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="U122">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="V122">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W122">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y122">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z122">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA122">
         <v>1.84</v>
       </c>
       <c r="AB122">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AC122">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD122">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE122">
         <v>1.06</v>
       </c>
       <c r="AF122">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG122">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK122">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="O123">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P123">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q123">
-        <v>2.5</v>
+        <v>3.21</v>
       </c>
       <c r="R123">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S123">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T123">
-        <v>2.84</v>
+        <v>2.59</v>
       </c>
       <c r="U123">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="V123">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W123">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X123">
         <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z123">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AA123">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB123">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC123">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD123">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE123">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF123">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG123">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AK123">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="O124">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P124">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q124">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R124">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S124">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T124">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="U124">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="V124">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W124">
         <v>1.05</v>
       </c>
       <c r="X124">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z124">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA124">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB124">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AC124">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD124">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE124">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF124">
         <v>1.83</v>
       </c>
       <c r="AG124">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK124">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O125">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P125">
+        <v>2.87</v>
+      </c>
+      <c r="Q125">
+        <v>2.88</v>
+      </c>
+      <c r="R125">
+        <v>2.04</v>
+      </c>
+      <c r="S125">
+        <v>1.41</v>
+      </c>
+      <c r="T125">
+        <v>2.62</v>
+      </c>
+      <c r="U125">
         <v>2.7</v>
       </c>
-      <c r="Q125">
-        <v>3.2</v>
-      </c>
-      <c r="R125">
-        <v>2.05</v>
-      </c>
-      <c r="S125">
-        <v>1.44</v>
-      </c>
-      <c r="T125">
-        <v>2.54</v>
-      </c>
-      <c r="U125">
-        <v>2.75</v>
-      </c>
       <c r="V125">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W125">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X125">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y125">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z125">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AA125">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB125">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC125">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="AD125">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE125">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF125">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AG125">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK125">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="O126">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P126">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q126">
-        <v>3.21</v>
+        <v>2.45</v>
       </c>
       <c r="R126">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S126">
         <v>1.36</v>
       </c>
       <c r="T126">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="U126">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="V126">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W126">
+        <v>1.04</v>
+      </c>
+      <c r="X126">
         <v>1.03</v>
-      </c>
-      <c r="X126">
-        <v>1.04</v>
       </c>
       <c r="Y126">
         <v>1.27</v>
       </c>
       <c r="Z126">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA126">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AB126">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC126">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD126">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE126">
         <v>1.06</v>
       </c>
       <c r="AF126">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG126">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AK126">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,80 +21010,80 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O127">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P127">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Q127">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="R127">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S127">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T127">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="U127">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V127">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W127">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y127">
+        <v>1.38</v>
+      </c>
+      <c r="Z127">
+        <v>3</v>
+      </c>
+      <c r="AA127">
+        <v>2.15</v>
+      </c>
+      <c r="AB127">
+        <v>1.7</v>
+      </c>
+      <c r="AC127">
+        <v>3.58</v>
+      </c>
+      <c r="AD127">
+        <v>1.21</v>
+      </c>
+      <c r="AE127">
+        <v>1.07</v>
+      </c>
+      <c r="AF127">
+        <v>1.81</v>
+      </c>
+      <c r="AG127">
+        <v>1.9</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127">
         <v>1.33</v>
       </c>
-      <c r="Z127">
-        <v>3.35</v>
-      </c>
-      <c r="AA127">
-        <v>1.92</v>
-      </c>
-      <c r="AB127">
-        <v>1.76</v>
-      </c>
-      <c r="AC127">
-        <v>3.35</v>
-      </c>
-      <c r="AD127">
-        <v>1.27</v>
-      </c>
-      <c r="AE127">
-        <v>1.12</v>
-      </c>
-      <c r="AF127">
-        <v>1.71</v>
-      </c>
-      <c r="AG127">
-        <v>2</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>1.36</v>
-      </c>
       <c r="AK127">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.64</v>
+        <v>2.17</v>
       </c>
       <c r="O145">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="P145">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="Q145">
-        <v>3.36</v>
+        <v>2.8</v>
       </c>
       <c r="R145">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="S145">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T145">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U145">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V145">
         <v>1.44</v>
       </c>
       <c r="W145">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X145">
         <v>1.02</v>
       </c>
       <c r="Y145">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z145">
-        <v>3.35</v>
+        <v>3.92</v>
       </c>
       <c r="AA145">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB145">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC145">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AD145">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE145">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG145">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AK145">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,52 +24107,52 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O146">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="P146">
+        <v>2.9</v>
+      </c>
+      <c r="Q146">
+        <v>2.69</v>
+      </c>
+      <c r="R146">
+        <v>2.25</v>
+      </c>
+      <c r="S146">
+        <v>1.33</v>
+      </c>
+      <c r="T146">
+        <v>2.85</v>
+      </c>
+      <c r="U146">
         <v>2.67</v>
       </c>
-      <c r="Q146">
-        <v>2.8</v>
-      </c>
-      <c r="R146">
-        <v>2.31</v>
-      </c>
-      <c r="S146">
-        <v>1.32</v>
-      </c>
-      <c r="T146">
-        <v>2.86</v>
-      </c>
-      <c r="U146">
-        <v>2.59</v>
-      </c>
       <c r="V146">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W146">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X146">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z146">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="AA146">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB146">
         <v>1.98</v>
       </c>
       <c r="AC146">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="AD146">
         <v>1.38</v>
@@ -24161,10 +24161,10 @@
         <v>1.1</v>
       </c>
       <c r="AF146">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG146">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK146">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.87</v>
+        <v>2.64</v>
       </c>
       <c r="O147">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P147">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q147">
-        <v>2.38</v>
+        <v>3.36</v>
       </c>
       <c r="R147">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S147">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T147">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U147">
         <v>2.5</v>
       </c>
       <c r="V147">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W147">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X147">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y147">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z147">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="AA147">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB147">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC147">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD147">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE147">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF147">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG147">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK147">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
+        <v>1.87</v>
+      </c>
+      <c r="O148">
+        <v>3.5</v>
+      </c>
+      <c r="P148">
+        <v>3.9</v>
+      </c>
+      <c r="Q148">
+        <v>2.38</v>
+      </c>
+      <c r="R148">
         <v>2.15</v>
       </c>
-      <c r="O148">
-        <v>3.6</v>
-      </c>
-      <c r="P148">
-        <v>2.9</v>
-      </c>
-      <c r="Q148">
-        <v>2.69</v>
-      </c>
-      <c r="R148">
-        <v>2.25</v>
-      </c>
       <c r="S148">
+        <v>1.29</v>
+      </c>
+      <c r="T148">
+        <v>3.3</v>
+      </c>
+      <c r="U148">
+        <v>2.5</v>
+      </c>
+      <c r="V148">
+        <v>1.43</v>
+      </c>
+      <c r="W148">
+        <v>1.07</v>
+      </c>
+      <c r="X148">
+        <v>1</v>
+      </c>
+      <c r="Y148">
+        <v>1.22</v>
+      </c>
+      <c r="Z148">
+        <v>3.75</v>
+      </c>
+      <c r="AA148">
+        <v>1.8</v>
+      </c>
+      <c r="AB148">
+        <v>1.93</v>
+      </c>
+      <c r="AC148">
+        <v>3</v>
+      </c>
+      <c r="AD148">
         <v>1.33</v>
-      </c>
-      <c r="T148">
-        <v>2.85</v>
-      </c>
-      <c r="U148">
-        <v>2.67</v>
-      </c>
-      <c r="V148">
-        <v>1.45</v>
-      </c>
-      <c r="W148">
-        <v>1.08</v>
-      </c>
-      <c r="X148">
-        <v>1.01</v>
-      </c>
-      <c r="Y148">
-        <v>1.21</v>
-      </c>
-      <c r="Z148">
-        <v>3.62</v>
-      </c>
-      <c r="AA148">
-        <v>1.77</v>
-      </c>
-      <c r="AB148">
-        <v>1.98</v>
-      </c>
-      <c r="AC148">
-        <v>2.99</v>
-      </c>
-      <c r="AD148">
-        <v>1.38</v>
       </c>
       <c r="AE148">
         <v>1.1</v>
       </c>
       <c r="AF148">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG148">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK148">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.61</v>
+        <v>2.34</v>
       </c>
       <c r="O164">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P164">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q164">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="R164">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S164">
         <v>1.33</v>
       </c>
       <c r="T164">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="U164">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V164">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W164">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X164">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y164">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z164">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="AA164">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB164">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AC164">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD164">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE164">
         <v>1.09</v>
       </c>
       <c r="AF164">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AG164">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK164">
-        <v>2.17</v>
+        <v>1.46</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.34</v>
+        <v>1.61</v>
       </c>
       <c r="O165">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P165">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q165">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="R165">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S165">
         <v>1.33</v>
       </c>
       <c r="T165">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="U165">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V165">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W165">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X165">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y165">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z165">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="AA165">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB165">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AC165">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AD165">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE165">
         <v>1.09</v>
       </c>
       <c r="AF165">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AG165">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AK165">
-        <v>1.46</v>
+        <v>2.17</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -41548,22 +41548,22 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O253">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P253">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q253">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="R253">
         <v>1.91</v>
       </c>
       <c r="S253">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="T253">
         <v>2.2</v>
@@ -41587,25 +41587,25 @@
         <v>2.33</v>
       </c>
       <c r="AA253">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="AB253">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AC253">
         <v>5.65</v>
       </c>
       <c r="AD253">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE253">
         <v>1.03</v>
       </c>
       <c r="AF253">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AG253">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>2.44</v>
       </c>
       <c r="R266">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S266">
         <v>1.57</v>
@@ -43697,7 +43697,7 @@
         <v>1.03</v>
       </c>
       <c r="X266">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y266">
         <v>1.57</v>
@@ -43709,7 +43709,7 @@
         <v>2.7</v>
       </c>
       <c r="AB266">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC266">
         <v>5.75</v>
@@ -43724,7 +43724,7 @@
         <v>2.28</v>
       </c>
       <c r="AG266">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK266">
         <v>1.92</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="O275">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P275">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="Q275">
         <v>2.45</v>
       </c>
       <c r="R275">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S275">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T275">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U275">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="V275">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W275">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X275">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y275">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z275">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="AA275">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AB275">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC275">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="AD275">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE275">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF275">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG275">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK275">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="O276">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P276">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="Q276">
         <v>2.45</v>
       </c>
       <c r="R276">
+        <v>2.15</v>
+      </c>
+      <c r="S276">
+        <v>1.41</v>
+      </c>
+      <c r="T276">
+        <v>2.88</v>
+      </c>
+      <c r="U276">
+        <v>3.05</v>
+      </c>
+      <c r="V276">
+        <v>1.36</v>
+      </c>
+      <c r="W276">
+        <v>1.06</v>
+      </c>
+      <c r="X276">
+        <v>1.03</v>
+      </c>
+      <c r="Y276">
+        <v>1.3</v>
+      </c>
+      <c r="Z276">
+        <v>3.53</v>
+      </c>
+      <c r="AA276">
         <v>2.12</v>
       </c>
-      <c r="S276">
-        <v>1.35</v>
-      </c>
-      <c r="T276">
-        <v>2.81</v>
-      </c>
-      <c r="U276">
-        <v>2.8</v>
-      </c>
-      <c r="V276">
-        <v>1.39</v>
-      </c>
-      <c r="W276">
-        <v>1.05</v>
-      </c>
-      <c r="X276">
-        <v>1.01</v>
-      </c>
-      <c r="Y276">
-        <v>1.29</v>
-      </c>
-      <c r="Z276">
-        <v>3.6</v>
-      </c>
-      <c r="AA276">
-        <v>1.94</v>
-      </c>
       <c r="AB276">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC276">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="AD276">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE276">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF276">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG276">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK276">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G288">
@@ -47262,71 +47262,71 @@
         <v>0</v>
       </c>
       <c r="Q288">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R288">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="S288">
+        <v>1.29</v>
+      </c>
+      <c r="T288">
+        <v>2.96</v>
+      </c>
+      <c r="U288">
+        <v>2.62</v>
+      </c>
+      <c r="V288">
         <v>1.4</v>
       </c>
-      <c r="T288">
-        <v>2.62</v>
-      </c>
-      <c r="U288">
-        <v>3</v>
-      </c>
-      <c r="V288">
-        <v>1.32</v>
-      </c>
       <c r="W288">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X288">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y288">
+        <v>1.2</v>
+      </c>
+      <c r="Z288">
+        <v>3.58</v>
+      </c>
+      <c r="AA288">
+        <v>1.85</v>
+      </c>
+      <c r="AB288">
+        <v>1.95</v>
+      </c>
+      <c r="AC288">
+        <v>2.65</v>
+      </c>
+      <c r="AD288">
+        <v>1.38</v>
+      </c>
+      <c r="AE288">
+        <v>1.08</v>
+      </c>
+      <c r="AF288">
+        <v>1.6</v>
+      </c>
+      <c r="AG288">
+        <v>2.15</v>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ288">
+        <v>1.25</v>
+      </c>
+      <c r="AK288">
         <v>1.3</v>
-      </c>
-      <c r="Z288">
-        <v>2.97</v>
-      </c>
-      <c r="AA288">
-        <v>2.1</v>
-      </c>
-      <c r="AB288">
-        <v>1.7</v>
-      </c>
-      <c r="AC288">
-        <v>3.58</v>
-      </c>
-      <c r="AD288">
-        <v>1.21</v>
-      </c>
-      <c r="AE288">
-        <v>1.03</v>
-      </c>
-      <c r="AF288">
-        <v>1.77</v>
-      </c>
-      <c r="AG288">
-        <v>1.85</v>
-      </c>
-      <c r="AH288" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI288" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ288">
-        <v>1.4</v>
-      </c>
-      <c r="AK288">
-        <v>1.48</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G289">
@@ -47425,71 +47425,71 @@
         <v>0</v>
       </c>
       <c r="Q289">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R289">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="S289">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T289">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="U289">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V289">
+        <v>1.32</v>
+      </c>
+      <c r="W289">
+        <v>1.02</v>
+      </c>
+      <c r="X289">
+        <v>1</v>
+      </c>
+      <c r="Y289">
+        <v>1.3</v>
+      </c>
+      <c r="Z289">
+        <v>2.97</v>
+      </c>
+      <c r="AA289">
+        <v>2.1</v>
+      </c>
+      <c r="AB289">
+        <v>1.7</v>
+      </c>
+      <c r="AC289">
+        <v>3.58</v>
+      </c>
+      <c r="AD289">
+        <v>1.21</v>
+      </c>
+      <c r="AE289">
+        <v>1.03</v>
+      </c>
+      <c r="AF289">
+        <v>1.77</v>
+      </c>
+      <c r="AG289">
+        <v>1.85</v>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ289">
         <v>1.4</v>
       </c>
-      <c r="W289">
-        <v>1.05</v>
-      </c>
-      <c r="X289">
-        <v>1.05</v>
-      </c>
-      <c r="Y289">
-        <v>1.2</v>
-      </c>
-      <c r="Z289">
-        <v>3.58</v>
-      </c>
-      <c r="AA289">
-        <v>1.85</v>
-      </c>
-      <c r="AB289">
-        <v>1.95</v>
-      </c>
-      <c r="AC289">
-        <v>2.65</v>
-      </c>
-      <c r="AD289">
-        <v>1.38</v>
-      </c>
-      <c r="AE289">
-        <v>1.08</v>
-      </c>
-      <c r="AF289">
-        <v>1.6</v>
-      </c>
-      <c r="AG289">
-        <v>2.15</v>
-      </c>
-      <c r="AH289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI289" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ289">
-        <v>1.25</v>
-      </c>
       <c r="AK289">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47579,7 +47579,7 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O290">
         <v>2.65</v>
@@ -47588,10 +47588,10 @@
         <v>3.1</v>
       </c>
       <c r="Q290">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="R290">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="S290">
         <v>1.7</v>
@@ -47603,7 +47603,7 @@
         <v>4.5</v>
       </c>
       <c r="V290">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="W290">
         <v>1.02</v>
@@ -47615,7 +47615,7 @@
         <v>1.79</v>
       </c>
       <c r="Z290">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AA290">
         <v>3.6</v>
@@ -47630,7 +47630,7 @@
         <v>1.06</v>
       </c>
       <c r="AE290">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF290">
         <v>2.5</v>
@@ -47748,19 +47748,19 @@
         <v>2.7</v>
       </c>
       <c r="P291">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="Q291">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="R291">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="S291">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="T291">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="U291">
         <v>4.15</v>
@@ -47778,16 +47778,16 @@
         <v>1.69</v>
       </c>
       <c r="Z291">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AA291">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AB291">
         <v>1.36</v>
       </c>
       <c r="AC291">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="AD291">
         <v>1.06</v>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK291">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G307">
@@ -50359,55 +50359,55 @@
         <v>0</v>
       </c>
       <c r="Q307">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="R307">
+        <v>1.94</v>
+      </c>
+      <c r="S307">
+        <v>1.45</v>
+      </c>
+      <c r="T307">
+        <v>2.44</v>
+      </c>
+      <c r="U307">
+        <v>3.2</v>
+      </c>
+      <c r="V307">
+        <v>1.27</v>
+      </c>
+      <c r="W307">
+        <v>1.03</v>
+      </c>
+      <c r="X307">
+        <v>1.03</v>
+      </c>
+      <c r="Y307">
+        <v>1.36</v>
+      </c>
+      <c r="Z307">
+        <v>2.7</v>
+      </c>
+      <c r="AA307">
         <v>2.21</v>
       </c>
-      <c r="S307">
-        <v>1.28</v>
-      </c>
-      <c r="T307">
-        <v>3.14</v>
-      </c>
-      <c r="U307">
-        <v>2.34</v>
-      </c>
-      <c r="V307">
-        <v>1.49</v>
-      </c>
-      <c r="W307">
-        <v>1.11</v>
-      </c>
-      <c r="X307">
+      <c r="AB307">
+        <v>1.58</v>
+      </c>
+      <c r="AC307">
+        <v>4.05</v>
+      </c>
+      <c r="AD307">
+        <v>1.17</v>
+      </c>
+      <c r="AE307">
         <v>1.02</v>
       </c>
-      <c r="Y307">
-        <v>1.15</v>
-      </c>
-      <c r="Z307">
-        <v>4.25</v>
-      </c>
-      <c r="AA307">
-        <v>1.6</v>
-      </c>
-      <c r="AB307">
-        <v>2.12</v>
-      </c>
-      <c r="AC307">
-        <v>2.46</v>
-      </c>
-      <c r="AD307">
-        <v>1.43</v>
-      </c>
-      <c r="AE307">
-        <v>1.14</v>
-      </c>
       <c r="AF307">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="AG307">
-        <v>2.26</v>
+        <v>1.74</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK307">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G308">
@@ -50522,71 +50522,71 @@
         <v>0</v>
       </c>
       <c r="Q308">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="R308">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="S308">
+        <v>1.28</v>
+      </c>
+      <c r="T308">
+        <v>3.14</v>
+      </c>
+      <c r="U308">
+        <v>2.34</v>
+      </c>
+      <c r="V308">
+        <v>1.49</v>
+      </c>
+      <c r="W308">
+        <v>1.11</v>
+      </c>
+      <c r="X308">
+        <v>1.02</v>
+      </c>
+      <c r="Y308">
+        <v>1.15</v>
+      </c>
+      <c r="Z308">
+        <v>4.25</v>
+      </c>
+      <c r="AA308">
+        <v>1.6</v>
+      </c>
+      <c r="AB308">
+        <v>2.12</v>
+      </c>
+      <c r="AC308">
+        <v>2.46</v>
+      </c>
+      <c r="AD308">
+        <v>1.43</v>
+      </c>
+      <c r="AE308">
+        <v>1.14</v>
+      </c>
+      <c r="AF308">
         <v>1.54</v>
       </c>
-      <c r="T308">
-        <v>2.28</v>
-      </c>
-      <c r="U308">
-        <v>3.58</v>
-      </c>
-      <c r="V308">
+      <c r="AG308">
+        <v>2.26</v>
+      </c>
+      <c r="AH308" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI308" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ308">
         <v>1.21</v>
       </c>
-      <c r="W308">
-        <v>1.01</v>
-      </c>
-      <c r="X308">
-        <v>1.05</v>
-      </c>
-      <c r="Y308">
-        <v>1.49</v>
-      </c>
-      <c r="Z308">
-        <v>2.41</v>
-      </c>
-      <c r="AA308">
-        <v>2.49</v>
-      </c>
-      <c r="AB308">
-        <v>1.42</v>
-      </c>
-      <c r="AC308">
-        <v>4.95</v>
-      </c>
-      <c r="AD308">
-        <v>1.11</v>
-      </c>
-      <c r="AE308">
-        <v>1.03</v>
-      </c>
-      <c r="AF308">
-        <v>2.18</v>
-      </c>
-      <c r="AG308">
-        <v>1.58</v>
-      </c>
-      <c r="AH308" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI308" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ308">
-        <v>1.19</v>
-      </c>
       <c r="AK308">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G309">
@@ -50685,56 +50685,56 @@
         <v>0</v>
       </c>
       <c r="Q309">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="R309">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="S309">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="T309">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="U309">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="V309">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="W309">
+        <v>1.01</v>
+      </c>
+      <c r="X309">
+        <v>1.05</v>
+      </c>
+      <c r="Y309">
+        <v>1.49</v>
+      </c>
+      <c r="Z309">
+        <v>2.41</v>
+      </c>
+      <c r="AA309">
+        <v>2.49</v>
+      </c>
+      <c r="AB309">
+        <v>1.42</v>
+      </c>
+      <c r="AC309">
+        <v>4.95</v>
+      </c>
+      <c r="AD309">
+        <v>1.11</v>
+      </c>
+      <c r="AE309">
         <v>1.03</v>
       </c>
-      <c r="X309">
-        <v>1.03</v>
-      </c>
-      <c r="Y309">
-        <v>1.36</v>
-      </c>
-      <c r="Z309">
-        <v>2.7</v>
-      </c>
-      <c r="AA309">
-        <v>2.21</v>
-      </c>
-      <c r="AB309">
+      <c r="AF309">
+        <v>2.18</v>
+      </c>
+      <c r="AG309">
         <v>1.58</v>
       </c>
-      <c r="AC309">
-        <v>4.05</v>
-      </c>
-      <c r="AD309">
-        <v>1.17</v>
-      </c>
-      <c r="AE309">
-        <v>1.02</v>
-      </c>
-      <c r="AF309">
-        <v>1.93</v>
-      </c>
-      <c r="AG309">
-        <v>1.74</v>
-      </c>
       <c r="AH309" t="inlineStr">
         <is>
           <t>[]</t>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK309">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -51346,7 +51346,7 @@
         <v>1.38</v>
       </c>
       <c r="T313">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U313">
         <v>3</v>
@@ -51361,19 +51361,19 @@
         <v>1</v>
       </c>
       <c r="Y313">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z313">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AA313">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AB313">
         <v>1.71</v>
       </c>
       <c r="AC313">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD313">
         <v>1.22</v>
@@ -52146,16 +52146,16 @@
         <v>2.2</v>
       </c>
       <c r="O318">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P318">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="Q318">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="R318">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S318">
         <v>1.29</v>
@@ -52170,22 +52170,22 @@
         <v>1.51</v>
       </c>
       <c r="W318">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X318">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y318">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z318">
         <v>4.1</v>
       </c>
       <c r="AA318">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB318">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC318">
         <v>2.63</v>
@@ -52197,10 +52197,10 @@
         <v>1.12</v>
       </c>
       <c r="AF318">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG318">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52807,19 +52807,19 @@
         <v>2.5</v>
       </c>
       <c r="R322">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S322">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T322">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U322">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V322">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W322">
         <v>1.06</v>
@@ -52828,31 +52828,31 @@
         <v>1.01</v>
       </c>
       <c r="Y322">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z322">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="AA322">
         <v>1.75</v>
       </c>
       <c r="AB322">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC322">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD322">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE322">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF322">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG322">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>1.21</v>
       </c>
       <c r="AK322">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52958,16 +52958,16 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="O323">
+        <v>3.7</v>
+      </c>
+      <c r="P323">
         <v>3.95</v>
       </c>
-      <c r="P323">
-        <v>3.85</v>
-      </c>
       <c r="Q323">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="R323">
         <v>2.4</v>
@@ -52976,13 +52976,13 @@
         <v>1.25</v>
       </c>
       <c r="T323">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U323">
         <v>2.2</v>
       </c>
       <c r="V323">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W323">
         <v>1.12</v>
@@ -52994,19 +52994,19 @@
         <v>1.16</v>
       </c>
       <c r="Z323">
-        <v>4.87</v>
+        <v>4.75</v>
       </c>
       <c r="AA323">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB323">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC323">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AD323">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE323">
         <v>1.27</v>
@@ -53015,7 +53015,7 @@
         <v>1.51</v>
       </c>
       <c r="AG323">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53121,16 +53121,16 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O324">
         <v>3.65</v>
       </c>
       <c r="P324">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q324">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R324">
         <v>2.35</v>
@@ -53139,13 +53139,13 @@
         <v>1.29</v>
       </c>
       <c r="T324">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U324">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="V324">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W324">
         <v>1.09</v>
@@ -53160,10 +53160,10 @@
         <v>3.9</v>
       </c>
       <c r="AA324">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB324">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AC324">
         <v>2.82</v>
@@ -53194,7 +53194,7 @@
         <v>1.22</v>
       </c>
       <c r="AK324">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53293,25 +53293,25 @@
         <v>0</v>
       </c>
       <c r="Q325">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="R325">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S325">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T325">
         <v>3.2</v>
       </c>
       <c r="U325">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V325">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W325">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X325">
         <v>1.03</v>
@@ -53338,10 +53338,10 @@
         <v>1.12</v>
       </c>
       <c r="AF325">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG325">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK325">
         <v>1.4</v>
@@ -54609,13 +54609,13 @@
         <v>3.1</v>
       </c>
       <c r="U333">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V333">
         <v>1.44</v>
       </c>
       <c r="W333">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X333">
         <v>1.04</v>
@@ -54624,13 +54624,13 @@
         <v>1.21</v>
       </c>
       <c r="Z333">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA333">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AB333">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AC333">
         <v>2.88</v>
@@ -54645,7 +54645,7 @@
         <v>1.67</v>
       </c>
       <c r="AG333">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH333" t="inlineStr">
         <is>
@@ -54658,10 +54658,10 @@
         </is>
       </c>
       <c r="AJ333">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK333">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL333">
         <v>0</v>
@@ -54763,16 +54763,16 @@
         <v>2.25</v>
       </c>
       <c r="R334">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S334">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T334">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="U334">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="V334">
         <v>1.41</v>
@@ -54802,7 +54802,7 @@
         <v>1.33</v>
       </c>
       <c r="AE334">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF334">
         <v>1.75</v>
@@ -54821,7 +54821,7 @@
         </is>
       </c>
       <c r="AJ334">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK334">
         <v>1.91</v>
@@ -54914,28 +54914,28 @@
         </is>
       </c>
       <c r="N335">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="O335">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P335">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q335">
         <v>2.7</v>
       </c>
       <c r="R335">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S335">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T335">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="U335">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V335">
         <v>1.35</v>
@@ -54947,31 +54947,31 @@
         <v>1.02</v>
       </c>
       <c r="Y335">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z335">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="AA335">
         <v>2</v>
       </c>
       <c r="AB335">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC335">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="AD335">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE335">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF335">
         <v>1.8</v>
       </c>
       <c r="AG335">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>1.29</v>
       </c>
       <c r="AK335">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL335">
         <v>0</v>
@@ -55442,16 +55442,16 @@
         <v>3.25</v>
       </c>
       <c r="AA338">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="AB338">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC338">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="AD338">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE338">
         <v>1.05</v>
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,34 +55892,34 @@
         </is>
       </c>
       <c r="N341">
-        <v>5.9</v>
+        <v>1.75</v>
       </c>
       <c r="O341">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="P341">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q341">
-        <v>5.8</v>
+        <v>2.25</v>
       </c>
       <c r="R341">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="S341">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T341">
-        <v>4.33</v>
+        <v>3.88</v>
       </c>
       <c r="U341">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="V341">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W341">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X341">
         <v>0</v>
@@ -55928,29 +55928,29 @@
         <v>1.13</v>
       </c>
       <c r="Z341">
-        <v>5.84</v>
+        <v>5.6</v>
       </c>
       <c r="AA341">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AB341">
+        <v>2.79</v>
+      </c>
+      <c r="AC341">
+        <v>2.16</v>
+      </c>
+      <c r="AD341">
+        <v>1.67</v>
+      </c>
+      <c r="AE341">
+        <v>1.29</v>
+      </c>
+      <c r="AF341">
+        <v>1.4</v>
+      </c>
+      <c r="AG341">
         <v>2.7</v>
       </c>
-      <c r="AC341">
-        <v>1.92</v>
-      </c>
-      <c r="AD341">
-        <v>1.74</v>
-      </c>
-      <c r="AE341">
-        <v>1.3</v>
-      </c>
-      <c r="AF341">
-        <v>1.57</v>
-      </c>
-      <c r="AG341">
-        <v>2.48</v>
-      </c>
       <c r="AH341" t="inlineStr">
         <is>
           <t>[]</t>
@@ -55962,10 +55962,10 @@
         </is>
       </c>
       <c r="AJ341">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="AK341">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="AL341">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,34 +56055,34 @@
         </is>
       </c>
       <c r="N342">
-        <v>1.75</v>
+        <v>5.9</v>
       </c>
       <c r="O342">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="P342">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q342">
-        <v>2.25</v>
+        <v>5.8</v>
       </c>
       <c r="R342">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="S342">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T342">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="U342">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="V342">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W342">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X342">
         <v>0</v>
@@ -56091,44 +56091,44 @@
         <v>1.13</v>
       </c>
       <c r="Z342">
-        <v>5.6</v>
+        <v>5.84</v>
       </c>
       <c r="AA342">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB342">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AC342">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AD342">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AE342">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF342">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG342">
+        <v>2.48</v>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ342">
         <v>2.7</v>
       </c>
-      <c r="AH342" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI342" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ342">
-        <v>1.24</v>
-      </c>
       <c r="AK342">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="AL342">
         <v>0</v>
@@ -56218,25 +56218,25 @@
         </is>
       </c>
       <c r="N343">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="O343">
-        <v>5.55</v>
+        <v>5.45</v>
       </c>
       <c r="P343">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Q343">
         <v>1.62</v>
       </c>
       <c r="R343">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="S343">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T343">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U343">
         <v>1.95</v>
@@ -56245,37 +56245,37 @@
         <v>1.66</v>
       </c>
       <c r="W343">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X343">
         <v>1.02</v>
       </c>
       <c r="Y343">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z343">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA343">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AB343">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AC343">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AD343">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE343">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF343">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AG343">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH343" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>1.05</v>
       </c>
       <c r="AK343">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AL343">
         <v>0</v>
@@ -56399,7 +56399,7 @@
         <v>1.26</v>
       </c>
       <c r="T344">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="U344">
         <v>2.07</v>
@@ -56417,28 +56417,28 @@
         <v>1.13</v>
       </c>
       <c r="Z344">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA344">
         <v>1.57</v>
       </c>
       <c r="AB344">
+        <v>2.25</v>
+      </c>
+      <c r="AC344">
         <v>2.38</v>
-      </c>
-      <c r="AC344">
-        <v>2.16</v>
       </c>
       <c r="AD344">
         <v>1.56</v>
       </c>
       <c r="AE344">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF344">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG344">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH344" t="inlineStr">
         <is>
@@ -56451,10 +56451,10 @@
         </is>
       </c>
       <c r="AJ344">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK344">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56565,7 +56565,7 @@
         <v>3.08</v>
       </c>
       <c r="U345">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V345">
         <v>1.47</v>
@@ -56614,10 +56614,10 @@
         </is>
       </c>
       <c r="AJ345">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK345">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL345">
         <v>0</v>
@@ -56903,16 +56903,16 @@
         <v>1.01</v>
       </c>
       <c r="Y347">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z347">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AA347">
         <v>1.95</v>
       </c>
       <c r="AB347">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC347">
         <v>3.34</v>
@@ -57036,25 +57036,25 @@
         <v>1.89</v>
       </c>
       <c r="O348">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P348">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q348">
         <v>2.4</v>
       </c>
       <c r="R348">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S348">
         <v>1.32</v>
       </c>
       <c r="T348">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U348">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="V348">
         <v>1.46</v>
@@ -57066,7 +57066,7 @@
         <v>1</v>
       </c>
       <c r="Y348">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z348">
         <v>3.95</v>
@@ -57196,7 +57196,7 @@
         </is>
       </c>
       <c r="N349">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O349">
         <v>3.55</v>
@@ -57208,52 +57208,52 @@
         <v>3.74</v>
       </c>
       <c r="R349">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="S349">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T349">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U349">
         <v>2.5</v>
       </c>
       <c r="V349">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W349">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X349">
         <v>1.04</v>
       </c>
       <c r="Y349">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z349">
         <v>3.78</v>
       </c>
       <c r="AA349">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB349">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC349">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD349">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE349">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF349">
         <v>1.53</v>
       </c>
       <c r="AG349">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH349" t="inlineStr">
         <is>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="O4">
         <v>3.37</v>
       </c>
       <c r="P4">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="Q4">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R4">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S4">
         <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="V4">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
         <v>1.08</v>
@@ -994,7 +994,7 @@
         <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
         <v>4.2</v>
@@ -1006,19 +1006,19 @@
         <v>2.18</v>
       </c>
       <c r="AC4">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AD4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF4">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AG4">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
         <v>1.44</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>2.56</v>
+        <v>3.6</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="R28">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z28">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AB28">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AC28">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P29">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q29">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="R29">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T29">
+        <v>2.88</v>
+      </c>
+      <c r="U29">
+        <v>2.89</v>
+      </c>
+      <c r="V29">
+        <v>1.36</v>
+      </c>
+      <c r="W29">
+        <v>1.03</v>
+      </c>
+      <c r="X29">
+        <v>1.03</v>
+      </c>
+      <c r="Y29">
+        <v>1.3</v>
+      </c>
+      <c r="Z29">
         <v>3.3</v>
       </c>
-      <c r="U29">
-        <v>2.38</v>
-      </c>
-      <c r="V29">
-        <v>1.5</v>
-      </c>
-      <c r="W29">
-        <v>1.11</v>
-      </c>
-      <c r="X29">
-        <v>1</v>
-      </c>
-      <c r="Y29">
-        <v>1.2</v>
-      </c>
-      <c r="Z29">
-        <v>4.1</v>
-      </c>
       <c r="AA29">
+        <v>1.98</v>
+      </c>
+      <c r="AB29">
+        <v>1.78</v>
+      </c>
+      <c r="AC29">
+        <v>3.38</v>
+      </c>
+      <c r="AD29">
+        <v>1.24</v>
+      </c>
+      <c r="AE29">
+        <v>1.06</v>
+      </c>
+      <c r="AF29">
         <v>1.7</v>
       </c>
-      <c r="AB29">
-        <v>2.07</v>
-      </c>
-      <c r="AC29">
-        <v>2.68</v>
-      </c>
-      <c r="AD29">
-        <v>1.42</v>
-      </c>
-      <c r="AE29">
-        <v>1.13</v>
-      </c>
-      <c r="AF29">
-        <v>1.62</v>
-      </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK29">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="O31">
+        <v>3.3</v>
+      </c>
+      <c r="P31">
+        <v>3.35</v>
+      </c>
+      <c r="Q31">
+        <v>2.65</v>
+      </c>
+      <c r="R31">
+        <v>2.16</v>
+      </c>
+      <c r="S31">
+        <v>1.39</v>
+      </c>
+      <c r="T31">
+        <v>2.88</v>
+      </c>
+      <c r="U31">
+        <v>2.88</v>
+      </c>
+      <c r="V31">
+        <v>1.36</v>
+      </c>
+      <c r="W31">
+        <v>1.04</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
+        <v>1.33</v>
+      </c>
+      <c r="Z31">
         <v>3.1</v>
       </c>
-      <c r="P31">
-        <v>2.1</v>
-      </c>
-      <c r="Q31">
-        <v>3.7</v>
-      </c>
-      <c r="R31">
-        <v>2.1</v>
-      </c>
-      <c r="S31">
-        <v>1.36</v>
-      </c>
-      <c r="T31">
-        <v>2.95</v>
-      </c>
-      <c r="U31">
-        <v>2.65</v>
-      </c>
-      <c r="V31">
-        <v>1.42</v>
-      </c>
-      <c r="W31">
-        <v>1.08</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
-        <v>1.25</v>
-      </c>
-      <c r="Z31">
-        <v>3.3</v>
-      </c>
       <c r="AA31">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AB31">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AC31">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD31">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE31">
         <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG31">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="Q32">
+        <v>3.39</v>
+      </c>
+      <c r="R32">
+        <v>2.1</v>
+      </c>
+      <c r="S32">
+        <v>1.36</v>
+      </c>
+      <c r="T32">
+        <v>2.91</v>
+      </c>
+      <c r="U32">
         <v>2.65</v>
       </c>
-      <c r="R32">
-        <v>2.16</v>
-      </c>
-      <c r="S32">
-        <v>1.39</v>
-      </c>
-      <c r="T32">
-        <v>2.88</v>
-      </c>
-      <c r="U32">
-        <v>2.88</v>
-      </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z32">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA32">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB32">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AC32">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="AD32">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q33">
-        <v>3.39</v>
+        <v>3.7</v>
       </c>
       <c r="R33">
         <v>2.1</v>
@@ -5706,7 +5706,7 @@
         <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="U33">
         <v>2.65</v>
@@ -5715,28 +5715,28 @@
         <v>1.42</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
+        <v>1.25</v>
+      </c>
+      <c r="Z33">
+        <v>3.3</v>
+      </c>
+      <c r="AA33">
+        <v>1.86</v>
+      </c>
+      <c r="AB33">
+        <v>1.82</v>
+      </c>
+      <c r="AC33">
+        <v>3.1</v>
+      </c>
+      <c r="AD33">
         <v>1.29</v>
-      </c>
-      <c r="Z33">
-        <v>3.4</v>
-      </c>
-      <c r="AA33">
-        <v>1.9</v>
-      </c>
-      <c r="AB33">
-        <v>1.78</v>
-      </c>
-      <c r="AC33">
-        <v>2.8</v>
-      </c>
-      <c r="AD33">
-        <v>1.34</v>
       </c>
       <c r="AE33">
         <v>1.05</v>
@@ -5745,7 +5745,7 @@
         <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
         <v>3.85</v>
@@ -5866,19 +5866,19 @@
         <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U34">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
         <v>1.06</v>
@@ -5899,16 +5899,16 @@
         <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE34">
         <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,40 +6014,40 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="O35">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="P35">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="Q35">
         <v>2.35</v>
       </c>
       <c r="R35">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="S35">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T35">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="U35">
+        <v>1.84</v>
+      </c>
+      <c r="V35">
         <v>1.8</v>
       </c>
-      <c r="V35">
-        <v>1.79</v>
-      </c>
       <c r="W35">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z35">
         <v>6.25</v>
@@ -6059,19 +6059,19 @@
         <v>3.1</v>
       </c>
       <c r="AC35">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AD35">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AE35">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF35">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG35">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -9600,31 +9600,31 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="O57">
         <v>5</v>
       </c>
       <c r="P57">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="Q57">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R57">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="S57">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T57">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="U57">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V57">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="W57">
         <v>1.2</v>
@@ -9633,22 +9633,22 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z57">
         <v>6.62</v>
       </c>
       <c r="AA57">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AB57">
         <v>3.14</v>
       </c>
       <c r="AC57">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AD57">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AE57">
         <v>1.33</v>
@@ -9657,7 +9657,7 @@
         <v>1.6</v>
       </c>
       <c r="AG57">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK57">
         <v>3.46</v>
@@ -9766,13 +9766,13 @@
         <v>1.59</v>
       </c>
       <c r="O58">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="P58">
-        <v>5.25</v>
+        <v>3.92</v>
       </c>
       <c r="Q58">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="R58">
         <v>2.19</v>
@@ -9787,34 +9787,34 @@
         <v>2.65</v>
       </c>
       <c r="V58">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W58">
+        <v>1.1</v>
+      </c>
+      <c r="X58">
+        <v>1.03</v>
+      </c>
+      <c r="Y58">
+        <v>1.28</v>
+      </c>
+      <c r="Z58">
+        <v>3.42</v>
+      </c>
+      <c r="AA58">
+        <v>1.86</v>
+      </c>
+      <c r="AB58">
+        <v>1.9</v>
+      </c>
+      <c r="AC58">
+        <v>3.25</v>
+      </c>
+      <c r="AD58">
+        <v>1.3</v>
+      </c>
+      <c r="AE58">
         <v>1.07</v>
-      </c>
-      <c r="X58">
-        <v>1.04</v>
-      </c>
-      <c r="Y58">
-        <v>1.23</v>
-      </c>
-      <c r="Z58">
-        <v>3.7</v>
-      </c>
-      <c r="AA58">
-        <v>1.87</v>
-      </c>
-      <c r="AB58">
-        <v>1.86</v>
-      </c>
-      <c r="AC58">
-        <v>3.15</v>
-      </c>
-      <c r="AD58">
-        <v>1.34</v>
-      </c>
-      <c r="AE58">
-        <v>1.06</v>
       </c>
       <c r="AF58">
         <v>1.8</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.98</v>
+        <v>1.48</v>
       </c>
       <c r="O65">
-        <v>3.62</v>
+        <v>4.5</v>
       </c>
       <c r="P65">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q65">
-        <v>3.35</v>
+        <v>2.02</v>
       </c>
       <c r="R65">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="S65">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="U65">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V65">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA65">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AB65">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="AC65">
-        <v>2.76</v>
+        <v>2.21</v>
       </c>
       <c r="AD65">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="AE65">
+        <v>1.22</v>
+      </c>
+      <c r="AF65">
+        <v>1.62</v>
+      </c>
+      <c r="AG65">
+        <v>2.18</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
         <v>1.11</v>
       </c>
-      <c r="AF65">
-        <v>1.57</v>
-      </c>
-      <c r="AG65">
-        <v>2.2</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.56</v>
-      </c>
       <c r="AK65">
-        <v>1.32</v>
+        <v>2.62</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,65 +11067,65 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.48</v>
+        <v>2.98</v>
       </c>
       <c r="O66">
-        <v>4.5</v>
+        <v>3.62</v>
       </c>
       <c r="P66">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q66">
-        <v>2.02</v>
+        <v>3.35</v>
       </c>
       <c r="R66">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T66">
-        <v>3.55</v>
+        <v>3.27</v>
       </c>
       <c r="U66">
+        <v>2.5</v>
+      </c>
+      <c r="V66">
+        <v>1.44</v>
+      </c>
+      <c r="W66">
+        <v>1.07</v>
+      </c>
+      <c r="X66">
+        <v>1.03</v>
+      </c>
+      <c r="Y66">
+        <v>1.18</v>
+      </c>
+      <c r="Z66">
+        <v>4</v>
+      </c>
+      <c r="AA66">
+        <v>1.67</v>
+      </c>
+      <c r="AB66">
+        <v>1.98</v>
+      </c>
+      <c r="AC66">
+        <v>2.76</v>
+      </c>
+      <c r="AD66">
+        <v>1.39</v>
+      </c>
+      <c r="AE66">
+        <v>1.11</v>
+      </c>
+      <c r="AF66">
+        <v>1.57</v>
+      </c>
+      <c r="AG66">
         <v>2.2</v>
       </c>
-      <c r="V66">
-        <v>1.62</v>
-      </c>
-      <c r="W66">
-        <v>1.13</v>
-      </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.11</v>
-      </c>
-      <c r="Z66">
-        <v>5</v>
-      </c>
-      <c r="AA66">
-        <v>1.5</v>
-      </c>
-      <c r="AB66">
-        <v>2.43</v>
-      </c>
-      <c r="AC66">
-        <v>2.21</v>
-      </c>
-      <c r="AD66">
-        <v>1.59</v>
-      </c>
-      <c r="AE66">
-        <v>1.22</v>
-      </c>
-      <c r="AF66">
-        <v>1.62</v>
-      </c>
-      <c r="AG66">
-        <v>2.18</v>
-      </c>
       <c r="AH66" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AK66">
-        <v>2.62</v>
+        <v>1.32</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>3.2</v>
       </c>
       <c r="AA72">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB72">
         <v>1.77</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R80">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="S80">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T80">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="U80">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="V80">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="W80">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y80">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Z80">
-        <v>2.98</v>
+        <v>2.57</v>
       </c>
       <c r="AA80">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AB80">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC80">
-        <v>3.93</v>
+        <v>4.64</v>
       </c>
       <c r="AD80">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AE80">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF80">
-        <v>1.84</v>
+        <v>2.21</v>
       </c>
       <c r="AG80">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK80">
-        <v>1.4</v>
+        <v>1.97</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q81">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R81">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S81">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T81">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="U81">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="V81">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W81">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z81">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="AA81">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AB81">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC81">
-        <v>4.64</v>
+        <v>3.93</v>
       </c>
       <c r="AD81">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AE81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF81">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="AG81">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK81">
-        <v>1.97</v>
+        <v>1.4</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14200,7 +14200,7 @@
         <v>1.34</v>
       </c>
       <c r="Z85">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AA85">
         <v>2.19</v>
@@ -15320,10 +15320,10 @@
         <v>2.15</v>
       </c>
       <c r="S92">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T92">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="U92">
         <v>2.73</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,65 +16609,65 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.45</v>
+        <v>4.55</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P100">
-        <v>2.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q100">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="R100">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S100">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="T100">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="U100">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="V100">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="W100">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X100">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z100">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AA100">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AB100">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC100">
+        <v>2.15</v>
+      </c>
+      <c r="AD100">
+        <v>1.67</v>
+      </c>
+      <c r="AE100">
+        <v>1.29</v>
+      </c>
+      <c r="AF100">
+        <v>1.44</v>
+      </c>
+      <c r="AG100">
         <v>2.63</v>
       </c>
-      <c r="AD100">
-        <v>1.52</v>
-      </c>
-      <c r="AE100">
-        <v>1.16</v>
-      </c>
-      <c r="AF100">
-        <v>1.47</v>
-      </c>
-      <c r="AG100">
-        <v>2.33</v>
-      </c>
       <c r="AH100" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AK100">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
-        <v>4.55</v>
+        <v>2.45</v>
       </c>
       <c r="O101">
+        <v>3.6</v>
+      </c>
+      <c r="P101">
+        <v>2.64</v>
+      </c>
+      <c r="Q101">
+        <v>2.98</v>
+      </c>
+      <c r="R101">
+        <v>2.38</v>
+      </c>
+      <c r="S101">
+        <v>1.31</v>
+      </c>
+      <c r="T101">
+        <v>3.42</v>
+      </c>
+      <c r="U101">
+        <v>2.3</v>
+      </c>
+      <c r="V101">
+        <v>1.55</v>
+      </c>
+      <c r="W101">
+        <v>1.12</v>
+      </c>
+      <c r="X101">
+        <v>1.04</v>
+      </c>
+      <c r="Y101">
+        <v>1.2</v>
+      </c>
+      <c r="Z101">
         <v>4.5</v>
       </c>
-      <c r="P101">
-        <v>1.56</v>
-      </c>
-      <c r="Q101">
-        <v>4</v>
-      </c>
-      <c r="R101">
-        <v>2.6</v>
-      </c>
-      <c r="S101">
-        <v>1.23</v>
-      </c>
-      <c r="T101">
-        <v>3.94</v>
-      </c>
-      <c r="U101">
-        <v>2.04</v>
-      </c>
-      <c r="V101">
-        <v>1.67</v>
-      </c>
-      <c r="W101">
-        <v>1.18</v>
-      </c>
-      <c r="X101">
-        <v>1.01</v>
-      </c>
-      <c r="Y101">
-        <v>1.11</v>
-      </c>
-      <c r="Z101">
-        <v>6</v>
-      </c>
       <c r="AA101">
+        <v>1.63</v>
+      </c>
+      <c r="AB101">
+        <v>2.2</v>
+      </c>
+      <c r="AC101">
+        <v>2.63</v>
+      </c>
+      <c r="AD101">
+        <v>1.52</v>
+      </c>
+      <c r="AE101">
+        <v>1.16</v>
+      </c>
+      <c r="AF101">
+        <v>1.47</v>
+      </c>
+      <c r="AG101">
+        <v>2.33</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
         <v>1.44</v>
       </c>
-      <c r="AB101">
-        <v>2.6</v>
-      </c>
-      <c r="AC101">
-        <v>2.15</v>
-      </c>
-      <c r="AD101">
-        <v>1.67</v>
-      </c>
-      <c r="AE101">
-        <v>1.29</v>
-      </c>
-      <c r="AF101">
-        <v>1.44</v>
-      </c>
-      <c r="AG101">
-        <v>2.63</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.23</v>
-      </c>
       <c r="AK101">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -19552,16 +19552,16 @@
         <v>2.08</v>
       </c>
       <c r="Q118">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="R118">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S118">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T118">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U118">
         <v>2.99</v>
@@ -19573,19 +19573,19 @@
         <v>1.03</v>
       </c>
       <c r="X118">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z118">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA118">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AB118">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC118">
         <v>3.5</v>
@@ -19597,10 +19597,10 @@
         <v>1.04</v>
       </c>
       <c r="AF118">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG118">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK118">
         <v>1.26</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>3.75</v>
+        <v>1.72</v>
       </c>
       <c r="O119">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P119">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="Q119">
-        <v>3.58</v>
+        <v>2.24</v>
       </c>
       <c r="R119">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S119">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T119">
+        <v>3.2</v>
+      </c>
+      <c r="U119">
+        <v>2.55</v>
+      </c>
+      <c r="V119">
+        <v>1.44</v>
+      </c>
+      <c r="W119">
+        <v>1.07</v>
+      </c>
+      <c r="X119">
+        <v>1.05</v>
+      </c>
+      <c r="Y119">
+        <v>1.23</v>
+      </c>
+      <c r="Z119">
+        <v>3.65</v>
+      </c>
+      <c r="AA119">
+        <v>1.8</v>
+      </c>
+      <c r="AB119">
+        <v>2</v>
+      </c>
+      <c r="AC119">
         <v>2.88</v>
       </c>
-      <c r="U119">
-        <v>2.85</v>
-      </c>
-      <c r="V119">
-        <v>1.39</v>
-      </c>
-      <c r="W119">
-        <v>1.06</v>
-      </c>
-      <c r="X119">
-        <v>1.01</v>
-      </c>
-      <c r="Y119">
-        <v>1.27</v>
-      </c>
-      <c r="Z119">
-        <v>3.14</v>
-      </c>
-      <c r="AA119">
-        <v>2</v>
-      </c>
-      <c r="AB119">
-        <v>1.76</v>
-      </c>
-      <c r="AC119">
-        <v>3.42</v>
-      </c>
       <c r="AD119">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE119">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF119">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG119">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK119">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.72</v>
+        <v>3.35</v>
       </c>
       <c r="O120">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P120">
-        <v>4.5</v>
+        <v>2.09</v>
       </c>
       <c r="Q120">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="R120">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="S120">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T120">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="U120">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V120">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W120">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X120">
         <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z120">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AA120">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB120">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC120">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AD120">
         <v>1.33</v>
       </c>
       <c r="AE120">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF120">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG120">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK120">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="O121">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P121">
-        <v>2.09</v>
+        <v>3.85</v>
       </c>
       <c r="Q121">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="R121">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S121">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T121">
-        <v>2.77</v>
+        <v>3.03</v>
       </c>
       <c r="U121">
         <v>2.75</v>
       </c>
       <c r="V121">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W121">
         <v>1.06</v>
       </c>
       <c r="X121">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z121">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA121">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB121">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC121">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AD121">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE121">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF121">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AG121">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK121">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,61 +20195,61 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="O122">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P122">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q122">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="R122">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S122">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T122">
-        <v>3.03</v>
+        <v>2.54</v>
       </c>
       <c r="U122">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="V122">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W122">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X122">
+        <v>1.07</v>
+      </c>
+      <c r="Y122">
+        <v>1.38</v>
+      </c>
+      <c r="Z122">
+        <v>3</v>
+      </c>
+      <c r="AA122">
+        <v>2.1</v>
+      </c>
+      <c r="AB122">
+        <v>1.7</v>
+      </c>
+      <c r="AC122">
+        <v>3.58</v>
+      </c>
+      <c r="AD122">
+        <v>1.25</v>
+      </c>
+      <c r="AE122">
         <v>1.03</v>
       </c>
-      <c r="Y122">
-        <v>1.27</v>
-      </c>
-      <c r="Z122">
-        <v>3.6</v>
-      </c>
-      <c r="AA122">
-        <v>1.84</v>
-      </c>
-      <c r="AB122">
-        <v>1.87</v>
-      </c>
-      <c r="AC122">
-        <v>3.15</v>
-      </c>
-      <c r="AD122">
-        <v>1.3</v>
-      </c>
-      <c r="AE122">
-        <v>1.11</v>
-      </c>
       <c r="AF122">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AG122">
         <v>1.95</v>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK122">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,80 +20358,80 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="O123">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P123">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q123">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="R123">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T123">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="U123">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="V123">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W123">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X123">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y123">
+        <v>1.33</v>
+      </c>
+      <c r="Z123">
+        <v>3.3</v>
+      </c>
+      <c r="AA123">
+        <v>1.97</v>
+      </c>
+      <c r="AB123">
+        <v>1.79</v>
+      </c>
+      <c r="AC123">
+        <v>3.35</v>
+      </c>
+      <c r="AD123">
+        <v>1.27</v>
+      </c>
+      <c r="AE123">
+        <v>1.12</v>
+      </c>
+      <c r="AF123">
+        <v>1.71</v>
+      </c>
+      <c r="AG123">
+        <v>2</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ123">
         <v>1.28</v>
       </c>
-      <c r="Z123">
-        <v>3.05</v>
-      </c>
-      <c r="AA123">
-        <v>1.95</v>
-      </c>
-      <c r="AB123">
-        <v>1.76</v>
-      </c>
-      <c r="AC123">
-        <v>3.42</v>
-      </c>
-      <c r="AD123">
-        <v>1.28</v>
-      </c>
-      <c r="AE123">
-        <v>1.09</v>
-      </c>
-      <c r="AF123">
-        <v>1.83</v>
-      </c>
-      <c r="AG123">
-        <v>1.85</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>1.25</v>
-      </c>
       <c r="AK123">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O124">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P124">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q124">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R124">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S124">
         <v>1.4</v>
       </c>
       <c r="T124">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="U124">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V124">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W124">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X124">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z124">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="AA124">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB124">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC124">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="AD124">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE124">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF124">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG124">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK124">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,28 +20684,28 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="O125">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P125">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="Q125">
+        <v>2.3</v>
+      </c>
+      <c r="R125">
+        <v>2.1</v>
+      </c>
+      <c r="S125">
+        <v>1.4</v>
+      </c>
+      <c r="T125">
+        <v>2.69</v>
+      </c>
+      <c r="U125">
         <v>2.88</v>
-      </c>
-      <c r="R125">
-        <v>2.04</v>
-      </c>
-      <c r="S125">
-        <v>1.41</v>
-      </c>
-      <c r="T125">
-        <v>2.62</v>
-      </c>
-      <c r="U125">
-        <v>2.96</v>
       </c>
       <c r="V125">
         <v>1.38</v>
@@ -20714,34 +20714,34 @@
         <v>1.05</v>
       </c>
       <c r="X125">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y125">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z125">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AA125">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AB125">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC125">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AD125">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE125">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF125">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AG125">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>1.28</v>
       </c>
       <c r="AK125">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="O126">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P126">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="Q126">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R126">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="S126">
         <v>1.36</v>
       </c>
       <c r="T126">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U126">
         <v>2.85</v>
       </c>
       <c r="V126">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W126">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X126">
         <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z126">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="AA126">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB126">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC126">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD126">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE126">
         <v>1.06</v>
       </c>
       <c r="AF126">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG126">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK126">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,61 +21010,61 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O127">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P127">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q127">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R127">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S127">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T127">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="U127">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="V127">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W127">
         <v>1.03</v>
       </c>
       <c r="X127">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z127">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AA127">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB127">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC127">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD127">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE127">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF127">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AG127">
         <v>1.95</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK127">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="O136">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="P136">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q136">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R136">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S136">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T136">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U136">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="V136">
         <v>1.34</v>
       </c>
       <c r="W136">
+        <v>1.02</v>
+      </c>
+      <c r="X136">
         <v>1.05</v>
       </c>
-      <c r="X136">
-        <v>1.04</v>
-      </c>
       <c r="Y136">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z136">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="AA136">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AB136">
         <v>1.73</v>
       </c>
       <c r="AC136">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AD136">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE136">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF136">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG136">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AK136">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="O137">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P137">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q137">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R137">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S137">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T137">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U137">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="V137">
         <v>1.34</v>
       </c>
       <c r="W137">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X137">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y137">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z137">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AA137">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AB137">
         <v>1.73</v>
       </c>
       <c r="AC137">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AD137">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE137">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF137">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG137">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AK137">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22993,7 +22993,7 @@
         <v>1.8</v>
       </c>
       <c r="W139">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X139">
         <v>1.01</v>
@@ -23129,7 +23129,7 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="O140">
         <v>3.5</v>
@@ -23138,7 +23138,7 @@
         <v>2.75</v>
       </c>
       <c r="Q140">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="R140">
         <v>2.17</v>
@@ -23150,7 +23150,7 @@
         <v>2.99</v>
       </c>
       <c r="U140">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="V140">
         <v>1.44</v>
@@ -23168,10 +23168,10 @@
         <v>3.8</v>
       </c>
       <c r="AA140">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB140">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC140">
         <v>2.72</v>
@@ -23202,7 +23202,7 @@
         <v>1.28</v>
       </c>
       <c r="AK140">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O141">
         <v>3.95</v>
@@ -23307,13 +23307,13 @@
         <v>2.25</v>
       </c>
       <c r="S141">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T141">
         <v>2.95</v>
       </c>
       <c r="U141">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="V141">
         <v>1.44</v>
@@ -23349,7 +23349,7 @@
         <v>1.67</v>
       </c>
       <c r="AG141">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P144">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="Q144">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="R144">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="S144">
+        <v>1.36</v>
+      </c>
+      <c r="T144">
+        <v>2.9</v>
+      </c>
+      <c r="U144">
+        <v>2.89</v>
+      </c>
+      <c r="V144">
+        <v>1.37</v>
+      </c>
+      <c r="W144">
+        <v>1.04</v>
+      </c>
+      <c r="X144">
+        <v>1.02</v>
+      </c>
+      <c r="Y144">
+        <v>1.28</v>
+      </c>
+      <c r="Z144">
+        <v>3.08</v>
+      </c>
+      <c r="AA144">
+        <v>1.97</v>
+      </c>
+      <c r="AB144">
+        <v>1.79</v>
+      </c>
+      <c r="AC144">
+        <v>3.52</v>
+      </c>
+      <c r="AD144">
         <v>1.29</v>
       </c>
-      <c r="T144">
-        <v>2.85</v>
-      </c>
-      <c r="U144">
-        <v>2.67</v>
-      </c>
-      <c r="V144">
-        <v>1.44</v>
-      </c>
-      <c r="W144">
-        <v>1.11</v>
-      </c>
-      <c r="X144">
-        <v>1.01</v>
-      </c>
-      <c r="Y144">
-        <v>1.26</v>
-      </c>
-      <c r="Z144">
-        <v>3.4</v>
-      </c>
-      <c r="AA144">
-        <v>1.8</v>
-      </c>
-      <c r="AB144">
-        <v>2</v>
-      </c>
-      <c r="AC144">
-        <v>2.99</v>
-      </c>
-      <c r="AD144">
-        <v>1.38</v>
-      </c>
       <c r="AE144">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF144">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG144">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
+        <v>2.15</v>
+      </c>
+      <c r="O147">
+        <v>3.5</v>
+      </c>
+      <c r="P147">
+        <v>2.75</v>
+      </c>
+      <c r="Q147">
+        <v>2.55</v>
+      </c>
+      <c r="R147">
         <v>2.25</v>
       </c>
-      <c r="O147">
-        <v>3.3</v>
-      </c>
-      <c r="P147">
-        <v>2.72</v>
-      </c>
-      <c r="Q147">
-        <v>2.78</v>
-      </c>
-      <c r="R147">
-        <v>2.04</v>
-      </c>
       <c r="S147">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T147">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U147">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="V147">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W147">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X147">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z147">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA147">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AB147">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AC147">
-        <v>3.52</v>
+        <v>2.99</v>
       </c>
       <c r="AD147">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AE147">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF147">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG147">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK147">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q151">
         <v>3</v>
@@ -26244,7 +26244,7 @@
         <v>1.22</v>
       </c>
       <c r="T159">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="U159">
         <v>2.21</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="O164">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P164">
-        <v>2.83</v>
+        <v>4.6</v>
       </c>
       <c r="Q164">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="R164">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="S164">
         <v>1.33</v>
       </c>
       <c r="T164">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U164">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V164">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W164">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X164">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y164">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z164">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="AA164">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AB164">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC164">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AD164">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE164">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF164">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AG164">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK164">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="O165">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P165">
-        <v>4.6</v>
+        <v>2.83</v>
       </c>
       <c r="Q165">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="R165">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="S165">
         <v>1.33</v>
       </c>
       <c r="T165">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U165">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V165">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W165">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X165">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y165">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z165">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="AA165">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB165">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC165">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="AD165">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE165">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF165">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AG165">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK165">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O171">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q171">
         <v>4.04</v>
@@ -28227,10 +28227,10 @@
         <v>2.04</v>
       </c>
       <c r="AC171">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AD171">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE171">
         <v>1.11</v>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="AK171">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28686,10 +28686,10 @@
         <v>2.12</v>
       </c>
       <c r="S174">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T174">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U174">
         <v>2.88</v>
@@ -28716,7 +28716,7 @@
         <v>1.75</v>
       </c>
       <c r="AC174">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD174">
         <v>1.43</v>
@@ -28741,7 +28741,7 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK174">
         <v>2.5</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G192">
@@ -35366,7 +35366,7 @@
         <v>2.91</v>
       </c>
       <c r="R215">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="S215">
         <v>1.38</v>
@@ -35375,7 +35375,7 @@
         <v>2.7</v>
       </c>
       <c r="U215">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="V215">
         <v>1.36</v>
@@ -35393,16 +35393,16 @@
         <v>3.2</v>
       </c>
       <c r="AA215">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB215">
         <v>1.8</v>
       </c>
       <c r="AC215">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD215">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE215">
         <v>1.06</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
+        <v>2.24</v>
+      </c>
+      <c r="O223">
         <v>3.3</v>
       </c>
-      <c r="O223">
-        <v>3.18</v>
-      </c>
       <c r="P223">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q223">
-        <v>3.9</v>
+        <v>2.89</v>
       </c>
       <c r="R223">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="S223">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T223">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U223">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V223">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W223">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X223">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y223">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="Z223">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AA223">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB223">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC223">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="AD223">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE223">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF223">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG223">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK223">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,64 +36821,64 @@
         </is>
       </c>
       <c r="N224">
-        <v>2.24</v>
+        <v>1.61</v>
       </c>
       <c r="O224">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P224">
+        <v>5</v>
+      </c>
+      <c r="Q224">
+        <v>2.15</v>
+      </c>
+      <c r="R224">
+        <v>2.31</v>
+      </c>
+      <c r="S224">
+        <v>1.35</v>
+      </c>
+      <c r="T224">
         <v>3.1</v>
       </c>
-      <c r="Q224">
-        <v>2.89</v>
-      </c>
-      <c r="R224">
-        <v>2.06</v>
-      </c>
-      <c r="S224">
+      <c r="U224">
+        <v>2.6</v>
+      </c>
+      <c r="V224">
         <v>1.44</v>
       </c>
-      <c r="T224">
-        <v>2.75</v>
-      </c>
-      <c r="U224">
+      <c r="W224">
+        <v>1.11</v>
+      </c>
+      <c r="X224">
+        <v>1.03</v>
+      </c>
+      <c r="Y224">
+        <v>1.22</v>
+      </c>
+      <c r="Z224">
+        <v>3.76</v>
+      </c>
+      <c r="AA224">
+        <v>1.8</v>
+      </c>
+      <c r="AB224">
+        <v>2</v>
+      </c>
+      <c r="AC224">
         <v>3</v>
       </c>
-      <c r="V224">
+      <c r="AD224">
         <v>1.36</v>
       </c>
-      <c r="W224">
-        <v>1.05</v>
-      </c>
-      <c r="X224">
-        <v>1</v>
-      </c>
-      <c r="Y224">
-        <v>1.29</v>
-      </c>
-      <c r="Z224">
-        <v>2.96</v>
-      </c>
-      <c r="AA224">
-        <v>2.05</v>
-      </c>
-      <c r="AB224">
-        <v>1.81</v>
-      </c>
-      <c r="AC224">
-        <v>3.55</v>
-      </c>
-      <c r="AD224">
-        <v>1.26</v>
-      </c>
       <c r="AE224">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF224">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG224">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK224">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="O225">
+        <v>3.18</v>
+      </c>
+      <c r="P225">
+        <v>2.25</v>
+      </c>
+      <c r="Q225">
         <v>3.9</v>
       </c>
-      <c r="P225">
-        <v>5</v>
-      </c>
-      <c r="Q225">
-        <v>2.15</v>
-      </c>
       <c r="R225">
-        <v>2.31</v>
+        <v>1.96</v>
       </c>
       <c r="S225">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T225">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="U225">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="V225">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W225">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X225">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y225">
+        <v>1.41</v>
+      </c>
+      <c r="Z225">
+        <v>2.9</v>
+      </c>
+      <c r="AA225">
+        <v>2.2</v>
+      </c>
+      <c r="AB225">
+        <v>1.71</v>
+      </c>
+      <c r="AC225">
+        <v>4.33</v>
+      </c>
+      <c r="AD225">
         <v>1.22</v>
       </c>
-      <c r="Z225">
-        <v>3.76</v>
-      </c>
-      <c r="AA225">
-        <v>1.8</v>
-      </c>
-      <c r="AB225">
-        <v>2</v>
-      </c>
-      <c r="AC225">
-        <v>3</v>
-      </c>
-      <c r="AD225">
-        <v>1.36</v>
-      </c>
       <c r="AE225">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AF225">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG225">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AK225">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -38451,7 +38451,7 @@
         </is>
       </c>
       <c r="N234">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O234">
         <v>4.15</v>
@@ -38508,7 +38508,7 @@
         <v>1.44</v>
       </c>
       <c r="AG234">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O253">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P253">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q253">
         <v>2.72</v>
@@ -41602,7 +41602,7 @@
         <v>1.03</v>
       </c>
       <c r="AF253">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AG253">
         <v>1.64</v>
@@ -43673,7 +43673,7 @@
         <v>3.1</v>
       </c>
       <c r="P266">
-        <v>5</v>
+        <v>5.57</v>
       </c>
       <c r="Q266">
         <v>2.44</v>
@@ -43724,7 +43724,7 @@
         <v>2.28</v>
       </c>
       <c r="AG266">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,80 +45134,80 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="O275">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P275">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q275">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R275">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S275">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T275">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U275">
         <v>2.8</v>
       </c>
       <c r="V275">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W275">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X275">
+        <v>1.05</v>
+      </c>
+      <c r="Y275">
+        <v>1.35</v>
+      </c>
+      <c r="Z275">
+        <v>3.4</v>
+      </c>
+      <c r="AA275">
+        <v>2.12</v>
+      </c>
+      <c r="AB275">
+        <v>1.8</v>
+      </c>
+      <c r="AC275">
+        <v>3.9</v>
+      </c>
+      <c r="AD275">
+        <v>1.24</v>
+      </c>
+      <c r="AE275">
         <v>1.06</v>
       </c>
-      <c r="Y275">
-        <v>1.29</v>
-      </c>
-      <c r="Z275">
-        <v>3.41</v>
-      </c>
-      <c r="AA275">
-        <v>1.94</v>
-      </c>
-      <c r="AB275">
-        <v>1.78</v>
-      </c>
-      <c r="AC275">
-        <v>3.4</v>
-      </c>
-      <c r="AD275">
-        <v>1.26</v>
-      </c>
-      <c r="AE275">
-        <v>1.1</v>
-      </c>
       <c r="AF275">
+        <v>1.89</v>
+      </c>
+      <c r="AG275">
+        <v>1.88</v>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ275">
+        <v>1.25</v>
+      </c>
+      <c r="AK275">
         <v>1.85</v>
-      </c>
-      <c r="AG275">
-        <v>1.94</v>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI275" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ275">
-        <v>1.22</v>
-      </c>
-      <c r="AK275">
-        <v>1.87</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O276">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P276">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q276">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R276">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S276">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T276">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U276">
         <v>2.8</v>
       </c>
       <c r="V276">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W276">
+        <v>1.08</v>
+      </c>
+      <c r="X276">
         <v>1.06</v>
       </c>
-      <c r="X276">
-        <v>1.05</v>
-      </c>
       <c r="Y276">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z276">
+        <v>3.41</v>
+      </c>
+      <c r="AA276">
+        <v>1.94</v>
+      </c>
+      <c r="AB276">
+        <v>1.78</v>
+      </c>
+      <c r="AC276">
         <v>3.4</v>
       </c>
-      <c r="AA276">
-        <v>2.12</v>
-      </c>
-      <c r="AB276">
-        <v>1.8</v>
-      </c>
-      <c r="AC276">
-        <v>3.9</v>
-      </c>
       <c r="AD276">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE276">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF276">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG276">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK276">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -46459,7 +46459,7 @@
         <v>2.88</v>
       </c>
       <c r="U283">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V283">
         <v>1.41</v>
@@ -46471,10 +46471,10 @@
         <v>1</v>
       </c>
       <c r="Y283">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z283">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA283">
         <v>1.8</v>
@@ -46508,7 +46508,7 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK283">
         <v>1.53</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
+        <v>2.5</v>
+      </c>
+      <c r="O288">
         <v>3.15</v>
       </c>
-      <c r="O288">
-        <v>3.35</v>
-      </c>
       <c r="P288">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="Q288">
-        <v>3.74</v>
+        <v>3.22</v>
       </c>
       <c r="R288">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S288">
+        <v>1.4</v>
+      </c>
+      <c r="T288">
+        <v>2.62</v>
+      </c>
+      <c r="U288">
+        <v>3</v>
+      </c>
+      <c r="V288">
         <v>1.32</v>
       </c>
-      <c r="T288">
-        <v>2.96</v>
-      </c>
-      <c r="U288">
-        <v>2.62</v>
-      </c>
-      <c r="V288">
-        <v>1.4</v>
-      </c>
       <c r="W288">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X288">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y288">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z288">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="AA288">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB288">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AC288">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD288">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE288">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF288">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AG288">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK288">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="O289">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P289">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="Q289">
-        <v>3.22</v>
+        <v>3.74</v>
       </c>
       <c r="R289">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="S289">
+        <v>1.32</v>
+      </c>
+      <c r="T289">
+        <v>2.96</v>
+      </c>
+      <c r="U289">
+        <v>2.62</v>
+      </c>
+      <c r="V289">
         <v>1.4</v>
       </c>
-      <c r="T289">
-        <v>2.62</v>
-      </c>
-      <c r="U289">
-        <v>3</v>
-      </c>
-      <c r="V289">
-        <v>1.32</v>
-      </c>
       <c r="W289">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X289">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z289">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="AA289">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB289">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AC289">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD289">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE289">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF289">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AG289">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK289">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O290">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="P290">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q290">
         <v>3.5</v>
@@ -47748,7 +47748,7 @@
         <v>2.7</v>
       </c>
       <c r="P291">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q291">
         <v>3.5</v>
@@ -47815,7 +47815,7 @@
         <v>1.36</v>
       </c>
       <c r="AK291">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G308">
@@ -50522,55 +50522,55 @@
         <v>0</v>
       </c>
       <c r="Q308">
-        <v>2.63</v>
+        <v>2.24</v>
       </c>
       <c r="R308">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="S308">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="T308">
-        <v>2.28</v>
+        <v>2.67</v>
       </c>
       <c r="U308">
-        <v>3.58</v>
+        <v>2.71</v>
       </c>
       <c r="V308">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="W308">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X308">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y308">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Z308">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="AA308">
-        <v>2.49</v>
+        <v>1.9</v>
       </c>
       <c r="AB308">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="AC308">
-        <v>5.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD308">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AE308">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF308">
-        <v>2.22</v>
+        <v>1.81</v>
       </c>
       <c r="AG308">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK308">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G309">
@@ -50685,55 +50685,55 @@
         <v>0</v>
       </c>
       <c r="Q309">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="R309">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="S309">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="T309">
-        <v>2.67</v>
+        <v>2.28</v>
       </c>
       <c r="U309">
-        <v>2.71</v>
+        <v>3.58</v>
       </c>
       <c r="V309">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="W309">
+        <v>1.04</v>
+      </c>
+      <c r="X309">
         <v>1.07</v>
       </c>
-      <c r="X309">
-        <v>1.01</v>
-      </c>
       <c r="Y309">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Z309">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AA309">
-        <v>1.9</v>
+        <v>2.49</v>
       </c>
       <c r="AB309">
-        <v>1.87</v>
+        <v>1.43</v>
       </c>
       <c r="AC309">
-        <v>3.05</v>
+        <v>5.25</v>
       </c>
       <c r="AD309">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AE309">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF309">
-        <v>1.81</v>
+        <v>2.22</v>
       </c>
       <c r="AG309">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK309">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -51328,40 +51328,40 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q313">
         <v>3.6</v>
       </c>
       <c r="R313">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="S313">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="T313">
         <v>2.75</v>
       </c>
       <c r="U313">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V313">
+        <v>1.3</v>
+      </c>
+      <c r="W313">
+        <v>1.01</v>
+      </c>
+      <c r="X313">
+        <v>1.03</v>
+      </c>
+      <c r="Y313">
         <v>1.33</v>
-      </c>
-      <c r="W313">
-        <v>1.02</v>
-      </c>
-      <c r="X313">
-        <v>1</v>
-      </c>
-      <c r="Y313">
-        <v>1.28</v>
       </c>
       <c r="Z313">
         <v>2.95</v>
@@ -51370,22 +51370,22 @@
         <v>1.98</v>
       </c>
       <c r="AB313">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AC313">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AD313">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE313">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF313">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG313">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK313">
         <v>1.3</v>
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O316">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P316">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="Q316">
         <v>0</v>
@@ -51980,19 +51980,19 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="O317">
         <v>3.6</v>
       </c>
       <c r="P317">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q317">
         <v>2.3</v>
       </c>
       <c r="R317">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S317">
         <v>1.41</v>
@@ -52010,7 +52010,7 @@
         <v>1.07</v>
       </c>
       <c r="X317">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y317">
         <v>1.34</v>
@@ -52028,13 +52028,13 @@
         <v>3.6</v>
       </c>
       <c r="AD317">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE317">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF317">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG317">
         <v>1.85</v>
@@ -52050,7 +52050,7 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AK317">
         <v>2.1</v>
@@ -52306,7 +52306,7 @@
         </is>
       </c>
       <c r="N319">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O319">
         <v>3</v>
@@ -52342,7 +52342,7 @@
         <v>1.5</v>
       </c>
       <c r="Z319">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AA319">
         <v>2.39</v>
@@ -52354,7 +52354,7 @@
         <v>4.45</v>
       </c>
       <c r="AD319">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE319">
         <v>1.01</v>
@@ -52363,7 +52363,7 @@
         <v>2.1</v>
       </c>
       <c r="AG319">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52644,16 +52644,16 @@
         <v>2.56</v>
       </c>
       <c r="R321">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S321">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T321">
         <v>2.81</v>
       </c>
       <c r="U321">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V321">
         <v>1.36</v>
@@ -52668,7 +52668,7 @@
         <v>1.3</v>
       </c>
       <c r="Z321">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AA321">
         <v>2.06</v>
@@ -52686,10 +52686,10 @@
         <v>1.05</v>
       </c>
       <c r="AF321">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG321">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52804,7 +52804,7 @@
         <v>0</v>
       </c>
       <c r="Q322">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R322">
         <v>2.2</v>
@@ -52816,10 +52816,10 @@
         <v>3.12</v>
       </c>
       <c r="U322">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V322">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W322">
         <v>1.06</v>
@@ -52828,25 +52828,25 @@
         <v>1.01</v>
       </c>
       <c r="Y322">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z322">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="AA322">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB322">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC322">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AD322">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE322">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF322">
         <v>1.62</v>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O323">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P323">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="Q323">
         <v>2.17</v>
@@ -53012,10 +53012,10 @@
         <v>1.27</v>
       </c>
       <c r="AF323">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG323">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53160,10 +53160,10 @@
         <v>3.9</v>
       </c>
       <c r="AA324">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB324">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC324">
         <v>2.82</v>
@@ -54615,7 +54615,7 @@
         <v>1.44</v>
       </c>
       <c r="W333">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X333">
         <v>1.04</v>
@@ -54751,7 +54751,7 @@
         </is>
       </c>
       <c r="N334">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O334">
         <v>3.4</v>
@@ -54790,7 +54790,7 @@
         <v>3.34</v>
       </c>
       <c r="AA334">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB334">
         <v>1.88</v>
@@ -55249,7 +55249,7 @@
         <v>0</v>
       </c>
       <c r="Q337">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="R337">
         <v>2.15</v>
@@ -55270,13 +55270,13 @@
         <v>1.08</v>
       </c>
       <c r="X337">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y337">
         <v>1.3</v>
       </c>
       <c r="Z337">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA337">
         <v>2.09</v>
@@ -55291,10 +55291,10 @@
         <v>1.28</v>
       </c>
       <c r="AE337">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF337">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG337">
         <v>2.02</v>
@@ -55409,7 +55409,7 @@
         <v>3.2</v>
       </c>
       <c r="P338">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q338">
         <v>3.25</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,40 +55566,40 @@
         </is>
       </c>
       <c r="N339">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="O339">
-        <v>3.95</v>
+        <v>4.44</v>
       </c>
       <c r="P339">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q339">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="R339">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S339">
         <v>1.22</v>
       </c>
       <c r="T339">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U339">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V339">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W339">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X339">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y339">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z339">
         <v>5.25</v>
@@ -55608,22 +55608,22 @@
         <v>1.47</v>
       </c>
       <c r="AB339">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AC339">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AD339">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE339">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF339">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG339">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK339">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,64 +55729,64 @@
         </is>
       </c>
       <c r="N340">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O340">
-        <v>4.44</v>
+        <v>4</v>
       </c>
       <c r="P340">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q340">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R340">
         <v>2.4</v>
       </c>
       <c r="S340">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T340">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="U340">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V340">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W340">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X340">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y340">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z340">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA340">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB340">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="AC340">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AD340">
         <v>1.67</v>
       </c>
       <c r="AE340">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF340">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG340">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK340">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AL340">
         <v>0</v>
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,31 +55892,31 @@
         </is>
       </c>
       <c r="N341">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="O341">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="P341">
-        <v>3.6</v>
+        <v>1.39</v>
       </c>
       <c r="Q341">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="R341">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S341">
         <v>1.2</v>
       </c>
       <c r="T341">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="U341">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V341">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W341">
         <v>1.17</v>
@@ -55925,47 +55925,47 @@
         <v>0</v>
       </c>
       <c r="Y341">
+        <v>1.13</v>
+      </c>
+      <c r="Z341">
+        <v>5.9</v>
+      </c>
+      <c r="AA341">
+        <v>1.43</v>
+      </c>
+      <c r="AB341">
+        <v>2.8</v>
+      </c>
+      <c r="AC341">
+        <v>1.92</v>
+      </c>
+      <c r="AD341">
+        <v>1.75</v>
+      </c>
+      <c r="AE341">
+        <v>1.31</v>
+      </c>
+      <c r="AF341">
+        <v>1.57</v>
+      </c>
+      <c r="AG341">
+        <v>2.45</v>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ341">
+        <v>2.75</v>
+      </c>
+      <c r="AK341">
         <v>1.12</v>
-      </c>
-      <c r="Z341">
-        <v>5.6</v>
-      </c>
-      <c r="AA341">
-        <v>1.46</v>
-      </c>
-      <c r="AB341">
-        <v>2.61</v>
-      </c>
-      <c r="AC341">
-        <v>2.09</v>
-      </c>
-      <c r="AD341">
-        <v>1.67</v>
-      </c>
-      <c r="AE341">
-        <v>1.26</v>
-      </c>
-      <c r="AF341">
-        <v>1.4</v>
-      </c>
-      <c r="AG341">
-        <v>2.7</v>
-      </c>
-      <c r="AH341" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI341" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ341">
-        <v>1.24</v>
-      </c>
-      <c r="AK341">
-        <v>2</v>
       </c>
       <c r="AL341">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,80 +56055,80 @@
         </is>
       </c>
       <c r="N342">
-        <v>6</v>
+        <v>1.63</v>
       </c>
       <c r="O342">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="P342">
-        <v>1.39</v>
+        <v>4</v>
       </c>
       <c r="Q342">
-        <v>5</v>
+        <v>2.06</v>
       </c>
       <c r="R342">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="S342">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T342">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="U342">
+        <v>2.18</v>
+      </c>
+      <c r="V342">
+        <v>1.62</v>
+      </c>
+      <c r="W342">
+        <v>1.15</v>
+      </c>
+      <c r="X342">
+        <v>0</v>
+      </c>
+      <c r="Y342">
+        <v>1.15</v>
+      </c>
+      <c r="Z342">
+        <v>5.25</v>
+      </c>
+      <c r="AA342">
+        <v>1.47</v>
+      </c>
+      <c r="AB342">
+        <v>2.55</v>
+      </c>
+      <c r="AC342">
+        <v>2.13</v>
+      </c>
+      <c r="AD342">
+        <v>1.62</v>
+      </c>
+      <c r="AE342">
+        <v>1.26</v>
+      </c>
+      <c r="AF342">
+        <v>1.5</v>
+      </c>
+      <c r="AG342">
+        <v>2.4</v>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ342">
+        <v>1.15</v>
+      </c>
+      <c r="AK342">
         <v>2.1</v>
-      </c>
-      <c r="V342">
-        <v>1.71</v>
-      </c>
-      <c r="W342">
-        <v>1.17</v>
-      </c>
-      <c r="X342">
-        <v>0</v>
-      </c>
-      <c r="Y342">
-        <v>1.13</v>
-      </c>
-      <c r="Z342">
-        <v>5.9</v>
-      </c>
-      <c r="AA342">
-        <v>1.43</v>
-      </c>
-      <c r="AB342">
-        <v>2.8</v>
-      </c>
-      <c r="AC342">
-        <v>1.92</v>
-      </c>
-      <c r="AD342">
-        <v>1.75</v>
-      </c>
-      <c r="AE342">
-        <v>1.31</v>
-      </c>
-      <c r="AF342">
-        <v>1.57</v>
-      </c>
-      <c r="AG342">
-        <v>2.45</v>
-      </c>
-      <c r="AH342" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI342" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ342">
-        <v>2.75</v>
-      </c>
-      <c r="AK342">
-        <v>1.12</v>
       </c>
       <c r="AL342">
         <v>0</v>
@@ -56381,25 +56381,25 @@
         </is>
       </c>
       <c r="N344">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O344">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P344">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q344">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R344">
         <v>2.45</v>
       </c>
       <c r="S344">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T344">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="U344">
         <v>2.07</v>
@@ -56414,31 +56414,31 @@
         <v>1.01</v>
       </c>
       <c r="Y344">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z344">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="AA344">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB344">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC344">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AD344">
         <v>1.56</v>
       </c>
       <c r="AE344">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF344">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG344">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH344" t="inlineStr">
         <is>
@@ -56454,7 +56454,7 @@
         <v>1.2</v>
       </c>
       <c r="AK344">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56544,58 +56544,58 @@
         </is>
       </c>
       <c r="N345">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O345">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P345">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q345">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="R345">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S345">
         <v>1.3</v>
       </c>
       <c r="T345">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="U345">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V345">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W345">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X345">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y345">
         <v>1.2</v>
       </c>
       <c r="Z345">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AA345">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AB345">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AC345">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AD345">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE345">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF345">
         <v>1.57</v>
@@ -56617,7 +56617,7 @@
         <v>1.29</v>
       </c>
       <c r="AK345">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL345">
         <v>0</v>
@@ -56870,10 +56870,10 @@
         </is>
       </c>
       <c r="N347">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O347">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P347">
         <v>1.88</v>
@@ -57036,7 +57036,7 @@
         <v>1.89</v>
       </c>
       <c r="O348">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P348">
         <v>3.55</v>
@@ -57196,13 +57196,13 @@
         </is>
       </c>
       <c r="N349">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O349">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P349">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="Q349">
         <v>3.74</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q15">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="R15">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="S15">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="U15">
-        <v>2.96</v>
+        <v>2.25</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
+        <v>1.09</v>
+      </c>
+      <c r="X15">
         <v>1.03</v>
       </c>
-      <c r="X15">
-        <v>1.02</v>
-      </c>
       <c r="Y15">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="AA15">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="AB15">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AC15">
-        <v>3.58</v>
+        <v>2.6</v>
       </c>
       <c r="AD15">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.23</v>
+        <v>2.87</v>
       </c>
       <c r="O16">
-        <v>3.61</v>
+        <v>2.98</v>
       </c>
       <c r="P16">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="Q16">
-        <v>2.69</v>
+        <v>3.72</v>
       </c>
       <c r="R16">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="U16">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
+        <v>1.36</v>
+      </c>
+      <c r="W16">
+        <v>1.04</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>1.39</v>
+      </c>
+      <c r="Z16">
+        <v>2.74</v>
+      </c>
+      <c r="AA16">
+        <v>2.15</v>
+      </c>
+      <c r="AB16">
+        <v>1.61</v>
+      </c>
+      <c r="AC16">
+        <v>4.15</v>
+      </c>
+      <c r="AD16">
+        <v>1.16</v>
+      </c>
+      <c r="AE16">
+        <v>1.01</v>
+      </c>
+      <c r="AF16">
+        <v>1.85</v>
+      </c>
+      <c r="AG16">
+        <v>1.8</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.5</v>
       </c>
-      <c r="W16">
-        <v>1.09</v>
-      </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
-      <c r="Y16">
-        <v>1.18</v>
-      </c>
-      <c r="Z16">
-        <v>4.3</v>
-      </c>
-      <c r="AA16">
-        <v>1.6</v>
-      </c>
-      <c r="AB16">
-        <v>2.02</v>
-      </c>
-      <c r="AC16">
-        <v>2.6</v>
-      </c>
-      <c r="AD16">
-        <v>1.44</v>
-      </c>
-      <c r="AE16">
-        <v>1.15</v>
-      </c>
-      <c r="AF16">
-        <v>1.55</v>
-      </c>
-      <c r="AG16">
-        <v>2.38</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.22</v>
-      </c>
       <c r="AK16">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="O17">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>2.27</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>3.72</v>
+        <v>2.61</v>
       </c>
       <c r="R17">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="U17">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA17">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AB17">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AC17">
-        <v>4.15</v>
+        <v>3.58</v>
       </c>
       <c r="AD17">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
         <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>1.88</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
         <v>3.6</v>
@@ -4888,16 +4888,16 @@
         <v>2.17</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U28">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W28">
         <v>1.08</v>
@@ -4906,10 +4906,10 @@
         <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA28">
         <v>1.72</v>
@@ -4918,7 +4918,7 @@
         <v>2.14</v>
       </c>
       <c r="AC28">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="AD28">
         <v>1.42</v>
@@ -4930,7 +4930,7 @@
         <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O29">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -5054,10 +5054,10 @@
         <v>1.38</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U29">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="V29">
         <v>1.36</v>
@@ -5075,19 +5075,19 @@
         <v>3.3</v>
       </c>
       <c r="AA29">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB29">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC29">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AD29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
         <v>1.7</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.29</v>
+        <v>1.68</v>
       </c>
       <c r="O50">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
-        <v>2.89</v>
+        <v>2.22</v>
       </c>
       <c r="R50">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
         <v>2.81</v>
       </c>
       <c r="U50">
-        <v>2.99</v>
+        <v>2.51</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
         <v>1.02</v>
       </c>
-      <c r="X50">
-        <v>1</v>
-      </c>
       <c r="Y50">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="AA50">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AB50">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC50">
-        <v>3.55</v>
+        <v>3.07</v>
       </c>
       <c r="AD50">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AE50">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF50">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="O51">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="P51">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q51">
-        <v>2.22</v>
+        <v>2.89</v>
       </c>
       <c r="R51">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
         <v>2.81</v>
       </c>
       <c r="U51">
-        <v>2.51</v>
+        <v>2.99</v>
       </c>
       <c r="V51">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y51">
+        <v>1.36</v>
+      </c>
+      <c r="Z51">
+        <v>3.25</v>
+      </c>
+      <c r="AA51">
+        <v>2.04</v>
+      </c>
+      <c r="AB51">
+        <v>1.7</v>
+      </c>
+      <c r="AC51">
+        <v>3.55</v>
+      </c>
+      <c r="AD51">
         <v>1.22</v>
       </c>
-      <c r="Z51">
-        <v>3.54</v>
-      </c>
-      <c r="AA51">
-        <v>1.88</v>
-      </c>
-      <c r="AB51">
-        <v>1.92</v>
-      </c>
-      <c r="AC51">
-        <v>3.07</v>
-      </c>
-      <c r="AD51">
-        <v>1.37</v>
-      </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG51">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK51">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
         <v>3</v>
       </c>
       <c r="P81">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="Q81">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R81">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="S81">
         <v>1.4</v>
       </c>
       <c r="T81">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U81">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="V81">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z81">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="AA81">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB81">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC81">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="AD81">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE81">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF81">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG81">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK81">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="R82">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S82">
+        <v>1.47</v>
+      </c>
+      <c r="T82">
+        <v>2.58</v>
+      </c>
+      <c r="U82">
+        <v>3.25</v>
+      </c>
+      <c r="V82">
+        <v>1.29</v>
+      </c>
+      <c r="W82">
+        <v>1.06</v>
+      </c>
+      <c r="X82">
+        <v>1.04</v>
+      </c>
+      <c r="Y82">
         <v>1.4</v>
       </c>
-      <c r="T82">
-        <v>2.7</v>
-      </c>
-      <c r="U82">
-        <v>3.08</v>
-      </c>
-      <c r="V82">
-        <v>1.33</v>
-      </c>
-      <c r="W82">
-        <v>1.01</v>
-      </c>
-      <c r="X82">
-        <v>1.01</v>
-      </c>
-      <c r="Y82">
-        <v>1.31</v>
-      </c>
       <c r="Z82">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AA82">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AB82">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AC82">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD82">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE82">
         <v>1.02</v>
       </c>
       <c r="AF82">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG82">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK82">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,28 +13838,28 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q83">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S83">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="U83">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V83">
         <v>1.29</v>
@@ -13868,50 +13868,50 @@
         <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
+        <v>1.35</v>
+      </c>
+      <c r="Z83">
+        <v>2.98</v>
+      </c>
+      <c r="AA83">
+        <v>2.15</v>
+      </c>
+      <c r="AB83">
+        <v>1.65</v>
+      </c>
+      <c r="AC83">
+        <v>3.93</v>
+      </c>
+      <c r="AD83">
+        <v>1.23</v>
+      </c>
+      <c r="AE83">
+        <v>1.03</v>
+      </c>
+      <c r="AF83">
+        <v>1.84</v>
+      </c>
+      <c r="AG83">
+        <v>1.84</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.28</v>
+      </c>
+      <c r="AK83">
         <v>1.4</v>
-      </c>
-      <c r="Z83">
-        <v>2.8</v>
-      </c>
-      <c r="AA83">
-        <v>2.18</v>
-      </c>
-      <c r="AB83">
-        <v>1.58</v>
-      </c>
-      <c r="AC83">
-        <v>4.4</v>
-      </c>
-      <c r="AD83">
-        <v>1.16</v>
-      </c>
-      <c r="AE83">
-        <v>1.02</v>
-      </c>
-      <c r="AF83">
-        <v>1.93</v>
-      </c>
-      <c r="AG83">
-        <v>1.78</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.27</v>
-      </c>
-      <c r="AK83">
-        <v>1.57</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,61 +20032,61 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="O121">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P121">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q121">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="R121">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S121">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T121">
-        <v>3.03</v>
+        <v>2.54</v>
       </c>
       <c r="U121">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="V121">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W121">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X121">
+        <v>1.07</v>
+      </c>
+      <c r="Y121">
+        <v>1.38</v>
+      </c>
+      <c r="Z121">
+        <v>3</v>
+      </c>
+      <c r="AA121">
+        <v>2.1</v>
+      </c>
+      <c r="AB121">
+        <v>1.7</v>
+      </c>
+      <c r="AC121">
+        <v>3.58</v>
+      </c>
+      <c r="AD121">
+        <v>1.25</v>
+      </c>
+      <c r="AE121">
         <v>1.03</v>
       </c>
-      <c r="Y121">
-        <v>1.27</v>
-      </c>
-      <c r="Z121">
-        <v>3.6</v>
-      </c>
-      <c r="AA121">
-        <v>1.84</v>
-      </c>
-      <c r="AB121">
-        <v>1.87</v>
-      </c>
-      <c r="AC121">
-        <v>3.15</v>
-      </c>
-      <c r="AD121">
-        <v>1.3</v>
-      </c>
-      <c r="AE121">
-        <v>1.11</v>
-      </c>
       <c r="AF121">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AG121">
         <v>1.95</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK121">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O122">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P122">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q122">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="R122">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S122">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T122">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="U122">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="V122">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W122">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y122">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z122">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA122">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB122">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AC122">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="AD122">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE122">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF122">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AG122">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK122">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="O123">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P123">
-        <v>2.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q123">
+        <v>3.58</v>
+      </c>
+      <c r="R123">
+        <v>2.15</v>
+      </c>
+      <c r="S123">
+        <v>1.36</v>
+      </c>
+      <c r="T123">
         <v>2.88</v>
       </c>
-      <c r="R123">
-        <v>2.04</v>
-      </c>
-      <c r="S123">
-        <v>1.41</v>
-      </c>
-      <c r="T123">
-        <v>2.62</v>
-      </c>
       <c r="U123">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="V123">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W123">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X123">
+        <v>1.01</v>
+      </c>
+      <c r="Y123">
+        <v>1.27</v>
+      </c>
+      <c r="Z123">
+        <v>3.14</v>
+      </c>
+      <c r="AA123">
+        <v>2</v>
+      </c>
+      <c r="AB123">
+        <v>1.76</v>
+      </c>
+      <c r="AC123">
+        <v>3.42</v>
+      </c>
+      <c r="AD123">
+        <v>1.23</v>
+      </c>
+      <c r="AE123">
         <v>1.06</v>
       </c>
-      <c r="Y123">
-        <v>1.33</v>
-      </c>
-      <c r="Z123">
-        <v>3.3</v>
-      </c>
-      <c r="AA123">
-        <v>1.97</v>
-      </c>
-      <c r="AB123">
-        <v>1.79</v>
-      </c>
-      <c r="AC123">
-        <v>3.35</v>
-      </c>
-      <c r="AD123">
-        <v>1.27</v>
-      </c>
-      <c r="AE123">
-        <v>1.12</v>
-      </c>
       <c r="AF123">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG123">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,80 +20521,80 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O124">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P124">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q124">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R124">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S124">
         <v>1.4</v>
       </c>
       <c r="T124">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="U124">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V124">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W124">
+        <v>1.05</v>
+      </c>
+      <c r="X124">
+        <v>1.03</v>
+      </c>
+      <c r="Y124">
+        <v>1.3</v>
+      </c>
+      <c r="Z124">
+        <v>3.36</v>
+      </c>
+      <c r="AA124">
+        <v>1.84</v>
+      </c>
+      <c r="AB124">
+        <v>1.8</v>
+      </c>
+      <c r="AC124">
+        <v>3.15</v>
+      </c>
+      <c r="AD124">
+        <v>1.3</v>
+      </c>
+      <c r="AE124">
         <v>1.08</v>
       </c>
-      <c r="X124">
-        <v>1.04</v>
-      </c>
-      <c r="Y124">
+      <c r="AF124">
+        <v>1.8</v>
+      </c>
+      <c r="AG124">
+        <v>1.9</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ124">
         <v>1.28</v>
       </c>
-      <c r="Z124">
-        <v>3.05</v>
-      </c>
-      <c r="AA124">
-        <v>1.95</v>
-      </c>
-      <c r="AB124">
-        <v>1.76</v>
-      </c>
-      <c r="AC124">
-        <v>3.42</v>
-      </c>
-      <c r="AD124">
-        <v>1.28</v>
-      </c>
-      <c r="AE124">
-        <v>1.09</v>
-      </c>
-      <c r="AF124">
-        <v>1.83</v>
-      </c>
-      <c r="AG124">
-        <v>1.85</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>1.25</v>
-      </c>
       <c r="AK124">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O125">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P125">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q125">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R125">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S125">
         <v>1.4</v>
       </c>
       <c r="T125">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="U125">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V125">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W125">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X125">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y125">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z125">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="AA125">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB125">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC125">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="AD125">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE125">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF125">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG125">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK125">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="O126">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P126">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q126">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R126">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S126">
         <v>1.36</v>
       </c>
       <c r="T126">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="U126">
         <v>2.85</v>
       </c>
       <c r="V126">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W126">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
         <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z126">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="AA126">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB126">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC126">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD126">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE126">
         <v>1.06</v>
       </c>
       <c r="AF126">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG126">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK126">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,61 +21010,61 @@
         </is>
       </c>
       <c r="N127">
+        <v>1.95</v>
+      </c>
+      <c r="O127">
+        <v>3.6</v>
+      </c>
+      <c r="P127">
+        <v>3.85</v>
+      </c>
+      <c r="Q127">
         <v>2.5</v>
       </c>
-      <c r="O127">
-        <v>3.15</v>
-      </c>
-      <c r="P127">
-        <v>2.6</v>
-      </c>
-      <c r="Q127">
-        <v>3.18</v>
-      </c>
       <c r="R127">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="S127">
         <v>1.36</v>
       </c>
       <c r="T127">
-        <v>2.59</v>
+        <v>3.03</v>
       </c>
       <c r="U127">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="V127">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W127">
+        <v>1.06</v>
+      </c>
+      <c r="X127">
         <v>1.03</v>
       </c>
-      <c r="X127">
-        <v>1.01</v>
-      </c>
       <c r="Y127">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z127">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="AA127">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AB127">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC127">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AD127">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE127">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF127">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG127">
         <v>1.95</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK127">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="O136">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P136">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q136">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R136">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T136">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U136">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="V136">
         <v>1.34</v>
       </c>
       <c r="W136">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X136">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y136">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z136">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AA136">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AB136">
         <v>1.73</v>
       </c>
       <c r="AC136">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AD136">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE136">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF136">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG136">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AK136">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="O137">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="P137">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q137">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R137">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S137">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T137">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U137">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="V137">
         <v>1.34</v>
       </c>
       <c r="W137">
+        <v>1.02</v>
+      </c>
+      <c r="X137">
         <v>1.05</v>
       </c>
-      <c r="X137">
-        <v>1.04</v>
-      </c>
       <c r="Y137">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z137">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="AA137">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AB137">
         <v>1.73</v>
       </c>
       <c r="AC137">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AD137">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE137">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF137">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG137">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AK137">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.74</v>
+        <v>2.16</v>
       </c>
       <c r="O145">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P145">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="Q145">
-        <v>3.36</v>
+        <v>2.8</v>
       </c>
       <c r="R145">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="S145">
         <v>1.33</v>
       </c>
       <c r="T145">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="U145">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="V145">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W145">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X145">
         <v>1.02</v>
       </c>
       <c r="Y145">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z145">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AA145">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB145">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC145">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AD145">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE145">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
         <v>1.62</v>
       </c>
       <c r="AG145">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK145">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="O146">
         <v>3.5</v>
       </c>
       <c r="P146">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q146">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="R146">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S146">
         <v>1.29</v>
       </c>
       <c r="T146">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="U146">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="V146">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W146">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X146">
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z146">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA146">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB146">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC146">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AD146">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE146">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF146">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG146">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK146">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,80 +24270,80 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="O147">
         <v>3.5</v>
       </c>
       <c r="P147">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q147">
-        <v>2.55</v>
+        <v>3.36</v>
       </c>
       <c r="R147">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S147">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T147">
         <v>2.85</v>
       </c>
       <c r="U147">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="V147">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W147">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X147">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y147">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z147">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AA147">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB147">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC147">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AD147">
+        <v>1.34</v>
+      </c>
+      <c r="AE147">
+        <v>1.14</v>
+      </c>
+      <c r="AF147">
+        <v>1.62</v>
+      </c>
+      <c r="AG147">
+        <v>2.15</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ147">
+        <v>1.29</v>
+      </c>
+      <c r="AK147">
         <v>1.38</v>
-      </c>
-      <c r="AE147">
-        <v>1.13</v>
-      </c>
-      <c r="AF147">
-        <v>1.6</v>
-      </c>
-      <c r="AG147">
-        <v>2.13</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>1.3</v>
-      </c>
-      <c r="AK147">
-        <v>1.6</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="O148">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P148">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="Q148">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="R148">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="S148">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T148">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="U148">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V148">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W148">
         <v>1.06</v>
       </c>
       <c r="X148">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z148">
         <v>3.8</v>
       </c>
       <c r="AA148">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AB148">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AC148">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AD148">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE148">
         <v>1.1</v>
       </c>
       <c r="AF148">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG148">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK148">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O275">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P275">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q275">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R275">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S275">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T275">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U275">
         <v>2.8</v>
       </c>
       <c r="V275">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W275">
+        <v>1.08</v>
+      </c>
+      <c r="X275">
         <v>1.06</v>
       </c>
-      <c r="X275">
-        <v>1.05</v>
-      </c>
       <c r="Y275">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z275">
+        <v>3.41</v>
+      </c>
+      <c r="AA275">
+        <v>1.94</v>
+      </c>
+      <c r="AB275">
+        <v>1.78</v>
+      </c>
+      <c r="AC275">
         <v>3.4</v>
       </c>
-      <c r="AA275">
-        <v>2.12</v>
-      </c>
-      <c r="AB275">
-        <v>1.8</v>
-      </c>
-      <c r="AC275">
-        <v>3.9</v>
-      </c>
       <c r="AD275">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE275">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF275">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG275">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK275">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,80 +45297,80 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="O276">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P276">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q276">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R276">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S276">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T276">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U276">
         <v>2.8</v>
       </c>
       <c r="V276">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W276">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X276">
+        <v>1.05</v>
+      </c>
+      <c r="Y276">
+        <v>1.35</v>
+      </c>
+      <c r="Z276">
+        <v>3.4</v>
+      </c>
+      <c r="AA276">
+        <v>2.12</v>
+      </c>
+      <c r="AB276">
+        <v>1.8</v>
+      </c>
+      <c r="AC276">
+        <v>3.9</v>
+      </c>
+      <c r="AD276">
+        <v>1.24</v>
+      </c>
+      <c r="AE276">
         <v>1.06</v>
       </c>
-      <c r="Y276">
-        <v>1.29</v>
-      </c>
-      <c r="Z276">
-        <v>3.41</v>
-      </c>
-      <c r="AA276">
-        <v>1.94</v>
-      </c>
-      <c r="AB276">
-        <v>1.78</v>
-      </c>
-      <c r="AC276">
-        <v>3.4</v>
-      </c>
-      <c r="AD276">
-        <v>1.26</v>
-      </c>
-      <c r="AE276">
-        <v>1.1</v>
-      </c>
       <c r="AF276">
+        <v>1.89</v>
+      </c>
+      <c r="AG276">
+        <v>1.88</v>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ276">
+        <v>1.25</v>
+      </c>
+      <c r="AK276">
         <v>1.85</v>
-      </c>
-      <c r="AG276">
-        <v>1.94</v>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ276">
-        <v>1.22</v>
-      </c>
-      <c r="AK276">
-        <v>1.87</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="O288">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P288">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="Q288">
-        <v>3.22</v>
+        <v>3.74</v>
       </c>
       <c r="R288">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="S288">
+        <v>1.32</v>
+      </c>
+      <c r="T288">
+        <v>2.96</v>
+      </c>
+      <c r="U288">
+        <v>2.62</v>
+      </c>
+      <c r="V288">
         <v>1.4</v>
       </c>
-      <c r="T288">
-        <v>2.62</v>
-      </c>
-      <c r="U288">
-        <v>3</v>
-      </c>
-      <c r="V288">
-        <v>1.32</v>
-      </c>
       <c r="W288">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X288">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y288">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z288">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="AA288">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB288">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AC288">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD288">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE288">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF288">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AG288">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK288">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
+        <v>2.5</v>
+      </c>
+      <c r="O289">
         <v>3.15</v>
       </c>
-      <c r="O289">
-        <v>3.35</v>
-      </c>
       <c r="P289">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="Q289">
-        <v>3.74</v>
+        <v>3.22</v>
       </c>
       <c r="R289">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S289">
+        <v>1.4</v>
+      </c>
+      <c r="T289">
+        <v>2.62</v>
+      </c>
+      <c r="U289">
+        <v>3</v>
+      </c>
+      <c r="V289">
         <v>1.32</v>
       </c>
-      <c r="T289">
-        <v>2.96</v>
-      </c>
-      <c r="U289">
-        <v>2.62</v>
-      </c>
-      <c r="V289">
-        <v>1.4</v>
-      </c>
       <c r="W289">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X289">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y289">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z289">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="AA289">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB289">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AC289">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD289">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE289">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF289">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AG289">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK289">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G307">
@@ -50359,55 +50359,55 @@
         <v>0</v>
       </c>
       <c r="Q307">
-        <v>2.43</v>
+        <v>2.24</v>
       </c>
       <c r="R307">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S307">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T307">
-        <v>3.14</v>
+        <v>2.67</v>
       </c>
       <c r="U307">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="V307">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W307">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X307">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y307">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z307">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA307">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB307">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AC307">
-        <v>2.43</v>
+        <v>3.05</v>
       </c>
       <c r="AD307">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE307">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF307">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AG307">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK307">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G308">
@@ -50522,55 +50522,55 @@
         <v>0</v>
       </c>
       <c r="Q308">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="R308">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="S308">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="T308">
-        <v>2.67</v>
+        <v>2.28</v>
       </c>
       <c r="U308">
-        <v>2.71</v>
+        <v>3.58</v>
       </c>
       <c r="V308">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="W308">
+        <v>1.04</v>
+      </c>
+      <c r="X308">
         <v>1.07</v>
       </c>
-      <c r="X308">
-        <v>1.01</v>
-      </c>
       <c r="Y308">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Z308">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AA308">
-        <v>1.9</v>
+        <v>2.49</v>
       </c>
       <c r="AB308">
-        <v>1.87</v>
+        <v>1.43</v>
       </c>
       <c r="AC308">
-        <v>3.05</v>
+        <v>5.25</v>
       </c>
       <c r="AD308">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AE308">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF308">
-        <v>1.81</v>
+        <v>2.22</v>
       </c>
       <c r="AG308">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK308">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G309">
@@ -50685,55 +50685,55 @@
         <v>0</v>
       </c>
       <c r="Q309">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R309">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="S309">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="T309">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="U309">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="V309">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="W309">
         <v>1.04</v>
       </c>
       <c r="X309">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y309">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z309">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="AA309">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AB309">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AC309">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="AD309">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE309">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF309">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="AG309">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>1.27</v>
       </c>
       <c r="AK309">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G310">
@@ -50848,55 +50848,55 @@
         <v>0</v>
       </c>
       <c r="Q310">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="R310">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="S310">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="T310">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="U310">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="V310">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="W310">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X310">
         <v>1.02</v>
       </c>
       <c r="Y310">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="Z310">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="AA310">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="AB310">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AC310">
-        <v>3.9</v>
+        <v>2.43</v>
       </c>
       <c r="AD310">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AE310">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF310">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="AG310">
-        <v>1.81</v>
+        <v>2.29</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK310">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,64 +55729,64 @@
         </is>
       </c>
       <c r="N340">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="O340">
+        <v>3.95</v>
+      </c>
+      <c r="P340">
         <v>4</v>
       </c>
-      <c r="P340">
-        <v>3.6</v>
-      </c>
       <c r="Q340">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="R340">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S340">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T340">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="U340">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="V340">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W340">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X340">
         <v>0</v>
       </c>
       <c r="Y340">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z340">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="AA340">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB340">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="AC340">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AD340">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE340">
         <v>1.26</v>
       </c>
       <c r="AF340">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG340">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK340">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL340">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,64 +56055,64 @@
         </is>
       </c>
       <c r="N342">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="O342">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P342">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q342">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="R342">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S342">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T342">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="U342">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="V342">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W342">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X342">
         <v>0</v>
       </c>
       <c r="Y342">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z342">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA342">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB342">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="AC342">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AD342">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE342">
         <v>1.26</v>
       </c>
       <c r="AF342">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG342">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AH342" t="inlineStr">
         <is>
@@ -56125,10 +56125,10 @@
         </is>
       </c>
       <c r="AJ342">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK342">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL342">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q42">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="R42">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U42">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V42">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W42">
         <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA42">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB42">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AC42">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AD42">
         <v>1.61</v>
       </c>
       <c r="AE42">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF42">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG42">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.23</v>
       </c>
       <c r="AK42">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O43">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P43">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q43">
+        <v>2.74</v>
+      </c>
+      <c r="R43">
         <v>2.48</v>
       </c>
-      <c r="R43">
-        <v>2.3</v>
-      </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U43">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="V43">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W43">
         <v>1.13</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA43">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB43">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="AC43">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AD43">
         <v>1.61</v>
       </c>
       <c r="AE43">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF43">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.23</v>
       </c>
       <c r="AK43">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="P50">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
-        <v>2.22</v>
+        <v>2.89</v>
       </c>
       <c r="R50">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
         <v>2.81</v>
       </c>
       <c r="U50">
-        <v>2.51</v>
+        <v>2.99</v>
       </c>
       <c r="V50">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y50">
+        <v>1.36</v>
+      </c>
+      <c r="Z50">
+        <v>3.25</v>
+      </c>
+      <c r="AA50">
+        <v>2.04</v>
+      </c>
+      <c r="AB50">
+        <v>1.7</v>
+      </c>
+      <c r="AC50">
+        <v>3.55</v>
+      </c>
+      <c r="AD50">
         <v>1.22</v>
       </c>
-      <c r="Z50">
-        <v>3.54</v>
-      </c>
-      <c r="AA50">
-        <v>1.88</v>
-      </c>
-      <c r="AB50">
-        <v>1.92</v>
-      </c>
-      <c r="AC50">
-        <v>3.07</v>
-      </c>
-      <c r="AD50">
-        <v>1.37</v>
-      </c>
       <c r="AE50">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF50">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG50">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.29</v>
+        <v>1.68</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="P51">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q51">
-        <v>2.89</v>
+        <v>2.22</v>
       </c>
       <c r="R51">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
         <v>2.81</v>
       </c>
       <c r="U51">
-        <v>2.99</v>
+        <v>2.51</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W51">
+        <v>1.07</v>
+      </c>
+      <c r="X51">
         <v>1.02</v>
       </c>
-      <c r="X51">
-        <v>1</v>
-      </c>
       <c r="Y51">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="AA51">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AB51">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC51">
-        <v>3.55</v>
+        <v>3.07</v>
       </c>
       <c r="AD51">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AE51">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,28 +13675,28 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q82">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R82">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S82">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T82">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="U82">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V82">
         <v>1.29</v>
@@ -13705,50 +13705,50 @@
         <v>1.06</v>
       </c>
       <c r="X82">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
+        <v>1.35</v>
+      </c>
+      <c r="Z82">
+        <v>2.98</v>
+      </c>
+      <c r="AA82">
+        <v>2.15</v>
+      </c>
+      <c r="AB82">
+        <v>1.65</v>
+      </c>
+      <c r="AC82">
+        <v>3.93</v>
+      </c>
+      <c r="AD82">
+        <v>1.23</v>
+      </c>
+      <c r="AE82">
+        <v>1.03</v>
+      </c>
+      <c r="AF82">
+        <v>1.84</v>
+      </c>
+      <c r="AG82">
+        <v>1.84</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
+        <v>1.28</v>
+      </c>
+      <c r="AK82">
         <v>1.4</v>
-      </c>
-      <c r="Z82">
-        <v>2.8</v>
-      </c>
-      <c r="AA82">
-        <v>2.18</v>
-      </c>
-      <c r="AB82">
-        <v>1.58</v>
-      </c>
-      <c r="AC82">
-        <v>4.4</v>
-      </c>
-      <c r="AD82">
-        <v>1.16</v>
-      </c>
-      <c r="AE82">
-        <v>1.02</v>
-      </c>
-      <c r="AF82">
-        <v>1.93</v>
-      </c>
-      <c r="AG82">
-        <v>1.78</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.27</v>
-      </c>
-      <c r="AK82">
-        <v>1.57</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,28 +13838,28 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="R83">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T83">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="U83">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V83">
         <v>1.29</v>
@@ -13868,34 +13868,34 @@
         <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z83">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AA83">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB83">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC83">
-        <v>3.93</v>
+        <v>4.4</v>
       </c>
       <c r="AD83">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE83">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF83">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AG83">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK83">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15308,10 +15308,10 @@
         <v>3.5</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P92">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="Q92">
         <v>4.2</v>
@@ -15326,7 +15326,7 @@
         <v>3</v>
       </c>
       <c r="U92">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V92">
         <v>1.4</v>
@@ -15335,7 +15335,7 @@
         <v>1.08</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
         <v>1.26</v>
@@ -15344,22 +15344,22 @@
         <v>3.46</v>
       </c>
       <c r="AA92">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB92">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC92">
         <v>3.3</v>
       </c>
       <c r="AD92">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE92">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF92">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG92">
         <v>1.95</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,80 +16609,80 @@
         </is>
       </c>
       <c r="N100">
-        <v>4.55</v>
+        <v>2.45</v>
       </c>
       <c r="O100">
+        <v>3.6</v>
+      </c>
+      <c r="P100">
+        <v>2.64</v>
+      </c>
+      <c r="Q100">
+        <v>2.98</v>
+      </c>
+      <c r="R100">
+        <v>2.38</v>
+      </c>
+      <c r="S100">
+        <v>1.31</v>
+      </c>
+      <c r="T100">
+        <v>3.42</v>
+      </c>
+      <c r="U100">
+        <v>2.3</v>
+      </c>
+      <c r="V100">
+        <v>1.55</v>
+      </c>
+      <c r="W100">
+        <v>1.12</v>
+      </c>
+      <c r="X100">
+        <v>1.04</v>
+      </c>
+      <c r="Y100">
+        <v>1.2</v>
+      </c>
+      <c r="Z100">
         <v>4.5</v>
       </c>
-      <c r="P100">
-        <v>1.56</v>
-      </c>
-      <c r="Q100">
-        <v>4</v>
-      </c>
-      <c r="R100">
-        <v>2.6</v>
-      </c>
-      <c r="S100">
-        <v>1.23</v>
-      </c>
-      <c r="T100">
-        <v>3.94</v>
-      </c>
-      <c r="U100">
-        <v>2.04</v>
-      </c>
-      <c r="V100">
-        <v>1.67</v>
-      </c>
-      <c r="W100">
-        <v>1.18</v>
-      </c>
-      <c r="X100">
-        <v>1.01</v>
-      </c>
-      <c r="Y100">
-        <v>1.11</v>
-      </c>
-      <c r="Z100">
-        <v>6</v>
-      </c>
       <c r="AA100">
+        <v>1.63</v>
+      </c>
+      <c r="AB100">
+        <v>2.2</v>
+      </c>
+      <c r="AC100">
+        <v>2.63</v>
+      </c>
+      <c r="AD100">
+        <v>1.52</v>
+      </c>
+      <c r="AE100">
+        <v>1.16</v>
+      </c>
+      <c r="AF100">
+        <v>1.47</v>
+      </c>
+      <c r="AG100">
+        <v>2.33</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ100">
         <v>1.44</v>
       </c>
-      <c r="AB100">
-        <v>2.6</v>
-      </c>
-      <c r="AC100">
-        <v>2.15</v>
-      </c>
-      <c r="AD100">
-        <v>1.67</v>
-      </c>
-      <c r="AE100">
-        <v>1.29</v>
-      </c>
-      <c r="AF100">
-        <v>1.44</v>
-      </c>
-      <c r="AG100">
-        <v>2.63</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>1.23</v>
-      </c>
       <c r="AK100">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,65 +16772,65 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.45</v>
+        <v>4.55</v>
       </c>
       <c r="O101">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P101">
-        <v>2.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q101">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="R101">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S101">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="T101">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="U101">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="V101">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="W101">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X101">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z101">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AA101">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AB101">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC101">
+        <v>2.15</v>
+      </c>
+      <c r="AD101">
+        <v>1.67</v>
+      </c>
+      <c r="AE101">
+        <v>1.29</v>
+      </c>
+      <c r="AF101">
+        <v>1.44</v>
+      </c>
+      <c r="AG101">
         <v>2.63</v>
       </c>
-      <c r="AD101">
-        <v>1.52</v>
-      </c>
-      <c r="AE101">
-        <v>1.16</v>
-      </c>
-      <c r="AF101">
-        <v>1.47</v>
-      </c>
-      <c r="AG101">
-        <v>2.33</v>
-      </c>
       <c r="AH101" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AK101">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17433,25 +17433,25 @@
         <v>4.6</v>
       </c>
       <c r="Q105">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R105">
         <v>2.53</v>
       </c>
       <c r="S105">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T105">
         <v>3.5</v>
       </c>
       <c r="U105">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="V105">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W105">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X105">
         <v>1.01</v>
@@ -17466,13 +17466,13 @@
         <v>1.56</v>
       </c>
       <c r="AB105">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AC105">
         <v>2.34</v>
       </c>
       <c r="AD105">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE105">
         <v>1.16</v>
@@ -17481,7 +17481,7 @@
         <v>1.62</v>
       </c>
       <c r="AG105">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="O121">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P121">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q121">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="R121">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S121">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T121">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="U121">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V121">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W121">
+        <v>1.05</v>
+      </c>
+      <c r="X121">
         <v>1.03</v>
       </c>
-      <c r="X121">
-        <v>1.07</v>
-      </c>
       <c r="Y121">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z121">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AA121">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AB121">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC121">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="AD121">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE121">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG121">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK121">
-        <v>1.46</v>
+        <v>1.89</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="O122">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P122">
-        <v>2.87</v>
+        <v>3.85</v>
       </c>
       <c r="Q122">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R122">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S122">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T122">
-        <v>2.62</v>
+        <v>3.03</v>
       </c>
       <c r="U122">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="V122">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W122">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X122">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z122">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA122">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AB122">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AC122">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AD122">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE122">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF122">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG122">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="O123">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P123">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q123">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="R123">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S123">
         <v>1.36</v>
       </c>
       <c r="T123">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="U123">
         <v>2.85</v>
       </c>
       <c r="V123">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W123">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X123">
         <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z123">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="AA123">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB123">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC123">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD123">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE123">
         <v>1.06</v>
       </c>
       <c r="AF123">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG123">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK123">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="O124">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P124">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q124">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="R124">
+        <v>2.05</v>
+      </c>
+      <c r="S124">
+        <v>1.44</v>
+      </c>
+      <c r="T124">
+        <v>2.54</v>
+      </c>
+      <c r="U124">
+        <v>2.86</v>
+      </c>
+      <c r="V124">
+        <v>1.35</v>
+      </c>
+      <c r="W124">
+        <v>1.03</v>
+      </c>
+      <c r="X124">
+        <v>1.07</v>
+      </c>
+      <c r="Y124">
+        <v>1.38</v>
+      </c>
+      <c r="Z124">
+        <v>3</v>
+      </c>
+      <c r="AA124">
         <v>2.1</v>
       </c>
-      <c r="S124">
-        <v>1.4</v>
-      </c>
-      <c r="T124">
-        <v>2.69</v>
-      </c>
-      <c r="U124">
-        <v>2.88</v>
-      </c>
-      <c r="V124">
-        <v>1.38</v>
-      </c>
-      <c r="W124">
-        <v>1.05</v>
-      </c>
-      <c r="X124">
+      <c r="AB124">
+        <v>1.7</v>
+      </c>
+      <c r="AC124">
+        <v>3.58</v>
+      </c>
+      <c r="AD124">
+        <v>1.25</v>
+      </c>
+      <c r="AE124">
         <v>1.03</v>
       </c>
-      <c r="Y124">
-        <v>1.3</v>
-      </c>
-      <c r="Z124">
-        <v>3.36</v>
-      </c>
-      <c r="AA124">
-        <v>1.84</v>
-      </c>
-      <c r="AB124">
-        <v>1.8</v>
-      </c>
-      <c r="AC124">
-        <v>3.15</v>
-      </c>
-      <c r="AD124">
-        <v>1.3</v>
-      </c>
-      <c r="AE124">
-        <v>1.08</v>
-      </c>
       <c r="AF124">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG124">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK124">
-        <v>1.89</v>
+        <v>1.46</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,46 +20684,46 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.93</v>
+        <v>3.75</v>
       </c>
       <c r="O125">
         <v>3.4</v>
       </c>
       <c r="P125">
-        <v>3.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q125">
-        <v>2.45</v>
+        <v>3.58</v>
       </c>
       <c r="R125">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S125">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T125">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U125">
         <v>2.85</v>
       </c>
       <c r="V125">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W125">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X125">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z125">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA125">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB125">
         <v>1.76</v>
@@ -20732,16 +20732,16 @@
         <v>3.42</v>
       </c>
       <c r="AD125">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE125">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF125">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG125">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>1.25</v>
       </c>
       <c r="AK125">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O126">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P126">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q126">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="R126">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S126">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T126">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U126">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="V126">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W126">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y126">
         <v>1.33</v>
       </c>
       <c r="Z126">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="AA126">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AB126">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC126">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD126">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE126">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF126">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG126">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK126">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
+        <v>1.93</v>
+      </c>
+      <c r="O127">
+        <v>3.4</v>
+      </c>
+      <c r="P127">
+        <v>3.8</v>
+      </c>
+      <c r="Q127">
+        <v>2.45</v>
+      </c>
+      <c r="R127">
+        <v>2.02</v>
+      </c>
+      <c r="S127">
+        <v>1.4</v>
+      </c>
+      <c r="T127">
+        <v>2.84</v>
+      </c>
+      <c r="U127">
+        <v>2.85</v>
+      </c>
+      <c r="V127">
+        <v>1.36</v>
+      </c>
+      <c r="W127">
+        <v>1.08</v>
+      </c>
+      <c r="X127">
+        <v>1.04</v>
+      </c>
+      <c r="Y127">
+        <v>1.28</v>
+      </c>
+      <c r="Z127">
+        <v>3.05</v>
+      </c>
+      <c r="AA127">
         <v>1.95</v>
       </c>
-      <c r="O127">
-        <v>3.6</v>
-      </c>
-      <c r="P127">
-        <v>3.85</v>
-      </c>
-      <c r="Q127">
-        <v>2.5</v>
-      </c>
-      <c r="R127">
-        <v>2.2</v>
-      </c>
-      <c r="S127">
-        <v>1.36</v>
-      </c>
-      <c r="T127">
-        <v>3.03</v>
-      </c>
-      <c r="U127">
-        <v>2.75</v>
-      </c>
-      <c r="V127">
-        <v>1.4</v>
-      </c>
-      <c r="W127">
-        <v>1.06</v>
-      </c>
-      <c r="X127">
-        <v>1.03</v>
-      </c>
-      <c r="Y127">
-        <v>1.27</v>
-      </c>
-      <c r="Z127">
-        <v>3.6</v>
-      </c>
-      <c r="AA127">
-        <v>1.84</v>
-      </c>
       <c r="AB127">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AC127">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="AD127">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE127">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF127">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG127">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="O144">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P144">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="Q144">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R144">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="S144">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="U144">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="V144">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W144">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X144">
         <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z144">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="AA144">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AB144">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AC144">
-        <v>3.52</v>
+        <v>2.85</v>
       </c>
       <c r="AD144">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AE144">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF144">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG144">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK144">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O145">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="Q145">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="R145">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S145">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T145">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="U145">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="V145">
         <v>1.44</v>
       </c>
       <c r="W145">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X145">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z145">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA145">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB145">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC145">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="AD145">
         <v>1.38</v>
       </c>
       <c r="AE145">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF145">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK145">
         <v>1.6</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="O146">
         <v>3.5</v>
       </c>
       <c r="P146">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="Q146">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="R146">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S146">
         <v>1.29</v>
       </c>
       <c r="T146">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="U146">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="V146">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W146">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X146">
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z146">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA146">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB146">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC146">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AD146">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE146">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF146">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG146">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK146">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,80 +24270,80 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="O147">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P147">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="Q147">
-        <v>3.36</v>
+        <v>2.78</v>
       </c>
       <c r="R147">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S147">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T147">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U147">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="V147">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W147">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X147">
         <v>1.02</v>
       </c>
       <c r="Y147">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z147">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AA147">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AB147">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AC147">
-        <v>2.97</v>
+        <v>3.52</v>
       </c>
       <c r="AD147">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE147">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF147">
+        <v>1.75</v>
+      </c>
+      <c r="AG147">
+        <v>1.96</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ147">
+        <v>1.25</v>
+      </c>
+      <c r="AK147">
         <v>1.62</v>
-      </c>
-      <c r="AG147">
-        <v>2.15</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>1.29</v>
-      </c>
-      <c r="AK147">
-        <v>1.38</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,80 +24433,80 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.87</v>
+        <v>2.74</v>
       </c>
       <c r="O148">
         <v>3.5</v>
       </c>
       <c r="P148">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q148">
-        <v>2.42</v>
+        <v>3.36</v>
       </c>
       <c r="R148">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S148">
+        <v>1.33</v>
+      </c>
+      <c r="T148">
+        <v>2.85</v>
+      </c>
+      <c r="U148">
+        <v>2.45</v>
+      </c>
+      <c r="V148">
+        <v>1.48</v>
+      </c>
+      <c r="W148">
+        <v>1.07</v>
+      </c>
+      <c r="X148">
+        <v>1.02</v>
+      </c>
+      <c r="Y148">
+        <v>1.27</v>
+      </c>
+      <c r="Z148">
+        <v>3.35</v>
+      </c>
+      <c r="AA148">
+        <v>1.76</v>
+      </c>
+      <c r="AB148">
+        <v>1.98</v>
+      </c>
+      <c r="AC148">
+        <v>2.97</v>
+      </c>
+      <c r="AD148">
+        <v>1.34</v>
+      </c>
+      <c r="AE148">
+        <v>1.14</v>
+      </c>
+      <c r="AF148">
+        <v>1.62</v>
+      </c>
+      <c r="AG148">
+        <v>2.15</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ148">
         <v>1.29</v>
       </c>
-      <c r="T148">
-        <v>3.3</v>
-      </c>
-      <c r="U148">
-        <v>2.6</v>
-      </c>
-      <c r="V148">
-        <v>1.43</v>
-      </c>
-      <c r="W148">
-        <v>1.06</v>
-      </c>
-      <c r="X148">
-        <v>1.01</v>
-      </c>
-      <c r="Y148">
-        <v>1.23</v>
-      </c>
-      <c r="Z148">
-        <v>3.8</v>
-      </c>
-      <c r="AA148">
-        <v>1.83</v>
-      </c>
-      <c r="AB148">
-        <v>1.93</v>
-      </c>
-      <c r="AC148">
-        <v>3</v>
-      </c>
-      <c r="AD148">
-        <v>1.33</v>
-      </c>
-      <c r="AE148">
-        <v>1.1</v>
-      </c>
-      <c r="AF148">
-        <v>1.67</v>
-      </c>
-      <c r="AG148">
-        <v>2.01</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ148">
-        <v>1.22</v>
-      </c>
       <c r="AK148">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -30630,16 +30630,16 @@
         <v>2.1</v>
       </c>
       <c r="O186">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P186">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q186">
         <v>2.97</v>
       </c>
       <c r="R186">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="S186">
         <v>1.57</v>
@@ -30648,16 +30648,16 @@
         <v>2.3</v>
       </c>
       <c r="U186">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="V186">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W186">
         <v>1.02</v>
       </c>
       <c r="X186">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y186">
         <v>1.49</v>
@@ -30669,7 +30669,7 @@
         <v>2.71</v>
       </c>
       <c r="AB186">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC186">
         <v>5.25</v>
@@ -30681,10 +30681,10 @@
         <v>1.04</v>
       </c>
       <c r="AF186">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG186">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>1.33</v>
       </c>
       <c r="AK186">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O194">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="P194">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O195">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P195">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="O196">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P196">
-        <v>5.23</v>
+        <v>3.9</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S204">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T204">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U204">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V204">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W204">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X204">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y204">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z204">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA204">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB204">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC204">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD204">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG204">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AK204">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O205">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P205">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA205">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD205">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF205">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33887,19 +33887,19 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q206">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="R206">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S206">
         <v>1.4</v>
@@ -33908,7 +33908,7 @@
         <v>2.75</v>
       </c>
       <c r="U206">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="V206">
         <v>1.28</v>
@@ -33932,35 +33932,35 @@
         <v>1.6</v>
       </c>
       <c r="AC206">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="AD206">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE206">
         <v>1.02</v>
       </c>
       <c r="AF206">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG206">
+        <v>1.72</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ206">
+        <v>1.25</v>
+      </c>
+      <c r="AK206">
         <v>1.83</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ206">
-        <v>1.29</v>
-      </c>
-      <c r="AK206">
-        <v>1.41</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34711,10 +34711,10 @@
         <v>3.26</v>
       </c>
       <c r="Q211">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="R211">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S211">
         <v>1.4</v>
@@ -34723,43 +34723,43 @@
         <v>2.88</v>
       </c>
       <c r="U211">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V211">
         <v>1.36</v>
       </c>
       <c r="W211">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X211">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z211">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA211">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB211">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC211">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD211">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE211">
         <v>1.04</v>
       </c>
       <c r="AF211">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AG211">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK211">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -36332,7 +36332,7 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="O221">
         <v>4.9</v>
@@ -36347,16 +36347,16 @@
         <v>2.62</v>
       </c>
       <c r="S221">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T221">
         <v>3.75</v>
       </c>
       <c r="U221">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V221">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W221">
         <v>1.17</v>
@@ -36368,13 +36368,13 @@
         <v>1.1</v>
       </c>
       <c r="Z221">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="AA221">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB221">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AC221">
         <v>2.16</v>
@@ -36383,13 +36383,13 @@
         <v>1.62</v>
       </c>
       <c r="AE221">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF221">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG221">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>1.1</v>
       </c>
       <c r="AK221">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36513,13 +36513,13 @@
         <v>1.33</v>
       </c>
       <c r="T222">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U222">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V222">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W222">
         <v>1.11</v>
@@ -36534,25 +36534,25 @@
         <v>3.7</v>
       </c>
       <c r="AA222">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB222">
         <v>2</v>
       </c>
       <c r="AC222">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AD222">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE222">
         <v>1.1</v>
       </c>
       <c r="AF222">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG222">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK222">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -39918,64 +39918,64 @@
         </is>
       </c>
       <c r="N243">
-        <v>2.87</v>
+        <v>2.17</v>
       </c>
       <c r="O243">
         <v>3.35</v>
       </c>
       <c r="P243">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="Q243">
-        <v>3.52</v>
+        <v>2.72</v>
       </c>
       <c r="R243">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S243">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T243">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="U243">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="V243">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W243">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X243">
         <v>1.01</v>
       </c>
       <c r="Y243">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z243">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="AA243">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AB243">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC243">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AD243">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE243">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF243">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AG243">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AK243">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="O271">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P271">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -46601,65 +46601,65 @@
         </is>
       </c>
       <c r="N284">
+        <v>1.8</v>
+      </c>
+      <c r="O284">
+        <v>3.1</v>
+      </c>
+      <c r="P284">
+        <v>4.2</v>
+      </c>
+      <c r="Q284">
+        <v>2.53</v>
+      </c>
+      <c r="R284">
+        <v>1.98</v>
+      </c>
+      <c r="S284">
+        <v>1.43</v>
+      </c>
+      <c r="T284">
+        <v>2.5</v>
+      </c>
+      <c r="U284">
+        <v>3.04</v>
+      </c>
+      <c r="V284">
+        <v>1.3</v>
+      </c>
+      <c r="W284">
+        <v>1.02</v>
+      </c>
+      <c r="X284">
+        <v>1.02</v>
+      </c>
+      <c r="Y284">
+        <v>1.33</v>
+      </c>
+      <c r="Z284">
+        <v>2.83</v>
+      </c>
+      <c r="AA284">
+        <v>2.12</v>
+      </c>
+      <c r="AB284">
+        <v>1.63</v>
+      </c>
+      <c r="AC284">
+        <v>3.8</v>
+      </c>
+      <c r="AD284">
+        <v>1.19</v>
+      </c>
+      <c r="AE284">
+        <v>1.03</v>
+      </c>
+      <c r="AF284">
+        <v>1.9</v>
+      </c>
+      <c r="AG284">
         <v>1.76</v>
       </c>
-      <c r="O284">
-        <v>3.25</v>
-      </c>
-      <c r="P284">
-        <v>4.65</v>
-      </c>
-      <c r="Q284">
-        <v>0</v>
-      </c>
-      <c r="R284">
-        <v>0</v>
-      </c>
-      <c r="S284">
-        <v>0</v>
-      </c>
-      <c r="T284">
-        <v>0</v>
-      </c>
-      <c r="U284">
-        <v>0</v>
-      </c>
-      <c r="V284">
-        <v>0</v>
-      </c>
-      <c r="W284">
-        <v>0</v>
-      </c>
-      <c r="X284">
-        <v>0</v>
-      </c>
-      <c r="Y284">
-        <v>0</v>
-      </c>
-      <c r="Z284">
-        <v>0</v>
-      </c>
-      <c r="AA284">
-        <v>0</v>
-      </c>
-      <c r="AB284">
-        <v>0</v>
-      </c>
-      <c r="AC284">
-        <v>0</v>
-      </c>
-      <c r="AD284">
-        <v>0</v>
-      </c>
-      <c r="AE284">
-        <v>0</v>
-      </c>
-      <c r="AF284">
-        <v>0</v>
-      </c>
-      <c r="AG284">
-        <v>0</v>
-      </c>
       <c r="AH284" t="inlineStr">
         <is>
           <t>[]</t>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK284">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="O285">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P285">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q285">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S285">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T285">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U285">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V285">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W285">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X285">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y285">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z285">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC285">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD285">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE285">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG285">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK285">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O286">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P286">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q286">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T286">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U286">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V286">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W286">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X286">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y286">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z286">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE286">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF286">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK286">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
+        <v>2.5</v>
+      </c>
+      <c r="O288">
         <v>3.15</v>
       </c>
-      <c r="O288">
-        <v>3.35</v>
-      </c>
       <c r="P288">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="Q288">
-        <v>3.74</v>
+        <v>3.22</v>
       </c>
       <c r="R288">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S288">
+        <v>1.4</v>
+      </c>
+      <c r="T288">
+        <v>2.62</v>
+      </c>
+      <c r="U288">
+        <v>3</v>
+      </c>
+      <c r="V288">
         <v>1.32</v>
       </c>
-      <c r="T288">
-        <v>2.96</v>
-      </c>
-      <c r="U288">
-        <v>2.62</v>
-      </c>
-      <c r="V288">
-        <v>1.4</v>
-      </c>
       <c r="W288">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X288">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y288">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z288">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="AA288">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB288">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AC288">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD288">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE288">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF288">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AG288">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK288">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="O289">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P289">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="Q289">
-        <v>3.22</v>
+        <v>3.74</v>
       </c>
       <c r="R289">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="S289">
+        <v>1.32</v>
+      </c>
+      <c r="T289">
+        <v>2.96</v>
+      </c>
+      <c r="U289">
+        <v>2.62</v>
+      </c>
+      <c r="V289">
         <v>1.4</v>
       </c>
-      <c r="T289">
-        <v>2.62</v>
-      </c>
-      <c r="U289">
-        <v>3</v>
-      </c>
-      <c r="V289">
-        <v>1.32</v>
-      </c>
       <c r="W289">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X289">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z289">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="AA289">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB289">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AC289">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD289">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE289">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF289">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AG289">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK289">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O292">
         <v>3.1</v>
       </c>
       <c r="P292">
-        <v>2.94</v>
+        <v>2.15</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O293">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P293">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q293">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R293">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S293">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T293">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U293">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V293">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W293">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X293">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y293">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z293">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA293">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB293">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC293">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD293">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE293">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF293">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG293">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK293">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q294">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R294">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S294">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T294">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U294">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V294">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W294">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X294">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y294">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z294">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA294">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB294">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC294">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD294">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE294">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF294">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG294">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK294">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O311">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P311">
-        <v>0</v>
+        <v>6.56</v>
       </c>
       <c r="Q311">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G26">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.27</v>
+        <v>1.73</v>
       </c>
       <c r="O50">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
-        <v>2.89</v>
+        <v>2.22</v>
       </c>
       <c r="R50">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U50">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.25</v>
+        <v>3.82</v>
       </c>
       <c r="AA50">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>3.54</v>
+        <v>3.07</v>
       </c>
       <c r="AD50">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE50">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.55</v>
+        <v>2.09</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="O51">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="P51">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="Q51">
-        <v>2.22</v>
+        <v>2.89</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U51">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z51">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="AA51">
+        <v>2.1</v>
+      </c>
+      <c r="AB51">
+        <v>1.7</v>
+      </c>
+      <c r="AC51">
+        <v>3.54</v>
+      </c>
+      <c r="AD51">
+        <v>1.27</v>
+      </c>
+      <c r="AE51">
+        <v>1.03</v>
+      </c>
+      <c r="AF51">
         <v>1.8</v>
       </c>
-      <c r="AB51">
-        <v>2</v>
-      </c>
-      <c r="AC51">
-        <v>3.07</v>
-      </c>
-      <c r="AD51">
-        <v>1.37</v>
-      </c>
-      <c r="AE51">
-        <v>1.09</v>
-      </c>
-      <c r="AF51">
-        <v>1.75</v>
-      </c>
       <c r="AG51">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK51">
-        <v>2.09</v>
+        <v>1.55</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="O120">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P120">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q120">
-        <v>3.95</v>
+        <v>3.18</v>
       </c>
       <c r="R120">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S120">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T120">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="U120">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V120">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W120">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X120">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y120">
         <v>1.27</v>
       </c>
       <c r="Z120">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="AA120">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB120">
         <v>1.75</v>
       </c>
       <c r="AC120">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="AD120">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE120">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF120">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG120">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK120">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,61 +20032,61 @@
         </is>
       </c>
       <c r="N121">
+        <v>3.3</v>
+      </c>
+      <c r="O121">
+        <v>3.3</v>
+      </c>
+      <c r="P121">
+        <v>2.1</v>
+      </c>
+      <c r="Q121">
+        <v>3.6</v>
+      </c>
+      <c r="R121">
+        <v>2.04</v>
+      </c>
+      <c r="S121">
+        <v>1.37</v>
+      </c>
+      <c r="T121">
+        <v>2.97</v>
+      </c>
+      <c r="U121">
+        <v>2.63</v>
+      </c>
+      <c r="V121">
+        <v>1.39</v>
+      </c>
+      <c r="W121">
+        <v>1.07</v>
+      </c>
+      <c r="X121">
+        <v>1.05</v>
+      </c>
+      <c r="Y121">
+        <v>1.24</v>
+      </c>
+      <c r="Z121">
+        <v>3.4</v>
+      </c>
+      <c r="AA121">
         <v>1.95</v>
       </c>
-      <c r="O121">
-        <v>3.35</v>
-      </c>
-      <c r="P121">
-        <v>3.25</v>
-      </c>
-      <c r="Q121">
-        <v>2.45</v>
-      </c>
-      <c r="R121">
-        <v>2.08</v>
-      </c>
-      <c r="S121">
-        <v>1.36</v>
-      </c>
-      <c r="T121">
-        <v>2.85</v>
-      </c>
-      <c r="U121">
-        <v>2.75</v>
-      </c>
-      <c r="V121">
-        <v>1.4</v>
-      </c>
-      <c r="W121">
-        <v>1.06</v>
-      </c>
-      <c r="X121">
-        <v>1.03</v>
-      </c>
-      <c r="Y121">
-        <v>1.27</v>
-      </c>
-      <c r="Z121">
-        <v>3.55</v>
-      </c>
-      <c r="AA121">
-        <v>1.91</v>
-      </c>
       <c r="AB121">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC121">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="AD121">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE121">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF121">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG121">
         <v>2</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK121">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="O122">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P122">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q122">
-        <v>3.18</v>
+        <v>2.3</v>
       </c>
       <c r="R122">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T122">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="U122">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V122">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W122">
+        <v>1.05</v>
+      </c>
+      <c r="X122">
         <v>1.03</v>
       </c>
-      <c r="X122">
-        <v>1.06</v>
-      </c>
       <c r="Y122">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z122">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="AA122">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AB122">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC122">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="AD122">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE122">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG122">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK122">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="O123">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P123">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q123">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="R123">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T123">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U123">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V123">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W123">
         <v>1.05</v>
       </c>
       <c r="X123">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y123">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z123">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA123">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB123">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC123">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="AD123">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE123">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF123">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG123">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>1.28</v>
       </c>
       <c r="AK123">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,65 +20521,65 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="O124">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P124">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q124">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="R124">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S124">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T124">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="U124">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V124">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W124">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X124">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z124">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="AA124">
         <v>1.95</v>
       </c>
       <c r="AB124">
+        <v>1.73</v>
+      </c>
+      <c r="AC124">
+        <v>3.34</v>
+      </c>
+      <c r="AD124">
+        <v>1.25</v>
+      </c>
+      <c r="AE124">
+        <v>1.06</v>
+      </c>
+      <c r="AF124">
+        <v>1.82</v>
+      </c>
+      <c r="AG124">
         <v>1.85</v>
       </c>
-      <c r="AC124">
-        <v>3.14</v>
-      </c>
-      <c r="AD124">
-        <v>1.33</v>
-      </c>
-      <c r="AE124">
-        <v>1.09</v>
-      </c>
-      <c r="AF124">
-        <v>1.66</v>
-      </c>
-      <c r="AG124">
-        <v>2</v>
-      </c>
       <c r="AH124" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK124">
-        <v>1.28</v>
+        <v>1.81</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,61 +20684,61 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="O125">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P125">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="Q125">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="R125">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S125">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T125">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="U125">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="V125">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W125">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X125">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y125">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z125">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="AA125">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AB125">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AC125">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AD125">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE125">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF125">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG125">
         <v>2</v>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK125">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,80 +20847,80 @@
         </is>
       </c>
       <c r="N126">
+        <v>3.55</v>
+      </c>
+      <c r="O126">
+        <v>3.55</v>
+      </c>
+      <c r="P126">
         <v>1.9</v>
       </c>
-      <c r="O126">
-        <v>3.4</v>
-      </c>
-      <c r="P126">
-        <v>3.75</v>
-      </c>
       <c r="Q126">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="R126">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S126">
         <v>1.39</v>
       </c>
       <c r="T126">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U126">
         <v>2.88</v>
       </c>
       <c r="V126">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W126">
         <v>1.05</v>
       </c>
       <c r="X126">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z126">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AA126">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB126">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC126">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD126">
+        <v>1.23</v>
+      </c>
+      <c r="AE126">
+        <v>1.09</v>
+      </c>
+      <c r="AF126">
+        <v>1.75</v>
+      </c>
+      <c r="AG126">
+        <v>1.91</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126">
         <v>1.25</v>
       </c>
-      <c r="AE126">
-        <v>1.06</v>
-      </c>
-      <c r="AF126">
-        <v>1.82</v>
-      </c>
-      <c r="AG126">
-        <v>1.85</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>1.17</v>
-      </c>
       <c r="AK126">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="O144">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P144">
-        <v>3.09</v>
+        <v>2.4</v>
       </c>
       <c r="Q144">
-        <v>2.78</v>
+        <v>3.38</v>
       </c>
       <c r="R144">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S144">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="U144">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="V144">
+        <v>1.45</v>
+      </c>
+      <c r="W144">
+        <v>1.06</v>
+      </c>
+      <c r="X144">
+        <v>1.05</v>
+      </c>
+      <c r="Y144">
+        <v>1.26</v>
+      </c>
+      <c r="Z144">
+        <v>3.35</v>
+      </c>
+      <c r="AA144">
+        <v>1.9</v>
+      </c>
+      <c r="AB144">
+        <v>2</v>
+      </c>
+      <c r="AC144">
+        <v>2.97</v>
+      </c>
+      <c r="AD144">
         <v>1.37</v>
       </c>
-      <c r="W144">
-        <v>1.04</v>
-      </c>
-      <c r="X144">
-        <v>1.02</v>
-      </c>
-      <c r="Y144">
-        <v>1.33</v>
-      </c>
-      <c r="Z144">
-        <v>3.08</v>
-      </c>
-      <c r="AA144">
-        <v>2</v>
-      </c>
-      <c r="AB144">
-        <v>1.79</v>
-      </c>
-      <c r="AC144">
-        <v>3.2</v>
-      </c>
-      <c r="AD144">
+      <c r="AE144">
+        <v>1.14</v>
+      </c>
+      <c r="AF144">
+        <v>1.62</v>
+      </c>
+      <c r="AG144">
+        <v>2.15</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
         <v>1.29</v>
       </c>
-      <c r="AE144">
-        <v>1.1</v>
-      </c>
-      <c r="AF144">
-        <v>1.75</v>
-      </c>
-      <c r="AG144">
-        <v>1.93</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.25</v>
-      </c>
       <c r="AK144">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="O145">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P145">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="Q145">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R145">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="S145">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T145">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="U145">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="V145">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W145">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y145">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z145">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA145">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB145">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC145">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="AD145">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE145">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG145">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK145">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,80 +24107,80 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="O146">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P146">
-        <v>2.4</v>
+        <v>3.09</v>
       </c>
       <c r="Q146">
-        <v>3.38</v>
+        <v>2.78</v>
       </c>
       <c r="R146">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S146">
+        <v>1.36</v>
+      </c>
+      <c r="T146">
+        <v>2.65</v>
+      </c>
+      <c r="U146">
+        <v>2.89</v>
+      </c>
+      <c r="V146">
+        <v>1.37</v>
+      </c>
+      <c r="W146">
+        <v>1.04</v>
+      </c>
+      <c r="X146">
+        <v>1.02</v>
+      </c>
+      <c r="Y146">
         <v>1.33</v>
       </c>
-      <c r="T146">
-        <v>2.85</v>
-      </c>
-      <c r="U146">
-        <v>2.62</v>
-      </c>
-      <c r="V146">
-        <v>1.45</v>
-      </c>
-      <c r="W146">
-        <v>1.06</v>
-      </c>
-      <c r="X146">
-        <v>1.05</v>
-      </c>
-      <c r="Y146">
-        <v>1.26</v>
-      </c>
       <c r="Z146">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AA146">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB146">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AC146">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AD146">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AE146">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF146">
+        <v>1.75</v>
+      </c>
+      <c r="AG146">
+        <v>1.93</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ146">
+        <v>1.25</v>
+      </c>
+      <c r="AK146">
         <v>1.62</v>
-      </c>
-      <c r="AG146">
-        <v>2.15</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>1.29</v>
-      </c>
-      <c r="AK146">
-        <v>1.4</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="O147">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P147">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q147">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="R147">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="S147">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T147">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="U147">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="V147">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W147">
+        <v>1.07</v>
+      </c>
+      <c r="X147">
+        <v>1.01</v>
+      </c>
+      <c r="Y147">
+        <v>1.22</v>
+      </c>
+      <c r="Z147">
+        <v>3.52</v>
+      </c>
+      <c r="AA147">
+        <v>1.83</v>
+      </c>
+      <c r="AB147">
+        <v>1.95</v>
+      </c>
+      <c r="AC147">
+        <v>2.86</v>
+      </c>
+      <c r="AD147">
+        <v>1.38</v>
+      </c>
+      <c r="AE147">
         <v>1.08</v>
       </c>
-      <c r="X147">
-        <v>1.02</v>
-      </c>
-      <c r="Y147">
-        <v>1.2</v>
-      </c>
-      <c r="Z147">
-        <v>3.8</v>
-      </c>
-      <c r="AA147">
-        <v>1.7</v>
-      </c>
-      <c r="AB147">
-        <v>2.01</v>
-      </c>
-      <c r="AC147">
-        <v>2.83</v>
-      </c>
-      <c r="AD147">
-        <v>1.4</v>
-      </c>
-      <c r="AE147">
-        <v>1.1</v>
-      </c>
       <c r="AF147">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG147">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK147">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="O148">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P148">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="Q148">
-        <v>2.41</v>
+        <v>2.71</v>
       </c>
       <c r="R148">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S148">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T148">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="U148">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="V148">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W148">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X148">
         <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z148">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="AA148">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB148">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC148">
-        <v>2.86</v>
+        <v>2.99</v>
       </c>
       <c r="AD148">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE148">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF148">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG148">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK148">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O288">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P288">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q288">
         <v>3.5</v>
       </c>
       <c r="R288">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="S288">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="T288">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="U288">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="V288">
         <v>1.17</v>
       </c>
       <c r="W288">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X288">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y288">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="Z288">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AA288">
-        <v>3.04</v>
+        <v>3.62</v>
       </c>
       <c r="AB288">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC288">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AD288">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE288">
         <v>1.02</v>
       </c>
       <c r="AF288">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG288">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK288">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O289">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P289">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q289">
         <v>3.5</v>
       </c>
       <c r="R289">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="S289">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="T289">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="U289">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="V289">
         <v>1.17</v>
       </c>
       <c r="W289">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X289">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y289">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="Z289">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AA289">
-        <v>3.62</v>
+        <v>3.04</v>
       </c>
       <c r="AB289">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC289">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AD289">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE289">
         <v>1.02</v>
       </c>
       <c r="AF289">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG289">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK289">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G305">
@@ -50033,55 +50033,55 @@
         <v>0</v>
       </c>
       <c r="Q305">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="R305">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="S305">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="T305">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="U305">
-        <v>3.12</v>
+        <v>3.58</v>
       </c>
       <c r="V305">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W305">
+        <v>1.01</v>
+      </c>
+      <c r="X305">
+        <v>1.06</v>
+      </c>
+      <c r="Y305">
+        <v>1.5</v>
+      </c>
+      <c r="Z305">
+        <v>2.38</v>
+      </c>
+      <c r="AA305">
+        <v>2.49</v>
+      </c>
+      <c r="AB305">
+        <v>1.42</v>
+      </c>
+      <c r="AC305">
+        <v>5</v>
+      </c>
+      <c r="AD305">
+        <v>1.1</v>
+      </c>
+      <c r="AE305">
         <v>1.04</v>
       </c>
-      <c r="X305">
-        <v>1.02</v>
-      </c>
-      <c r="Y305">
-        <v>1.34</v>
-      </c>
-      <c r="Z305">
-        <v>2.78</v>
-      </c>
-      <c r="AA305">
-        <v>2.23</v>
-      </c>
-      <c r="AB305">
-        <v>1.61</v>
-      </c>
-      <c r="AC305">
-        <v>3.9</v>
-      </c>
-      <c r="AD305">
-        <v>1.18</v>
-      </c>
-      <c r="AE305">
-        <v>1.02</v>
-      </c>
       <c r="AF305">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AG305">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK305">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G306">
@@ -50196,55 +50196,55 @@
         <v>0</v>
       </c>
       <c r="Q306">
+        <v>2.95</v>
+      </c>
+      <c r="R306">
+        <v>2.07</v>
+      </c>
+      <c r="S306">
+        <v>1.44</v>
+      </c>
+      <c r="T306">
         <v>2.63</v>
       </c>
-      <c r="R306">
-        <v>1.98</v>
-      </c>
-      <c r="S306">
-        <v>1.54</v>
-      </c>
-      <c r="T306">
-        <v>2.28</v>
-      </c>
       <c r="U306">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="V306">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W306">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X306">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y306">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z306">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="AA306">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AB306">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AC306">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AD306">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AE306">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF306">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AG306">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK306">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G307">
@@ -50359,55 +50359,55 @@
         <v>0</v>
       </c>
       <c r="Q307">
-        <v>2.43</v>
+        <v>2.24</v>
       </c>
       <c r="R307">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S307">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T307">
-        <v>3.14</v>
+        <v>2.67</v>
       </c>
       <c r="U307">
-        <v>2.34</v>
+        <v>2.71</v>
       </c>
       <c r="V307">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W307">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X307">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y307">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z307">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA307">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB307">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AC307">
-        <v>2.43</v>
+        <v>3.25</v>
       </c>
       <c r="AD307">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE307">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF307">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AG307">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK307">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G308">
@@ -50522,55 +50522,55 @@
         <v>0</v>
       </c>
       <c r="Q308">
-        <v>2.24</v>
+        <v>2.43</v>
       </c>
       <c r="R308">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S308">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T308">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="U308">
-        <v>2.71</v>
+        <v>2.34</v>
       </c>
       <c r="V308">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W308">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X308">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y308">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z308">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA308">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AB308">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC308">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="AD308">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AE308">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF308">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="AG308">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK308">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -51654,10 +51654,10 @@
         </is>
       </c>
       <c r="N315">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O315">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P315">
         <v>2.7</v>
@@ -51681,10 +51681,10 @@
         <v>1.51</v>
       </c>
       <c r="W315">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X315">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y315">
         <v>1.18</v>
@@ -51705,10 +51705,10 @@
         <v>1.46</v>
       </c>
       <c r="AE315">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF315">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG315">
         <v>2.25</v>
@@ -54431,7 +54431,7 @@
         <v>3.25</v>
       </c>
       <c r="P332">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q332">
         <v>2.7</v>
@@ -54440,25 +54440,25 @@
         <v>2.18</v>
       </c>
       <c r="S332">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T332">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U332">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="V332">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W332">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X332">
         <v>1.02</v>
       </c>
       <c r="Y332">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z332">
         <v>3.24</v>
@@ -54473,13 +54473,13 @@
         <v>3.64</v>
       </c>
       <c r="AD332">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE332">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF332">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG332">
         <v>1.79</v>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,64 +55077,64 @@
         </is>
       </c>
       <c r="N336">
-        <v>6.35</v>
+        <v>1.7</v>
       </c>
       <c r="O336">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P336">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="Q336">
-        <v>5</v>
+        <v>2.06</v>
       </c>
       <c r="R336">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="S336">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T336">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="U336">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V336">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="W336">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X336">
         <v>0</v>
       </c>
       <c r="Y336">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z336">
-        <v>5.9</v>
+        <v>5.25</v>
       </c>
       <c r="AA336">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB336">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="AC336">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="AD336">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AE336">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AF336">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG336">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55147,10 +55147,10 @@
         </is>
       </c>
       <c r="AJ336">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="AK336">
-        <v>1.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,64 +55240,64 @@
         </is>
       </c>
       <c r="N337">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="O337">
-        <v>4.5</v>
+        <v>3.83</v>
       </c>
       <c r="P337">
-        <v>3.82</v>
+        <v>3.28</v>
       </c>
       <c r="Q337">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="R337">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="S337">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T337">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U337">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V337">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W337">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X337">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y337">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z337">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA337">
         <v>1.45</v>
       </c>
       <c r="AB337">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="AC337">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AD337">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AE337">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF337">
         <v>1.44</v>
       </c>
       <c r="AG337">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH337" t="inlineStr">
         <is>
@@ -55310,10 +55310,10 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK337">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,64 +55403,64 @@
         </is>
       </c>
       <c r="N338">
-        <v>1.79</v>
+        <v>6.35</v>
       </c>
       <c r="O338">
-        <v>3.83</v>
+        <v>4.6</v>
       </c>
       <c r="P338">
-        <v>3.28</v>
+        <v>1.43</v>
       </c>
       <c r="Q338">
-        <v>2.26</v>
+        <v>5</v>
       </c>
       <c r="R338">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S338">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T338">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="U338">
         <v>2.1</v>
       </c>
       <c r="V338">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="W338">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X338">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y338">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z338">
-        <v>5.25</v>
+        <v>5.9</v>
       </c>
       <c r="AA338">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AB338">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="AC338">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="AD338">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE338">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF338">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG338">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55473,10 +55473,10 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>1.17</v>
+        <v>2.7</v>
       </c>
       <c r="AK338">
-        <v>2.03</v>
+        <v>1.12</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,80 +55566,80 @@
         </is>
       </c>
       <c r="N339">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O339">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P339">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="Q339">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="R339">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="S339">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T339">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U339">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="V339">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W339">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X339">
         <v>0</v>
       </c>
       <c r="Y339">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z339">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA339">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB339">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="AC339">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AD339">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AE339">
+        <v>1.29</v>
+      </c>
+      <c r="AF339">
+        <v>1.44</v>
+      </c>
+      <c r="AG339">
+        <v>2.7</v>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI339" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ339">
         <v>1.26</v>
       </c>
-      <c r="AF339">
-        <v>1.5</v>
-      </c>
-      <c r="AG339">
-        <v>2.4</v>
-      </c>
-      <c r="AH339" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI339" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ339">
-        <v>1.25</v>
-      </c>
       <c r="AK339">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AL339">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="O16">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q16">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="R16">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="S16">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="T16">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="U16">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="V16">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W16">
         <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="Z16">
+        <v>2.27</v>
+      </c>
+      <c r="AA16">
         <v>2.7</v>
       </c>
-      <c r="AA16">
+      <c r="AB16">
+        <v>1.44</v>
+      </c>
+      <c r="AC16">
+        <v>5.3</v>
+      </c>
+      <c r="AD16">
+        <v>1.13</v>
+      </c>
+      <c r="AE16">
+        <v>1.01</v>
+      </c>
+      <c r="AF16">
         <v>2.25</v>
       </c>
-      <c r="AB16">
-        <v>1.61</v>
-      </c>
-      <c r="AC16">
-        <v>3.88</v>
-      </c>
-      <c r="AD16">
-        <v>1.18</v>
-      </c>
-      <c r="AE16">
-        <v>1.03</v>
-      </c>
-      <c r="AF16">
-        <v>1.87</v>
-      </c>
       <c r="AG16">
+        <v>1.53</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.16</v>
+      </c>
+      <c r="AK16">
         <v>1.8</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.28</v>
-      </c>
-      <c r="AK16">
-        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O17">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q17">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="R17">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="S17">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="T17">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="U17">
-        <v>3.75</v>
+        <v>3.12</v>
       </c>
       <c r="V17">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
         <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="AA17">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AB17">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AC17">
-        <v>5.3</v>
+        <v>3.88</v>
       </c>
       <c r="AD17">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AG17">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O32">
         <v>3.2</v>
       </c>
       <c r="P32">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q32">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S32">
         <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="U32">
         <v>2.65</v>
@@ -5552,37 +5552,37 @@
         <v>1.42</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA32">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AB32">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC32">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD32">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
         <v>1.33</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O33">
         <v>3.2</v>
       </c>
       <c r="P33">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Q33">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R33">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
         <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="U33">
         <v>2.65</v>
@@ -5715,37 +5715,37 @@
         <v>1.42</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z33">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA33">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AB33">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC33">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD33">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE33">
         <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
         <v>1.33</v>
@@ -9283,10 +9283,10 @@
         <v>3.65</v>
       </c>
       <c r="Q55">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R55">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
         <v>1.25</v>
@@ -9310,19 +9310,19 @@
         <v>1.14</v>
       </c>
       <c r="Z55">
-        <v>4.9</v>
+        <v>4.45</v>
       </c>
       <c r="AA55">
         <v>1.61</v>
       </c>
       <c r="AB55">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC55">
         <v>2.45</v>
       </c>
       <c r="AD55">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE55">
         <v>1.2</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O56">
         <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -9455,10 +9455,10 @@
         <v>1.33</v>
       </c>
       <c r="T56">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="U56">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="V56">
         <v>1.46</v>
@@ -9482,7 +9482,7 @@
         <v>2.1</v>
       </c>
       <c r="AC56">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="AD56">
         <v>1.4</v>
@@ -9494,7 +9494,7 @@
         <v>1.58</v>
       </c>
       <c r="AG56">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AK56">
         <v>1.4</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.87</v>
+        <v>1.48</v>
       </c>
       <c r="O65">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="P65">
-        <v>2.05</v>
+        <v>5.5</v>
       </c>
       <c r="Q65">
-        <v>3.3</v>
+        <v>2.02</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T65">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="U65">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V65">
+        <v>1.62</v>
+      </c>
+      <c r="W65">
+        <v>1.13</v>
+      </c>
+      <c r="X65">
+        <v>1.02</v>
+      </c>
+      <c r="Y65">
+        <v>1.15</v>
+      </c>
+      <c r="Z65">
+        <v>4.9</v>
+      </c>
+      <c r="AA65">
         <v>1.44</v>
       </c>
-      <c r="W65">
-        <v>1.07</v>
-      </c>
-      <c r="X65">
-        <v>1.04</v>
-      </c>
-      <c r="Y65">
-        <v>1.18</v>
-      </c>
-      <c r="Z65">
-        <v>4</v>
-      </c>
-      <c r="AA65">
-        <v>1.75</v>
-      </c>
       <c r="AB65">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
       <c r="AC65">
-        <v>2.76</v>
+        <v>2.27</v>
       </c>
       <c r="AD65">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AE65">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF65">
         <v>1.62</v>
       </c>
       <c r="AG65">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="AK65">
-        <v>1.38</v>
+        <v>2.62</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.48</v>
+        <v>2.87</v>
       </c>
       <c r="O66">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="P66">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q66">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="R66">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="U66">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V66">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W66">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z66">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AA66">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AB66">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="AC66">
-        <v>2.27</v>
+        <v>2.76</v>
       </c>
       <c r="AD66">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="AE66">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF66">
         <v>1.62</v>
       </c>
       <c r="AG66">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="AK66">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11556,22 +11556,22 @@
         </is>
       </c>
       <c r="N69">
-        <v>5.8</v>
+        <v>6.34</v>
       </c>
       <c r="O69">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P69">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q69">
         <v>5.03</v>
       </c>
       <c r="R69">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="S69">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T69">
         <v>2.81</v>
@@ -11595,7 +11595,7 @@
         <v>3.24</v>
       </c>
       <c r="AA69">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AB69">
         <v>1.83</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>2.52</v>
+        <v>1.27</v>
       </c>
       <c r="AK69">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12697,31 +12697,31 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O76">
         <v>3.2</v>
       </c>
       <c r="P76">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q76">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="R76">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S76">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U76">
         <v>2.96</v>
       </c>
       <c r="V76">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W76">
         <v>1.03</v>
@@ -12730,19 +12730,19 @@
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z76">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA76">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AB76">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AC76">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
       <c r="AD76">
         <v>1.21</v>
@@ -12751,10 +12751,10 @@
         <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG76">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AK76">
         <v>1.35</v>
@@ -12860,46 +12860,46 @@
         </is>
       </c>
       <c r="N77">
+        <v>3.1</v>
+      </c>
+      <c r="O77">
         <v>3.2</v>
       </c>
-      <c r="O77">
-        <v>3.25</v>
-      </c>
       <c r="P77">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q77">
         <v>3.8</v>
       </c>
       <c r="R77">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S77">
         <v>1.42</v>
       </c>
       <c r="T77">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="U77">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V77">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
         <v>1.03</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
         <v>1.33</v>
       </c>
       <c r="Z77">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA77">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AB77">
         <v>1.66</v>
@@ -12911,13 +12911,13 @@
         <v>1.21</v>
       </c>
       <c r="AE77">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF77">
         <v>1.83</v>
       </c>
       <c r="AG77">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AK77">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,25 +13023,25 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P78">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q78">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R78">
         <v>2.01</v>
       </c>
       <c r="S78">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T78">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U78">
         <v>3</v>
@@ -13050,37 +13050,37 @@
         <v>1.32</v>
       </c>
       <c r="W78">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z78">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="AA78">
         <v>2.06</v>
       </c>
       <c r="AB78">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC78">
         <v>3.58</v>
       </c>
       <c r="AD78">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF78">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG78">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O79">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="P79">
-        <v>3.14</v>
+        <v>3.83</v>
       </c>
       <c r="Q79">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S79">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="T79">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="U79">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="V79">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="W79">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y79">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="Z79">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="AA79">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AB79">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AC79">
-        <v>3.15</v>
+        <v>4.85</v>
       </c>
       <c r="AD79">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AE79">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AG79">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK79">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="O80">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P80">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="Q80">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="R80">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S80">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="T80">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="U80">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="V80">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="W80">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X80">
+        <v>1.01</v>
+      </c>
+      <c r="Y80">
+        <v>1.33</v>
+      </c>
+      <c r="Z80">
+        <v>2.92</v>
+      </c>
+      <c r="AA80">
+        <v>2.09</v>
+      </c>
+      <c r="AB80">
+        <v>1.66</v>
+      </c>
+      <c r="AC80">
+        <v>3.8</v>
+      </c>
+      <c r="AD80">
+        <v>1.25</v>
+      </c>
+      <c r="AE80">
         <v>1.05</v>
       </c>
-      <c r="Y80">
-        <v>1.47</v>
-      </c>
-      <c r="Z80">
-        <v>2.49</v>
-      </c>
-      <c r="AA80">
-        <v>2.56</v>
-      </c>
-      <c r="AB80">
-        <v>1.44</v>
-      </c>
-      <c r="AC80">
-        <v>4.93</v>
-      </c>
-      <c r="AD80">
-        <v>1.11</v>
-      </c>
-      <c r="AE80">
-        <v>1.01</v>
-      </c>
       <c r="AF80">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AG80">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK80">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,61 +13512,61 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="O81">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P81">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="Q81">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="R81">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="S81">
         <v>1.4</v>
       </c>
       <c r="T81">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U81">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="V81">
+        <v>1.3</v>
+      </c>
+      <c r="W81">
+        <v>1.05</v>
+      </c>
+      <c r="X81">
+        <v>1.03</v>
+      </c>
+      <c r="Y81">
         <v>1.35</v>
       </c>
-      <c r="W81">
-        <v>1.01</v>
-      </c>
-      <c r="X81">
-        <v>1.01</v>
-      </c>
-      <c r="Y81">
-        <v>1.31</v>
-      </c>
       <c r="Z81">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA81">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AB81">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC81">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AD81">
         <v>1.19</v>
       </c>
       <c r="AE81">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF81">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG81">
         <v>1.85</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK81">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>2.75</v>
+      </c>
+      <c r="R82">
+        <v>2</v>
+      </c>
+      <c r="S82">
+        <v>1.47</v>
+      </c>
+      <c r="T82">
+        <v>2.41</v>
+      </c>
+      <c r="U82">
         <v>3</v>
       </c>
-      <c r="P82">
-        <v>2.6</v>
-      </c>
-      <c r="Q82">
-        <v>3</v>
-      </c>
-      <c r="R82">
-        <v>1.94</v>
-      </c>
-      <c r="S82">
-        <v>1.4</v>
-      </c>
-      <c r="T82">
-        <v>2.53</v>
-      </c>
-      <c r="U82">
-        <v>3.3</v>
-      </c>
       <c r="V82">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y82">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z82">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="AA82">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB82">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC82">
-        <v>3.93</v>
+        <v>4.34</v>
       </c>
       <c r="AD82">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF82">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AG82">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK82">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q83">
         <v>2.75</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="S83">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="U83">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="V83">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="W83">
+        <v>1.03</v>
+      </c>
+      <c r="X83">
         <v>1.01</v>
       </c>
-      <c r="X83">
-        <v>1.03</v>
-      </c>
       <c r="Y83">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z83">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA83">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="AB83">
+        <v>1.8</v>
+      </c>
+      <c r="AC83">
+        <v>3.28</v>
+      </c>
+      <c r="AD83">
+        <v>1.26</v>
+      </c>
+      <c r="AE83">
+        <v>1.05</v>
+      </c>
+      <c r="AF83">
+        <v>1.67</v>
+      </c>
+      <c r="AG83">
+        <v>1.96</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.25</v>
+      </c>
+      <c r="AK83">
         <v>1.61</v>
-      </c>
-      <c r="AC83">
-        <v>4.1</v>
-      </c>
-      <c r="AD83">
-        <v>1.16</v>
-      </c>
-      <c r="AE83">
-        <v>1.02</v>
-      </c>
-      <c r="AF83">
-        <v>1.85</v>
-      </c>
-      <c r="AG83">
-        <v>1.77</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.27</v>
-      </c>
-      <c r="AK83">
-        <v>1.57</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15311,7 +15311,7 @@
         <v>3.3</v>
       </c>
       <c r="P92">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q92">
         <v>4.2</v>
@@ -15323,7 +15323,7 @@
         <v>1.37</v>
       </c>
       <c r="T92">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U92">
         <v>2.7</v>
@@ -15335,13 +15335,13 @@
         <v>1.08</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y92">
         <v>1.26</v>
       </c>
       <c r="Z92">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AA92">
         <v>1.95</v>
@@ -15350,19 +15350,19 @@
         <v>1.85</v>
       </c>
       <c r="AC92">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD92">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE92">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF92">
         <v>1.75</v>
       </c>
       <c r="AG92">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -16120,43 +16120,43 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O97">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P97">
         <v>4.7</v>
       </c>
       <c r="Q97">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="R97">
         <v>2.37</v>
       </c>
       <c r="S97">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
         <v>4</v>
       </c>
       <c r="U97">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="V97">
         <v>1.65</v>
       </c>
       <c r="W97">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X97">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
         <v>1.11</v>
       </c>
       <c r="Z97">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA97">
         <v>1.5</v>
@@ -16165,7 +16165,7 @@
         <v>2.51</v>
       </c>
       <c r="AC97">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD97">
         <v>1.68</v>
@@ -16177,7 +16177,7 @@
         <v>1.54</v>
       </c>
       <c r="AG97">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="O98">
         <v>3.6</v>
@@ -16292,7 +16292,7 @@
         <v>2.28</v>
       </c>
       <c r="Q98">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="R98">
         <v>2.45</v>
@@ -16304,16 +16304,16 @@
         <v>3.8</v>
       </c>
       <c r="U98">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V98">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="W98">
         <v>1.15</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y98">
         <v>1.17</v>
@@ -16322,22 +16322,22 @@
         <v>5</v>
       </c>
       <c r="AA98">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB98">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AC98">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AD98">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE98">
         <v>1.22</v>
       </c>
       <c r="AF98">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG98">
         <v>2.66</v>
@@ -16356,7 +16356,7 @@
         <v>1.57</v>
       </c>
       <c r="AK98">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16449,19 +16449,19 @@
         <v>1.7</v>
       </c>
       <c r="O99">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P99">
         <v>4.7</v>
       </c>
       <c r="Q99">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="R99">
         <v>2.38</v>
       </c>
       <c r="S99">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T99">
         <v>3.6</v>
@@ -16470,7 +16470,7 @@
         <v>2.45</v>
       </c>
       <c r="V99">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W99">
         <v>1.13</v>
@@ -16479,7 +16479,7 @@
         <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z99">
         <v>4.4</v>
@@ -16488,16 +16488,16 @@
         <v>1.67</v>
       </c>
       <c r="AB99">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AC99">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AD99">
         <v>1.46</v>
       </c>
       <c r="AE99">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF99">
         <v>1.63</v>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK99">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,19 +16609,19 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="O100">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="P100">
         <v>2.55</v>
       </c>
       <c r="Q100">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="R100">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="S100">
         <v>1.3</v>
@@ -16639,22 +16639,22 @@
         <v>1.12</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y100">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z100">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA100">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB100">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC100">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD100">
         <v>1.55</v>
@@ -16772,16 +16772,16 @@
         </is>
       </c>
       <c r="N101">
-        <v>4.68</v>
+        <v>4.71</v>
       </c>
       <c r="O101">
-        <v>4.59</v>
+        <v>4.6</v>
       </c>
       <c r="P101">
         <v>1.59</v>
       </c>
       <c r="Q101">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="R101">
         <v>2.6</v>
@@ -16799,13 +16799,13 @@
         <v>1.67</v>
       </c>
       <c r="W101">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z101">
         <v>6</v>
@@ -16820,10 +16820,10 @@
         <v>2.15</v>
       </c>
       <c r="AD101">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE101">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF101">
         <v>1.5</v>
@@ -17427,31 +17427,31 @@
         <v>1.55</v>
       </c>
       <c r="O105">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="P105">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q105">
         <v>2</v>
       </c>
       <c r="R105">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="S105">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T105">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="U105">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V105">
         <v>1.53</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
         <v>1.01</v>
@@ -17463,25 +17463,25 @@
         <v>4.5</v>
       </c>
       <c r="AA105">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB105">
         <v>2.23</v>
       </c>
       <c r="AC105">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD105">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE105">
         <v>1.16</v>
       </c>
       <c r="AF105">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG105">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK105">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="O120">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P120">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q120">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="R120">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S120">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T120">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="U120">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="V120">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W120">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z120">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="AA120">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB120">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC120">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="AD120">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE120">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF120">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG120">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK120">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
+        <v>1.85</v>
+      </c>
+      <c r="O121">
+        <v>3.5</v>
+      </c>
+      <c r="P121">
+        <v>3.6</v>
+      </c>
+      <c r="Q121">
+        <v>2.3</v>
+      </c>
+      <c r="R121">
+        <v>2.25</v>
+      </c>
+      <c r="S121">
+        <v>1.4</v>
+      </c>
+      <c r="T121">
+        <v>2.69</v>
+      </c>
+      <c r="U121">
+        <v>2.88</v>
+      </c>
+      <c r="V121">
+        <v>1.38</v>
+      </c>
+      <c r="W121">
+        <v>1.05</v>
+      </c>
+      <c r="X121">
+        <v>1.03</v>
+      </c>
+      <c r="Y121">
+        <v>1.3</v>
+      </c>
+      <c r="Z121">
         <v>3.3</v>
       </c>
-      <c r="O121">
-        <v>3.3</v>
-      </c>
-      <c r="P121">
-        <v>2.1</v>
-      </c>
-      <c r="Q121">
-        <v>3.6</v>
-      </c>
-      <c r="R121">
-        <v>2.04</v>
-      </c>
-      <c r="S121">
-        <v>1.37</v>
-      </c>
-      <c r="T121">
-        <v>2.97</v>
-      </c>
-      <c r="U121">
-        <v>2.63</v>
-      </c>
-      <c r="V121">
-        <v>1.39</v>
-      </c>
-      <c r="W121">
-        <v>1.07</v>
-      </c>
-      <c r="X121">
-        <v>1.05</v>
-      </c>
-      <c r="Y121">
-        <v>1.24</v>
-      </c>
-      <c r="Z121">
-        <v>3.4</v>
-      </c>
       <c r="AA121">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB121">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC121">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="AD121">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE121">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AG121">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK121">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O122">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P122">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q122">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="R122">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="S122">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T122">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="U122">
         <v>2.88</v>
       </c>
       <c r="V122">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W122">
         <v>1.05</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z122">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AA122">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB122">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC122">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="AD122">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE122">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF122">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG122">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK122">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O123">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P123">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q123">
+        <v>3.2</v>
+      </c>
+      <c r="R123">
+        <v>2.1</v>
+      </c>
+      <c r="S123">
+        <v>1.44</v>
+      </c>
+      <c r="T123">
+        <v>2.54</v>
+      </c>
+      <c r="U123">
+        <v>2.75</v>
+      </c>
+      <c r="V123">
+        <v>1.35</v>
+      </c>
+      <c r="W123">
+        <v>1.03</v>
+      </c>
+      <c r="X123">
+        <v>1.03</v>
+      </c>
+      <c r="Y123">
+        <v>1.32</v>
+      </c>
+      <c r="Z123">
         <v>2.88</v>
       </c>
-      <c r="R123">
-        <v>2.04</v>
-      </c>
-      <c r="S123">
-        <v>1.41</v>
-      </c>
-      <c r="T123">
-        <v>2.62</v>
-      </c>
-      <c r="U123">
-        <v>2.96</v>
-      </c>
-      <c r="V123">
-        <v>1.37</v>
-      </c>
-      <c r="W123">
-        <v>1.05</v>
-      </c>
-      <c r="X123">
-        <v>1.06</v>
-      </c>
-      <c r="Y123">
-        <v>1.28</v>
-      </c>
-      <c r="Z123">
-        <v>3.08</v>
-      </c>
       <c r="AA123">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="AB123">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AC123">
-        <v>3.35</v>
+        <v>3.83</v>
       </c>
       <c r="AD123">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE123">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG123">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK123">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,80 +20521,80 @@
         </is>
       </c>
       <c r="N124">
+        <v>3.55</v>
+      </c>
+      <c r="O124">
+        <v>3.55</v>
+      </c>
+      <c r="P124">
         <v>1.9</v>
       </c>
-      <c r="O124">
-        <v>3.4</v>
-      </c>
-      <c r="P124">
-        <v>3.75</v>
-      </c>
       <c r="Q124">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="R124">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S124">
         <v>1.39</v>
       </c>
       <c r="T124">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U124">
         <v>2.88</v>
       </c>
       <c r="V124">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W124">
         <v>1.05</v>
       </c>
       <c r="X124">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z124">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AA124">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB124">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC124">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD124">
+        <v>1.23</v>
+      </c>
+      <c r="AE124">
+        <v>1.09</v>
+      </c>
+      <c r="AF124">
+        <v>1.75</v>
+      </c>
+      <c r="AG124">
+        <v>1.91</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ124">
         <v>1.25</v>
       </c>
-      <c r="AE124">
-        <v>1.06</v>
-      </c>
-      <c r="AF124">
-        <v>1.82</v>
-      </c>
-      <c r="AG124">
-        <v>1.85</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>1.17</v>
-      </c>
       <c r="AK124">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,61 +20684,61 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="O125">
+        <v>3.3</v>
+      </c>
+      <c r="P125">
+        <v>2.87</v>
+      </c>
+      <c r="Q125">
+        <v>2.88</v>
+      </c>
+      <c r="R125">
+        <v>2.04</v>
+      </c>
+      <c r="S125">
+        <v>1.41</v>
+      </c>
+      <c r="T125">
+        <v>2.62</v>
+      </c>
+      <c r="U125">
+        <v>2.96</v>
+      </c>
+      <c r="V125">
+        <v>1.37</v>
+      </c>
+      <c r="W125">
+        <v>1.05</v>
+      </c>
+      <c r="X125">
+        <v>1.06</v>
+      </c>
+      <c r="Y125">
+        <v>1.28</v>
+      </c>
+      <c r="Z125">
+        <v>3.08</v>
+      </c>
+      <c r="AA125">
+        <v>1.97</v>
+      </c>
+      <c r="AB125">
+        <v>1.79</v>
+      </c>
+      <c r="AC125">
         <v>3.35</v>
       </c>
-      <c r="P125">
-        <v>3.25</v>
-      </c>
-      <c r="Q125">
-        <v>2.45</v>
-      </c>
-      <c r="R125">
-        <v>2.08</v>
-      </c>
-      <c r="S125">
-        <v>1.36</v>
-      </c>
-      <c r="T125">
-        <v>2.85</v>
-      </c>
-      <c r="U125">
-        <v>2.75</v>
-      </c>
-      <c r="V125">
-        <v>1.4</v>
-      </c>
-      <c r="W125">
-        <v>1.06</v>
-      </c>
-      <c r="X125">
-        <v>1.03</v>
-      </c>
-      <c r="Y125">
+      <c r="AD125">
         <v>1.27</v>
       </c>
-      <c r="Z125">
-        <v>3.55</v>
-      </c>
-      <c r="AA125">
-        <v>1.91</v>
-      </c>
-      <c r="AB125">
-        <v>1.88</v>
-      </c>
-      <c r="AC125">
-        <v>3.15</v>
-      </c>
-      <c r="AD125">
-        <v>1.29</v>
-      </c>
       <c r="AE125">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF125">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG125">
         <v>2</v>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK125">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="O126">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P126">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q126">
-        <v>3.95</v>
+        <v>3.18</v>
       </c>
       <c r="R126">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S126">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T126">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="U126">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V126">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W126">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y126">
         <v>1.27</v>
       </c>
       <c r="Z126">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="AA126">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB126">
         <v>1.75</v>
       </c>
       <c r="AC126">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="AD126">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE126">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF126">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG126">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK126">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,80 +21010,80 @@
         </is>
       </c>
       <c r="N127">
+        <v>1.95</v>
+      </c>
+      <c r="O127">
+        <v>3.35</v>
+      </c>
+      <c r="P127">
+        <v>3.25</v>
+      </c>
+      <c r="Q127">
         <v>2.45</v>
       </c>
-      <c r="O127">
-        <v>3</v>
-      </c>
-      <c r="P127">
-        <v>2.75</v>
-      </c>
-      <c r="Q127">
-        <v>3.2</v>
-      </c>
       <c r="R127">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S127">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T127">
-        <v>2.54</v>
+        <v>2.85</v>
       </c>
       <c r="U127">
         <v>2.75</v>
       </c>
       <c r="V127">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W127">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X127">
         <v>1.03</v>
       </c>
       <c r="Y127">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z127">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="AA127">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AB127">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC127">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="AD127">
+        <v>1.29</v>
+      </c>
+      <c r="AE127">
+        <v>1.08</v>
+      </c>
+      <c r="AF127">
+        <v>1.72</v>
+      </c>
+      <c r="AG127">
+        <v>2</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127">
         <v>1.25</v>
       </c>
-      <c r="AE127">
-        <v>1.03</v>
-      </c>
-      <c r="AF127">
-        <v>1.73</v>
-      </c>
-      <c r="AG127">
-        <v>1.85</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>1.33</v>
-      </c>
       <c r="AK127">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="O136">
         <v>3.3</v>
       </c>
       <c r="P136">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="Q136">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="R136">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="S136">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T136">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="U136">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="V136">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W136">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X136">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y136">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z136">
         <v>2.94</v>
       </c>
       <c r="AA136">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AB136">
         <v>1.73</v>
       </c>
       <c r="AC136">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AD136">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE136">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF136">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG136">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AK136">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="O137">
         <v>3.3</v>
       </c>
       <c r="P137">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="Q137">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="R137">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S137">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T137">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="U137">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="V137">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W137">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X137">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y137">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z137">
         <v>2.94</v>
       </c>
       <c r="AA137">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AB137">
         <v>1.73</v>
       </c>
       <c r="AC137">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AD137">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE137">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF137">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG137">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AK137">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O142">
         <v>3.43</v>
       </c>
       <c r="P142">
-        <v>3.53</v>
+        <v>4</v>
       </c>
       <c r="Q142">
         <v>2.4</v>
@@ -23473,7 +23473,7 @@
         <v>1.36</v>
       </c>
       <c r="T142">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U142">
         <v>2.65</v>
@@ -23488,19 +23488,19 @@
         <v>1.03</v>
       </c>
       <c r="Y142">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z142">
-        <v>3.78</v>
+        <v>3.62</v>
       </c>
       <c r="AA142">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB142">
         <v>2</v>
       </c>
       <c r="AC142">
-        <v>2.89</v>
+        <v>3.07</v>
       </c>
       <c r="AD142">
         <v>1.36</v>
@@ -23509,10 +23509,10 @@
         <v>1.08</v>
       </c>
       <c r="AF142">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG142">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.19</v>
+        <v>2.77</v>
       </c>
       <c r="O143">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P143">
-        <v>2.98</v>
+        <v>2.24</v>
       </c>
       <c r="Q143">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="R143">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="S143">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T143">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="U143">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="V143">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W143">
+        <v>1.06</v>
+      </c>
+      <c r="X143">
         <v>1.05</v>
       </c>
-      <c r="X143">
-        <v>1.07</v>
-      </c>
       <c r="Y143">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z143">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AA143">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB143">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AC143">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="AD143">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE143">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF143">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG143">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK143">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,28 +23781,28 @@
         </is>
       </c>
       <c r="N144">
+        <v>2.16</v>
+      </c>
+      <c r="O144">
+        <v>3.62</v>
+      </c>
+      <c r="P144">
+        <v>2.9</v>
+      </c>
+      <c r="Q144">
+        <v>2.8</v>
+      </c>
+      <c r="R144">
+        <v>2.31</v>
+      </c>
+      <c r="S144">
+        <v>1.32</v>
+      </c>
+      <c r="T144">
         <v>2.87</v>
       </c>
-      <c r="O144">
-        <v>3.5</v>
-      </c>
-      <c r="P144">
-        <v>2.4</v>
-      </c>
-      <c r="Q144">
-        <v>3.38</v>
-      </c>
-      <c r="R144">
-        <v>2.1</v>
-      </c>
-      <c r="S144">
-        <v>1.33</v>
-      </c>
-      <c r="T144">
-        <v>2.85</v>
-      </c>
       <c r="U144">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V144">
         <v>1.45</v>
@@ -23811,28 +23811,28 @@
         <v>1.06</v>
       </c>
       <c r="X144">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z144">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AA144">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AB144">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC144">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AD144">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE144">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF144">
         <v>1.62</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK144">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O145">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P145">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="Q145">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="R145">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S145">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T145">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="U145">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="V145">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W145">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X145">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z145">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA145">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AB145">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC145">
-        <v>2.83</v>
+        <v>2.99</v>
       </c>
       <c r="AD145">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE145">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF145">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG145">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK145">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24110,22 +24110,22 @@
         <v>2.3</v>
       </c>
       <c r="O146">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="P146">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="Q146">
         <v>2.78</v>
       </c>
       <c r="R146">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="S146">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T146">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U146">
         <v>2.89</v>
@@ -24134,13 +24134,13 @@
         <v>1.37</v>
       </c>
       <c r="W146">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X146">
         <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z146">
         <v>3.08</v>
@@ -24149,13 +24149,13 @@
         <v>2</v>
       </c>
       <c r="AB146">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC146">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD146">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE146">
         <v>1.1</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="O147">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P147">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="Q147">
-        <v>2.41</v>
+        <v>2.93</v>
       </c>
       <c r="R147">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="S147">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="T147">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="U147">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="V147">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W147">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X147">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y147">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z147">
-        <v>3.52</v>
+        <v>3.12</v>
       </c>
       <c r="AA147">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AB147">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC147">
-        <v>2.86</v>
+        <v>3.62</v>
       </c>
       <c r="AD147">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE147">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF147">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AG147">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK147">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="O148">
         <v>3.5</v>
       </c>
       <c r="P148">
-        <v>2.94</v>
+        <v>3.92</v>
       </c>
       <c r="Q148">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="R148">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S148">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T148">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="U148">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="V148">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W148">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X148">
         <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z148">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="AA148">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB148">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC148">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="AD148">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE148">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF148">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG148">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK148">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24928,25 +24928,25 @@
         <v>3.45</v>
       </c>
       <c r="P151">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q151">
         <v>3</v>
       </c>
       <c r="R151">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S151">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T151">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="U151">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="V151">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="W151">
         <v>1.14</v>
@@ -24955,31 +24955,31 @@
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z151">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="AA151">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AB151">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC151">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD151">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AE151">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF151">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG151">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK151">
         <v>1.4</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="O156">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P156">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="Q156">
         <v>2.2</v>
@@ -25752,7 +25752,7 @@
         <v>2.23</v>
       </c>
       <c r="S156">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
         <v>2.89</v>
@@ -25761,7 +25761,7 @@
         <v>2.81</v>
       </c>
       <c r="V156">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W156">
         <v>1.06</v>
@@ -25776,13 +25776,13 @@
         <v>3.55</v>
       </c>
       <c r="AA156">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB156">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC156">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="AD156">
         <v>1.29</v>
@@ -25810,7 +25810,7 @@
         <v>1.27</v>
       </c>
       <c r="AK156">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25900,28 +25900,28 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="O157">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="P157">
-        <v>2.93</v>
+        <v>3.45</v>
       </c>
       <c r="Q157">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R157">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S157">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T157">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="U157">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="V157">
         <v>1.33</v>
@@ -25930,34 +25930,34 @@
         <v>1.07</v>
       </c>
       <c r="X157">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y157">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z157">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AA157">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB157">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC157">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AD157">
         <v>1.25</v>
       </c>
       <c r="AE157">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF157">
         <v>1.82</v>
       </c>
       <c r="AG157">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK157">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26063,31 +26063,31 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O158">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="P158">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q158">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="R158">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S158">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="T158">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="U158">
         <v>3.3</v>
       </c>
       <c r="V158">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W158">
         <v>1</v>
@@ -26099,7 +26099,7 @@
         <v>1.42</v>
       </c>
       <c r="Z158">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="AA158">
         <v>2.35</v>
@@ -26108,7 +26108,7 @@
         <v>1.57</v>
       </c>
       <c r="AC158">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="AD158">
         <v>1.17</v>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AK158">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -27856,10 +27856,10 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="O169">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P169">
         <v>2.25</v>
@@ -27868,16 +27868,16 @@
         <v>3.3</v>
       </c>
       <c r="R169">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S169">
         <v>1.35</v>
       </c>
       <c r="T169">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="U169">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="V169">
         <v>1.45</v>
@@ -27910,10 +27910,10 @@
         <v>1.1</v>
       </c>
       <c r="AF169">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG169">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AK169">
         <v>1.34</v>
@@ -28182,28 +28182,28 @@
         </is>
       </c>
       <c r="N171">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O171">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P171">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q171">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="R171">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S171">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T171">
         <v>3.25</v>
       </c>
       <c r="U171">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="V171">
         <v>1.5</v>
@@ -28215,7 +28215,7 @@
         <v>1.02</v>
       </c>
       <c r="Y171">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z171">
         <v>4.1</v>
@@ -28239,7 +28239,7 @@
         <v>1.55</v>
       </c>
       <c r="AG171">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="AK171">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -30627,7 +30627,7 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O186">
         <v>2.9</v>
@@ -30636,16 +30636,16 @@
         <v>3.4</v>
       </c>
       <c r="Q186">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="R186">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S186">
         <v>1.57</v>
       </c>
       <c r="T186">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U186">
         <v>3.4</v>
@@ -30657,22 +30657,22 @@
         <v>1.02</v>
       </c>
       <c r="X186">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y186">
         <v>1.49</v>
       </c>
       <c r="Z186">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="AA186">
         <v>2.71</v>
       </c>
       <c r="AB186">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC186">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AD186">
         <v>1.1</v>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK186">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30953,34 +30953,34 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O188">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P188">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q188">
         <v>2.88</v>
       </c>
       <c r="R188">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S188">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T188">
         <v>2.86</v>
       </c>
       <c r="U188">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="V188">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W188">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X188">
         <v>1.01</v>
@@ -30992,25 +30992,25 @@
         <v>3.2</v>
       </c>
       <c r="AA188">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB188">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC188">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD188">
         <v>1.28</v>
       </c>
       <c r="AE188">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF188">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG188">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31125,16 +31125,16 @@
         <v>3.14</v>
       </c>
       <c r="Q189">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="R189">
         <v>2.07</v>
       </c>
       <c r="S189">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T189">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="U189">
         <v>2.79</v>
@@ -31143,7 +31143,7 @@
         <v>1.35</v>
       </c>
       <c r="W189">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X189">
         <v>1.01</v>
@@ -31152,19 +31152,19 @@
         <v>1.25</v>
       </c>
       <c r="Z189">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA189">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AB189">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC189">
         <v>3.28</v>
       </c>
       <c r="AD189">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE189">
         <v>1.05</v>
@@ -31173,7 +31173,7 @@
         <v>1.72</v>
       </c>
       <c r="AG189">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK189">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31454,19 +31454,19 @@
         <v>3.06</v>
       </c>
       <c r="R191">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S191">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T191">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U191">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V191">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W191">
         <v>1.05</v>
@@ -31481,25 +31481,25 @@
         <v>3</v>
       </c>
       <c r="AA191">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB191">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC191">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD191">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE191">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF191">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG191">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK191">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31614,34 +31614,34 @@
         <v>6</v>
       </c>
       <c r="Q192">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R192">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S192">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T192">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U192">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V192">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W192">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X192">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y192">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z192">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="AA192">
         <v>1.65</v>
@@ -31650,19 +31650,19 @@
         <v>2.2</v>
       </c>
       <c r="AC192">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD192">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE192">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF192">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG192">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>1.16</v>
       </c>
       <c r="AK192">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31931,28 +31931,28 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O194">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P194">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q194">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="R194">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="S194">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T194">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="U194">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="V194">
         <v>1.29</v>
@@ -31961,34 +31961,34 @@
         <v>1.02</v>
       </c>
       <c r="X194">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y194">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z194">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA194">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB194">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC194">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="AD194">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE194">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF194">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG194">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK194">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="O195">
         <v>3</v>
       </c>
       <c r="P195">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q195">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="R195">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S195">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T195">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="U195">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="V195">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W195">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X195">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y195">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="Z195">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AA195">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="AB195">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AC195">
-        <v>3.74</v>
+        <v>4.8</v>
       </c>
       <c r="AD195">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE195">
         <v>1.03</v>
       </c>
       <c r="AF195">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AG195">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK195">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O196">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P196">
         <v>3.2</v>
       </c>
       <c r="Q196">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="R196">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S196">
+        <v>1.55</v>
+      </c>
+      <c r="T196">
+        <v>2.27</v>
+      </c>
+      <c r="U196">
+        <v>3.3</v>
+      </c>
+      <c r="V196">
+        <v>1.25</v>
+      </c>
+      <c r="W196">
+        <v>1.04</v>
+      </c>
+      <c r="X196">
+        <v>1.06</v>
+      </c>
+      <c r="Y196">
         <v>1.44</v>
       </c>
-      <c r="T196">
-        <v>2.46</v>
-      </c>
-      <c r="U196">
-        <v>3.2</v>
-      </c>
-      <c r="V196">
-        <v>1.28</v>
-      </c>
-      <c r="W196">
-        <v>1.01</v>
-      </c>
-      <c r="X196">
-        <v>1.03</v>
-      </c>
-      <c r="Y196">
-        <v>1.36</v>
-      </c>
       <c r="Z196">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AA196">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="AB196">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC196">
-        <v>3.98</v>
+        <v>5.25</v>
       </c>
       <c r="AD196">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE196">
         <v>1.02</v>
       </c>
       <c r="AF196">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AG196">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK196">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="O203">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P203">
         <v>2.3</v>
       </c>
       <c r="Q203">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="R203">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S203">
         <v>1.48</v>
       </c>
       <c r="T203">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U203">
         <v>3.12</v>
       </c>
       <c r="V203">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W203">
         <v>1.02</v>
       </c>
       <c r="X203">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y203">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z203">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="AA203">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB203">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC203">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="AD203">
         <v>1.18</v>
       </c>
       <c r="AE203">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF203">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG203">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AK203">
         <v>1.36</v>
@@ -33570,55 +33570,55 @@
         <v>2.3</v>
       </c>
       <c r="Q204">
-        <v>3.92</v>
+        <v>4.17</v>
       </c>
       <c r="R204">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="S204">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T204">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U204">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V204">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W204">
         <v>1.02</v>
       </c>
       <c r="X204">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y204">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z204">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AA204">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB204">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AC204">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="AD204">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE204">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF204">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG204">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK204">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O205">
         <v>3.1</v>
       </c>
       <c r="P205">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q205">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R205">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S205">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T205">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U205">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="V205">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W205">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X205">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z205">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA205">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AB205">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC205">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="AD205">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE205">
         <v>1.02</v>
       </c>
       <c r="AF205">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG205">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK205">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33887,16 +33887,16 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="O206">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P206">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Q206">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="R206">
         <v>2.17</v>
@@ -33914,28 +33914,28 @@
         <v>1.4</v>
       </c>
       <c r="W206">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X206">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y206">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z206">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="AA206">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB206">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC206">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD206">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE206">
         <v>1.08</v>
@@ -34050,34 +34050,34 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="O207">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P207">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="Q207">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R207">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S207">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T207">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U207">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="V207">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W207">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X207">
         <v>1.05</v>
@@ -34089,13 +34089,13 @@
         <v>2.88</v>
       </c>
       <c r="AA207">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AB207">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC207">
-        <v>3.35</v>
+        <v>3.98</v>
       </c>
       <c r="AD207">
         <v>1.2</v>
@@ -34107,7 +34107,7 @@
         <v>1.85</v>
       </c>
       <c r="AG207">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK207">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O208">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P208">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34376,25 +34376,25 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="O209">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P209">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="Q209">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R209">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S209">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T209">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="U209">
         <v>2.63</v>
@@ -34403,25 +34403,25 @@
         <v>1.39</v>
       </c>
       <c r="W209">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X209">
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z209">
         <v>3.45</v>
       </c>
       <c r="AA209">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB209">
         <v>1.89</v>
       </c>
       <c r="AC209">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AD209">
         <v>1.31</v>
@@ -34449,7 +34449,7 @@
         <v>1.24</v>
       </c>
       <c r="AK209">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34539,37 +34539,37 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.19</v>
+        <v>1.89</v>
       </c>
       <c r="O210">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P210">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="Q210">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="R210">
         <v>2.03</v>
       </c>
       <c r="S210">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T210">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U210">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V210">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W210">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X210">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y210">
         <v>1.28</v>
@@ -34578,10 +34578,10 @@
         <v>3.08</v>
       </c>
       <c r="AA210">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB210">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC210">
         <v>3.42</v>
@@ -34593,10 +34593,10 @@
         <v>1.04</v>
       </c>
       <c r="AF210">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG210">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK210">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -36169,19 +36169,19 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O220">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P220">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Q220">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R220">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="S220">
         <v>1.22</v>
@@ -36205,22 +36205,22 @@
         <v>1.1</v>
       </c>
       <c r="Z220">
-        <v>5.15</v>
+        <v>6</v>
       </c>
       <c r="AA220">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB220">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC220">
         <v>2.16</v>
       </c>
       <c r="AD220">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE220">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF220">
         <v>1.67</v>
@@ -36242,7 +36242,7 @@
         <v>1.1</v>
       </c>
       <c r="AK220">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="O221">
         <v>3.35</v>
       </c>
       <c r="P221">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q221">
         <v>2.88</v>
@@ -36347,7 +36347,7 @@
         <v>2.2</v>
       </c>
       <c r="S221">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T221">
         <v>3.2</v>
@@ -36359,7 +36359,7 @@
         <v>1.43</v>
       </c>
       <c r="W221">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X221">
         <v>1.02</v>
@@ -36371,13 +36371,13 @@
         <v>3.7</v>
       </c>
       <c r="AA221">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB221">
         <v>2</v>
       </c>
       <c r="AC221">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="AD221">
         <v>1.34</v>
@@ -36389,7 +36389,7 @@
         <v>1.61</v>
       </c>
       <c r="AG221">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK221">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,65 +36658,65 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="O223">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="P223">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q223">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="R223">
-        <v>2.31</v>
+        <v>1.96</v>
       </c>
       <c r="S223">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T223">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="U223">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="V223">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W223">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X223">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y223">
+        <v>1.4</v>
+      </c>
+      <c r="Z223">
+        <v>2.9</v>
+      </c>
+      <c r="AA223">
+        <v>2.25</v>
+      </c>
+      <c r="AB223">
+        <v>1.66</v>
+      </c>
+      <c r="AC223">
+        <v>4.33</v>
+      </c>
+      <c r="AD223">
         <v>1.22</v>
       </c>
-      <c r="Z223">
-        <v>3.76</v>
-      </c>
-      <c r="AA223">
+      <c r="AE223">
+        <v>1.01</v>
+      </c>
+      <c r="AF223">
+        <v>1.88</v>
+      </c>
+      <c r="AG223">
         <v>1.8</v>
       </c>
-      <c r="AB223">
-        <v>2.02</v>
-      </c>
-      <c r="AC223">
-        <v>3.02</v>
-      </c>
-      <c r="AD223">
-        <v>1.41</v>
-      </c>
-      <c r="AE223">
-        <v>1.11</v>
-      </c>
-      <c r="AF223">
-        <v>1.78</v>
-      </c>
-      <c r="AG223">
-        <v>1.95</v>
-      </c>
       <c r="AH223" t="inlineStr">
         <is>
           <t>[]</t>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AK223">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,64 +36821,64 @@
         </is>
       </c>
       <c r="N224">
+        <v>1.6</v>
+      </c>
+      <c r="O224">
+        <v>4.05</v>
+      </c>
+      <c r="P224">
+        <v>5.2</v>
+      </c>
+      <c r="Q224">
+        <v>2.15</v>
+      </c>
+      <c r="R224">
+        <v>2.31</v>
+      </c>
+      <c r="S224">
+        <v>1.35</v>
+      </c>
+      <c r="T224">
         <v>3.1</v>
       </c>
-      <c r="O224">
-        <v>3.1</v>
-      </c>
-      <c r="P224">
-        <v>2.3</v>
-      </c>
-      <c r="Q224">
-        <v>3.8</v>
-      </c>
-      <c r="R224">
-        <v>1.96</v>
-      </c>
-      <c r="S224">
-        <v>1.42</v>
-      </c>
-      <c r="T224">
-        <v>2.53</v>
-      </c>
       <c r="U224">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="V224">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W224">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X224">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y224">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z224">
-        <v>2.9</v>
+        <v>3.76</v>
       </c>
       <c r="AA224">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AB224">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="AC224">
-        <v>4.33</v>
+        <v>3.02</v>
       </c>
       <c r="AD224">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE224">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF224">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG224">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="AK224">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36996,7 +36996,7 @@
         <v>1.7</v>
       </c>
       <c r="R225">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="S225">
         <v>1.2</v>
@@ -37017,7 +37017,7 @@
         <v>1.03</v>
       </c>
       <c r="Y225">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z225">
         <v>5.5</v>
@@ -37038,7 +37038,7 @@
         <v>1.25</v>
       </c>
       <c r="AF225">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG225">
         <v>1.95</v>
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O235">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P235">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q235">
         <v>3.58</v>
@@ -38650,13 +38650,13 @@
         <v>1.16</v>
       </c>
       <c r="Z235">
-        <v>4.76</v>
+        <v>4.4</v>
       </c>
       <c r="AA235">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB235">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="AC235">
         <v>2.41</v>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK235">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38786,7 +38786,7 @@
         <v>3.9</v>
       </c>
       <c r="Q236">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="R236">
         <v>2.18</v>
@@ -38801,7 +38801,7 @@
         <v>2.73</v>
       </c>
       <c r="V236">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W236">
         <v>1.06</v>
@@ -38810,10 +38810,10 @@
         <v>1.01</v>
       </c>
       <c r="Y236">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z236">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="AA236">
         <v>1.94</v>
@@ -38828,7 +38828,7 @@
         <v>1.31</v>
       </c>
       <c r="AE236">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF236">
         <v>1.73</v>
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="O241">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="P241">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q241">
         <v>8.34</v>
@@ -39613,31 +39613,31 @@
         <v>3.15</v>
       </c>
       <c r="U241">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="V241">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W241">
         <v>1.08</v>
       </c>
       <c r="X241">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y241">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z241">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA241">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB241">
         <v>2.14</v>
       </c>
       <c r="AC241">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD241">
         <v>1.45</v>
@@ -39755,16 +39755,16 @@
         </is>
       </c>
       <c r="N242">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O242">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P242">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q242">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R242">
         <v>2.3</v>
@@ -39779,37 +39779,37 @@
         <v>2.47</v>
       </c>
       <c r="V242">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W242">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X242">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y242">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z242">
         <v>3.72</v>
       </c>
       <c r="AA242">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB242">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AC242">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD242">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE242">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF242">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG242">
         <v>2.21</v>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK242">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O246">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="P246">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Q246">
         <v>1.87</v>
@@ -40422,10 +40422,10 @@
         <v>2.45</v>
       </c>
       <c r="S246">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T246">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U246">
         <v>2.43</v>
@@ -40440,13 +40440,13 @@
         <v>1.02</v>
       </c>
       <c r="Y246">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z246">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA246">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB246">
         <v>2.15</v>
@@ -40461,7 +40461,7 @@
         <v>1.15</v>
       </c>
       <c r="AF246">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG246">
         <v>1.93</v>
@@ -43830,7 +43830,7 @@
         </is>
       </c>
       <c r="N267">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O267">
         <v>3.2</v>
@@ -43839,22 +43839,22 @@
         <v>2.92</v>
       </c>
       <c r="Q267">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="R267">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S267">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T267">
         <v>2.7</v>
       </c>
       <c r="U267">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V267">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W267">
         <v>1.05</v>
@@ -43863,16 +43863,16 @@
         <v>1.03</v>
       </c>
       <c r="Y267">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z267">
-        <v>3.43</v>
+        <v>3.14</v>
       </c>
       <c r="AA267">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB267">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC267">
         <v>3.3</v>
@@ -43881,7 +43881,7 @@
         <v>1.29</v>
       </c>
       <c r="AE267">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF267">
         <v>1.7</v>
@@ -43900,7 +43900,7 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK267">
         <v>1.53</v>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="O268">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P268">
-        <v>5.5</v>
+        <v>5.49</v>
       </c>
       <c r="Q268">
         <v>2.06</v>
@@ -44008,49 +44008,49 @@
         <v>2.17</v>
       </c>
       <c r="S268">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T268">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="U268">
         <v>2.38</v>
       </c>
       <c r="V268">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W268">
         <v>1.04</v>
       </c>
       <c r="X268">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y268">
+        <v>1.24</v>
+      </c>
+      <c r="Z268">
+        <v>3.34</v>
+      </c>
+      <c r="AA268">
+        <v>1.87</v>
+      </c>
+      <c r="AB268">
+        <v>1.83</v>
+      </c>
+      <c r="AC268">
+        <v>2.75</v>
+      </c>
+      <c r="AD268">
         <v>1.29</v>
-      </c>
-      <c r="Z268">
-        <v>3.6</v>
-      </c>
-      <c r="AA268">
-        <v>1.93</v>
-      </c>
-      <c r="AB268">
-        <v>1.84</v>
-      </c>
-      <c r="AC268">
-        <v>3.24</v>
-      </c>
-      <c r="AD268">
-        <v>1.27</v>
       </c>
       <c r="AE268">
         <v>1.06</v>
       </c>
       <c r="AF268">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG268">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK268">
         <v>2.36</v>
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O269">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P269">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -46275,25 +46275,25 @@
         </is>
       </c>
       <c r="N282">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O282">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P282">
         <v>4.2</v>
       </c>
       <c r="Q282">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="R282">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S282">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T282">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U282">
         <v>3.04</v>
@@ -46305,34 +46305,34 @@
         <v>1.02</v>
       </c>
       <c r="X282">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y282">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z282">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA282">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AB282">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AC282">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD282">
         <v>1.19</v>
       </c>
       <c r="AE282">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF282">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG282">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>1.25</v>
       </c>
       <c r="AK282">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="O283">
         <v>2.9</v>
       </c>
       <c r="P283">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q283">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R283">
         <v>1.95</v>
       </c>
       <c r="S283">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T283">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="U283">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="V283">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W283">
         <v>1.02</v>
       </c>
       <c r="X283">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y283">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z283">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AA283">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AB283">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AC283">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="AD283">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE283">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF283">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AG283">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK283">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46601,7 +46601,7 @@
         </is>
       </c>
       <c r="N284">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O284">
         <v>3.1</v>
@@ -46610,55 +46610,55 @@
         <v>1.95</v>
       </c>
       <c r="Q284">
-        <v>4.34</v>
+        <v>4.72</v>
       </c>
       <c r="R284">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S284">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T284">
-        <v>2.53</v>
+        <v>2.68</v>
       </c>
       <c r="U284">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="V284">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W284">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X284">
         <v>1.02</v>
       </c>
       <c r="Y284">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z284">
-        <v>2.81</v>
+        <v>3.09</v>
       </c>
       <c r="AA284">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AB284">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC284">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AD284">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE284">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF284">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG284">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK284">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O290">
         <v>3.1</v>
       </c>
       <c r="P290">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47618,10 +47618,10 @@
         <v>0</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC290">
         <v>0</v>
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O291">
         <v>2.95</v>
       </c>
       <c r="P291">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q291">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="R291">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="S291">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="T291">
-        <v>2.56</v>
+        <v>2.37</v>
       </c>
       <c r="U291">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="V291">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W291">
         <v>1.01</v>
       </c>
       <c r="X291">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y291">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z291">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AA291">
+        <v>2.55</v>
+      </c>
+      <c r="AB291">
+        <v>1.48</v>
+      </c>
+      <c r="AC291">
+        <v>5</v>
+      </c>
+      <c r="AD291">
+        <v>1.17</v>
+      </c>
+      <c r="AE291">
+        <v>1.05</v>
+      </c>
+      <c r="AF291">
         <v>2.1</v>
       </c>
-      <c r="AB291">
-        <v>1.64</v>
-      </c>
-      <c r="AC291">
-        <v>3.86</v>
-      </c>
-      <c r="AD291">
-        <v>1.18</v>
-      </c>
-      <c r="AE291">
-        <v>1.02</v>
-      </c>
-      <c r="AF291">
-        <v>1.86</v>
-      </c>
       <c r="AG291">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
+        <v>1.53</v>
+      </c>
+      <c r="AK291">
         <v>1.25</v>
-      </c>
-      <c r="AK291">
-        <v>1.22</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47914,55 +47914,55 @@
         <v>4.5</v>
       </c>
       <c r="Q292">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="R292">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="S292">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T292">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U292">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="V292">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W292">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X292">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y292">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z292">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="AA292">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AB292">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AC292">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD292">
         <v>1.2</v>
       </c>
       <c r="AE292">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF292">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AG292">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK292">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G307">
@@ -50359,55 +50359,55 @@
         <v>0</v>
       </c>
       <c r="Q307">
-        <v>2.24</v>
+        <v>2.43</v>
       </c>
       <c r="R307">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S307">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T307">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="U307">
-        <v>2.71</v>
+        <v>2.34</v>
       </c>
       <c r="V307">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W307">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X307">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y307">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z307">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA307">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AB307">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC307">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="AD307">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AE307">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF307">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="AG307">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK307">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G308">
@@ -50522,55 +50522,55 @@
         <v>0</v>
       </c>
       <c r="Q308">
-        <v>2.43</v>
+        <v>2.24</v>
       </c>
       <c r="R308">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S308">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T308">
-        <v>3.14</v>
+        <v>2.67</v>
       </c>
       <c r="U308">
-        <v>2.34</v>
+        <v>2.71</v>
       </c>
       <c r="V308">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W308">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X308">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y308">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z308">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA308">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB308">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AC308">
-        <v>2.43</v>
+        <v>3.25</v>
       </c>
       <c r="AD308">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE308">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF308">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AG308">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK308">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50866,13 +50866,13 @@
         <v>1.33</v>
       </c>
       <c r="W310">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X310">
         <v>1.03</v>
       </c>
       <c r="Y310">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z310">
         <v>3.05</v>
@@ -50884,19 +50884,19 @@
         <v>1.71</v>
       </c>
       <c r="AC310">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="AD310">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE310">
         <v>1.05</v>
       </c>
       <c r="AF310">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AG310">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -51989,10 +51989,10 @@
         <v>0</v>
       </c>
       <c r="Q317">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R317">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S317">
         <v>1.25</v>
@@ -52001,10 +52001,10 @@
         <v>3.6</v>
       </c>
       <c r="U317">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="V317">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W317">
         <v>1.11</v>
@@ -52022,16 +52022,16 @@
         <v>1.61</v>
       </c>
       <c r="AB317">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AC317">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AD317">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE317">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF317">
         <v>1.54</v>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK317">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52315,22 +52315,22 @@
         <v>0</v>
       </c>
       <c r="Q319">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R319">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S319">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T319">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U319">
         <v>2.56</v>
       </c>
       <c r="V319">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W319">
         <v>1.05</v>
@@ -52342,7 +52342,7 @@
         <v>1.2</v>
       </c>
       <c r="Z319">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="AA319">
         <v>1.77</v>
@@ -52354,13 +52354,13 @@
         <v>2.92</v>
       </c>
       <c r="AD319">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE319">
         <v>1.13</v>
       </c>
       <c r="AF319">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG319">
         <v>2.15</v>
@@ -52376,7 +52376,7 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK319">
         <v>1.58</v>
@@ -52475,7 +52475,7 @@
         <v>4.05</v>
       </c>
       <c r="P320">
-        <v>3.42</v>
+        <v>3.95</v>
       </c>
       <c r="Q320">
         <v>2.18</v>
@@ -52487,7 +52487,7 @@
         <v>1.22</v>
       </c>
       <c r="T320">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="U320">
         <v>2.2</v>
@@ -52517,7 +52517,7 @@
         <v>2.29</v>
       </c>
       <c r="AD320">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AE320">
         <v>1.18</v>
@@ -52526,7 +52526,7 @@
         <v>1.52</v>
       </c>
       <c r="AG320">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,7 +52539,7 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK320">
         <v>2.1</v>
@@ -52644,22 +52644,22 @@
         <v>2.4</v>
       </c>
       <c r="R321">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S321">
         <v>1.29</v>
       </c>
       <c r="T321">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U321">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V321">
         <v>1.48</v>
       </c>
       <c r="W321">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X321">
         <v>1</v>
@@ -52689,7 +52689,7 @@
         <v>1.58</v>
       </c>
       <c r="AG321">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52810,7 +52810,7 @@
         <v>2.21</v>
       </c>
       <c r="S322">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T322">
         <v>3.3</v>
@@ -52819,7 +52819,7 @@
         <v>2.33</v>
       </c>
       <c r="V322">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W322">
         <v>1.12</v>
@@ -52837,7 +52837,7 @@
         <v>1.65</v>
       </c>
       <c r="AB322">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC322">
         <v>2.59</v>
@@ -52868,7 +52868,7 @@
         <v>1.48</v>
       </c>
       <c r="AK322">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -54099,16 +54099,16 @@
         </is>
       </c>
       <c r="N330">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="O330">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P330">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q330">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="R330">
         <v>2.25</v>
@@ -54117,34 +54117,34 @@
         <v>1.3</v>
       </c>
       <c r="T330">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="U330">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="V330">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W330">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X330">
         <v>1.04</v>
       </c>
       <c r="Y330">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z330">
         <v>3.7</v>
       </c>
       <c r="AA330">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AB330">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC330">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD330">
         <v>1.32</v>
@@ -54153,10 +54153,10 @@
         <v>1.08</v>
       </c>
       <c r="AF330">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG330">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK330">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54262,7 +54262,7 @@
         </is>
       </c>
       <c r="N331">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O331">
         <v>3.35</v>
@@ -54277,13 +54277,13 @@
         <v>2.2</v>
       </c>
       <c r="S331">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T331">
         <v>2.91</v>
       </c>
       <c r="U331">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="V331">
         <v>1.41</v>
@@ -54313,7 +54313,7 @@
         <v>1.33</v>
       </c>
       <c r="AE331">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF331">
         <v>1.75</v>
@@ -54935,7 +54935,7 @@
         <v>2.88</v>
       </c>
       <c r="U335">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V335">
         <v>1.38</v>
@@ -54959,7 +54959,7 @@
         <v>1.78</v>
       </c>
       <c r="AC335">
-        <v>3</v>
+        <v>3.51</v>
       </c>
       <c r="AD335">
         <v>1.28</v>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,37 +55077,37 @@
         </is>
       </c>
       <c r="N336">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="O336">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="P336">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="Q336">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="R336">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S336">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T336">
         <v>3.8</v>
       </c>
       <c r="U336">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V336">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W336">
         <v>1.14</v>
       </c>
       <c r="X336">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y336">
         <v>1.15</v>
@@ -55116,25 +55116,25 @@
         <v>5.25</v>
       </c>
       <c r="AA336">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB336">
         <v>2.55</v>
       </c>
       <c r="AC336">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AD336">
         <v>1.62</v>
       </c>
       <c r="AE336">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF336">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG336">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55147,10 +55147,10 @@
         </is>
       </c>
       <c r="AJ336">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK336">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,37 +55240,37 @@
         </is>
       </c>
       <c r="N337">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="O337">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="P337">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="Q337">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="R337">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S337">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T337">
         <v>3.8</v>
       </c>
       <c r="U337">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V337">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W337">
         <v>1.14</v>
       </c>
       <c r="X337">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y337">
         <v>1.15</v>
@@ -55279,41 +55279,41 @@
         <v>5.25</v>
       </c>
       <c r="AA337">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB337">
         <v>2.55</v>
       </c>
       <c r="AC337">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AD337">
         <v>1.62</v>
       </c>
       <c r="AE337">
+        <v>1.26</v>
+      </c>
+      <c r="AF337">
+        <v>1.5</v>
+      </c>
+      <c r="AG337">
+        <v>2.4</v>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ337">
         <v>1.25</v>
       </c>
-      <c r="AF337">
-        <v>1.44</v>
-      </c>
-      <c r="AG337">
-        <v>2.5</v>
-      </c>
-      <c r="AH337" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI337" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ337">
-        <v>1.17</v>
-      </c>
       <c r="AK337">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -55738,22 +55738,22 @@
         <v>8.6</v>
       </c>
       <c r="Q340">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="R340">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="S340">
         <v>1.25</v>
       </c>
       <c r="T340">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U340">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V340">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W340">
         <v>1.13</v>
@@ -55768,16 +55768,16 @@
         <v>4.8</v>
       </c>
       <c r="AA340">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB340">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC340">
         <v>2.28</v>
       </c>
       <c r="AD340">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AE340">
         <v>1.19</v>
@@ -55928,7 +55928,7 @@
         <v>1.15</v>
       </c>
       <c r="Z341">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA341">
         <v>1.66</v>
@@ -55943,7 +55943,7 @@
         <v>1.56</v>
       </c>
       <c r="AE341">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AF341">
         <v>1.48</v>
@@ -55962,7 +55962,7 @@
         </is>
       </c>
       <c r="AJ341">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK341">
         <v>2.05</v>
@@ -56073,7 +56073,7 @@
         <v>1.3</v>
       </c>
       <c r="T342">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="U342">
         <v>2.63</v>
@@ -56091,7 +56091,7 @@
         <v>1.2</v>
       </c>
       <c r="Z342">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="AA342">
         <v>1.79</v>
@@ -56112,7 +56112,7 @@
         <v>1.61</v>
       </c>
       <c r="AG342">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AH342" t="inlineStr">
         <is>
@@ -56381,16 +56381,16 @@
         </is>
       </c>
       <c r="N344">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="O344">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P344">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q344">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R344">
         <v>2.1</v>
@@ -56429,7 +56429,7 @@
         <v>3.47</v>
       </c>
       <c r="AD344">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE344">
         <v>1.04</v>
@@ -56451,7 +56451,7 @@
         </is>
       </c>
       <c r="AJ344">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK344">
         <v>1.21</v>
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="O345">
         <v>3.27</v>
       </c>
       <c r="P345">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="Q345">
         <v>2.4</v>
@@ -56559,7 +56559,7 @@
         <v>2.3</v>
       </c>
       <c r="S345">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T345">
         <v>3.02</v>
@@ -56568,7 +56568,7 @@
         <v>2.44</v>
       </c>
       <c r="V345">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W345">
         <v>1.08</v>
@@ -56577,7 +56577,7 @@
         <v>1</v>
       </c>
       <c r="Y345">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z345">
         <v>3.95</v>
@@ -56601,7 +56601,7 @@
         <v>1.62</v>
       </c>
       <c r="AG345">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH345" t="inlineStr">
         <is>
@@ -56614,10 +56614,10 @@
         </is>
       </c>
       <c r="AJ345">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK345">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AL345">
         <v>0</v>
@@ -56707,13 +56707,13 @@
         </is>
       </c>
       <c r="N346">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="O346">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="P346">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q346">
         <v>3.74</v>
@@ -56722,10 +56722,10 @@
         <v>2.19</v>
       </c>
       <c r="S346">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T346">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U346">
         <v>2.67</v>
@@ -56755,7 +56755,7 @@
         <v>2.74</v>
       </c>
       <c r="AD346">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AE346">
         <v>1.09</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -5205,7 +5205,7 @@
         <v>3.55</v>
       </c>
       <c r="P30">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="Q30">
         <v>2.45</v>
@@ -5217,7 +5217,7 @@
         <v>1.33</v>
       </c>
       <c r="T30">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U30">
         <v>2.66</v>
@@ -5226,28 +5226,28 @@
         <v>1.39</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
         <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AA30">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AB30">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC30">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD30">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE30">
         <v>1.07</v>
@@ -5256,7 +5256,7 @@
         <v>1.71</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK30">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,40 +5362,40 @@
         </is>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O31">
         <v>3.3</v>
       </c>
       <c r="P31">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q31">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="R31">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S31">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T31">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="U31">
         <v>2.73</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z31">
         <v>3.24</v>
@@ -5404,13 +5404,13 @@
         <v>2</v>
       </c>
       <c r="AB31">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC31">
         <v>3.61</v>
       </c>
       <c r="AD31">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE31">
         <v>1.05</v>
@@ -5419,7 +5419,7 @@
         <v>1.79</v>
       </c>
       <c r="AG31">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O32">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P32">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -5540,43 +5540,43 @@
         <v>2.07</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T32">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="U32">
         <v>2.91</v>
       </c>
       <c r="V32">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z32">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA32">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB32">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC32">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD32">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
         <v>1.72</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q33">
-        <v>3.39</v>
+        <v>3.78</v>
       </c>
       <c r="R33">
         <v>2.1</v>
@@ -5706,34 +5706,34 @@
         <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.93</v>
+        <v>2.62</v>
       </c>
       <c r="U33">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z33">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB33">
         <v>1.79</v>
       </c>
       <c r="AC33">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD33">
         <v>1.29</v>
@@ -5742,10 +5742,10 @@
         <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="O50">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q50">
+        <v>2.27</v>
+      </c>
+      <c r="R50">
+        <v>2.19</v>
+      </c>
+      <c r="S50">
+        <v>1.3</v>
+      </c>
+      <c r="T50">
+        <v>2.94</v>
+      </c>
+      <c r="U50">
+        <v>2.65</v>
+      </c>
+      <c r="V50">
+        <v>1.44</v>
+      </c>
+      <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
+        <v>1.01</v>
+      </c>
+      <c r="Y50">
+        <v>1.22</v>
+      </c>
+      <c r="Z50">
+        <v>3.54</v>
+      </c>
+      <c r="AA50">
+        <v>1.9</v>
+      </c>
+      <c r="AB50">
+        <v>1.9</v>
+      </c>
+      <c r="AC50">
         <v>2.89</v>
       </c>
-      <c r="R50">
-        <v>2.03</v>
-      </c>
-      <c r="S50">
-        <v>1.4</v>
-      </c>
-      <c r="T50">
-        <v>2.82</v>
-      </c>
-      <c r="U50">
-        <v>2.99</v>
-      </c>
-      <c r="V50">
-        <v>1.35</v>
-      </c>
-      <c r="W50">
-        <v>1.02</v>
-      </c>
-      <c r="X50">
-        <v>1.04</v>
-      </c>
-      <c r="Y50">
-        <v>1.35</v>
-      </c>
-      <c r="Z50">
-        <v>3.25</v>
-      </c>
-      <c r="AA50">
-        <v>2.1</v>
-      </c>
-      <c r="AB50">
-        <v>1.7</v>
-      </c>
-      <c r="AC50">
-        <v>3.75</v>
-      </c>
       <c r="AD50">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE50">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="O51">
+        <v>3.3</v>
+      </c>
+      <c r="P51">
+        <v>3.1</v>
+      </c>
+      <c r="Q51">
+        <v>2.89</v>
+      </c>
+      <c r="R51">
+        <v>2.03</v>
+      </c>
+      <c r="S51">
+        <v>1.4</v>
+      </c>
+      <c r="T51">
+        <v>2.82</v>
+      </c>
+      <c r="U51">
+        <v>2.99</v>
+      </c>
+      <c r="V51">
+        <v>1.35</v>
+      </c>
+      <c r="W51">
+        <v>1.02</v>
+      </c>
+      <c r="X51">
+        <v>1.04</v>
+      </c>
+      <c r="Y51">
+        <v>1.35</v>
+      </c>
+      <c r="Z51">
+        <v>3.25</v>
+      </c>
+      <c r="AA51">
+        <v>2.1</v>
+      </c>
+      <c r="AB51">
+        <v>1.7</v>
+      </c>
+      <c r="AC51">
         <v>3.75</v>
       </c>
-      <c r="P51">
-        <v>4.5</v>
-      </c>
-      <c r="Q51">
-        <v>2.27</v>
-      </c>
-      <c r="R51">
-        <v>2.19</v>
-      </c>
-      <c r="S51">
-        <v>1.3</v>
-      </c>
-      <c r="T51">
-        <v>2.94</v>
-      </c>
-      <c r="U51">
-        <v>2.65</v>
-      </c>
-      <c r="V51">
-        <v>1.44</v>
-      </c>
-      <c r="W51">
-        <v>1.07</v>
-      </c>
-      <c r="X51">
-        <v>1.01</v>
-      </c>
-      <c r="Y51">
-        <v>1.22</v>
-      </c>
-      <c r="Z51">
-        <v>3.54</v>
-      </c>
-      <c r="AA51">
-        <v>1.9</v>
-      </c>
-      <c r="AB51">
-        <v>1.9</v>
-      </c>
-      <c r="AC51">
-        <v>2.89</v>
-      </c>
       <c r="AD51">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK51">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,31 +19869,31 @@
         </is>
       </c>
       <c r="N120">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="O120">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P120">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q120">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="R120">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="S120">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T120">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="U120">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="V120">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W120">
         <v>1.05</v>
@@ -19902,28 +19902,28 @@
         <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z120">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA120">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AB120">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC120">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="AD120">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE120">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF120">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG120">
         <v>2</v>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK120">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,55 +20032,55 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O121">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P121">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q121">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="R121">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S121">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T121">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="U121">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="V121">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W121">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
         <v>1.27</v>
       </c>
       <c r="Z121">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AA121">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB121">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AC121">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD121">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE121">
         <v>1.06</v>
@@ -20089,7 +20089,7 @@
         <v>1.71</v>
       </c>
       <c r="AG121">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK121">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="O122">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P122">
-        <v>3.35</v>
+        <v>2.53</v>
       </c>
       <c r="Q122">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="R122">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="S122">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T122">
-        <v>2.85</v>
+        <v>2.61</v>
       </c>
       <c r="U122">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="V122">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W122">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z122">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA122">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB122">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC122">
-        <v>3.57</v>
+        <v>3.51</v>
       </c>
       <c r="AD122">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE122">
         <v>1.06</v>
       </c>
       <c r="AF122">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG122">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O123">
         <v>3.45</v>
       </c>
       <c r="P123">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q123">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R123">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S123">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T123">
         <v>2.85</v>
       </c>
       <c r="U123">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="V123">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W123">
         <v>1.04</v>
       </c>
       <c r="X123">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
+        <v>1.31</v>
+      </c>
+      <c r="Z123">
+        <v>3.08</v>
+      </c>
+      <c r="AA123">
+        <v>1.95</v>
+      </c>
+      <c r="AB123">
+        <v>1.75</v>
+      </c>
+      <c r="AC123">
+        <v>3.57</v>
+      </c>
+      <c r="AD123">
         <v>1.27</v>
-      </c>
-      <c r="Z123">
-        <v>3.58</v>
-      </c>
-      <c r="AA123">
-        <v>1.9</v>
-      </c>
-      <c r="AB123">
-        <v>1.88</v>
-      </c>
-      <c r="AC123">
-        <v>3.3</v>
-      </c>
-      <c r="AD123">
-        <v>1.3</v>
       </c>
       <c r="AE123">
         <v>1.06</v>
       </c>
       <c r="AF123">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG123">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK123">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="O124">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P124">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q124">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="R124">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="S124">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T124">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="U124">
-        <v>3.17</v>
+        <v>2.88</v>
       </c>
       <c r="V124">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W124">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X124">
         <v>1.03</v>
       </c>
       <c r="Y124">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z124">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="AA124">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB124">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AC124">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="AD124">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE124">
         <v>1.07</v>
       </c>
       <c r="AF124">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG124">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK124">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.83</v>
+        <v>3.6</v>
       </c>
       <c r="O125">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P125">
-        <v>4.1</v>
+        <v>1.89</v>
       </c>
       <c r="Q125">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="R125">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S125">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T125">
-        <v>2.63</v>
+        <v>2.89</v>
       </c>
       <c r="U125">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V125">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W125">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z125">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA125">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB125">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC125">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD125">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE125">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF125">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG125">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK125">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,65 +20847,65 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="O126">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="P126">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="Q126">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R126">
+        <v>2.11</v>
+      </c>
+      <c r="S126">
+        <v>1.44</v>
+      </c>
+      <c r="T126">
+        <v>2.54</v>
+      </c>
+      <c r="U126">
+        <v>3.17</v>
+      </c>
+      <c r="V126">
+        <v>1.33</v>
+      </c>
+      <c r="W126">
+        <v>1.04</v>
+      </c>
+      <c r="X126">
+        <v>1.03</v>
+      </c>
+      <c r="Y126">
+        <v>1.32</v>
+      </c>
+      <c r="Z126">
+        <v>2.76</v>
+      </c>
+      <c r="AA126">
         <v>2.15</v>
       </c>
-      <c r="S126">
-        <v>1.39</v>
-      </c>
-      <c r="T126">
-        <v>2.89</v>
-      </c>
-      <c r="U126">
-        <v>2.85</v>
-      </c>
-      <c r="V126">
-        <v>1.36</v>
-      </c>
-      <c r="W126">
-        <v>1.03</v>
-      </c>
-      <c r="X126">
-        <v>1.01</v>
-      </c>
-      <c r="Y126">
-        <v>1.27</v>
-      </c>
-      <c r="Z126">
-        <v>3.14</v>
-      </c>
-      <c r="AA126">
-        <v>1.93</v>
-      </c>
       <c r="AB126">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC126">
-        <v>3.42</v>
+        <v>3.83</v>
       </c>
       <c r="AD126">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE126">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF126">
+        <v>1.81</v>
+      </c>
+      <c r="AG126">
         <v>1.87</v>
       </c>
-      <c r="AG126">
-        <v>1.91</v>
-      </c>
       <c r="AH126" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK126">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,61 +21010,61 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="O127">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P127">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="Q127">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R127">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="S127">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T127">
-        <v>2.61</v>
+        <v>2.85</v>
       </c>
       <c r="U127">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="V127">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W127">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X127">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
+        <v>1.29</v>
+      </c>
+      <c r="Z127">
+        <v>3.4</v>
+      </c>
+      <c r="AA127">
+        <v>1.85</v>
+      </c>
+      <c r="AB127">
+        <v>1.9</v>
+      </c>
+      <c r="AC127">
+        <v>3.14</v>
+      </c>
+      <c r="AD127">
         <v>1.3</v>
       </c>
-      <c r="Z127">
-        <v>3.14</v>
-      </c>
-      <c r="AA127">
-        <v>2</v>
-      </c>
-      <c r="AB127">
-        <v>1.8</v>
-      </c>
-      <c r="AC127">
-        <v>3.51</v>
-      </c>
-      <c r="AD127">
-        <v>1.24</v>
-      </c>
       <c r="AE127">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF127">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG127">
         <v>2</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK127">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="O140">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P140">
-        <v>2.75</v>
+        <v>4.15</v>
       </c>
       <c r="Q140">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="R140">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S140">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T140">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U140">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="V140">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W140">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X140">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y140">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z140">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AA140">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB140">
         <v>2</v>
       </c>
       <c r="AC140">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="AD140">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE140">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF140">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AG140">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK140">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="O141">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P141">
-        <v>4.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q141">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="R141">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S141">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T141">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U141">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="V141">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W141">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X141">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y141">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z141">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AA141">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB141">
         <v>2</v>
       </c>
       <c r="AC141">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD141">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE141">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF141">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AG141">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK141">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O144">
-        <v>3.62</v>
+        <v>3.24</v>
       </c>
       <c r="P144">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q144">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R144">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S144">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T144">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="U144">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="V144">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W144">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X144">
         <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z144">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA144">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB144">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC144">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="AD144">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE144">
         <v>1.1</v>
       </c>
       <c r="AF144">
+        <v>1.75</v>
+      </c>
+      <c r="AG144">
+        <v>1.93</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
+        <v>1.25</v>
+      </c>
+      <c r="AK144">
         <v>1.62</v>
-      </c>
-      <c r="AG144">
-        <v>2.15</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.26</v>
-      </c>
-      <c r="AK144">
-        <v>1.63</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O145">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P145">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="Q145">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="R145">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="S145">
+        <v>1.45</v>
+      </c>
+      <c r="T145">
+        <v>2.5</v>
+      </c>
+      <c r="U145">
+        <v>2.86</v>
+      </c>
+      <c r="V145">
         <v>1.33</v>
       </c>
-      <c r="T145">
-        <v>2.84</v>
-      </c>
-      <c r="U145">
-        <v>2.67</v>
-      </c>
-      <c r="V145">
-        <v>1.44</v>
-      </c>
       <c r="W145">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y145">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z145">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA145">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="AB145">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC145">
-        <v>2.99</v>
+        <v>3.62</v>
       </c>
       <c r="AD145">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE145">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF145">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AG145">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK145">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,80 +24107,80 @@
         </is>
       </c>
       <c r="N146">
+        <v>2.15</v>
+      </c>
+      <c r="O146">
+        <v>3.45</v>
+      </c>
+      <c r="P146">
+        <v>2.98</v>
+      </c>
+      <c r="Q146">
+        <v>2.55</v>
+      </c>
+      <c r="R146">
         <v>2.3</v>
       </c>
-      <c r="O146">
-        <v>3.24</v>
-      </c>
-      <c r="P146">
-        <v>3</v>
-      </c>
-      <c r="Q146">
-        <v>2.78</v>
-      </c>
-      <c r="R146">
-        <v>2.19</v>
-      </c>
       <c r="S146">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T146">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="U146">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="V146">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W146">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X146">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
+        <v>1.25</v>
+      </c>
+      <c r="Z146">
+        <v>3.4</v>
+      </c>
+      <c r="AA146">
+        <v>1.78</v>
+      </c>
+      <c r="AB146">
+        <v>2</v>
+      </c>
+      <c r="AC146">
+        <v>2.99</v>
+      </c>
+      <c r="AD146">
+        <v>1.38</v>
+      </c>
+      <c r="AE146">
+        <v>1.11</v>
+      </c>
+      <c r="AF146">
+        <v>1.65</v>
+      </c>
+      <c r="AG146">
+        <v>2.2</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ146">
         <v>1.3</v>
       </c>
-      <c r="Z146">
-        <v>3.08</v>
-      </c>
-      <c r="AA146">
-        <v>2</v>
-      </c>
-      <c r="AB146">
-        <v>1.78</v>
-      </c>
-      <c r="AC146">
-        <v>3.3</v>
-      </c>
-      <c r="AD146">
-        <v>1.3</v>
-      </c>
-      <c r="AE146">
-        <v>1.1</v>
-      </c>
-      <c r="AF146">
-        <v>1.75</v>
-      </c>
-      <c r="AG146">
-        <v>1.93</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>1.25</v>
-      </c>
       <c r="AK146">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O147">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P147">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="Q147">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="R147">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="S147">
+        <v>1.32</v>
+      </c>
+      <c r="T147">
+        <v>2.87</v>
+      </c>
+      <c r="U147">
+        <v>2.64</v>
+      </c>
+      <c r="V147">
         <v>1.45</v>
       </c>
-      <c r="T147">
-        <v>2.5</v>
-      </c>
-      <c r="U147">
-        <v>2.86</v>
-      </c>
-      <c r="V147">
-        <v>1.33</v>
-      </c>
       <c r="W147">
+        <v>1.06</v>
+      </c>
+      <c r="X147">
         <v>1.02</v>
       </c>
-      <c r="X147">
-        <v>1.05</v>
-      </c>
       <c r="Y147">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z147">
-        <v>3.12</v>
+        <v>4.1</v>
       </c>
       <c r="AA147">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AB147">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC147">
-        <v>3.62</v>
+        <v>2.85</v>
       </c>
       <c r="AD147">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AE147">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF147">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AG147">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK147">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -26229,61 +26229,61 @@
         <v>2.25</v>
       </c>
       <c r="O159">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="P159">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q159">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="R159">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S159">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T159">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="U159">
         <v>2.21</v>
       </c>
       <c r="V159">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W159">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X159">
         <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z159">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA159">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB159">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC159">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD159">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE159">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF159">
         <v>1.42</v>
       </c>
       <c r="AG159">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK159">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -37147,28 +37147,28 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="O226">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="P226">
-        <v>6.65</v>
+        <v>6.03</v>
       </c>
       <c r="Q226">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R226">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="S226">
         <v>1.17</v>
       </c>
       <c r="T226">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U226">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="V226">
         <v>1.76</v>
@@ -37180,31 +37180,31 @@
         <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z226">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="AA226">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AB226">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AC226">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AD226">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AE226">
         <v>1.3</v>
       </c>
       <c r="AF226">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG226">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK226">
         <v>2.98</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>3.47</v>
+        <v>2.4</v>
       </c>
       <c r="O284">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P284">
-        <v>1.9</v>
+        <v>2.56</v>
       </c>
       <c r="Q284">
-        <v>4.05</v>
+        <v>3.04</v>
       </c>
       <c r="R284">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S284">
+        <v>1.4</v>
+      </c>
+      <c r="T284">
+        <v>2.72</v>
+      </c>
+      <c r="U284">
+        <v>2.96</v>
+      </c>
+      <c r="V284">
+        <v>1.32</v>
+      </c>
+      <c r="W284">
+        <v>1.02</v>
+      </c>
+      <c r="X284">
+        <v>1</v>
+      </c>
+      <c r="Y284">
+        <v>1.28</v>
+      </c>
+      <c r="Z284">
+        <v>3.25</v>
+      </c>
+      <c r="AA284">
+        <v>2.05</v>
+      </c>
+      <c r="AB284">
+        <v>1.73</v>
+      </c>
+      <c r="AC284">
+        <v>3.8</v>
+      </c>
+      <c r="AD284">
         <v>1.22</v>
       </c>
-      <c r="T284">
-        <v>3.18</v>
-      </c>
-      <c r="U284">
-        <v>2.44</v>
-      </c>
-      <c r="V284">
-        <v>1.47</v>
-      </c>
-      <c r="W284">
-        <v>1.07</v>
-      </c>
-      <c r="X284">
-        <v>1.02</v>
-      </c>
-      <c r="Y284">
-        <v>1.16</v>
-      </c>
-      <c r="Z284">
-        <v>4.15</v>
-      </c>
-      <c r="AA284">
-        <v>1.7</v>
-      </c>
-      <c r="AB284">
-        <v>2.1</v>
-      </c>
-      <c r="AC284">
-        <v>2.69</v>
-      </c>
-      <c r="AD284">
-        <v>1.39</v>
-      </c>
       <c r="AE284">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF284">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG284">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.79</v>
+        <v>1.3</v>
       </c>
       <c r="AK284">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,80 +46764,80 @@
         </is>
       </c>
       <c r="N285">
-        <v>2.4</v>
+        <v>3.47</v>
       </c>
       <c r="O285">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P285">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="Q285">
-        <v>3.04</v>
+        <v>4.05</v>
       </c>
       <c r="R285">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S285">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="T285">
-        <v>2.72</v>
+        <v>3.18</v>
       </c>
       <c r="U285">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="V285">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="W285">
+        <v>1.07</v>
+      </c>
+      <c r="X285">
         <v>1.02</v>
       </c>
-      <c r="X285">
-        <v>1</v>
-      </c>
       <c r="Y285">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z285">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="AA285">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AB285">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AC285">
-        <v>3.8</v>
+        <v>2.69</v>
       </c>
       <c r="AD285">
+        <v>1.39</v>
+      </c>
+      <c r="AE285">
+        <v>1.14</v>
+      </c>
+      <c r="AF285">
+        <v>1.57</v>
+      </c>
+      <c r="AG285">
+        <v>2.23</v>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ285">
+        <v>1.79</v>
+      </c>
+      <c r="AK285">
         <v>1.22</v>
-      </c>
-      <c r="AE285">
-        <v>1.04</v>
-      </c>
-      <c r="AF285">
-        <v>1.62</v>
-      </c>
-      <c r="AG285">
-        <v>2</v>
-      </c>
-      <c r="AH285" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI285" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ285">
-        <v>1.3</v>
-      </c>
-      <c r="AK285">
-        <v>1.5</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="O288">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P288">
         <v>2.2</v>
       </c>
       <c r="Q288">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R288">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T288">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U288">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V288">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W288">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X288">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA288">
+        <v>2.55</v>
+      </c>
+      <c r="AB288">
+        <v>1.48</v>
+      </c>
+      <c r="AC288">
+        <v>5</v>
+      </c>
+      <c r="AD288">
+        <v>1.17</v>
+      </c>
+      <c r="AE288">
+        <v>1.05</v>
+      </c>
+      <c r="AF288">
         <v>2.1</v>
       </c>
-      <c r="AB288">
-        <v>1.7</v>
-      </c>
-      <c r="AC288">
-        <v>0</v>
-      </c>
-      <c r="AD288">
-        <v>0</v>
-      </c>
-      <c r="AE288">
-        <v>0</v>
-      </c>
-      <c r="AF288">
-        <v>0</v>
-      </c>
       <c r="AG288">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK288">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,61 +47416,61 @@
         </is>
       </c>
       <c r="N289">
-        <v>3.25</v>
+        <v>1.71</v>
       </c>
       <c r="O289">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P289">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q289">
-        <v>3.8</v>
+        <v>2.34</v>
       </c>
       <c r="R289">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="S289">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="T289">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="U289">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="V289">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W289">
         <v>1.01</v>
       </c>
       <c r="X289">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y289">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z289">
-        <v>2.43</v>
+        <v>2.74</v>
       </c>
       <c r="AA289">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="AB289">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AC289">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AD289">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE289">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF289">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AG289">
         <v>1.67</v>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="AK289">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,64 +47579,64 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="O290">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P290">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q290">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="R290">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S290">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T290">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U290">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V290">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W290">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X290">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y290">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z290">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA290">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB290">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC290">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD290">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE290">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF290">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG290">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK290">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -48068,7 +48068,7 @@
         </is>
       </c>
       <c r="N293">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="O293">
         <v>4.3</v>
@@ -48077,22 +48077,22 @@
         <v>1.7</v>
       </c>
       <c r="Q293">
-        <v>3.7</v>
+        <v>4.54</v>
       </c>
       <c r="R293">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="S293">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T293">
         <v>4.05</v>
       </c>
       <c r="U293">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="V293">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W293">
         <v>1.16</v>
@@ -48104,25 +48104,25 @@
         <v>1.13</v>
       </c>
       <c r="Z293">
-        <v>6.18</v>
+        <v>6.2</v>
       </c>
       <c r="AA293">
         <v>1.44</v>
       </c>
       <c r="AB293">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AC293">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AD293">
         <v>1.78</v>
       </c>
       <c r="AE293">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AF293">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG293">
         <v>2.7</v>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>2.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK293">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,64 +49698,64 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="O303">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P303">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q303">
-        <v>2.27</v>
+        <v>2.52</v>
       </c>
       <c r="R303">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S303">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="T303">
+        <v>2.22</v>
+      </c>
+      <c r="U303">
+        <v>3.98</v>
+      </c>
+      <c r="V303">
+        <v>1.22</v>
+      </c>
+      <c r="W303">
+        <v>1.03</v>
+      </c>
+      <c r="X303">
+        <v>1.06</v>
+      </c>
+      <c r="Y303">
+        <v>1.64</v>
+      </c>
+      <c r="Z303">
+        <v>2.18</v>
+      </c>
+      <c r="AA303">
+        <v>2.91</v>
+      </c>
+      <c r="AB303">
+        <v>1.44</v>
+      </c>
+      <c r="AC303">
+        <v>5.95</v>
+      </c>
+      <c r="AD303">
+        <v>1.07</v>
+      </c>
+      <c r="AE303">
+        <v>1.02</v>
+      </c>
+      <c r="AF303">
         <v>2.5</v>
       </c>
-      <c r="U303">
-        <v>3.04</v>
-      </c>
-      <c r="V303">
-        <v>1.3</v>
-      </c>
-      <c r="W303">
-        <v>1.04</v>
-      </c>
-      <c r="X303">
-        <v>1.04</v>
-      </c>
-      <c r="Y303">
-        <v>1.33</v>
-      </c>
-      <c r="Z303">
-        <v>3</v>
-      </c>
-      <c r="AA303">
-        <v>2.15</v>
-      </c>
-      <c r="AB303">
-        <v>1.66</v>
-      </c>
-      <c r="AC303">
-        <v>3.9</v>
-      </c>
-      <c r="AD303">
-        <v>1.22</v>
-      </c>
-      <c r="AE303">
-        <v>1.05</v>
-      </c>
-      <c r="AF303">
-        <v>1.97</v>
-      </c>
       <c r="AG303">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49771,7 +49771,7 @@
         <v>1.3</v>
       </c>
       <c r="AK303">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,64 +49861,64 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="O304">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P304">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q304">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="R304">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S304">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="T304">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="U304">
-        <v>3.98</v>
+        <v>3.42</v>
       </c>
       <c r="V304">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W304">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X304">
         <v>1.06</v>
       </c>
       <c r="Y304">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="Z304">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="AA304">
-        <v>2.91</v>
+        <v>2.31</v>
       </c>
       <c r="AB304">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC304">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="AD304">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AE304">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF304">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG304">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK304">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,64 +50024,64 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.45</v>
+        <v>1.54</v>
       </c>
       <c r="O305">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="P305">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="Q305">
-        <v>3.3</v>
+        <v>2.11</v>
       </c>
       <c r="R305">
-        <v>1.86</v>
+        <v>2.13</v>
       </c>
       <c r="S305">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="T305">
-        <v>2.27</v>
+        <v>2.71</v>
       </c>
       <c r="U305">
-        <v>3.42</v>
+        <v>2.67</v>
       </c>
       <c r="V305">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="W305">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X305">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y305">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="Z305">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA305">
-        <v>2.31</v>
+        <v>1.84</v>
       </c>
       <c r="AB305">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AC305">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="AD305">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AE305">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AF305">
         <v>2</v>
       </c>
       <c r="AG305">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK305">
-        <v>1.47</v>
+        <v>2.38</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="O306">
+        <v>3.4</v>
+      </c>
+      <c r="P306">
+        <v>3.45</v>
+      </c>
+      <c r="Q306">
+        <v>2.43</v>
+      </c>
+      <c r="R306">
+        <v>2.08</v>
+      </c>
+      <c r="S306">
+        <v>1.35</v>
+      </c>
+      <c r="T306">
+        <v>2.77</v>
+      </c>
+      <c r="U306">
+        <v>2.6</v>
+      </c>
+      <c r="V306">
+        <v>1.43</v>
+      </c>
+      <c r="W306">
+        <v>1.06</v>
+      </c>
+      <c r="X306">
+        <v>1.02</v>
+      </c>
+      <c r="Y306">
+        <v>1.25</v>
+      </c>
+      <c r="Z306">
         <v>3.7</v>
       </c>
-      <c r="P306">
-        <v>5</v>
-      </c>
-      <c r="Q306">
-        <v>2.11</v>
-      </c>
-      <c r="R306">
-        <v>2.13</v>
-      </c>
-      <c r="S306">
-        <v>1.36</v>
-      </c>
-      <c r="T306">
-        <v>2.71</v>
-      </c>
-      <c r="U306">
-        <v>2.67</v>
-      </c>
-      <c r="V306">
-        <v>1.4</v>
-      </c>
-      <c r="W306">
-        <v>1.07</v>
-      </c>
-      <c r="X306">
-        <v>1.03</v>
-      </c>
-      <c r="Y306">
-        <v>1.24</v>
-      </c>
-      <c r="Z306">
-        <v>3.6</v>
-      </c>
       <c r="AA306">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB306">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC306">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="AD306">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE306">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF306">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG306">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK306">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,80 +50350,80 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="O307">
         <v>3.4</v>
       </c>
       <c r="P307">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q307">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="R307">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S307">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T307">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="U307">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="V307">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="W307">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X307">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y307">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z307">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="AA307">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AB307">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AC307">
-        <v>2.83</v>
+        <v>3.9</v>
       </c>
       <c r="AD307">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE307">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF307">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AG307">
+        <v>1.72</v>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ307">
+        <v>1.3</v>
+      </c>
+      <c r="AK307">
         <v>2.05</v>
-      </c>
-      <c r="AH307" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI307" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ307">
-        <v>1.23</v>
-      </c>
-      <c r="AK307">
-        <v>1.78</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G334">
@@ -54751,64 +54751,64 @@
         </is>
       </c>
       <c r="N334">
+        <v>1.8</v>
+      </c>
+      <c r="O334">
+        <v>4.61</v>
+      </c>
+      <c r="P334">
+        <v>3.75</v>
+      </c>
+      <c r="Q334">
+        <v>2.25</v>
+      </c>
+      <c r="R334">
+        <v>2.4</v>
+      </c>
+      <c r="S334">
+        <v>1.22</v>
+      </c>
+      <c r="T334">
+        <v>4.1</v>
+      </c>
+      <c r="U334">
+        <v>2.05</v>
+      </c>
+      <c r="V334">
         <v>1.7</v>
       </c>
-      <c r="O334">
-        <v>4</v>
-      </c>
-      <c r="P334">
-        <v>4.4</v>
-      </c>
-      <c r="Q334">
-        <v>2.17</v>
-      </c>
-      <c r="R334">
-        <v>2.63</v>
-      </c>
-      <c r="S334">
+      <c r="W334">
         <v>1.2</v>
       </c>
-      <c r="T334">
-        <v>3.28</v>
-      </c>
-      <c r="U334">
-        <v>2.12</v>
-      </c>
-      <c r="V334">
-        <v>1.65</v>
-      </c>
-      <c r="W334">
-        <v>1.13</v>
-      </c>
       <c r="X334">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y334">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z334">
-        <v>5.47</v>
+        <v>5.35</v>
       </c>
       <c r="AA334">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AB334">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="AC334">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD334">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AE334">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF334">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG334">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AH334" t="inlineStr">
         <is>
@@ -54821,10 +54821,10 @@
         </is>
       </c>
       <c r="AJ334">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK334">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AL334">
         <v>0</v>
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G335">
@@ -54914,65 +54914,65 @@
         </is>
       </c>
       <c r="N335">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O335">
-        <v>4.61</v>
+        <v>4</v>
       </c>
       <c r="P335">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q335">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="R335">
+        <v>2.63</v>
+      </c>
+      <c r="S335">
+        <v>1.2</v>
+      </c>
+      <c r="T335">
+        <v>3.28</v>
+      </c>
+      <c r="U335">
+        <v>2.12</v>
+      </c>
+      <c r="V335">
+        <v>1.65</v>
+      </c>
+      <c r="W335">
+        <v>1.13</v>
+      </c>
+      <c r="X335">
+        <v>1.01</v>
+      </c>
+      <c r="Y335">
+        <v>1.15</v>
+      </c>
+      <c r="Z335">
+        <v>5.47</v>
+      </c>
+      <c r="AA335">
+        <v>1.51</v>
+      </c>
+      <c r="AB335">
+        <v>2.55</v>
+      </c>
+      <c r="AC335">
+        <v>2.13</v>
+      </c>
+      <c r="AD335">
+        <v>1.61</v>
+      </c>
+      <c r="AE335">
+        <v>1.26</v>
+      </c>
+      <c r="AF335">
+        <v>1.47</v>
+      </c>
+      <c r="AG335">
         <v>2.4</v>
       </c>
-      <c r="S335">
-        <v>1.22</v>
-      </c>
-      <c r="T335">
-        <v>4.1</v>
-      </c>
-      <c r="U335">
-        <v>2.05</v>
-      </c>
-      <c r="V335">
-        <v>1.7</v>
-      </c>
-      <c r="W335">
-        <v>1.2</v>
-      </c>
-      <c r="X335">
-        <v>0</v>
-      </c>
-      <c r="Y335">
-        <v>1.11</v>
-      </c>
-      <c r="Z335">
-        <v>5.35</v>
-      </c>
-      <c r="AA335">
-        <v>1.4</v>
-      </c>
-      <c r="AB335">
-        <v>2.61</v>
-      </c>
-      <c r="AC335">
-        <v>2.1</v>
-      </c>
-      <c r="AD335">
-        <v>1.69</v>
-      </c>
-      <c r="AE335">
-        <v>1.27</v>
-      </c>
-      <c r="AF335">
-        <v>1.44</v>
-      </c>
-      <c r="AG335">
-        <v>2.7</v>
-      </c>
       <c r="AH335" t="inlineStr">
         <is>
           <t>[]</t>
@@ -54984,10 +54984,10 @@
         </is>
       </c>
       <c r="AJ335">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK335">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="AL335">
         <v>0</v>

--- a/jogos_2026-08-29.xlsx
+++ b/jogos_2026-08-29.xlsx
@@ -961,61 +961,61 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O4">
+        <v>3.4</v>
+      </c>
+      <c r="P4">
+        <v>2.22</v>
+      </c>
+      <c r="Q4">
+        <v>2.8</v>
+      </c>
+      <c r="R4">
+        <v>2.38</v>
+      </c>
+      <c r="S4">
+        <v>1.3</v>
+      </c>
+      <c r="T4">
         <v>3.3</v>
       </c>
-      <c r="P4">
-        <v>2.37</v>
-      </c>
-      <c r="Q4">
-        <v>3.14</v>
-      </c>
-      <c r="R4">
-        <v>2.17</v>
-      </c>
-      <c r="S4">
-        <v>1.29</v>
-      </c>
-      <c r="T4">
-        <v>3.22</v>
-      </c>
       <c r="U4">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V4">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA4">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC4">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AD4">
         <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG4">
         <v>2.32</v>
@@ -1034,7 +1034,7 @@
         <v>1.34</v>
       </c>
       <c r="AK4">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -5851,28 +5851,28 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S34">
         <v>1.39</v>
       </c>
       <c r="T34">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="U34">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="V34">
         <v>1.39</v>
@@ -5881,34 +5881,34 @@
         <v>1.04</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA34">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AC34">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG34">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O35">
         <v>3.8</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="Q35">
         <v>2.38</v>
       </c>
       <c r="R35">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="S35">
         <v>1.14</v>
@@ -6035,10 +6035,10 @@
         <v>4.8</v>
       </c>
       <c r="U35">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="V35">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="W35">
         <v>1.2</v>
@@ -6050,25 +6050,25 @@
         <v>1.06</v>
       </c>
       <c r="Z35">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="AA35">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB35">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AC35">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AD35">
         <v>1.9</v>
       </c>
       <c r="AE35">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AF35">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AG35">
         <v>3</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="Q42">
-        <v>2.98</v>
+        <v>2.48</v>
       </c>
       <c r="R42">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="S42">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T42">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U42">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="V42">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA42">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB42">
         <v>2.4</v>
       </c>
       <c r="AC42">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AD42">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE42">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF42">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
         <v>2.58</v>
@@ -7228,7 +7228,7 @@
         <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,61 +7318,61 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O43">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P43">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="Q43">
+        <v>2.98</v>
+      </c>
+      <c r="R43">
         <v>2.48</v>
       </c>
-      <c r="R43">
-        <v>2.36</v>
-      </c>
       <c r="S43">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U43">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="V43">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W43">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA43">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB43">
         <v>2.4</v>
       </c>
       <c r="AC43">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AD43">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE43">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG43">
         <v>2.58</v>
@@ -7391,7 +7391,7 @@
         <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9600,34 +9600,34 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O57">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P57">
-        <v>7.42</v>
+        <v>6.5</v>
       </c>
       <c r="Q57">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="R57">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
       <c r="S57">
         <v>1.17</v>
       </c>
       <c r="T57">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="U57">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="V57">
         <v>1.78</v>
       </c>
       <c r="W57">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X57">
         <v>1.01</v>
@@ -9636,28 +9636,28 @@
         <v>1.06</v>
       </c>
       <c r="Z57">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA57">
         <v>1.33</v>
       </c>
       <c r="AB57">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC57">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AD57">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AE57">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AF57">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG57">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK57">
-        <v>3.46</v>
+        <v>3.24</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,37 +9763,37 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O58">
         <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="Q58">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="R58">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S58">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U58">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="V58">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W58">
         <v>1.04</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
         <v>1.25</v>
@@ -9802,19 +9802,19 @@
         <v>3.6</v>
       </c>
       <c r="AA58">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB58">
         <v>1.86</v>
       </c>
       <c r="AC58">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="AD58">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE58">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF58">
         <v>1.85</v>
@@ -15311,7 +15311,7 @@
         <v>3.3</v>
       </c>
       <c r="P92">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q92">
         <v>4.2</v>
@@ -15332,28 +15332,28 @@
         <v>1.4</v>
       </c>
       <c r="W92">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y92">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z92">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA92">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB92">
         <v>1.85</v>
       </c>
       <c r="AC92">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD92">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE92">
         <v>1.07</v>
@@ -15362,7 +15362,7 @@
         <v>1.75</v>
       </c>
       <c r="AG92">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AK92">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -17107,55 +17107,55 @@
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17427,22 +17427,22 @@
         <v>1.55</v>
       </c>
       <c r="O105">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P105">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q105">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R105">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="S105">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T105">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="U105">
         <v>2.27</v>
@@ -17463,10 +17463,10 @@
         <v>4.5</v>
       </c>
       <c r="AA105">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB105">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AC105">
         <v>2.33</v>
@@ -17475,13 +17475,13 @@
         <v>1.48</v>
       </c>
       <c r="AE105">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF105">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG105">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK105">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,55 +19869,55 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O120">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P120">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q120">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="R120">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S120">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T120">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="U120">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="V120">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W120">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y120">
         <v>1.27</v>
       </c>
       <c r="Z120">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AA120">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB120">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AC120">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD120">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE120">
         <v>1.06</v>
@@ -19926,7 +19926,7 @@
         <v>1.71</v>
       </c>
       <c r="AG120">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK120">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="O121">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P121">
+        <v>2.53</v>
+      </c>
+      <c r="Q121">
         <v>3.25</v>
       </c>
-      <c r="Q121">
-        <v>2.4</v>
-      </c>
       <c r="R121">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S121">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T121">
-        <v>2.85</v>
+        <v>2.61</v>
       </c>
       <c r="U121">
-        <v>2.69</v>
+        <v>2.97</v>
       </c>
       <c r="V121">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W121">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X121">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y121">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z121">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AA121">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB121">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC121">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="AD121">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE121">
         <v>1.06</v>
       </c>
       <c r="AF121">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG121">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O122">
+        <v>3.1</v>
+      </c>
+      <c r="P122">
+        <v>2.75</v>
+      </c>
+      <c r="Q122">
         <v>3.2</v>
       </c>
-      <c r="P122">
-        <v>2.53</v>
-      </c>
-      <c r="Q122">
-        <v>3.25</v>
-      </c>
       <c r="R122">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="S122">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T122">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="U122">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="V122">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W122">
+        <v>1.04</v>
+      </c>
+      <c r="X122">
         <v>1.03</v>
       </c>
-      <c r="X122">
-        <v>1.05</v>
-      </c>
       <c r="Y122">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z122">
-        <v>3.14</v>
+        <v>2.76</v>
       </c>
       <c r="AA122">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB122">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC122">
-        <v>3.51</v>
+        <v>3.83</v>
       </c>
       <c r="AD122">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE122">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF122">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG122">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK122">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,25 +20358,25 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="O123">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P123">
-        <v>3.35</v>
+        <v>1.89</v>
       </c>
       <c r="Q123">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="R123">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S123">
         <v>1.39</v>
       </c>
       <c r="T123">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U123">
         <v>2.85</v>
@@ -20385,37 +20385,37 @@
         <v>1.36</v>
       </c>
       <c r="W123">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X123">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z123">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA123">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB123">
         <v>1.75</v>
       </c>
       <c r="AC123">
-        <v>3.57</v>
+        <v>3.42</v>
       </c>
       <c r="AD123">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE123">
         <v>1.06</v>
       </c>
       <c r="AF123">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG123">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,28 +20521,28 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="O124">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P124">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q124">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="R124">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="S124">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T124">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U124">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V124">
         <v>1.38</v>
@@ -20551,34 +20551,34 @@
         <v>1.05</v>
       </c>
       <c r="X124">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z124">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA124">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB124">
         <v>1.81</v>
       </c>
       <c r="AC124">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD124">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE124">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF124">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG124">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK124">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,25 +20684,25 @@
         </is>
       </c>
       <c r="N125">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="O125">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P125">
-        <v>1.89</v>
+        <v>3.35</v>
       </c>
       <c r="Q125">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="R125">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S125">
         <v>1.39</v>
       </c>
       <c r="T125">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U125">
         <v>2.85</v>
@@ -20711,38 +20711,38 @@
         <v>1.36</v>
       </c>
       <c r="W125">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X125">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y125">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z125">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA125">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB125">
         <v>1.75</v>
       </c>
       <c r="AC125">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="AD125">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE125">
         <v>1.06</v>
       </c>
       <c r="AF125">
+        <v>1.83</v>
+      </c>
+      <c r="AG125">
         <v>1.87</v>
       </c>
-      <c r="AG125">
-        <v>1.91</v>
-      </c>
       <c r="AH125" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK125">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="O126">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P126">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q126">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="R126">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="S126">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T126">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="U126">
-        <v>3.17</v>
+        <v>2.88</v>
       </c>
       <c r="V126">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W126">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
         <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z126">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="AA126">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB126">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AC126">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="AD126">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE126">
         <v>1.07</v>
       </c>
       <c r="AF126">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG126">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK126">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="O136">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="P136">
-        <v>3.7</v>
+        <v>2.91</v>
       </c>
       <c r="Q136">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="R136">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S136">
+        <v>1.43</v>
+      </c>
+      <c r="T136">
+        <v>2.62</v>
+      </c>
+      <c r="U136">
+        <v>2.88</v>
+      </c>
+      <c r="V136">
+        <v>1.36</v>
+      </c>
+      <c r="W136">
+        <v>1.04</v>
+      </c>
+      <c r="X136">
+        <v>1.04</v>
+      </c>
+      <c r="Y136">
         <v>1.32</v>
       </c>
-      <c r="T136">
+      <c r="Z136">
         <v>2.94</v>
       </c>
-      <c r="U136">
-        <v>2.65</v>
-      </c>
-      <c r="V136">
-        <v>1.42</v>
-      </c>
-      <c r="W136">
-        <v>1.07</v>
-      </c>
-      <c r="X136">
-        <v>1.02</v>
-      </c>
-      <c r="Y136">
-        <v>1.25</v>
-      </c>
-      <c r="Z136">
-        <v>3.8</v>
-      </c>
       <c r="AA136">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB136">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AC136">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
       <c r="AD136">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE136">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF136">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG136">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK136">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,80 +22640,80 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="O137">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="P137">
-        <v>2.91</v>
+        <v>3.7</v>
       </c>
       <c r="Q137">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="R137">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S137">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="T137">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="U137">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V137">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W137">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X137">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y137">
+        <v>1.25</v>
+      </c>
+      <c r="Z137">
+        <v>3.8</v>
+      </c>
+      <c r="AA137">
+        <v>1.8</v>
+      </c>
+      <c r="AB137">
+        <v>1.97</v>
+      </c>
+      <c r="AC137">
+        <v>2.79</v>
+      </c>
+      <c r="AD137">
         <v>1.32</v>
       </c>
-      <c r="Z137">
-        <v>2.94</v>
-      </c>
-      <c r="AA137">
-        <v>2</v>
-      </c>
-      <c r="AB137">
-        <v>1.77</v>
-      </c>
-      <c r="AC137">
-        <v>3.5</v>
-      </c>
-      <c r="AD137">
-        <v>1.27</v>
-      </c>
       <c r="AE137">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF137">
+        <v>1.68</v>
+      </c>
+      <c r="AG137">
+        <v>2.09</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <v>1.22</v>
+      </c>
+      <c r="AK137">
         <v>1.75</v>
-      </c>
-      <c r="AG137">
-        <v>1.95</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.28</v>
-      </c>
-      <c r="AK137">
-        <v>1.5</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="O140">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P140">
-        <v>4.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q140">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="R140">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S140">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T140">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U140">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="V140">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W140">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X140">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y140">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z140">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AA140">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB140">
         <v>2</v>
       </c>
       <c r="AC140">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD140">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE140">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF140">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AG140">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK140">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="O141">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P141">
-        <v>2.75</v>
+        <v>4.15</v>
       </c>
       <c r="Q141">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="R141">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S141">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T141">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U141">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="V141">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W141">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X141">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y141">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z141">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AA141">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB141">
         <v>2</v>
       </c>
       <c r="AC141">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="AD141">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE141">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF141">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AG141">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK141">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
+        <v>2.15</v>
+      </c>
+      <c r="O144">
+        <v>3.45</v>
+      </c>
+      <c r="P144">
+        <v>2.98</v>
+      </c>
+      <c r="Q144">
+        <v>2.55</v>
+      </c>
+      <c r="R144">
         <v>2.3</v>
       </c>
-      <c r="O144">
-        <v>3.24</v>
-      </c>
-      <c r="P144">
-        <v>3</v>
-      </c>
-      <c r="Q144">
-        <v>2.78</v>
-      </c>
-      <c r="R144">
-        <v>2.19</v>
-      </c>
       <c r="S144">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="U144">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="V144">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W144">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X144">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y144">
+        <v>1.25</v>
+      </c>
+      <c r="Z144">
+        <v>3.4</v>
+      </c>
+      <c r="AA144">
+        <v>1.78</v>
+      </c>
+      <c r="AB144">
+        <v>2</v>
+      </c>
+      <c r="AC144">
+        <v>2.99</v>
+      </c>
+      <c r="AD144">
+        <v>1.38</v>
+      </c>
+      <c r="AE144">
+        <v>1.11</v>
+      </c>
+      <c r="AF144">
+        <v>1.65</v>
+      </c>
+      <c r="AG144">
+        <v>2.2</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
         <v>1.3</v>
       </c>
-      <c r="Z144">
-        <v>3.08</v>
-      </c>
-      <c r="AA144">
-        <v>2</v>
-      </c>
-      <c r="AB144">
-        <v>1.78</v>
-      </c>
-      <c r="AC144">
-        <v>3.3</v>
-      </c>
-      <c r="AD144">
-        <v>1.3</v>
-      </c>
-      <c r="AE144">
-        <v>1.1</v>
-      </c>
-      <c r="AF144">
-        <v>1.75</v>
-      </c>
-      <c r="AG144">
-        <v>1.93</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.25</v>
-      </c>
       <c r="AK144">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O145">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P145">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="Q145">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="R145">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="S145">
+        <v>1.32</v>
+      </c>
+      <c r="T145">
+        <v>2.87</v>
+      </c>
+      <c r="U145">
+        <v>2.64</v>
+      </c>
+      <c r="V145">
         <v>1.45</v>
       </c>
-      <c r="T145">
-        <v>2.5</v>
-      </c>
-      <c r="U145">
-        <v>2.86</v>
-      </c>
-      <c r="V145">
-        <v>1.33</v>
-      </c>
       <c r="W145">
+        <v>1.06</v>
+      </c>
+      <c r="X145">
         <v>1.02</v>
       </c>
-      <c r="X145">
-        <v>1.05</v>
-      </c>
       <c r="Y145">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z145">
-        <v>3.12</v>
+        <v>4.1</v>
       </c>
       <c r="AA145">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AB145">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC145">
-        <v>3.62</v>
+        <v>2.85</v>
       </c>
       <c r="AD145">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AE145">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AG145">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK145">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,31 +24107,31 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="O146">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P146">
-        <v>2.98</v>
+        <v>3.92</v>
       </c>
       <c r="Q146">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="R146">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S146">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T146">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="U146">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="V146">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W146">
         <v>1.07</v>
@@ -24140,31 +24140,31 @@
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z146">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="AA146">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB146">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC146">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="AD146">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE146">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF146">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG146">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK146">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,80 +24270,80 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O147">
-        <v>3.62</v>
+        <v>3.24</v>
       </c>
       <c r="P147">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q147">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R147">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S147">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T147">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="U147">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="V147">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W147">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X147">
         <v>1.02</v>
       </c>
       <c r="Y147">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z147">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA147">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB147">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC147">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="AD147">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE147">
         <v>1.1</v>
       </c>
       <c r="AF147">
+        <v>1.75</v>
+      </c>
+      <c r="AG147">
+        <v>1.93</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ147">
+        <v>1.25</v>
+      </c>
+      <c r="AK147">
         <v>1.62</v>
-      </c>
-      <c r="AG147">
-        <v>2.15</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>1.26</v>
-      </c>
-      <c r="AK147">
-        <v>1.63</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="O148">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P148">
-        <v>3.92</v>
+        <v>3.18</v>
       </c>
       <c r="Q148">
-        <v>2.42</v>
+        <v>2.93</v>
       </c>
       <c r="R148">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="S148">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="T148">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="U148">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="V148">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="W148">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X148">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y148">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Z148">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="AA148">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AB148">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC148">
-        <v>3.03</v>
+        <v>3.62</v>
       </c>
       <c r="AD148">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AE148">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF148">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AG148">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK148">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,19 +27041,19 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="O164">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P164">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q164">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="R164">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="S164">
         <v>1.33</v>
@@ -27062,43 +27062,43 @@
         <v>3</v>
       </c>
       <c r="U164">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="V164">
         <v>1.41</v>
       </c>
       <c r="W164">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X164">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y164">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z164">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AA164">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB164">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC164">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD164">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE164">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF164">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AG164">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK164">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,19 +27204,19 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="O165">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P165">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="Q165">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="R165">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="S165">
         <v>1.33</v>
@@ -27225,43 +27225,43 @@
         <v>3</v>
       </c>
       <c r="U165">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="V165">
         <v>1.41</v>
       </c>
       <c r="W165">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X165">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y165">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z165">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA165">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB165">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC165">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD165">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE165">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF165">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AG165">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AK165">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -30627,7 +30627,7 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O186">
         <v>2.9</v>
@@ -30636,55 +30636,55 @@
         <v>3.4</v>
       </c>
       <c r="Q186">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="R186">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S186">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T186">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U186">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="V186">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W186">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X186">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y186">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z186">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AA186">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="AB186">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC186">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AD186">
         <v>1.1</v>
       </c>
       <c r="AE186">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF186">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AG186">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>1.25</v>
       </c>
       <c r="AK186">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="O193">
-        <v>3.49</v>
+        <v>3.65</v>
       </c>
       <c r="P193">
-        <v>6.62</v>
+        <v>7.5</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31940,10 +31940,10 @@
         <v>2.75</v>
       </c>
       <c r="Q194">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="R194">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="S194">
         <v>1.47</v>
@@ -31952,13 +31952,13 @@
         <v>2.48</v>
       </c>
       <c r="U194">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V194">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W194">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X194">
         <v>1.05</v>
@@ -31967,16 +31967,16 @@
         <v>1.4</v>
       </c>
       <c r="Z194">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA194">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB194">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AC194">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD194">
         <v>1.17</v>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK194">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32094,31 +32094,31 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="O195">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P195">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q195">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R195">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S195">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T195">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="U195">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="V195">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W195">
         <v>1.01</v>
@@ -32127,31 +32127,31 @@
         <v>1.05</v>
       </c>
       <c r="Y195">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z195">
         <v>2.56</v>
       </c>
       <c r="AA195">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AB195">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC195">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="AD195">
         <v>1.15</v>
       </c>
       <c r="AE195">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF195">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AG195">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK195">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,16 +32257,16 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O196">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P196">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q196">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R196">
         <v>1.91</v>
@@ -32275,7 +32275,7 @@
         <v>1.55</v>
       </c>
       <c r="T196">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="U196">
         <v>3.3</v>
@@ -32284,31 +32284,31 @@
         <v>1.25</v>
       </c>
       <c r="W196">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X196">
         <v>1.06</v>
       </c>
       <c r="Y196">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Z196">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AA196">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AB196">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC196">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="AD196">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE196">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF196">
         <v>2.03</v>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK196">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O203">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P203">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q203">
-        <v>3.93</v>
+        <v>3.5</v>
       </c>
       <c r="R203">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S203">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T203">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U203">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="V203">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W203">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X203">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y203">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z203">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AA203">
         <v>2.2</v>
       </c>
       <c r="AB203">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC203">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="AD203">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE203">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF203">
         <v>1.85</v>
       </c>
       <c r="AG203">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,80 +33561,80 @@
         </is>
       </c>
       <c r="N204">
+        <v>1.9</v>
+      </c>
+      <c r="O204">
+        <v>3.2</v>
+      </c>
+      <c r="P204">
+        <v>3.5</v>
+      </c>
+      <c r="Q204">
+        <v>2.52</v>
+      </c>
+      <c r="R204">
+        <v>2.07</v>
+      </c>
+      <c r="S204">
+        <v>1.4</v>
+      </c>
+      <c r="T204">
+        <v>2.63</v>
+      </c>
+      <c r="U204">
         <v>2.9</v>
       </c>
-      <c r="O204">
-        <v>2.9</v>
-      </c>
-      <c r="P204">
-        <v>2.3</v>
-      </c>
-      <c r="Q204">
-        <v>4.17</v>
-      </c>
-      <c r="R204">
-        <v>1.83</v>
-      </c>
-      <c r="S204">
-        <v>1.51</v>
-      </c>
-      <c r="T204">
-        <v>2.5</v>
-      </c>
-      <c r="U204">
-        <v>3.4</v>
-      </c>
       <c r="V204">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W204">
         <v>1.02</v>
       </c>
       <c r="X204">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y204">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z204">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AA204">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AB204">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AC204">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD204">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE204">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF204">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG204">
+        <v>1.79</v>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ204">
+        <v>1.29</v>
+      </c>
+      <c r="AK204">
         <v>1.75</v>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ204">
-        <v>1.5</v>
-      </c>
-      <c r="AK204">
-        <v>1.33</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,80 +33724,80 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.98</v>
+        <v>3.14</v>
       </c>
       <c r="O205">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P205">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q205">
-        <v>2.51</v>
+        <v>3.6</v>
       </c>
       <c r="R205">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="S205">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T205">
         <v>2.63</v>
       </c>
       <c r="U205">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="V205">
+        <v>1.27</v>
+      </c>
+      <c r="W205">
+        <v>1.02</v>
+      </c>
+      <c r="X205">
+        <v>1.05</v>
+      </c>
+      <c r="Y205">
+        <v>1.44</v>
+      </c>
+      <c r="Z205">
+        <v>2.53</v>
+      </c>
+      <c r="AA205">
+        <v>2.25</v>
+      </c>
+      <c r="AB205">
+        <v>1.55</v>
+      </c>
+      <c r="AC205">
+        <v>4.6</v>
+      </c>
+      <c r="AD205">
+        <v>1.17</v>
+      </c>
+      <c r="AE205">
+        <v>1.05</v>
+      </c>
+      <c r="AF205">
+        <v>2</v>
+      </c>
+      <c r="AG205">
+        <v>1.73</v>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ205">
+        <v>1.5</v>
+      </c>
+      <c r="AK205">
         <v>1.33</v>
-      </c>
-      <c r="W205">
-        <v>1.04</v>
-      </c>
-      <c r="X205">
-        <v>1.01</v>
-      </c>
-      <c r="Y205">
-        <v>1.33</v>
-      </c>
-      <c r="Z205">
-        <v>2.83</v>
-      </c>
-      <c r="AA205">
-        <v>2.16</v>
-      </c>
-      <c r="AB205">
-        <v>1.64</v>
-      </c>
-      <c r="AC205">
-        <v>3.85</v>
-      </c>
-      <c r="AD205">
-        <v>1.2</v>
-      </c>
-      <c r="AE205">
-        <v>1.02</v>
-      </c>
-      <c r="AF205">
-        <v>1.88</v>
-      </c>
-      <c r="AG205">
-        <v>1.79</v>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ205">
-        <v>1.29</v>
-      </c>
-      <c r="AK205">
-        <v>1.73</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34539,19 +34539,19 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="O210">
         <v>3.3</v>
       </c>
       <c r="P210">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="Q210">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="R210">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S210">
         <v>1.41</v>
@@ -34560,10 +34560,10 @@
         <v>2.73</v>
       </c>
       <c r="U210">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V210">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W210">
         <v>1.07</v>
@@ -34575,7 +34575,7 @@
         <v>1.28</v>
       </c>
       <c r="Z210">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AA210">
         <v>2.05</v>
@@ -34587,7 +34587,7 @@
         <v>3.42</v>
       </c>
       <c r="AD210">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE210">
         <v>1.04</v>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK210">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -36169,28 +36169,28 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O220">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P220">
         <v>7</v>
       </c>
       <c r="Q220">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R220">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="S220">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T220">
         <v>3.75</v>
       </c>
       <c r="U220">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V220">
         <v>1.63</v>
@@ -36202,31 +36202,31 @@
         <v>1.02</v>
       </c>
       <c r="Y220">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z220">
-        <v>6</v>
+        <v>5.31</v>
       </c>
       <c r="AA220">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB220">
         <v>2.5</v>
       </c>
       <c r="AC220">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AD220">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE220">
         <v>1.22</v>
       </c>
       <c r="AF220">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG220">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>1.1</v>
       </c>
       <c r="AK220">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36335,28 +36335,28 @@
         <v>2.23</v>
       </c>
       <c r="O221">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P221">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q221">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R221">
         <v>2.2</v>
       </c>
       <c r="S221">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T221">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U221">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="V221">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W221">
         <v>1.1</v>
@@ -36365,16 +36365,16 @@
         <v>1.02</v>
       </c>
       <c r="Y221">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z221">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="AA221">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB221">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC221">
         <v>2.78</v>
@@ -36383,13 +36383,13 @@
         <v>1.34</v>
       </c>
       <c r="AE221">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF221">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG221">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK221">
         <v>1.53</v>
@@ -39755,16 +39755,16 @@
         </is>
       </c>
       <c r="N242">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="O242">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P242">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="Q242">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="R242">
         <v>2.3</v>
@@ -39779,31 +39779,31 @@
         <v>2.47</v>
       </c>
       <c r="V242">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W242">
         <v>1.11</v>
       </c>
       <c r="X242">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y242">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z242">
         <v>3.72</v>
       </c>
       <c r="AA242">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB242">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AC242">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AD242">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE242">
         <v>1.12</v>
@@ -39812,7 +39812,7 @@
         <v>1.57</v>
       </c>
       <c r="AG242">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>1.28</v>
       </c>
       <c r="AK242">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -40733,64 +40733,64 @@
         </is>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S248">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T248">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U248">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V248">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W248">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X248">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y248">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z248">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA248">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB248">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC248">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD248">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.03</v>
 